--- a/솔바텍_URL도메인변경완료_순위반영_20261029.xlsx
+++ b/솔바텍_URL도메인변경완료_순위반영_20261029.xlsx
@@ -7,19 +7,24 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="입찰가 변경 전후" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="광고 기본 정보" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="키워드ID·링크" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="프린터 입찰가" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="입찰가 변경 전후" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="광고 기본 정보" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="키워드ID·링크" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'프린터 입찰가'!$A$13:$P$63</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="5">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0&quot;원&quot;"/>
+  </numFmts>
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,8 +50,16 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="FF595959"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -73,8 +86,18 @@
         <fgColor rgb="FFFFE5E5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFE0"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -96,11 +119,88 @@
         <color rgb="FFBFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -127,6 +227,53 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -493,6 +640,3105 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:P63"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>입찰가 인상 기준 (노란 칸 숫자를 바꾸면 추천 입찰가가 자동으로 다시 계산됩니다)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>판정</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>인상률</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>솔바텍 미노출</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>솔바텍 광고가 안 보임 → 노출되도록 크게 인상</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>순위 차이 큼</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>솔바텍이 다른 사이트보다 2계단 이상 아래</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>붙어있음(아래)</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>솔바텍이 다른 사이트 바로 아래 (예: 6위·5위)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>붙어있음(위)</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>솔바텍이 바로 위지만 붙어 있음 (예: 1위·2위) → 간격 벌리기</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>순위 낮음</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>다른 사이트는 없지만 솔바텍 순위가 낮음</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>유지</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>수정 대상 아님</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>입찰가 상한</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>추천 입찰가는 이 금액을 넘지 않음 (10원 단위 올림). 현재 입찰가가 이미 상한보다 높으면 현재 금액 유지</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>※ 네이버 광고관리 &gt; 키워드 &gt; 입찰가 변경 &gt; "순위별 평균 입찰가"에서 목표 순위 금액을 확인해 L열에 넣으면 그 금액이 최종 입찰가가 됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>키워드</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>상태</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>광고업체수</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="inlineStr">
+        <is>
+          <t>솔바텍</t>
+        </is>
+      </c>
+      <c r="E13" s="1" t="inlineStr">
+        <is>
+          <t>코스모스몰</t>
+        </is>
+      </c>
+      <c r="F13" s="1" t="inlineStr">
+        <is>
+          <t>sb렌탈</t>
+        </is>
+      </c>
+      <c r="G13" s="1" t="inlineStr">
+        <is>
+          <t>입찰가 수정</t>
+        </is>
+      </c>
+      <c r="H13" s="1" t="inlineStr">
+        <is>
+          <t>판정</t>
+        </is>
+      </c>
+      <c r="I13" s="1" t="inlineStr">
+        <is>
+          <t>현재 입찰가</t>
+        </is>
+      </c>
+      <c r="J13" s="1" t="inlineStr">
+        <is>
+          <t>인상률</t>
+        </is>
+      </c>
+      <c r="K13" s="1" t="inlineStr">
+        <is>
+          <t>추천 입찰가</t>
+        </is>
+      </c>
+      <c r="L13" s="17" t="inlineStr">
+        <is>
+          <t>네이버 목표순위 입찰가
+(직접 입력)</t>
+        </is>
+      </c>
+      <c r="M13" s="1" t="inlineStr">
+        <is>
+          <t>최종 변경 입찰가</t>
+        </is>
+      </c>
+      <c r="N13" s="1" t="inlineStr">
+        <is>
+          <t>노출수</t>
+        </is>
+      </c>
+      <c r="O13" s="1" t="inlineStr">
+        <is>
+          <t>클릭수</t>
+        </is>
+      </c>
+      <c r="P13" s="1" t="inlineStr">
+        <is>
+          <t>평균 CPC</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>감열식프린터</t>
+        </is>
+      </c>
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t>노출가능</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D14" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="F14" s="18" t="n"/>
+      <c r="G14" s="18" t="n"/>
+      <c r="H14" s="18" t="inlineStr">
+        <is>
+          <t>유지</t>
+        </is>
+      </c>
+      <c r="I14" s="19" t="n">
+        <v>800</v>
+      </c>
+      <c r="J14" s="20">
+        <f>VLOOKUP(H14,$A$3:$B$8,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="K14" s="19">
+        <f>IF(J14=0,I14,MAX(I14,MIN($B$10,ROUNDUP(I14*(1+J14),-1))))</f>
+        <v/>
+      </c>
+      <c r="L14" s="21" t="n"/>
+      <c r="M14" s="22">
+        <f>IF(L14&lt;&gt;"",MIN($B$10,L14),K14)</f>
+        <v/>
+      </c>
+      <c r="N14" s="18" t="n">
+        <v>23</v>
+      </c>
+      <c r="O14" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="18" t="inlineStr">
+        <is>
+          <t>0원</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>감열프린터</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t>노출가능</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D15" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" s="18" t="n"/>
+      <c r="F15" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="G15" s="18" t="n"/>
+      <c r="H15" s="18" t="inlineStr">
+        <is>
+          <t>유지</t>
+        </is>
+      </c>
+      <c r="I15" s="19" t="n">
+        <v>2000</v>
+      </c>
+      <c r="J15" s="20">
+        <f>VLOOKUP(H15,$A$3:$B$8,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="K15" s="19">
+        <f>IF(J15=0,I15,MAX(I15,MIN($B$10,ROUNDUP(I15*(1+J15),-1))))</f>
+        <v/>
+      </c>
+      <c r="L15" s="21" t="n"/>
+      <c r="M15" s="22">
+        <f>IF(L15&lt;&gt;"",MIN($B$10,L15),K15)</f>
+        <v/>
+      </c>
+      <c r="N15" s="18" t="n">
+        <v>27</v>
+      </c>
+      <c r="O15" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="18" t="inlineStr">
+        <is>
+          <t>0원</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>감열프린터기</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>노출가능</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="D16" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="E16" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="F16" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="G16" s="24" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="H16" s="23" t="inlineStr">
+        <is>
+          <t>순위 차이 큼</t>
+        </is>
+      </c>
+      <c r="I16" s="25" t="n">
+        <v>650</v>
+      </c>
+      <c r="J16" s="26">
+        <f>VLOOKUP(H16,$A$3:$B$8,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="K16" s="25">
+        <f>IF(J16=0,I16,MAX(I16,MIN($B$10,ROUNDUP(I16*(1+J16),-1))))</f>
+        <v/>
+      </c>
+      <c r="L16" s="21" t="n"/>
+      <c r="M16" s="27">
+        <f>IF(L16&lt;&gt;"",MIN($B$10,L16),K16)</f>
+        <v/>
+      </c>
+      <c r="N16" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="O16" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="23" t="inlineStr">
+        <is>
+          <t>0원</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>도시바프린터</t>
+        </is>
+      </c>
+      <c r="B17" s="18" t="inlineStr">
+        <is>
+          <t>노출가능</t>
+        </is>
+      </c>
+      <c r="C17" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D17" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" s="18" t="n"/>
+      <c r="F17" s="18" t="n"/>
+      <c r="G17" s="18" t="n"/>
+      <c r="H17" s="18" t="inlineStr">
+        <is>
+          <t>유지</t>
+        </is>
+      </c>
+      <c r="I17" s="19" t="n">
+        <v>1500</v>
+      </c>
+      <c r="J17" s="20">
+        <f>VLOOKUP(H17,$A$3:$B$8,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="K17" s="19">
+        <f>IF(J17=0,I17,MAX(I17,MIN($B$10,ROUNDUP(I17*(1+J17),-1))))</f>
+        <v/>
+      </c>
+      <c r="L17" s="21" t="n"/>
+      <c r="M17" s="22">
+        <f>IF(L17&lt;&gt;"",MIN($B$10,L17),K17)</f>
+        <v/>
+      </c>
+      <c r="N17" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="O17" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="18" t="inlineStr">
+        <is>
+          <t>0원</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>라밸프린터</t>
+        </is>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>노출가능</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="D18" s="23" t="n"/>
+      <c r="E18" s="23" t="n"/>
+      <c r="F18" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" s="24" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="H18" s="23" t="inlineStr">
+        <is>
+          <t>솔바텍 미노출</t>
+        </is>
+      </c>
+      <c r="I18" s="25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J18" s="26">
+        <f>VLOOKUP(H18,$A$3:$B$8,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="K18" s="25">
+        <f>IF(J18=0,I18,MAX(I18,MIN($B$10,ROUNDUP(I18*(1+J18),-1))))</f>
+        <v/>
+      </c>
+      <c r="L18" s="21" t="n"/>
+      <c r="M18" s="27">
+        <f>IF(L18&lt;&gt;"",MIN($B$10,L18),K18)</f>
+        <v/>
+      </c>
+      <c r="N18" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="23" t="inlineStr">
+        <is>
+          <t>0원</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>라벨기</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>노출가능</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="D19" s="23" t="n"/>
+      <c r="E19" s="23" t="n"/>
+      <c r="F19" s="23" t="n"/>
+      <c r="G19" s="24" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="H19" s="23" t="inlineStr">
+        <is>
+          <t>솔바텍 미노출</t>
+        </is>
+      </c>
+      <c r="I19" s="25" t="n">
+        <v>2000</v>
+      </c>
+      <c r="J19" s="26">
+        <f>VLOOKUP(H19,$A$3:$B$8,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="K19" s="25">
+        <f>IF(J19=0,I19,MAX(I19,MIN($B$10,ROUNDUP(I19*(1+J19),-1))))</f>
+        <v/>
+      </c>
+      <c r="L19" s="21" t="n"/>
+      <c r="M19" s="27">
+        <f>IF(L19&lt;&gt;"",MIN($B$10,L19),K19)</f>
+        <v/>
+      </c>
+      <c r="N19" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="O19" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="23" t="inlineStr">
+        <is>
+          <t>0원</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>라벨기계</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>노출가능</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="D20" s="23" t="n"/>
+      <c r="E20" s="23" t="n"/>
+      <c r="F20" s="23" t="n"/>
+      <c r="G20" s="24" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="H20" s="23" t="inlineStr">
+        <is>
+          <t>솔바텍 미노출</t>
+        </is>
+      </c>
+      <c r="I20" s="25" t="n">
+        <v>890</v>
+      </c>
+      <c r="J20" s="26">
+        <f>VLOOKUP(H20,$A$3:$B$8,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="K20" s="25">
+        <f>IF(J20=0,I20,MAX(I20,MIN($B$10,ROUNDUP(I20*(1+J20),-1))))</f>
+        <v/>
+      </c>
+      <c r="L20" s="21" t="n"/>
+      <c r="M20" s="27">
+        <f>IF(L20&lt;&gt;"",MIN($B$10,L20),K20)</f>
+        <v/>
+      </c>
+      <c r="N20" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="23" t="inlineStr">
+        <is>
+          <t>0원</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>라벨용지프린터</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>노출가능</t>
+        </is>
+      </c>
+      <c r="C21" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" s="23" t="n"/>
+      <c r="E21" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" s="23" t="n"/>
+      <c r="G21" s="24" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="H21" s="23" t="inlineStr">
+        <is>
+          <t>솔바텍 미노출</t>
+        </is>
+      </c>
+      <c r="I21" s="25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J21" s="26">
+        <f>VLOOKUP(H21,$A$3:$B$8,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="K21" s="25">
+        <f>IF(J21=0,I21,MAX(I21,MIN($B$10,ROUNDUP(I21*(1+J21),-1))))</f>
+        <v/>
+      </c>
+      <c r="L21" s="21" t="n"/>
+      <c r="M21" s="27">
+        <f>IF(L21&lt;&gt;"",MIN($B$10,L21),K21)</f>
+        <v/>
+      </c>
+      <c r="N21" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="23" t="inlineStr">
+        <is>
+          <t>0원</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>라벨인쇄기</t>
+        </is>
+      </c>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>노출가능</t>
+        </is>
+      </c>
+      <c r="C22" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="D22" s="23" t="n"/>
+      <c r="E22" s="23" t="n"/>
+      <c r="F22" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" s="24" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="H22" s="23" t="inlineStr">
+        <is>
+          <t>솔바텍 미노출</t>
+        </is>
+      </c>
+      <c r="I22" s="25" t="n">
+        <v>3500</v>
+      </c>
+      <c r="J22" s="26">
+        <f>VLOOKUP(H22,$A$3:$B$8,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="K22" s="25">
+        <f>IF(J22=0,I22,MAX(I22,MIN($B$10,ROUNDUP(I22*(1+J22),-1))))</f>
+        <v/>
+      </c>
+      <c r="L22" s="21" t="n"/>
+      <c r="M22" s="27">
+        <f>IF(L22&lt;&gt;"",MIN($B$10,L22),K22)</f>
+        <v/>
+      </c>
+      <c r="N22" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="O22" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="23" t="inlineStr">
+        <is>
+          <t>0원</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>라벨인쇄기계</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>노출가능</t>
+        </is>
+      </c>
+      <c r="C23" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="D23" s="23" t="n"/>
+      <c r="E23" s="23" t="n"/>
+      <c r="F23" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" s="24" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="H23" s="23" t="inlineStr">
+        <is>
+          <t>솔바텍 미노출</t>
+        </is>
+      </c>
+      <c r="I23" s="25" t="n">
+        <v>600</v>
+      </c>
+      <c r="J23" s="26">
+        <f>VLOOKUP(H23,$A$3:$B$8,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="K23" s="25">
+        <f>IF(J23=0,I23,MAX(I23,MIN($B$10,ROUNDUP(I23*(1+J23),-1))))</f>
+        <v/>
+      </c>
+      <c r="L23" s="21" t="n"/>
+      <c r="M23" s="27">
+        <f>IF(L23&lt;&gt;"",MIN($B$10,L23),K23)</f>
+        <v/>
+      </c>
+      <c r="N23" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="23" t="inlineStr">
+        <is>
+          <t>0원</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>라벨지프린터</t>
+        </is>
+      </c>
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>노출가능</t>
+        </is>
+      </c>
+      <c r="C24" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="D24" s="23" t="n"/>
+      <c r="E24" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="F24" s="23" t="n"/>
+      <c r="G24" s="24" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="H24" s="23" t="inlineStr">
+        <is>
+          <t>솔바텍 미노출</t>
+        </is>
+      </c>
+      <c r="I24" s="25" t="n">
+        <v>800</v>
+      </c>
+      <c r="J24" s="26">
+        <f>VLOOKUP(H24,$A$3:$B$8,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="K24" s="25">
+        <f>IF(J24=0,I24,MAX(I24,MIN($B$10,ROUNDUP(I24*(1+J24),-1))))</f>
+        <v/>
+      </c>
+      <c r="L24" s="21" t="n"/>
+      <c r="M24" s="27">
+        <f>IF(L24&lt;&gt;"",MIN($B$10,L24),K24)</f>
+        <v/>
+      </c>
+      <c r="N24" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="O24" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="23" t="inlineStr">
+        <is>
+          <t>0원</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>라벨출력기</t>
+        </is>
+      </c>
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>노출가능</t>
+        </is>
+      </c>
+      <c r="C25" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="D25" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="E25" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" s="23" t="n"/>
+      <c r="G25" s="24" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="H25" s="23" t="inlineStr">
+        <is>
+          <t>순위 차이 큼</t>
+        </is>
+      </c>
+      <c r="I25" s="25" t="n">
+        <v>1110</v>
+      </c>
+      <c r="J25" s="26">
+        <f>VLOOKUP(H25,$A$3:$B$8,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="K25" s="25">
+        <f>IF(J25=0,I25,MAX(I25,MIN($B$10,ROUNDUP(I25*(1+J25),-1))))</f>
+        <v/>
+      </c>
+      <c r="L25" s="21" t="n"/>
+      <c r="M25" s="27">
+        <f>IF(L25&lt;&gt;"",MIN($B$10,L25),K25)</f>
+        <v/>
+      </c>
+      <c r="N25" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" s="23" t="inlineStr">
+        <is>
+          <t>0원</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>라벨프린터업체</t>
+        </is>
+      </c>
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>노출가능</t>
+        </is>
+      </c>
+      <c r="C26" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="D26" s="23" t="n"/>
+      <c r="E26" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="F26" s="23" t="n"/>
+      <c r="G26" s="24" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="H26" s="23" t="inlineStr">
+        <is>
+          <t>솔바텍 미노출</t>
+        </is>
+      </c>
+      <c r="I26" s="25" t="n">
+        <v>530</v>
+      </c>
+      <c r="J26" s="26">
+        <f>VLOOKUP(H26,$A$3:$B$8,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="K26" s="25">
+        <f>IF(J26=0,I26,MAX(I26,MIN($B$10,ROUNDUP(I26*(1+J26),-1))))</f>
+        <v/>
+      </c>
+      <c r="L26" s="21" t="n"/>
+      <c r="M26" s="27">
+        <f>IF(L26&lt;&gt;"",MIN($B$10,L26),K26)</f>
+        <v/>
+      </c>
+      <c r="N26" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="23" t="inlineStr">
+        <is>
+          <t>0원</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>라벨프린터추천</t>
+        </is>
+      </c>
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>노출가능</t>
+        </is>
+      </c>
+      <c r="C27" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="D27" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="E27" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="F27" s="23" t="n"/>
+      <c r="G27" s="24" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="H27" s="23" t="inlineStr">
+        <is>
+          <t>붙어있음(위)</t>
+        </is>
+      </c>
+      <c r="I27" s="25" t="n">
+        <v>1580</v>
+      </c>
+      <c r="J27" s="26">
+        <f>VLOOKUP(H27,$A$3:$B$8,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="K27" s="25">
+        <f>IF(J27=0,I27,MAX(I27,MIN($B$10,ROUNDUP(I27*(1+J27),-1))))</f>
+        <v/>
+      </c>
+      <c r="L27" s="21" t="n"/>
+      <c r="M27" s="27">
+        <f>IF(L27&lt;&gt;"",MIN($B$10,L27),K27)</f>
+        <v/>
+      </c>
+      <c r="N27" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="O27" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" s="23" t="inlineStr">
+        <is>
+          <t>0원</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>롤라벨인쇄기</t>
+        </is>
+      </c>
+      <c r="B28" s="23" t="inlineStr">
+        <is>
+          <t>노출가능</t>
+        </is>
+      </c>
+      <c r="C28" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="D28" s="23" t="n"/>
+      <c r="E28" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="23" t="n"/>
+      <c r="G28" s="24" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="H28" s="23" t="inlineStr">
+        <is>
+          <t>솔바텍 미노출</t>
+        </is>
+      </c>
+      <c r="I28" s="25" t="n">
+        <v>70</v>
+      </c>
+      <c r="J28" s="26">
+        <f>VLOOKUP(H28,$A$3:$B$8,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="K28" s="25">
+        <f>IF(J28=0,I28,MAX(I28,MIN($B$10,ROUNDUP(I28*(1+J28),-1))))</f>
+        <v/>
+      </c>
+      <c r="L28" s="21" t="n"/>
+      <c r="M28" s="27">
+        <f>IF(L28&lt;&gt;"",MIN($B$10,L28),K28)</f>
+        <v/>
+      </c>
+      <c r="N28" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" s="23" t="inlineStr">
+        <is>
+          <t>0원</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>롤라벨출력기</t>
+        </is>
+      </c>
+      <c r="B29" s="23" t="inlineStr">
+        <is>
+          <t>노출가능</t>
+        </is>
+      </c>
+      <c r="C29" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="D29" s="23" t="n"/>
+      <c r="E29" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="F29" s="23" t="n"/>
+      <c r="G29" s="24" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="H29" s="23" t="inlineStr">
+        <is>
+          <t>솔바텍 미노출</t>
+        </is>
+      </c>
+      <c r="I29" s="25" t="n">
+        <v>100</v>
+      </c>
+      <c r="J29" s="26">
+        <f>VLOOKUP(H29,$A$3:$B$8,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="K29" s="25">
+        <f>IF(J29=0,I29,MAX(I29,MIN($B$10,ROUNDUP(I29*(1+J29),-1))))</f>
+        <v/>
+      </c>
+      <c r="L29" s="21" t="n"/>
+      <c r="M29" s="27">
+        <f>IF(L29&lt;&gt;"",MIN($B$10,L29),K29)</f>
+        <v/>
+      </c>
+      <c r="N29" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" s="23" t="inlineStr">
+        <is>
+          <t>0원</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>롤라벨프린터</t>
+        </is>
+      </c>
+      <c r="B30" s="23" t="inlineStr">
+        <is>
+          <t>노출가능</t>
+        </is>
+      </c>
+      <c r="C30" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="D30" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="E30" s="23" t="n"/>
+      <c r="F30" s="23" t="n"/>
+      <c r="G30" s="24" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="H30" s="23" t="inlineStr">
+        <is>
+          <t>순위 낮음</t>
+        </is>
+      </c>
+      <c r="I30" s="25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J30" s="26">
+        <f>VLOOKUP(H30,$A$3:$B$8,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="K30" s="25">
+        <f>IF(J30=0,I30,MAX(I30,MIN($B$10,ROUNDUP(I30*(1+J30),-1))))</f>
+        <v/>
+      </c>
+      <c r="L30" s="21" t="n"/>
+      <c r="M30" s="27">
+        <f>IF(L30&lt;&gt;"",MIN($B$10,L30),K30)</f>
+        <v/>
+      </c>
+      <c r="N30" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="O30" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="23" t="inlineStr">
+        <is>
+          <t>0원</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>바코드라벨인쇄기</t>
+        </is>
+      </c>
+      <c r="B31" s="23" t="inlineStr">
+        <is>
+          <t>노출가능</t>
+        </is>
+      </c>
+      <c r="C31" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="D31" s="23" t="n"/>
+      <c r="E31" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="F31" s="23" t="n"/>
+      <c r="G31" s="24" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="H31" s="23" t="inlineStr">
+        <is>
+          <t>솔바텍 미노출</t>
+        </is>
+      </c>
+      <c r="I31" s="25" t="n">
+        <v>400</v>
+      </c>
+      <c r="J31" s="26">
+        <f>VLOOKUP(H31,$A$3:$B$8,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="K31" s="25">
+        <f>IF(J31=0,I31,MAX(I31,MIN($B$10,ROUNDUP(I31*(1+J31),-1))))</f>
+        <v/>
+      </c>
+      <c r="L31" s="21" t="n"/>
+      <c r="M31" s="27">
+        <f>IF(L31&lt;&gt;"",MIN($B$10,L31),K31)</f>
+        <v/>
+      </c>
+      <c r="N31" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="23" t="inlineStr">
+        <is>
+          <t>0원</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>바코드라벨프린터</t>
+        </is>
+      </c>
+      <c r="B32" s="23" t="inlineStr">
+        <is>
+          <t>노출가능</t>
+        </is>
+      </c>
+      <c r="C32" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="D32" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="E32" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="F32" s="23" t="n"/>
+      <c r="G32" s="24" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="H32" s="23" t="inlineStr">
+        <is>
+          <t>순위 차이 큼</t>
+        </is>
+      </c>
+      <c r="I32" s="25" t="n">
+        <v>3000</v>
+      </c>
+      <c r="J32" s="26">
+        <f>VLOOKUP(H32,$A$3:$B$8,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="K32" s="25">
+        <f>IF(J32=0,I32,MAX(I32,MIN($B$10,ROUNDUP(I32*(1+J32),-1))))</f>
+        <v/>
+      </c>
+      <c r="L32" s="21" t="n"/>
+      <c r="M32" s="27">
+        <f>IF(L32&lt;&gt;"",MIN($B$10,L32),K32)</f>
+        <v/>
+      </c>
+      <c r="N32" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="O32" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="P32" s="23" t="inlineStr">
+        <is>
+          <t>3,100원</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>바코드라벨프린터업체</t>
+        </is>
+      </c>
+      <c r="B33" s="23" t="inlineStr">
+        <is>
+          <t>노출가능</t>
+        </is>
+      </c>
+      <c r="C33" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="D33" s="23" t="n"/>
+      <c r="E33" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="F33" s="23" t="n"/>
+      <c r="G33" s="24" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="H33" s="23" t="inlineStr">
+        <is>
+          <t>솔바텍 미노출</t>
+        </is>
+      </c>
+      <c r="I33" s="25" t="n">
+        <v>300</v>
+      </c>
+      <c r="J33" s="26">
+        <f>VLOOKUP(H33,$A$3:$B$8,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="K33" s="25">
+        <f>IF(J33=0,I33,MAX(I33,MIN($B$10,ROUNDUP(I33*(1+J33),-1))))</f>
+        <v/>
+      </c>
+      <c r="L33" s="21" t="n"/>
+      <c r="M33" s="27">
+        <f>IF(L33&lt;&gt;"",MIN($B$10,L33),K33)</f>
+        <v/>
+      </c>
+      <c r="N33" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="23" t="inlineStr">
+        <is>
+          <t>0원</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>바코드만들기</t>
+        </is>
+      </c>
+      <c r="B34" s="23" t="inlineStr">
+        <is>
+          <t>중지: 키워드 OFF</t>
+        </is>
+      </c>
+      <c r="C34" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="D34" s="23" t="n"/>
+      <c r="E34" s="23" t="n"/>
+      <c r="F34" s="23" t="n"/>
+      <c r="G34" s="24" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="H34" s="23" t="inlineStr">
+        <is>
+          <t>솔바텍 미노출</t>
+        </is>
+      </c>
+      <c r="I34" s="25" t="n">
+        <v>500</v>
+      </c>
+      <c r="J34" s="26">
+        <f>VLOOKUP(H34,$A$3:$B$8,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="K34" s="25">
+        <f>IF(J34=0,I34,MAX(I34,MIN($B$10,ROUNDUP(I34*(1+J34),-1))))</f>
+        <v/>
+      </c>
+      <c r="L34" s="21" t="n"/>
+      <c r="M34" s="27">
+        <f>IF(L34&lt;&gt;"",MIN($B$10,L34),K34)</f>
+        <v/>
+      </c>
+      <c r="N34" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="23" t="inlineStr">
+        <is>
+          <t>0원</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>바코드발행기</t>
+        </is>
+      </c>
+      <c r="B35" s="23" t="inlineStr">
+        <is>
+          <t>노출가능</t>
+        </is>
+      </c>
+      <c r="C35" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="D35" s="23" t="n"/>
+      <c r="E35" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="F35" s="23" t="n"/>
+      <c r="G35" s="24" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="H35" s="23" t="inlineStr">
+        <is>
+          <t>솔바텍 미노출</t>
+        </is>
+      </c>
+      <c r="I35" s="25" t="n">
+        <v>400</v>
+      </c>
+      <c r="J35" s="26">
+        <f>VLOOKUP(H35,$A$3:$B$8,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="K35" s="25">
+        <f>IF(J35=0,I35,MAX(I35,MIN($B$10,ROUNDUP(I35*(1+J35),-1))))</f>
+        <v/>
+      </c>
+      <c r="L35" s="21" t="n"/>
+      <c r="M35" s="27">
+        <f>IF(L35&lt;&gt;"",MIN($B$10,L35),K35)</f>
+        <v/>
+      </c>
+      <c r="N35" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" s="23" t="inlineStr">
+        <is>
+          <t>0원</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>바코드인쇄기</t>
+        </is>
+      </c>
+      <c r="B36" s="23" t="inlineStr">
+        <is>
+          <t>노출가능</t>
+        </is>
+      </c>
+      <c r="C36" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="D36" s="23" t="n"/>
+      <c r="E36" s="23" t="n"/>
+      <c r="F36" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="G36" s="24" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="H36" s="23" t="inlineStr">
+        <is>
+          <t>솔바텍 미노출</t>
+        </is>
+      </c>
+      <c r="I36" s="25" t="n">
+        <v>3300</v>
+      </c>
+      <c r="J36" s="26">
+        <f>VLOOKUP(H36,$A$3:$B$8,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="K36" s="25">
+        <f>IF(J36=0,I36,MAX(I36,MIN($B$10,ROUNDUP(I36*(1+J36),-1))))</f>
+        <v/>
+      </c>
+      <c r="L36" s="21" t="n"/>
+      <c r="M36" s="27">
+        <f>IF(L36&lt;&gt;"",MIN($B$10,L36),K36)</f>
+        <v/>
+      </c>
+      <c r="N36" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="O36" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" s="23" t="inlineStr">
+        <is>
+          <t>0원</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>바코드출력기</t>
+        </is>
+      </c>
+      <c r="B37" s="23" t="inlineStr">
+        <is>
+          <t>노출가능</t>
+        </is>
+      </c>
+      <c r="C37" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="D37" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="E37" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="F37" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="24" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="H37" s="23" t="inlineStr">
+        <is>
+          <t>순위 차이 큼</t>
+        </is>
+      </c>
+      <c r="I37" s="25" t="n">
+        <v>2500</v>
+      </c>
+      <c r="J37" s="26">
+        <f>VLOOKUP(H37,$A$3:$B$8,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="K37" s="25">
+        <f>IF(J37=0,I37,MAX(I37,MIN($B$10,ROUNDUP(I37*(1+J37),-1))))</f>
+        <v/>
+      </c>
+      <c r="L37" s="21" t="n"/>
+      <c r="M37" s="27">
+        <f>IF(L37&lt;&gt;"",MIN($B$10,L37),K37)</f>
+        <v/>
+      </c>
+      <c r="N37" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="O37" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" s="23" t="inlineStr">
+        <is>
+          <t>0원</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>바코드프린터기</t>
+        </is>
+      </c>
+      <c r="B38" s="23" t="inlineStr">
+        <is>
+          <t>노출가능</t>
+        </is>
+      </c>
+      <c r="C38" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="D38" s="23" t="n"/>
+      <c r="E38" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="23" t="n"/>
+      <c r="G38" s="24" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="H38" s="23" t="inlineStr">
+        <is>
+          <t>솔바텍 미노출</t>
+        </is>
+      </c>
+      <c r="I38" s="25" t="n">
+        <v>4000</v>
+      </c>
+      <c r="J38" s="26">
+        <f>VLOOKUP(H38,$A$3:$B$8,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="K38" s="25">
+        <f>IF(J38=0,I38,MAX(I38,MIN($B$10,ROUNDUP(I38*(1+J38),-1))))</f>
+        <v/>
+      </c>
+      <c r="L38" s="21" t="n"/>
+      <c r="M38" s="27">
+        <f>IF(L38&lt;&gt;"",MIN($B$10,L38),K38)</f>
+        <v/>
+      </c>
+      <c r="N38" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="O38" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" s="23" t="inlineStr">
+        <is>
+          <t>0원</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>바코드프린터라벨</t>
+        </is>
+      </c>
+      <c r="B39" s="23" t="inlineStr">
+        <is>
+          <t>노출가능</t>
+        </is>
+      </c>
+      <c r="C39" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="D39" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="E39" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="F39" s="23" t="n"/>
+      <c r="G39" s="24" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="H39" s="23" t="inlineStr">
+        <is>
+          <t>순위 차이 큼</t>
+        </is>
+      </c>
+      <c r="I39" s="25" t="n">
+        <v>1100</v>
+      </c>
+      <c r="J39" s="26">
+        <f>VLOOKUP(H39,$A$3:$B$8,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="K39" s="25">
+        <f>IF(J39=0,I39,MAX(I39,MIN($B$10,ROUNDUP(I39*(1+J39),-1))))</f>
+        <v/>
+      </c>
+      <c r="L39" s="21" t="n"/>
+      <c r="M39" s="27">
+        <f>IF(L39&lt;&gt;"",MIN($B$10,L39),K39)</f>
+        <v/>
+      </c>
+      <c r="N39" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="O39" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" s="23" t="inlineStr">
+        <is>
+          <t>0원</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>바코드프린터전문업체</t>
+        </is>
+      </c>
+      <c r="B40" s="23" t="inlineStr">
+        <is>
+          <t>노출가능</t>
+        </is>
+      </c>
+      <c r="C40" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="D40" s="23" t="n"/>
+      <c r="E40" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="F40" s="23" t="n"/>
+      <c r="G40" s="24" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="H40" s="23" t="inlineStr">
+        <is>
+          <t>솔바텍 미노출</t>
+        </is>
+      </c>
+      <c r="I40" s="25" t="n">
+        <v>700</v>
+      </c>
+      <c r="J40" s="26">
+        <f>VLOOKUP(H40,$A$3:$B$8,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="K40" s="25">
+        <f>IF(J40=0,I40,MAX(I40,MIN($B$10,ROUNDUP(I40*(1+J40),-1))))</f>
+        <v/>
+      </c>
+      <c r="L40" s="21" t="n"/>
+      <c r="M40" s="27">
+        <f>IF(L40&lt;&gt;"",MIN($B$10,L40),K40)</f>
+        <v/>
+      </c>
+      <c r="N40" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" s="23" t="inlineStr">
+        <is>
+          <t>0원</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>바코드프린터추천</t>
+        </is>
+      </c>
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>노출가능</t>
+        </is>
+      </c>
+      <c r="C41" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="D41" s="23" t="n"/>
+      <c r="E41" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="F41" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="24" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="H41" s="23" t="inlineStr">
+        <is>
+          <t>솔바텍 미노출</t>
+        </is>
+      </c>
+      <c r="I41" s="25" t="n">
+        <v>1700</v>
+      </c>
+      <c r="J41" s="26">
+        <f>VLOOKUP(H41,$A$3:$B$8,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="K41" s="25">
+        <f>IF(J41=0,I41,MAX(I41,MIN($B$10,ROUNDUP(I41*(1+J41),-1))))</f>
+        <v/>
+      </c>
+      <c r="L41" s="21" t="n"/>
+      <c r="M41" s="27">
+        <f>IF(L41&lt;&gt;"",MIN($B$10,L41),K41)</f>
+        <v/>
+      </c>
+      <c r="N41" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" s="23" t="inlineStr">
+        <is>
+          <t>0원</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>바코드프린터판매</t>
+        </is>
+      </c>
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>노출가능</t>
+        </is>
+      </c>
+      <c r="C42" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="D42" s="23" t="n"/>
+      <c r="E42" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="F42" s="23" t="n"/>
+      <c r="G42" s="24" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="H42" s="23" t="inlineStr">
+        <is>
+          <t>솔바텍 미노출</t>
+        </is>
+      </c>
+      <c r="I42" s="25" t="n">
+        <v>280</v>
+      </c>
+      <c r="J42" s="26">
+        <f>VLOOKUP(H42,$A$3:$B$8,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="K42" s="25">
+        <f>IF(J42=0,I42,MAX(I42,MIN($B$10,ROUNDUP(I42*(1+J42),-1))))</f>
+        <v/>
+      </c>
+      <c r="L42" s="21" t="n"/>
+      <c r="M42" s="27">
+        <f>IF(L42&lt;&gt;"",MIN($B$10,L42),K42)</f>
+        <v/>
+      </c>
+      <c r="N42" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" s="23" t="inlineStr">
+        <is>
+          <t>0원</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>바코드프린터프로그램</t>
+        </is>
+      </c>
+      <c r="B43" s="18" t="inlineStr">
+        <is>
+          <t>노출가능</t>
+        </is>
+      </c>
+      <c r="C43" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="D43" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E43" s="18" t="n"/>
+      <c r="F43" s="18" t="n"/>
+      <c r="G43" s="18" t="n"/>
+      <c r="H43" s="18" t="inlineStr">
+        <is>
+          <t>유지</t>
+        </is>
+      </c>
+      <c r="I43" s="19" t="n">
+        <v>2750</v>
+      </c>
+      <c r="J43" s="20">
+        <f>VLOOKUP(H43,$A$3:$B$8,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="K43" s="19">
+        <f>IF(J43=0,I43,MAX(I43,MIN($B$10,ROUNDUP(I43*(1+J43),-1))))</f>
+        <v/>
+      </c>
+      <c r="L43" s="21" t="n"/>
+      <c r="M43" s="22">
+        <f>IF(L43&lt;&gt;"",MIN($B$10,L43),K43)</f>
+        <v/>
+      </c>
+      <c r="N43" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="O43" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" s="18" t="inlineStr">
+        <is>
+          <t>0원</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>빅솔론</t>
+        </is>
+      </c>
+      <c r="B44" s="18" t="inlineStr">
+        <is>
+          <t>노출가능</t>
+        </is>
+      </c>
+      <c r="C44" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="D44" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E44" s="18" t="n"/>
+      <c r="F44" s="18" t="n"/>
+      <c r="G44" s="18" t="n"/>
+      <c r="H44" s="18" t="inlineStr">
+        <is>
+          <t>유지</t>
+        </is>
+      </c>
+      <c r="I44" s="19" t="n">
+        <v>800</v>
+      </c>
+      <c r="J44" s="20">
+        <f>VLOOKUP(H44,$A$3:$B$8,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="K44" s="19">
+        <f>IF(J44=0,I44,MAX(I44,MIN($B$10,ROUNDUP(I44*(1+J44),-1))))</f>
+        <v/>
+      </c>
+      <c r="L44" s="21" t="n"/>
+      <c r="M44" s="22">
+        <f>IF(L44&lt;&gt;"",MIN($B$10,L44),K44)</f>
+        <v/>
+      </c>
+      <c r="N44" s="18" t="n">
+        <v>562</v>
+      </c>
+      <c r="O44" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" s="18" t="inlineStr">
+        <is>
+          <t>0원</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>빅솔론총판</t>
+        </is>
+      </c>
+      <c r="B45" s="23" t="inlineStr">
+        <is>
+          <t>노출가능</t>
+        </is>
+      </c>
+      <c r="C45" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="D45" s="23" t="n"/>
+      <c r="E45" s="23" t="n"/>
+      <c r="F45" s="23" t="n"/>
+      <c r="G45" s="24" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="H45" s="23" t="inlineStr">
+        <is>
+          <t>솔바텍 미노출</t>
+        </is>
+      </c>
+      <c r="I45" s="25" t="n">
+        <v>70</v>
+      </c>
+      <c r="J45" s="26">
+        <f>VLOOKUP(H45,$A$3:$B$8,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="K45" s="25">
+        <f>IF(J45=0,I45,MAX(I45,MIN($B$10,ROUNDUP(I45*(1+J45),-1))))</f>
+        <v/>
+      </c>
+      <c r="L45" s="21" t="n"/>
+      <c r="M45" s="27">
+        <f>IF(L45&lt;&gt;"",MIN($B$10,L45),K45)</f>
+        <v/>
+      </c>
+      <c r="N45" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" s="23" t="inlineStr">
+        <is>
+          <t>0원</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>빅솔론프린터</t>
+        </is>
+      </c>
+      <c r="B46" s="23" t="inlineStr">
+        <is>
+          <t>노출가능</t>
+        </is>
+      </c>
+      <c r="C46" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="D46" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="E46" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" s="23" t="n"/>
+      <c r="G46" s="24" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="H46" s="23" t="inlineStr">
+        <is>
+          <t>순위 차이 큼</t>
+        </is>
+      </c>
+      <c r="I46" s="25" t="n">
+        <v>940</v>
+      </c>
+      <c r="J46" s="26">
+        <f>VLOOKUP(H46,$A$3:$B$8,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="K46" s="25">
+        <f>IF(J46=0,I46,MAX(I46,MIN($B$10,ROUNDUP(I46*(1+J46),-1))))</f>
+        <v/>
+      </c>
+      <c r="L46" s="21" t="n"/>
+      <c r="M46" s="27">
+        <f>IF(L46&lt;&gt;"",MIN($B$10,L46),K46)</f>
+        <v/>
+      </c>
+      <c r="N46" s="23" t="n">
+        <v>43</v>
+      </c>
+      <c r="O46" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" s="23" t="inlineStr">
+        <is>
+          <t>0원</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>산업용라벨프린터</t>
+        </is>
+      </c>
+      <c r="B47" s="18" t="inlineStr">
+        <is>
+          <t>노출가능</t>
+        </is>
+      </c>
+      <c r="C47" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="D47" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="E47" s="18" t="n"/>
+      <c r="F47" s="18" t="n"/>
+      <c r="G47" s="18" t="n"/>
+      <c r="H47" s="18" t="inlineStr">
+        <is>
+          <t>유지</t>
+        </is>
+      </c>
+      <c r="I47" s="19" t="n">
+        <v>5000</v>
+      </c>
+      <c r="J47" s="20">
+        <f>VLOOKUP(H47,$A$3:$B$8,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="K47" s="19">
+        <f>IF(J47=0,I47,MAX(I47,MIN($B$10,ROUNDUP(I47*(1+J47),-1))))</f>
+        <v/>
+      </c>
+      <c r="L47" s="21" t="n"/>
+      <c r="M47" s="22">
+        <f>IF(L47&lt;&gt;"",MIN($B$10,L47),K47)</f>
+        <v/>
+      </c>
+      <c r="N47" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="O47" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="P47" s="18" t="inlineStr">
+        <is>
+          <t>4,970원</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>산업용바코드프린터</t>
+        </is>
+      </c>
+      <c r="B48" s="23" t="inlineStr">
+        <is>
+          <t>노출가능</t>
+        </is>
+      </c>
+      <c r="C48" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="D48" s="23" t="n"/>
+      <c r="E48" s="23" t="n"/>
+      <c r="F48" s="23" t="n"/>
+      <c r="G48" s="24" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="H48" s="23" t="inlineStr">
+        <is>
+          <t>솔바텍 미노출</t>
+        </is>
+      </c>
+      <c r="I48" s="25" t="n">
+        <v>800</v>
+      </c>
+      <c r="J48" s="26">
+        <f>VLOOKUP(H48,$A$3:$B$8,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="K48" s="25">
+        <f>IF(J48=0,I48,MAX(I48,MIN($B$10,ROUNDUP(I48*(1+J48),-1))))</f>
+        <v/>
+      </c>
+      <c r="L48" s="21" t="n"/>
+      <c r="M48" s="27">
+        <f>IF(L48&lt;&gt;"",MIN($B$10,L48),K48)</f>
+        <v/>
+      </c>
+      <c r="N48" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" s="23" t="inlineStr">
+        <is>
+          <t>0원</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>산업용프린터</t>
+        </is>
+      </c>
+      <c r="B49" s="23" t="inlineStr">
+        <is>
+          <t>노출가능</t>
+        </is>
+      </c>
+      <c r="C49" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="D49" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="F49" s="23" t="n"/>
+      <c r="G49" s="24" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="H49" s="23" t="inlineStr">
+        <is>
+          <t>붙어있음(위)</t>
+        </is>
+      </c>
+      <c r="I49" s="25" t="n">
+        <v>6500</v>
+      </c>
+      <c r="J49" s="26">
+        <f>VLOOKUP(H49,$A$3:$B$8,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="K49" s="25">
+        <f>IF(J49=0,I49,MAX(I49,MIN($B$10,ROUNDUP(I49*(1+J49),-1))))</f>
+        <v/>
+      </c>
+      <c r="L49" s="21" t="n"/>
+      <c r="M49" s="27">
+        <f>IF(L49&lt;&gt;"",MIN($B$10,L49),K49)</f>
+        <v/>
+      </c>
+      <c r="N49" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="O49" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="P49" s="23" t="inlineStr">
+        <is>
+          <t>6,578원</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>소형바코드프린터</t>
+        </is>
+      </c>
+      <c r="B50" s="23" t="inlineStr">
+        <is>
+          <t>노출가능</t>
+        </is>
+      </c>
+      <c r="C50" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="D50" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="E50" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="F50" s="23" t="n"/>
+      <c r="G50" s="24" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="H50" s="23" t="inlineStr">
+        <is>
+          <t>붙어있음(아래)</t>
+        </is>
+      </c>
+      <c r="I50" s="25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J50" s="26">
+        <f>VLOOKUP(H50,$A$3:$B$8,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="K50" s="25">
+        <f>IF(J50=0,I50,MAX(I50,MIN($B$10,ROUNDUP(I50*(1+J50),-1))))</f>
+        <v/>
+      </c>
+      <c r="L50" s="21" t="n"/>
+      <c r="M50" s="27">
+        <f>IF(L50&lt;&gt;"",MIN($B$10,L50),K50)</f>
+        <v/>
+      </c>
+      <c r="N50" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" s="23" t="inlineStr">
+        <is>
+          <t>0원</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>스티커라벨기</t>
+        </is>
+      </c>
+      <c r="B51" s="23" t="inlineStr">
+        <is>
+          <t>노출가능</t>
+        </is>
+      </c>
+      <c r="C51" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="D51" s="23" t="n"/>
+      <c r="E51" s="23" t="n"/>
+      <c r="F51" s="23" t="n"/>
+      <c r="G51" s="24" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="H51" s="23" t="inlineStr">
+        <is>
+          <t>솔바텍 미노출</t>
+        </is>
+      </c>
+      <c r="I51" s="25" t="n">
+        <v>2300</v>
+      </c>
+      <c r="J51" s="26">
+        <f>VLOOKUP(H51,$A$3:$B$8,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="K51" s="25">
+        <f>IF(J51=0,I51,MAX(I51,MIN($B$10,ROUNDUP(I51*(1+J51),-1))))</f>
+        <v/>
+      </c>
+      <c r="L51" s="21" t="n"/>
+      <c r="M51" s="27">
+        <f>IF(L51&lt;&gt;"",MIN($B$10,L51),K51)</f>
+        <v/>
+      </c>
+      <c r="N51" s="23" t="n">
+        <v>21</v>
+      </c>
+      <c r="O51" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" s="23" t="inlineStr">
+        <is>
+          <t>0원</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>스티커인쇄기</t>
+        </is>
+      </c>
+      <c r="B52" s="18" t="inlineStr">
+        <is>
+          <t>노출가능</t>
+        </is>
+      </c>
+      <c r="C52" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="D52" s="18" t="n"/>
+      <c r="E52" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="F52" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="18" t="n"/>
+      <c r="H52" s="18" t="inlineStr">
+        <is>
+          <t>유지</t>
+        </is>
+      </c>
+      <c r="I52" s="19" t="n">
+        <v>800</v>
+      </c>
+      <c r="J52" s="20">
+        <f>VLOOKUP(H52,$A$3:$B$8,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="K52" s="19">
+        <f>IF(J52=0,I52,MAX(I52,MIN($B$10,ROUNDUP(I52*(1+J52),-1))))</f>
+        <v/>
+      </c>
+      <c r="L52" s="21" t="n"/>
+      <c r="M52" s="22">
+        <f>IF(L52&lt;&gt;"",MIN($B$10,L52),K52)</f>
+        <v/>
+      </c>
+      <c r="N52" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="O52" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" s="18" t="inlineStr">
+        <is>
+          <t>0원</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>스티커출력기</t>
+        </is>
+      </c>
+      <c r="B53" s="23" t="inlineStr">
+        <is>
+          <t>노출가능</t>
+        </is>
+      </c>
+      <c r="C53" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="D53" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="E53" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" s="23" t="n"/>
+      <c r="G53" s="24" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="H53" s="23" t="inlineStr">
+        <is>
+          <t>순위 차이 큼</t>
+        </is>
+      </c>
+      <c r="I53" s="25" t="n">
+        <v>400</v>
+      </c>
+      <c r="J53" s="26">
+        <f>VLOOKUP(H53,$A$3:$B$8,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="K53" s="25">
+        <f>IF(J53=0,I53,MAX(I53,MIN($B$10,ROUNDUP(I53*(1+J53),-1))))</f>
+        <v/>
+      </c>
+      <c r="L53" s="21" t="n"/>
+      <c r="M53" s="27">
+        <f>IF(L53&lt;&gt;"",MIN($B$10,L53),K53)</f>
+        <v/>
+      </c>
+      <c r="N53" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="O53" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" s="23" t="inlineStr">
+        <is>
+          <t>0원</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="8" t="inlineStr">
+        <is>
+          <t>스티커프린터</t>
+        </is>
+      </c>
+      <c r="B54" s="23" t="inlineStr">
+        <is>
+          <t>노출가능</t>
+        </is>
+      </c>
+      <c r="C54" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="D54" s="23" t="n"/>
+      <c r="E54" s="23" t="n"/>
+      <c r="F54" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="24" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="H54" s="23" t="inlineStr">
+        <is>
+          <t>솔바텍 미노출</t>
+        </is>
+      </c>
+      <c r="I54" s="25" t="n">
+        <v>1340</v>
+      </c>
+      <c r="J54" s="26">
+        <f>VLOOKUP(H54,$A$3:$B$8,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="K54" s="25">
+        <f>IF(J54=0,I54,MAX(I54,MIN($B$10,ROUNDUP(I54*(1+J54),-1))))</f>
+        <v/>
+      </c>
+      <c r="L54" s="21" t="n"/>
+      <c r="M54" s="27">
+        <f>IF(L54&lt;&gt;"",MIN($B$10,L54),K54)</f>
+        <v/>
+      </c>
+      <c r="N54" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="O54" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" s="23" t="inlineStr">
+        <is>
+          <t>0원</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>열전사프린터</t>
+        </is>
+      </c>
+      <c r="B55" s="23" t="inlineStr">
+        <is>
+          <t>노출가능</t>
+        </is>
+      </c>
+      <c r="C55" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="D55" s="23" t="n"/>
+      <c r="E55" s="23" t="n"/>
+      <c r="F55" s="23" t="n"/>
+      <c r="G55" s="24" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="H55" s="23" t="inlineStr">
+        <is>
+          <t>솔바텍 미노출</t>
+        </is>
+      </c>
+      <c r="I55" s="25" t="n">
+        <v>5500</v>
+      </c>
+      <c r="J55" s="26">
+        <f>VLOOKUP(H55,$A$3:$B$8,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="K55" s="25">
+        <f>IF(J55=0,I55,MAX(I55,MIN($B$10,ROUNDUP(I55*(1+J55),-1))))</f>
+        <v/>
+      </c>
+      <c r="L55" s="21" t="n"/>
+      <c r="M55" s="27">
+        <f>IF(L55&lt;&gt;"",MIN($B$10,L55),K55)</f>
+        <v/>
+      </c>
+      <c r="N55" s="23" t="n">
+        <v>13</v>
+      </c>
+      <c r="O55" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" s="23" t="inlineStr">
+        <is>
+          <t>0원</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>열전사프린터기</t>
+        </is>
+      </c>
+      <c r="B56" s="23" t="inlineStr">
+        <is>
+          <t>노출가능</t>
+        </is>
+      </c>
+      <c r="C56" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="D56" s="23" t="n"/>
+      <c r="E56" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="F56" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="G56" s="24" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="H56" s="23" t="inlineStr">
+        <is>
+          <t>솔바텍 미노출</t>
+        </is>
+      </c>
+      <c r="I56" s="25" t="n">
+        <v>450</v>
+      </c>
+      <c r="J56" s="26">
+        <f>VLOOKUP(H56,$A$3:$B$8,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="K56" s="25">
+        <f>IF(J56=0,I56,MAX(I56,MIN($B$10,ROUNDUP(I56*(1+J56),-1))))</f>
+        <v/>
+      </c>
+      <c r="L56" s="21" t="n"/>
+      <c r="M56" s="27">
+        <f>IF(L56&lt;&gt;"",MIN($B$10,L56),K56)</f>
+        <v/>
+      </c>
+      <c r="N56" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" s="23" t="inlineStr">
+        <is>
+          <t>0원</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>영수증프린터</t>
+        </is>
+      </c>
+      <c r="B57" s="23" t="inlineStr">
+        <is>
+          <t>노출가능</t>
+        </is>
+      </c>
+      <c r="C57" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="D57" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="E57" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="F57" s="23" t="n"/>
+      <c r="G57" s="24" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="H57" s="23" t="inlineStr">
+        <is>
+          <t>붙어있음(위)</t>
+        </is>
+      </c>
+      <c r="I57" s="25" t="n">
+        <v>1070</v>
+      </c>
+      <c r="J57" s="26">
+        <f>VLOOKUP(H57,$A$3:$B$8,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="K57" s="25">
+        <f>IF(J57=0,I57,MAX(I57,MIN($B$10,ROUNDUP(I57*(1+J57),-1))))</f>
+        <v/>
+      </c>
+      <c r="L57" s="21" t="n"/>
+      <c r="M57" s="27">
+        <f>IF(L57&lt;&gt;"",MIN($B$10,L57),K57)</f>
+        <v/>
+      </c>
+      <c r="N57" s="23" t="n">
+        <v>85</v>
+      </c>
+      <c r="O57" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" s="23" t="inlineStr">
+        <is>
+          <t>0원</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>제브라</t>
+        </is>
+      </c>
+      <c r="B58" s="18" t="inlineStr">
+        <is>
+          <t>노출가능</t>
+        </is>
+      </c>
+      <c r="C58" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D58" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="E58" s="18" t="n"/>
+      <c r="F58" s="18" t="n"/>
+      <c r="G58" s="18" t="n"/>
+      <c r="H58" s="18" t="inlineStr">
+        <is>
+          <t>유지</t>
+        </is>
+      </c>
+      <c r="I58" s="19" t="n">
+        <v>1500</v>
+      </c>
+      <c r="J58" s="20">
+        <f>VLOOKUP(H58,$A$3:$B$8,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="K58" s="19">
+        <f>IF(J58=0,I58,MAX(I58,MIN($B$10,ROUNDUP(I58*(1+J58),-1))))</f>
+        <v/>
+      </c>
+      <c r="L58" s="21" t="n"/>
+      <c r="M58" s="22">
+        <f>IF(L58&lt;&gt;"",MIN($B$10,L58),K58)</f>
+        <v/>
+      </c>
+      <c r="N58" s="18" t="n">
+        <v>115</v>
+      </c>
+      <c r="O58" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="P58" s="18" t="inlineStr">
+        <is>
+          <t>1,464원</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>제브라라벨프린터</t>
+        </is>
+      </c>
+      <c r="B59" s="23" t="inlineStr">
+        <is>
+          <t>노출가능</t>
+        </is>
+      </c>
+      <c r="C59" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="D59" s="23" t="n"/>
+      <c r="E59" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="F59" s="23" t="n"/>
+      <c r="G59" s="24" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="H59" s="23" t="inlineStr">
+        <is>
+          <t>솔바텍 미노출</t>
+        </is>
+      </c>
+      <c r="I59" s="25" t="n">
+        <v>700</v>
+      </c>
+      <c r="J59" s="26">
+        <f>VLOOKUP(H59,$A$3:$B$8,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="K59" s="25">
+        <f>IF(J59=0,I59,MAX(I59,MIN($B$10,ROUNDUP(I59*(1+J59),-1))))</f>
+        <v/>
+      </c>
+      <c r="L59" s="21" t="n"/>
+      <c r="M59" s="27">
+        <f>IF(L59&lt;&gt;"",MIN($B$10,L59),K59)</f>
+        <v/>
+      </c>
+      <c r="N59" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="O59" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" s="23" t="inlineStr">
+        <is>
+          <t>0원</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="inlineStr">
+        <is>
+          <t>제브라바코드프린터</t>
+        </is>
+      </c>
+      <c r="B60" s="23" t="inlineStr">
+        <is>
+          <t>노출가능</t>
+        </is>
+      </c>
+      <c r="C60" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="D60" s="23" t="n"/>
+      <c r="E60" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="F60" s="23" t="n"/>
+      <c r="G60" s="24" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="H60" s="23" t="inlineStr">
+        <is>
+          <t>솔바텍 미노출</t>
+        </is>
+      </c>
+      <c r="I60" s="25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J60" s="26">
+        <f>VLOOKUP(H60,$A$3:$B$8,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="K60" s="25">
+        <f>IF(J60=0,I60,MAX(I60,MIN($B$10,ROUNDUP(I60*(1+J60),-1))))</f>
+        <v/>
+      </c>
+      <c r="L60" s="21" t="n"/>
+      <c r="M60" s="27">
+        <f>IF(L60&lt;&gt;"",MIN($B$10,L60),K60)</f>
+        <v/>
+      </c>
+      <c r="N60" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="O60" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" s="23" t="inlineStr">
+        <is>
+          <t>0원</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="8" t="inlineStr">
+        <is>
+          <t>제브라프린터</t>
+        </is>
+      </c>
+      <c r="B61" s="23" t="inlineStr">
+        <is>
+          <t>노출가능</t>
+        </is>
+      </c>
+      <c r="C61" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="D61" s="23" t="n"/>
+      <c r="E61" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="F61" s="23" t="n"/>
+      <c r="G61" s="24" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="H61" s="23" t="inlineStr">
+        <is>
+          <t>솔바텍 미노출</t>
+        </is>
+      </c>
+      <c r="I61" s="25" t="n">
+        <v>1410</v>
+      </c>
+      <c r="J61" s="26">
+        <f>VLOOKUP(H61,$A$3:$B$8,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="K61" s="25">
+        <f>IF(J61=0,I61,MAX(I61,MIN($B$10,ROUNDUP(I61*(1+J61),-1))))</f>
+        <v/>
+      </c>
+      <c r="L61" s="21" t="n"/>
+      <c r="M61" s="27">
+        <f>IF(L61&lt;&gt;"",MIN($B$10,L61),K61)</f>
+        <v/>
+      </c>
+      <c r="N61" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="O61" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" s="23" t="inlineStr">
+        <is>
+          <t>0원</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="8" t="inlineStr">
+        <is>
+          <t>카드프린터기</t>
+        </is>
+      </c>
+      <c r="B62" s="23" t="inlineStr">
+        <is>
+          <t>중지: 키워드 OFF</t>
+        </is>
+      </c>
+      <c r="C62" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="D62" s="23" t="n"/>
+      <c r="E62" s="23" t="n"/>
+      <c r="F62" s="23" t="n"/>
+      <c r="G62" s="24" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="H62" s="23" t="inlineStr">
+        <is>
+          <t>솔바텍 미노출</t>
+        </is>
+      </c>
+      <c r="I62" s="25" t="n">
+        <v>70</v>
+      </c>
+      <c r="J62" s="26">
+        <f>VLOOKUP(H62,$A$3:$B$8,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="K62" s="25">
+        <f>IF(J62=0,I62,MAX(I62,MIN($B$10,ROUNDUP(I62*(1+J62),-1))))</f>
+        <v/>
+      </c>
+      <c r="L62" s="21" t="n"/>
+      <c r="M62" s="27">
+        <f>IF(L62&lt;&gt;"",MIN($B$10,L62),K62)</f>
+        <v/>
+      </c>
+      <c r="N62" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" s="23" t="inlineStr">
+        <is>
+          <t>0원</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>프린터관리</t>
+        </is>
+      </c>
+      <c r="B63" s="18" t="inlineStr">
+        <is>
+          <t>중지: 키워드 OFF</t>
+        </is>
+      </c>
+      <c r="C63" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="D63" s="18" t="n"/>
+      <c r="E63" s="18" t="n"/>
+      <c r="F63" s="18" t="n"/>
+      <c r="G63" s="18" t="n"/>
+      <c r="H63" s="18" t="inlineStr">
+        <is>
+          <t>유지</t>
+        </is>
+      </c>
+      <c r="I63" s="19" t="n">
+        <v>200</v>
+      </c>
+      <c r="J63" s="20">
+        <f>VLOOKUP(H63,$A$3:$B$8,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="K63" s="19">
+        <f>IF(J63=0,I63,MAX(I63,MIN($B$10,ROUNDUP(I63*(1+J63),-1))))</f>
+        <v/>
+      </c>
+      <c r="L63" s="21" t="n"/>
+      <c r="M63" s="22">
+        <f>IF(L63&lt;&gt;"",MIN($B$10,L63),K63)</f>
+        <v/>
+      </c>
+      <c r="N63" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" s="18" t="inlineStr">
+        <is>
+          <t>0원</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A13:P63"/>
+  <mergeCells count="8">
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="C2:F2"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="H14:H63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>=$A$3:$A$8</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:L432"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -521,22 +3767,23 @@
           <t>입찰가 변경 전</t>
         </is>
       </c>
-      <c r="C1" s="3" t="n"/>
-      <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="n"/>
-      <c r="G1" s="3" t="n"/>
+      <c r="C1" s="28" t="n"/>
+      <c r="D1" s="28" t="n"/>
+      <c r="E1" s="28" t="n"/>
+      <c r="F1" s="28" t="n"/>
+      <c r="G1" s="29" t="n"/>
       <c r="H1" s="4" t="inlineStr">
         <is>
           <t>입찰가 변경 후</t>
         </is>
       </c>
-      <c r="I1" s="5" t="n"/>
-      <c r="J1" s="5" t="n"/>
-      <c r="K1" s="5" t="n"/>
-      <c r="L1" s="5" t="n"/>
+      <c r="I1" s="28" t="n"/>
+      <c r="J1" s="28" t="n"/>
+      <c r="K1" s="28" t="n"/>
+      <c r="L1" s="29" t="n"/>
     </row>
     <row r="2">
+      <c r="A2" s="30" t="n"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>현재 입찰가</t>
@@ -6059,7 +9306,10 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H305" s="9" t="n"/>
+      <c r="H305" s="31">
+        <f>'프린터 입찰가'!M21</f>
+        <v/>
+      </c>
       <c r="I305" s="9" t="n"/>
       <c r="J305" s="9" t="n"/>
       <c r="K305" s="9" t="n"/>
@@ -6087,7 +9337,10 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H306" s="9" t="n"/>
+      <c r="H306" s="31">
+        <f>'프린터 입찰가'!M23</f>
+        <v/>
+      </c>
       <c r="I306" s="9" t="n"/>
       <c r="J306" s="9" t="n"/>
       <c r="K306" s="9" t="n"/>
@@ -6115,7 +9368,10 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H307" s="9" t="n"/>
+      <c r="H307" s="31">
+        <f>'프린터 입찰가'!M24</f>
+        <v/>
+      </c>
       <c r="I307" s="9" t="n"/>
       <c r="J307" s="9" t="n"/>
       <c r="K307" s="9" t="n"/>
@@ -6143,7 +9399,10 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H308" s="9" t="n"/>
+      <c r="H308" s="31">
+        <f>'프린터 입찰가'!M26</f>
+        <v/>
+      </c>
       <c r="I308" s="9" t="n"/>
       <c r="J308" s="9" t="n"/>
       <c r="K308" s="9" t="n"/>
@@ -6173,7 +9432,10 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H309" s="9" t="n"/>
+      <c r="H309" s="31">
+        <f>'프린터 입찰가'!M27</f>
+        <v/>
+      </c>
       <c r="I309" s="9" t="n"/>
       <c r="J309" s="9" t="n"/>
       <c r="K309" s="9" t="n"/>
@@ -6201,7 +9463,10 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H310" s="9" t="n"/>
+      <c r="H310" s="31">
+        <f>'프린터 입찰가'!M31</f>
+        <v/>
+      </c>
       <c r="I310" s="9" t="n"/>
       <c r="J310" s="9" t="n"/>
       <c r="K310" s="9" t="n"/>
@@ -6229,7 +9494,10 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H311" s="9" t="n"/>
+      <c r="H311" s="31">
+        <f>'프린터 입찰가'!M36</f>
+        <v/>
+      </c>
       <c r="I311" s="9" t="n"/>
       <c r="J311" s="9" t="n"/>
       <c r="K311" s="9" t="n"/>
@@ -6259,7 +9527,10 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H312" s="9" t="n"/>
+      <c r="H312" s="31">
+        <f>'프린터 입찰가'!M41</f>
+        <v/>
+      </c>
       <c r="I312" s="9" t="n"/>
       <c r="J312" s="9" t="n"/>
       <c r="K312" s="9" t="n"/>
@@ -6311,7 +9582,10 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H314" s="9" t="n"/>
+      <c r="H314" s="31">
+        <f>'프린터 입찰가'!M59</f>
+        <v/>
+      </c>
       <c r="I314" s="9" t="n"/>
       <c r="J314" s="9" t="n"/>
       <c r="K314" s="9" t="n"/>
@@ -6339,7 +9613,10 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H315" s="9" t="n"/>
+      <c r="H315" s="31">
+        <f>'프린터 입찰가'!M60</f>
+        <v/>
+      </c>
       <c r="I315" s="9" t="n"/>
       <c r="J315" s="9" t="n"/>
       <c r="K315" s="9" t="n"/>
@@ -6367,7 +9644,10 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H316" s="9" t="n"/>
+      <c r="H316" s="31">
+        <f>'프린터 입찰가'!M33</f>
+        <v/>
+      </c>
       <c r="I316" s="9" t="n"/>
       <c r="J316" s="9" t="n"/>
       <c r="K316" s="9" t="n"/>
@@ -6395,7 +9675,10 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H317" s="9" t="n"/>
+      <c r="H317" s="31">
+        <f>'프린터 입찰가'!M40</f>
+        <v/>
+      </c>
       <c r="I317" s="9" t="n"/>
       <c r="J317" s="9" t="n"/>
       <c r="K317" s="9" t="n"/>
@@ -6469,7 +9752,10 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H320" s="9" t="n"/>
+      <c r="H320" s="31">
+        <f>'프린터 입찰가'!M20</f>
+        <v/>
+      </c>
       <c r="I320" s="9" t="n"/>
       <c r="J320" s="9" t="n"/>
       <c r="K320" s="9" t="n"/>
@@ -6497,7 +9783,10 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H321" s="9" t="n"/>
+      <c r="H321" s="31">
+        <f>'프린터 입찰가'!M35</f>
+        <v/>
+      </c>
       <c r="I321" s="9" t="n"/>
       <c r="J321" s="9" t="n"/>
       <c r="K321" s="9" t="n"/>
@@ -6525,7 +9814,10 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H322" s="9" t="n"/>
+      <c r="H322" s="31">
+        <f>'프린터 입찰가'!M42</f>
+        <v/>
+      </c>
       <c r="I322" s="9" t="n"/>
       <c r="J322" s="9" t="n"/>
       <c r="K322" s="9" t="n"/>
@@ -6555,7 +9847,10 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H323" s="9" t="n"/>
+      <c r="H323" s="31">
+        <f>'프린터 입찰가'!M46</f>
+        <v/>
+      </c>
       <c r="I323" s="9" t="n"/>
       <c r="J323" s="9" t="n"/>
       <c r="K323" s="9" t="n"/>
@@ -6585,7 +9880,10 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H324" s="9" t="n"/>
+      <c r="H324" s="31">
+        <f>'프린터 입찰가'!M50</f>
+        <v/>
+      </c>
       <c r="I324" s="9" t="n"/>
       <c r="J324" s="9" t="n"/>
       <c r="K324" s="9" t="n"/>
@@ -6637,7 +9935,10 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H326" s="9" t="n"/>
+      <c r="H326" s="31">
+        <f>'프린터 입찰가'!M61</f>
+        <v/>
+      </c>
       <c r="I326" s="9" t="n"/>
       <c r="J326" s="9" t="n"/>
       <c r="K326" s="9" t="n"/>
@@ -6687,7 +9988,10 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H328" s="9" t="n"/>
+      <c r="H328" s="31">
+        <f>'프린터 입찰가'!M45</f>
+        <v/>
+      </c>
       <c r="I328" s="9" t="n"/>
       <c r="J328" s="9" t="n"/>
       <c r="K328" s="9" t="n"/>
@@ -6713,7 +10017,10 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H329" s="9" t="n"/>
+      <c r="H329" s="31">
+        <f>'프린터 입찰가'!M48</f>
+        <v/>
+      </c>
       <c r="I329" s="9" t="n"/>
       <c r="J329" s="9" t="n"/>
       <c r="K329" s="9" t="n"/>
@@ -6743,7 +10050,10 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H330" s="9" t="n"/>
+      <c r="H330" s="31">
+        <f>'프린터 입찰가'!M49</f>
+        <v/>
+      </c>
       <c r="I330" s="9" t="n"/>
       <c r="J330" s="9" t="n"/>
       <c r="K330" s="9" t="n"/>
@@ -6769,7 +10079,10 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H331" s="9" t="n"/>
+      <c r="H331" s="31">
+        <f>'프린터 입찰가'!M51</f>
+        <v/>
+      </c>
       <c r="I331" s="9" t="n"/>
       <c r="J331" s="9" t="n"/>
       <c r="K331" s="9" t="n"/>
@@ -6797,7 +10110,10 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H332" s="9" t="n"/>
+      <c r="H332" s="31">
+        <f>'프린터 입찰가'!M54</f>
+        <v/>
+      </c>
       <c r="I332" s="9" t="n"/>
       <c r="J332" s="9" t="n"/>
       <c r="K332" s="9" t="n"/>
@@ -6853,7 +10169,10 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H334" s="9" t="n"/>
+      <c r="H334" s="31">
+        <f>'프린터 입찰가'!M53</f>
+        <v/>
+      </c>
       <c r="I334" s="9" t="n"/>
       <c r="J334" s="9" t="n"/>
       <c r="K334" s="9" t="n"/>
@@ -6881,7 +10200,10 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H335" s="9" t="n"/>
+      <c r="H335" s="31">
+        <f>'프린터 입찰가'!M30</f>
+        <v/>
+      </c>
       <c r="I335" s="9" t="n"/>
       <c r="J335" s="9" t="n"/>
       <c r="K335" s="9" t="n"/>
@@ -6909,7 +10231,10 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H336" s="9" t="n"/>
+      <c r="H336" s="31">
+        <f>'프린터 입찰가'!M29</f>
+        <v/>
+      </c>
       <c r="I336" s="9" t="n"/>
       <c r="J336" s="9" t="n"/>
       <c r="K336" s="9" t="n"/>
@@ -6937,7 +10262,10 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H337" s="9" t="n"/>
+      <c r="H337" s="31">
+        <f>'프린터 입찰가'!M28</f>
+        <v/>
+      </c>
       <c r="I337" s="9" t="n"/>
       <c r="J337" s="9" t="n"/>
       <c r="K337" s="9" t="n"/>
@@ -6967,7 +10295,10 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H338" s="9" t="n"/>
+      <c r="H338" s="31">
+        <f>'프린터 입찰가'!M57</f>
+        <v/>
+      </c>
       <c r="I338" s="9" t="n"/>
       <c r="J338" s="9" t="n"/>
       <c r="K338" s="9" t="n"/>
@@ -6999,7 +10330,10 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H339" s="9" t="n"/>
+      <c r="H339" s="31">
+        <f>'프린터 입찰가'!M16</f>
+        <v/>
+      </c>
       <c r="I339" s="9" t="n"/>
       <c r="J339" s="9" t="n"/>
       <c r="K339" s="9" t="n"/>
@@ -7029,7 +10363,10 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H340" s="9" t="n"/>
+      <c r="H340" s="31">
+        <f>'프린터 입찰가'!M56</f>
+        <v/>
+      </c>
       <c r="I340" s="9" t="n"/>
       <c r="J340" s="9" t="n"/>
       <c r="K340" s="9" t="n"/>
@@ -7055,7 +10392,10 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H341" s="9" t="n"/>
+      <c r="H341" s="31">
+        <f>'프린터 입찰가'!M55</f>
+        <v/>
+      </c>
       <c r="I341" s="9" t="n"/>
       <c r="J341" s="9" t="n"/>
       <c r="K341" s="9" t="n"/>
@@ -7107,7 +10447,10 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H343" s="9" t="n"/>
+      <c r="H343" s="31">
+        <f>'프린터 입찰가'!M19</f>
+        <v/>
+      </c>
       <c r="I343" s="9" t="n"/>
       <c r="J343" s="9" t="n"/>
       <c r="K343" s="9" t="n"/>
@@ -7139,7 +10482,10 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H344" s="9" t="n"/>
+      <c r="H344" s="31">
+        <f>'프린터 입찰가'!M37</f>
+        <v/>
+      </c>
       <c r="I344" s="9" t="n"/>
       <c r="J344" s="9" t="n"/>
       <c r="K344" s="9" t="n"/>
@@ -7169,7 +10515,10 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H345" s="9" t="n"/>
+      <c r="H345" s="31">
+        <f>'프린터 입찰가'!M25</f>
+        <v/>
+      </c>
       <c r="I345" s="9" t="n"/>
       <c r="J345" s="9" t="n"/>
       <c r="K345" s="9" t="n"/>
@@ -7199,7 +10548,10 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H346" s="9" t="n"/>
+      <c r="H346" s="31">
+        <f>'프린터 입찰가'!M39</f>
+        <v/>
+      </c>
       <c r="I346" s="9" t="n"/>
       <c r="J346" s="9" t="n"/>
       <c r="K346" s="9" t="n"/>
@@ -7227,7 +10579,10 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H347" s="9" t="n"/>
+      <c r="H347" s="31">
+        <f>'프린터 입찰가'!M18</f>
+        <v/>
+      </c>
       <c r="I347" s="9" t="n"/>
       <c r="J347" s="9" t="n"/>
       <c r="K347" s="9" t="n"/>
@@ -7255,7 +10610,10 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H348" s="9" t="n"/>
+      <c r="H348" s="31">
+        <f>'프린터 입찰가'!M38</f>
+        <v/>
+      </c>
       <c r="I348" s="9" t="n"/>
       <c r="J348" s="9" t="n"/>
       <c r="K348" s="9" t="n"/>
@@ -7285,7 +10643,10 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H349" s="9" t="n"/>
+      <c r="H349" s="31">
+        <f>'프린터 입찰가'!M32</f>
+        <v/>
+      </c>
       <c r="I349" s="9" t="n"/>
       <c r="J349" s="9" t="n"/>
       <c r="K349" s="9" t="n"/>
@@ -7313,7 +10674,10 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H350" s="9" t="n"/>
+      <c r="H350" s="31">
+        <f>'프린터 입찰가'!M22</f>
+        <v/>
+      </c>
       <c r="I350" s="9" t="n"/>
       <c r="J350" s="9" t="n"/>
       <c r="K350" s="9" t="n"/>
@@ -8761,7 +12125,10 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H430" s="9" t="n"/>
+      <c r="H430" s="31">
+        <f>'프린터 입찰가'!M34</f>
+        <v/>
+      </c>
       <c r="I430" s="9" t="n"/>
       <c r="J430" s="9" t="n"/>
       <c r="K430" s="9" t="n"/>
@@ -8787,7 +12154,10 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H431" s="9" t="n"/>
+      <c r="H431" s="31">
+        <f>'프린터 입찰가'!M62</f>
+        <v/>
+      </c>
       <c r="I431" s="9" t="n"/>
       <c r="J431" s="9" t="n"/>
       <c r="K431" s="9" t="n"/>
@@ -8825,7 +12195,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -17783,7 +21153,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/솔바텍_URL도메인변경완료_순위반영_20261029.xlsx
+++ b/솔바텍_URL도메인변경완료_순위반영_20261029.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="키워드ID·링크" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'프린터 입찰가'!$A$13:$P$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'프린터 입찰가'!$A$2:$I$52</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -21,10 +21,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0&quot;원&quot;"/>
-  </numFmts>
-  <fonts count="7">
+  <numFmts count="0"/>
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,16 +48,8 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="FF595959"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -84,16 +74,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFE5E5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFE0"/>
       </patternFill>
     </fill>
   </fills>
@@ -200,7 +180,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -228,53 +208,24 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -640,3095 +591,1324 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P63"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="8" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="13" t="inlineStr">
         <is>
-          <t>입찰가 인상 기준 (노란 칸 숫자를 바꾸면 추천 입찰가가 자동으로 다시 계산됩니다)</t>
-        </is>
-      </c>
+          <t>키워드</t>
+        </is>
+      </c>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t>입찰가 수정</t>
+        </is>
+      </c>
+      <c r="C1" s="13" t="inlineStr">
+        <is>
+          <t>광고업체수</t>
+        </is>
+      </c>
+      <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>입찰가</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="15" t="inlineStr">
+        <is>
+          <t>노출순위</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="n"/>
+      <c r="I1" s="5" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>판정</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>인상률</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>설명</t>
+      <c r="D2" s="14" t="inlineStr">
+        <is>
+          <t>솔바텍</t>
+        </is>
+      </c>
+      <c r="E2" s="14" t="inlineStr">
+        <is>
+          <t>코스모스몰</t>
+        </is>
+      </c>
+      <c r="F2" s="14" t="inlineStr">
+        <is>
+          <t>sb렌탈</t>
+        </is>
+      </c>
+      <c r="G2" s="15" t="inlineStr">
+        <is>
+          <t>솔바텍</t>
+        </is>
+      </c>
+      <c r="H2" s="15" t="inlineStr">
+        <is>
+          <t>코스모스몰</t>
+        </is>
+      </c>
+      <c r="I2" s="15" t="inlineStr">
+        <is>
+          <t>sb렌탈</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>솔바텍 미노출</t>
-        </is>
-      </c>
-      <c r="B3" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>솔바텍 광고가 안 보임 → 노출되도록 크게 인상</t>
-        </is>
-      </c>
+          <t>감열식프린터</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="n"/>
+      <c r="C3" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="D3" s="16" t="n">
+        <v>800</v>
+      </c>
+      <c r="E3" s="16" t="n"/>
+      <c r="F3" s="16" t="n"/>
+      <c r="G3" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="I3" s="7" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>순위 차이 큼</t>
-        </is>
-      </c>
-      <c r="B4" s="14" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>솔바텍이 다른 사이트보다 2계단 이상 아래</t>
-        </is>
+          <t>감열프린터</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n"/>
+      <c r="C4" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="D4" s="16" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E4" s="16" t="n"/>
+      <c r="F4" s="16" t="n"/>
+      <c r="G4" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" s="7" t="n"/>
+      <c r="I4" s="7" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>붙어있음(아래)</t>
-        </is>
-      </c>
-      <c r="B5" s="14" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>솔바텍이 다른 사이트 바로 아래 (예: 6위·5위)</t>
-        </is>
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>감열프린터기</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D5" s="17" t="n">
+        <v>650</v>
+      </c>
+      <c r="E5" s="17" t="n"/>
+      <c r="F5" s="17" t="n"/>
+      <c r="G5" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="H5" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="I5" s="9" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>붙어있음(위)</t>
-        </is>
-      </c>
-      <c r="B6" s="14" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>솔바텍이 바로 위지만 붙어 있음 (예: 1위·2위) → 간격 벌리기</t>
-        </is>
-      </c>
+          <t>도시바프린터</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="D6" s="16" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E6" s="16" t="n"/>
+      <c r="F6" s="16" t="n"/>
+      <c r="G6" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" s="7" t="n"/>
+      <c r="I6" s="7" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>순위 낮음</t>
-        </is>
-      </c>
-      <c r="B7" s="14" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>다른 사이트는 없지만 솔바텍 순위가 낮음</t>
-        </is>
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>라밸프린터</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D7" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E7" s="17" t="n"/>
+      <c r="F7" s="17" t="n"/>
+      <c r="G7" s="9" t="n"/>
+      <c r="H7" s="9" t="n"/>
+      <c r="I7" s="9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>유지</t>
-        </is>
-      </c>
-      <c r="B8" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>수정 대상 아님</t>
-        </is>
-      </c>
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>라벨기</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D8" s="17" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E8" s="17" t="n"/>
+      <c r="F8" s="17" t="n"/>
+      <c r="G8" s="9" t="n"/>
+      <c r="H8" s="9" t="n"/>
+      <c r="I8" s="9" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>라벨기계</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D9" s="17" t="n">
+        <v>890</v>
+      </c>
+      <c r="E9" s="17" t="n"/>
+      <c r="F9" s="17" t="n"/>
+      <c r="G9" s="9" t="n"/>
+      <c r="H9" s="9" t="n"/>
+      <c r="I9" s="9" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>입찰가 상한</t>
-        </is>
-      </c>
-      <c r="B10" s="15" t="n">
-        <v>3000</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>추천 입찰가는 이 금액을 넘지 않음 (10원 단위 올림). 현재 입찰가가 이미 상한보다 높으면 현재 금액 유지</t>
-        </is>
-      </c>
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>라벨용지프린터</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="17" t="n"/>
+      <c r="G10" s="9" t="n"/>
+      <c r="H10" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" s="9" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="inlineStr">
-        <is>
-          <t>※ 네이버 광고관리 &gt; 키워드 &gt; 입찰가 변경 &gt; "순위별 평균 입찰가"에서 목표 순위 금액을 확인해 L열에 넣으면 그 금액이 최종 입찰가가 됩니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>키워드</t>
-        </is>
-      </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>상태</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>광고업체수</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="inlineStr">
-        <is>
-          <t>솔바텍</t>
-        </is>
-      </c>
-      <c r="E13" s="1" t="inlineStr">
-        <is>
-          <t>코스모스몰</t>
-        </is>
-      </c>
-      <c r="F13" s="1" t="inlineStr">
-        <is>
-          <t>sb렌탈</t>
-        </is>
-      </c>
-      <c r="G13" s="1" t="inlineStr">
-        <is>
-          <t>입찰가 수정</t>
-        </is>
-      </c>
-      <c r="H13" s="1" t="inlineStr">
-        <is>
-          <t>판정</t>
-        </is>
-      </c>
-      <c r="I13" s="1" t="inlineStr">
-        <is>
-          <t>현재 입찰가</t>
-        </is>
-      </c>
-      <c r="J13" s="1" t="inlineStr">
-        <is>
-          <t>인상률</t>
-        </is>
-      </c>
-      <c r="K13" s="1" t="inlineStr">
-        <is>
-          <t>추천 입찰가</t>
-        </is>
-      </c>
-      <c r="L13" s="17" t="inlineStr">
-        <is>
-          <t>네이버 목표순위 입찰가
-(직접 입력)</t>
-        </is>
-      </c>
-      <c r="M13" s="1" t="inlineStr">
-        <is>
-          <t>최종 변경 입찰가</t>
-        </is>
-      </c>
-      <c r="N13" s="1" t="inlineStr">
-        <is>
-          <t>노출수</t>
-        </is>
-      </c>
-      <c r="O13" s="1" t="inlineStr">
-        <is>
-          <t>클릭수</t>
-        </is>
-      </c>
-      <c r="P13" s="1" t="inlineStr">
-        <is>
-          <t>평균 CPC</t>
-        </is>
-      </c>
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>라벨인쇄기</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D11" s="17" t="n">
+        <v>3500</v>
+      </c>
+      <c r="E11" s="17" t="n"/>
+      <c r="F11" s="17" t="n"/>
+      <c r="G11" s="9" t="n"/>
+      <c r="H11" s="9" t="n"/>
+      <c r="I11" s="9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>라벨인쇄기계</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D12" s="17" t="n">
+        <v>600</v>
+      </c>
+      <c r="E12" s="17" t="n"/>
+      <c r="F12" s="17" t="n"/>
+      <c r="G12" s="9" t="n"/>
+      <c r="H12" s="9" t="n"/>
+      <c r="I12" s="9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>라벨지프린터</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D13" s="17" t="n">
+        <v>800</v>
+      </c>
+      <c r="E13" s="17" t="n"/>
+      <c r="F13" s="17" t="n"/>
+      <c r="G13" s="9" t="n"/>
+      <c r="H13" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="I13" s="9" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>감열식프린터</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>노출가능</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="n">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>라벨출력기</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="D14" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="E14" s="18" t="n">
-        <v>6</v>
-      </c>
-      <c r="F14" s="18" t="n"/>
-      <c r="G14" s="18" t="n"/>
-      <c r="H14" s="18" t="inlineStr">
-        <is>
-          <t>유지</t>
-        </is>
-      </c>
-      <c r="I14" s="19" t="n">
-        <v>800</v>
-      </c>
-      <c r="J14" s="20">
-        <f>VLOOKUP(H14,$A$3:$B$8,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="K14" s="19">
-        <f>IF(J14=0,I14,MAX(I14,MIN($B$10,ROUNDUP(I14*(1+J14),-1))))</f>
-        <v/>
-      </c>
-      <c r="L14" s="21" t="n"/>
-      <c r="M14" s="22">
-        <f>IF(L14&lt;&gt;"",MIN($B$10,L14),K14)</f>
-        <v/>
-      </c>
-      <c r="N14" s="18" t="n">
-        <v>23</v>
-      </c>
-      <c r="O14" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" s="18" t="inlineStr">
-        <is>
-          <t>0원</t>
-        </is>
-      </c>
+      <c r="D14" s="17" t="n">
+        <v>1110</v>
+      </c>
+      <c r="E14" s="17" t="n"/>
+      <c r="F14" s="17" t="n"/>
+      <c r="G14" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="H14" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" s="9" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>감열프린터</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>노출가능</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="n">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>라벨프린터업체</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="D15" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="E15" s="18" t="n"/>
-      <c r="F15" s="18" t="n">
+      <c r="D15" s="17" t="n">
+        <v>530</v>
+      </c>
+      <c r="E15" s="17" t="n"/>
+      <c r="F15" s="17" t="n"/>
+      <c r="G15" s="9" t="n"/>
+      <c r="H15" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="G15" s="18" t="n"/>
-      <c r="H15" s="18" t="inlineStr">
-        <is>
-          <t>유지</t>
-        </is>
-      </c>
-      <c r="I15" s="19" t="n">
-        <v>2000</v>
-      </c>
-      <c r="J15" s="20">
-        <f>VLOOKUP(H15,$A$3:$B$8,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="K15" s="19">
-        <f>IF(J15=0,I15,MAX(I15,MIN($B$10,ROUNDUP(I15*(1+J15),-1))))</f>
-        <v/>
-      </c>
-      <c r="L15" s="21" t="n"/>
-      <c r="M15" s="22">
-        <f>IF(L15&lt;&gt;"",MIN($B$10,L15),K15)</f>
-        <v/>
-      </c>
-      <c r="N15" s="18" t="n">
-        <v>27</v>
-      </c>
-      <c r="O15" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" s="18" t="inlineStr">
-        <is>
-          <t>0원</t>
-        </is>
-      </c>
+      <c r="I15" s="9" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>감열프린터기</t>
-        </is>
-      </c>
-      <c r="B16" s="23" t="inlineStr">
-        <is>
-          <t>노출가능</t>
-        </is>
-      </c>
-      <c r="C16" s="23" t="n">
+          <t>라벨프린터추천</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="D16" s="23" t="n">
-        <v>9</v>
-      </c>
-      <c r="E16" s="23" t="n">
+      <c r="D16" s="17" t="n">
+        <v>1580</v>
+      </c>
+      <c r="E16" s="17" t="n"/>
+      <c r="F16" s="17" t="n"/>
+      <c r="G16" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="F16" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="G16" s="24" t="inlineStr">
+      <c r="H16" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="I16" s="9" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>롤라벨인쇄기</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H16" s="23" t="inlineStr">
-        <is>
-          <t>순위 차이 큼</t>
-        </is>
-      </c>
-      <c r="I16" s="25" t="n">
-        <v>650</v>
-      </c>
-      <c r="J16" s="26">
-        <f>VLOOKUP(H16,$A$3:$B$8,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="K16" s="25">
-        <f>IF(J16=0,I16,MAX(I16,MIN($B$10,ROUNDUP(I16*(1+J16),-1))))</f>
-        <v/>
-      </c>
-      <c r="L16" s="21" t="n"/>
-      <c r="M16" s="27">
-        <f>IF(L16&lt;&gt;"",MIN($B$10,L16),K16)</f>
-        <v/>
-      </c>
-      <c r="N16" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="O16" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" s="23" t="inlineStr">
-        <is>
-          <t>0원</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>도시바프린터</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>노출가능</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="n">
+      <c r="C17" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="D17" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="E17" s="18" t="n"/>
-      <c r="F17" s="18" t="n"/>
-      <c r="G17" s="18" t="n"/>
-      <c r="H17" s="18" t="inlineStr">
-        <is>
-          <t>유지</t>
-        </is>
-      </c>
-      <c r="I17" s="19" t="n">
-        <v>1500</v>
-      </c>
-      <c r="J17" s="20">
-        <f>VLOOKUP(H17,$A$3:$B$8,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="K17" s="19">
-        <f>IF(J17=0,I17,MAX(I17,MIN($B$10,ROUNDUP(I17*(1+J17),-1))))</f>
-        <v/>
-      </c>
-      <c r="L17" s="21" t="n"/>
-      <c r="M17" s="22">
-        <f>IF(L17&lt;&gt;"",MIN($B$10,L17),K17)</f>
-        <v/>
-      </c>
-      <c r="N17" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="O17" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" s="18" t="inlineStr">
-        <is>
-          <t>0원</t>
-        </is>
-      </c>
+      <c r="D17" s="17" t="n">
+        <v>70</v>
+      </c>
+      <c r="E17" s="17" t="n"/>
+      <c r="F17" s="17" t="n"/>
+      <c r="G17" s="9" t="n"/>
+      <c r="H17" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="9" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>라밸프린터</t>
-        </is>
-      </c>
-      <c r="B18" s="23" t="inlineStr">
-        <is>
-          <t>노출가능</t>
-        </is>
-      </c>
-      <c r="C18" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="D18" s="23" t="n"/>
-      <c r="E18" s="23" t="n"/>
-      <c r="F18" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="G18" s="24" t="inlineStr">
+          <t>롤라벨출력기</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H18" s="23" t="inlineStr">
-        <is>
-          <t>솔바텍 미노출</t>
-        </is>
-      </c>
-      <c r="I18" s="25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J18" s="26">
-        <f>VLOOKUP(H18,$A$3:$B$8,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="K18" s="25">
-        <f>IF(J18=0,I18,MAX(I18,MIN($B$10,ROUNDUP(I18*(1+J18),-1))))</f>
-        <v/>
-      </c>
-      <c r="L18" s="21" t="n"/>
-      <c r="M18" s="27">
-        <f>IF(L18&lt;&gt;"",MIN($B$10,L18),K18)</f>
-        <v/>
-      </c>
-      <c r="N18" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" s="23" t="inlineStr">
-        <is>
-          <t>0원</t>
-        </is>
-      </c>
+      <c r="C18" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="E18" s="17" t="n"/>
+      <c r="F18" s="17" t="n"/>
+      <c r="G18" s="9" t="n"/>
+      <c r="H18" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I18" s="9" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>라벨기</t>
-        </is>
-      </c>
-      <c r="B19" s="23" t="inlineStr">
-        <is>
-          <t>노출가능</t>
-        </is>
-      </c>
-      <c r="C19" s="23" t="n">
+          <t>롤라벨프린터</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="D19" s="23" t="n"/>
-      <c r="E19" s="23" t="n"/>
-      <c r="F19" s="23" t="n"/>
-      <c r="G19" s="24" t="inlineStr">
-        <is>
-          <t>수정필요</t>
-        </is>
-      </c>
-      <c r="H19" s="23" t="inlineStr">
-        <is>
-          <t>솔바텍 미노출</t>
-        </is>
-      </c>
-      <c r="I19" s="25" t="n">
-        <v>2000</v>
-      </c>
-      <c r="J19" s="26">
-        <f>VLOOKUP(H19,$A$3:$B$8,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="K19" s="25">
-        <f>IF(J19=0,I19,MAX(I19,MIN($B$10,ROUNDUP(I19*(1+J19),-1))))</f>
-        <v/>
-      </c>
-      <c r="L19" s="21" t="n"/>
-      <c r="M19" s="27">
-        <f>IF(L19&lt;&gt;"",MIN($B$10,L19),K19)</f>
-        <v/>
-      </c>
-      <c r="N19" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="O19" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" s="23" t="inlineStr">
-        <is>
-          <t>0원</t>
-        </is>
-      </c>
+      <c r="D19" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E19" s="17" t="n"/>
+      <c r="F19" s="17" t="n"/>
+      <c r="G19" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="H19" s="9" t="n"/>
+      <c r="I19" s="9" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>라벨기계</t>
-        </is>
-      </c>
-      <c r="B20" s="23" t="inlineStr">
-        <is>
-          <t>노출가능</t>
-        </is>
-      </c>
-      <c r="C20" s="23" t="n">
+          <t>바코드라벨인쇄기</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="D20" s="23" t="n"/>
-      <c r="E20" s="23" t="n"/>
-      <c r="F20" s="23" t="n"/>
-      <c r="G20" s="24" t="inlineStr">
-        <is>
-          <t>수정필요</t>
-        </is>
-      </c>
-      <c r="H20" s="23" t="inlineStr">
-        <is>
-          <t>솔바텍 미노출</t>
-        </is>
-      </c>
-      <c r="I20" s="25" t="n">
-        <v>890</v>
-      </c>
-      <c r="J20" s="26">
-        <f>VLOOKUP(H20,$A$3:$B$8,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="K20" s="25">
-        <f>IF(J20=0,I20,MAX(I20,MIN($B$10,ROUNDUP(I20*(1+J20),-1))))</f>
-        <v/>
-      </c>
-      <c r="L20" s="21" t="n"/>
-      <c r="M20" s="27">
-        <f>IF(L20&lt;&gt;"",MIN($B$10,L20),K20)</f>
-        <v/>
-      </c>
-      <c r="N20" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" s="23" t="inlineStr">
-        <is>
-          <t>0원</t>
-        </is>
-      </c>
+      <c r="D20" s="17" t="n">
+        <v>400</v>
+      </c>
+      <c r="E20" s="17" t="n"/>
+      <c r="F20" s="17" t="n"/>
+      <c r="G20" s="9" t="n"/>
+      <c r="H20" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I20" s="9" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>라벨용지프린터</t>
-        </is>
-      </c>
-      <c r="B21" s="23" t="inlineStr">
-        <is>
-          <t>노출가능</t>
-        </is>
-      </c>
-      <c r="C21" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="D21" s="23" t="n"/>
-      <c r="E21" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="F21" s="23" t="n"/>
-      <c r="G21" s="24" t="inlineStr">
+          <t>바코드라벨프린터</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H21" s="23" t="inlineStr">
-        <is>
-          <t>솔바텍 미노출</t>
-        </is>
-      </c>
-      <c r="I21" s="25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J21" s="26">
-        <f>VLOOKUP(H21,$A$3:$B$8,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="K21" s="25">
-        <f>IF(J21=0,I21,MAX(I21,MIN($B$10,ROUNDUP(I21*(1+J21),-1))))</f>
-        <v/>
-      </c>
-      <c r="L21" s="21" t="n"/>
-      <c r="M21" s="27">
-        <f>IF(L21&lt;&gt;"",MIN($B$10,L21),K21)</f>
-        <v/>
-      </c>
-      <c r="N21" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" s="23" t="inlineStr">
-        <is>
-          <t>0원</t>
-        </is>
-      </c>
+      <c r="C21" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D21" s="17" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E21" s="17" t="n"/>
+      <c r="F21" s="17" t="n"/>
+      <c r="G21" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="H21" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="I21" s="9" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>라벨인쇄기</t>
-        </is>
-      </c>
-      <c r="B22" s="23" t="inlineStr">
-        <is>
-          <t>노출가능</t>
-        </is>
-      </c>
-      <c r="C22" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="D22" s="23" t="n"/>
-      <c r="E22" s="23" t="n"/>
-      <c r="F22" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="G22" s="24" t="inlineStr">
+          <t>바코드라벨프린터업체</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H22" s="23" t="inlineStr">
-        <is>
-          <t>솔바텍 미노출</t>
-        </is>
-      </c>
-      <c r="I22" s="25" t="n">
-        <v>3500</v>
-      </c>
-      <c r="J22" s="26">
-        <f>VLOOKUP(H22,$A$3:$B$8,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="K22" s="25">
-        <f>IF(J22=0,I22,MAX(I22,MIN($B$10,ROUNDUP(I22*(1+J22),-1))))</f>
-        <v/>
-      </c>
-      <c r="L22" s="21" t="n"/>
-      <c r="M22" s="27">
-        <f>IF(L22&lt;&gt;"",MIN($B$10,L22),K22)</f>
-        <v/>
-      </c>
-      <c r="N22" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="O22" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" s="23" t="inlineStr">
-        <is>
-          <t>0원</t>
-        </is>
-      </c>
+      <c r="C22" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="E22" s="17" t="n"/>
+      <c r="F22" s="17" t="n"/>
+      <c r="G22" s="9" t="n"/>
+      <c r="H22" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I22" s="9" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>라벨인쇄기계</t>
-        </is>
-      </c>
-      <c r="B23" s="23" t="inlineStr">
-        <is>
-          <t>노출가능</t>
-        </is>
-      </c>
-      <c r="C23" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="D23" s="23" t="n"/>
-      <c r="E23" s="23" t="n"/>
-      <c r="F23" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="G23" s="24" t="inlineStr">
+          <t>바코드만들기</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H23" s="23" t="inlineStr">
-        <is>
-          <t>솔바텍 미노출</t>
-        </is>
-      </c>
-      <c r="I23" s="25" t="n">
-        <v>600</v>
-      </c>
-      <c r="J23" s="26">
-        <f>VLOOKUP(H23,$A$3:$B$8,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="K23" s="25">
-        <f>IF(J23=0,I23,MAX(I23,MIN($B$10,ROUNDUP(I23*(1+J23),-1))))</f>
-        <v/>
-      </c>
-      <c r="L23" s="21" t="n"/>
-      <c r="M23" s="27">
-        <f>IF(L23&lt;&gt;"",MIN($B$10,L23),K23)</f>
-        <v/>
-      </c>
-      <c r="N23" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" s="23" t="inlineStr">
-        <is>
-          <t>0원</t>
-        </is>
-      </c>
+      <c r="C23" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="D23" s="17" t="n">
+        <v>500</v>
+      </c>
+      <c r="E23" s="17" t="n"/>
+      <c r="F23" s="17" t="n"/>
+      <c r="G23" s="9" t="n"/>
+      <c r="H23" s="9" t="n"/>
+      <c r="I23" s="9" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>라벨지프린터</t>
-        </is>
-      </c>
-      <c r="B24" s="23" t="inlineStr">
-        <is>
-          <t>노출가능</t>
-        </is>
-      </c>
-      <c r="C24" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="D24" s="23" t="n"/>
-      <c r="E24" s="23" t="n">
-        <v>6</v>
-      </c>
-      <c r="F24" s="23" t="n"/>
-      <c r="G24" s="24" t="inlineStr">
+          <t>바코드발행기</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
         <is>
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H24" s="23" t="inlineStr">
-        <is>
-          <t>솔바텍 미노출</t>
-        </is>
-      </c>
-      <c r="I24" s="25" t="n">
-        <v>800</v>
-      </c>
-      <c r="J24" s="26">
-        <f>VLOOKUP(H24,$A$3:$B$8,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="K24" s="25">
-        <f>IF(J24=0,I24,MAX(I24,MIN($B$10,ROUNDUP(I24*(1+J24),-1))))</f>
-        <v/>
-      </c>
-      <c r="L24" s="21" t="n"/>
-      <c r="M24" s="27">
-        <f>IF(L24&lt;&gt;"",MIN($B$10,L24),K24)</f>
-        <v/>
-      </c>
-      <c r="N24" s="23" t="n">
+      <c r="C24" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="O24" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" s="23" t="inlineStr">
-        <is>
-          <t>0원</t>
-        </is>
-      </c>
+      <c r="D24" s="17" t="n">
+        <v>400</v>
+      </c>
+      <c r="E24" s="17" t="n"/>
+      <c r="F24" s="17" t="n"/>
+      <c r="G24" s="9" t="n"/>
+      <c r="H24" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I24" s="9" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>라벨출력기</t>
-        </is>
-      </c>
-      <c r="B25" s="23" t="inlineStr">
-        <is>
-          <t>노출가능</t>
-        </is>
-      </c>
-      <c r="C25" s="23" t="n">
+          <t>바코드인쇄기</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="D25" s="23" t="n">
+      <c r="D25" s="17" t="n">
+        <v>3300</v>
+      </c>
+      <c r="E25" s="17" t="n"/>
+      <c r="F25" s="17" t="n"/>
+      <c r="G25" s="9" t="n"/>
+      <c r="H25" s="9" t="n"/>
+      <c r="I25" s="9" t="n">
         <v>7</v>
-      </c>
-      <c r="E25" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="F25" s="23" t="n"/>
-      <c r="G25" s="24" t="inlineStr">
-        <is>
-          <t>수정필요</t>
-        </is>
-      </c>
-      <c r="H25" s="23" t="inlineStr">
-        <is>
-          <t>순위 차이 큼</t>
-        </is>
-      </c>
-      <c r="I25" s="25" t="n">
-        <v>1110</v>
-      </c>
-      <c r="J25" s="26">
-        <f>VLOOKUP(H25,$A$3:$B$8,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="K25" s="25">
-        <f>IF(J25=0,I25,MAX(I25,MIN($B$10,ROUNDUP(I25*(1+J25),-1))))</f>
-        <v/>
-      </c>
-      <c r="L25" s="21" t="n"/>
-      <c r="M25" s="27">
-        <f>IF(L25&lt;&gt;"",MIN($B$10,L25),K25)</f>
-        <v/>
-      </c>
-      <c r="N25" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" s="23" t="inlineStr">
-        <is>
-          <t>0원</t>
-        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>라벨프린터업체</t>
-        </is>
-      </c>
-      <c r="B26" s="23" t="inlineStr">
-        <is>
-          <t>노출가능</t>
-        </is>
-      </c>
-      <c r="C26" s="23" t="n">
+          <t>바코드출력기</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="D26" s="23" t="n"/>
-      <c r="E26" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="F26" s="23" t="n"/>
-      <c r="G26" s="24" t="inlineStr">
-        <is>
-          <t>수정필요</t>
-        </is>
-      </c>
-      <c r="H26" s="23" t="inlineStr">
-        <is>
-          <t>솔바텍 미노출</t>
-        </is>
-      </c>
-      <c r="I26" s="25" t="n">
-        <v>530</v>
-      </c>
-      <c r="J26" s="26">
-        <f>VLOOKUP(H26,$A$3:$B$8,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="K26" s="25">
-        <f>IF(J26=0,I26,MAX(I26,MIN($B$10,ROUNDUP(I26*(1+J26),-1))))</f>
-        <v/>
-      </c>
-      <c r="L26" s="21" t="n"/>
-      <c r="M26" s="27">
-        <f>IF(L26&lt;&gt;"",MIN($B$10,L26),K26)</f>
-        <v/>
-      </c>
-      <c r="N26" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" s="23" t="inlineStr">
-        <is>
-          <t>0원</t>
-        </is>
+      <c r="D26" s="17" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E26" s="17" t="n"/>
+      <c r="F26" s="17" t="n"/>
+      <c r="G26" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="H26" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="I26" s="9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>라벨프린터추천</t>
-        </is>
-      </c>
-      <c r="B27" s="23" t="inlineStr">
-        <is>
-          <t>노출가능</t>
-        </is>
-      </c>
-      <c r="C27" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="D27" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="E27" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="F27" s="23" t="n"/>
-      <c r="G27" s="24" t="inlineStr">
+          <t>바코드프린터기</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
         <is>
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H27" s="23" t="inlineStr">
-        <is>
-          <t>붙어있음(위)</t>
-        </is>
-      </c>
-      <c r="I27" s="25" t="n">
-        <v>1580</v>
-      </c>
-      <c r="J27" s="26">
-        <f>VLOOKUP(H27,$A$3:$B$8,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="K27" s="25">
-        <f>IF(J27=0,I27,MAX(I27,MIN($B$10,ROUNDUP(I27*(1+J27),-1))))</f>
-        <v/>
-      </c>
-      <c r="L27" s="21" t="n"/>
-      <c r="M27" s="27">
-        <f>IF(L27&lt;&gt;"",MIN($B$10,L27),K27)</f>
-        <v/>
-      </c>
-      <c r="N27" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="O27" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" s="23" t="inlineStr">
-        <is>
-          <t>0원</t>
-        </is>
-      </c>
+      <c r="C27" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="D27" s="17" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E27" s="17" t="n"/>
+      <c r="F27" s="17" t="n"/>
+      <c r="G27" s="9" t="n"/>
+      <c r="H27" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="9" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>롤라벨인쇄기</t>
-        </is>
-      </c>
-      <c r="B28" s="23" t="inlineStr">
-        <is>
-          <t>노출가능</t>
-        </is>
-      </c>
-      <c r="C28" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="D28" s="23" t="n"/>
-      <c r="E28" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" s="23" t="n"/>
-      <c r="G28" s="24" t="inlineStr">
+          <t>바코드프린터라벨</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
         <is>
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H28" s="23" t="inlineStr">
-        <is>
-          <t>솔바텍 미노출</t>
-        </is>
-      </c>
-      <c r="I28" s="25" t="n">
-        <v>70</v>
-      </c>
-      <c r="J28" s="26">
-        <f>VLOOKUP(H28,$A$3:$B$8,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="K28" s="25">
-        <f>IF(J28=0,I28,MAX(I28,MIN($B$10,ROUNDUP(I28*(1+J28),-1))))</f>
-        <v/>
-      </c>
-      <c r="L28" s="21" t="n"/>
-      <c r="M28" s="27">
-        <f>IF(L28&lt;&gt;"",MIN($B$10,L28),K28)</f>
-        <v/>
-      </c>
-      <c r="N28" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" s="23" t="inlineStr">
-        <is>
-          <t>0원</t>
-        </is>
-      </c>
+      <c r="C28" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="D28" s="17" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E28" s="17" t="n"/>
+      <c r="F28" s="17" t="n"/>
+      <c r="G28" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="H28" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I28" s="9" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>롤라벨출력기</t>
-        </is>
-      </c>
-      <c r="B29" s="23" t="inlineStr">
-        <is>
-          <t>노출가능</t>
-        </is>
-      </c>
-      <c r="C29" s="23" t="n">
+          <t>바코드프린터전문업체</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D29" s="23" t="n"/>
-      <c r="E29" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="F29" s="23" t="n"/>
-      <c r="G29" s="24" t="inlineStr">
-        <is>
-          <t>수정필요</t>
-        </is>
-      </c>
-      <c r="H29" s="23" t="inlineStr">
-        <is>
-          <t>솔바텍 미노출</t>
-        </is>
-      </c>
-      <c r="I29" s="25" t="n">
-        <v>100</v>
-      </c>
-      <c r="J29" s="26">
-        <f>VLOOKUP(H29,$A$3:$B$8,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="K29" s="25">
-        <f>IF(J29=0,I29,MAX(I29,MIN($B$10,ROUNDUP(I29*(1+J29),-1))))</f>
-        <v/>
-      </c>
-      <c r="L29" s="21" t="n"/>
-      <c r="M29" s="27">
-        <f>IF(L29&lt;&gt;"",MIN($B$10,L29),K29)</f>
-        <v/>
-      </c>
-      <c r="N29" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" s="23" t="inlineStr">
-        <is>
-          <t>0원</t>
-        </is>
-      </c>
+      <c r="D29" s="17" t="n">
+        <v>700</v>
+      </c>
+      <c r="E29" s="17" t="n"/>
+      <c r="F29" s="17" t="n"/>
+      <c r="G29" s="9" t="n"/>
+      <c r="H29" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I29" s="9" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>롤라벨프린터</t>
-        </is>
-      </c>
-      <c r="B30" s="23" t="inlineStr">
-        <is>
-          <t>노출가능</t>
-        </is>
-      </c>
-      <c r="C30" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="D30" s="23" t="n">
+          <t>바코드프린터추천</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="E30" s="23" t="n"/>
-      <c r="F30" s="23" t="n"/>
-      <c r="G30" s="24" t="inlineStr">
-        <is>
-          <t>수정필요</t>
-        </is>
-      </c>
-      <c r="H30" s="23" t="inlineStr">
-        <is>
-          <t>순위 낮음</t>
-        </is>
-      </c>
-      <c r="I30" s="25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J30" s="26">
-        <f>VLOOKUP(H30,$A$3:$B$8,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="K30" s="25">
-        <f>IF(J30=0,I30,MAX(I30,MIN($B$10,ROUNDUP(I30*(1+J30),-1))))</f>
-        <v/>
-      </c>
-      <c r="L30" s="21" t="n"/>
-      <c r="M30" s="27">
-        <f>IF(L30&lt;&gt;"",MIN($B$10,L30),K30)</f>
-        <v/>
-      </c>
-      <c r="N30" s="23" t="n">
+      <c r="D30" s="17" t="n">
+        <v>1700</v>
+      </c>
+      <c r="E30" s="17" t="n"/>
+      <c r="F30" s="17" t="n"/>
+      <c r="G30" s="9" t="n"/>
+      <c r="H30" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="I30" s="9" t="n">
         <v>1</v>
-      </c>
-      <c r="O30" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" s="23" t="inlineStr">
-        <is>
-          <t>0원</t>
-        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>바코드라벨인쇄기</t>
-        </is>
-      </c>
-      <c r="B31" s="23" t="inlineStr">
-        <is>
-          <t>노출가능</t>
-        </is>
-      </c>
-      <c r="C31" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="D31" s="23" t="n"/>
-      <c r="E31" s="23" t="n">
+          <t>바코드프린터판매</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="F31" s="23" t="n"/>
-      <c r="G31" s="24" t="inlineStr">
-        <is>
-          <t>수정필요</t>
-        </is>
-      </c>
-      <c r="H31" s="23" t="inlineStr">
-        <is>
-          <t>솔바텍 미노출</t>
-        </is>
-      </c>
-      <c r="I31" s="25" t="n">
-        <v>400</v>
-      </c>
-      <c r="J31" s="26">
-        <f>VLOOKUP(H31,$A$3:$B$8,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="K31" s="25">
-        <f>IF(J31=0,I31,MAX(I31,MIN($B$10,ROUNDUP(I31*(1+J31),-1))))</f>
-        <v/>
-      </c>
-      <c r="L31" s="21" t="n"/>
-      <c r="M31" s="27">
-        <f>IF(L31&lt;&gt;"",MIN($B$10,L31),K31)</f>
-        <v/>
-      </c>
-      <c r="N31" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" s="23" t="inlineStr">
-        <is>
-          <t>0원</t>
-        </is>
-      </c>
+      <c r="D31" s="17" t="n">
+        <v>280</v>
+      </c>
+      <c r="E31" s="17" t="n"/>
+      <c r="F31" s="17" t="n"/>
+      <c r="G31" s="9" t="n"/>
+      <c r="H31" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" s="9" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t>바코드라벨프린터</t>
-        </is>
-      </c>
-      <c r="B32" s="23" t="inlineStr">
-        <is>
-          <t>노출가능</t>
-        </is>
-      </c>
-      <c r="C32" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="D32" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="E32" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="F32" s="23" t="n"/>
-      <c r="G32" s="24" t="inlineStr">
-        <is>
-          <t>수정필요</t>
-        </is>
-      </c>
-      <c r="H32" s="23" t="inlineStr">
-        <is>
-          <t>순위 차이 큼</t>
-        </is>
-      </c>
-      <c r="I32" s="25" t="n">
-        <v>3000</v>
-      </c>
-      <c r="J32" s="26">
-        <f>VLOOKUP(H32,$A$3:$B$8,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="K32" s="25">
-        <f>IF(J32=0,I32,MAX(I32,MIN($B$10,ROUNDUP(I32*(1+J32),-1))))</f>
-        <v/>
-      </c>
-      <c r="L32" s="21" t="n"/>
-      <c r="M32" s="27">
-        <f>IF(L32&lt;&gt;"",MIN($B$10,L32),K32)</f>
-        <v/>
-      </c>
-      <c r="N32" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="O32" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="P32" s="23" t="inlineStr">
-        <is>
-          <t>3,100원</t>
-        </is>
-      </c>
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>바코드프린터프로그램</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="n"/>
+      <c r="C32" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D32" s="16" t="n">
+        <v>2750</v>
+      </c>
+      <c r="E32" s="16" t="n"/>
+      <c r="F32" s="16" t="n"/>
+      <c r="G32" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H32" s="7" t="n"/>
+      <c r="I32" s="7" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="inlineStr">
-        <is>
-          <t>바코드라벨프린터업체</t>
-        </is>
-      </c>
-      <c r="B33" s="23" t="inlineStr">
-        <is>
-          <t>노출가능</t>
-        </is>
-      </c>
-      <c r="C33" s="23" t="n">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>빅솔론</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="n"/>
+      <c r="C33" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D33" s="16" t="n">
+        <v>800</v>
+      </c>
+      <c r="E33" s="16" t="n"/>
+      <c r="F33" s="16" t="n"/>
+      <c r="G33" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="D33" s="23" t="n"/>
-      <c r="E33" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="F33" s="23" t="n"/>
-      <c r="G33" s="24" t="inlineStr">
-        <is>
-          <t>수정필요</t>
-        </is>
-      </c>
-      <c r="H33" s="23" t="inlineStr">
-        <is>
-          <t>솔바텍 미노출</t>
-        </is>
-      </c>
-      <c r="I33" s="25" t="n">
-        <v>300</v>
-      </c>
-      <c r="J33" s="26">
-        <f>VLOOKUP(H33,$A$3:$B$8,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="K33" s="25">
-        <f>IF(J33=0,I33,MAX(I33,MIN($B$10,ROUNDUP(I33*(1+J33),-1))))</f>
-        <v/>
-      </c>
-      <c r="L33" s="21" t="n"/>
-      <c r="M33" s="27">
-        <f>IF(L33&lt;&gt;"",MIN($B$10,L33),K33)</f>
-        <v/>
-      </c>
-      <c r="N33" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" s="23" t="inlineStr">
-        <is>
-          <t>0원</t>
-        </is>
-      </c>
+      <c r="H33" s="7" t="n"/>
+      <c r="I33" s="7" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>바코드만들기</t>
-        </is>
-      </c>
-      <c r="B34" s="23" t="inlineStr">
-        <is>
-          <t>중지: 키워드 OFF</t>
-        </is>
-      </c>
-      <c r="C34" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="D34" s="23" t="n"/>
-      <c r="E34" s="23" t="n"/>
-      <c r="F34" s="23" t="n"/>
-      <c r="G34" s="24" t="inlineStr">
+          <t>빅솔론총판</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
         <is>
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H34" s="23" t="inlineStr">
-        <is>
-          <t>솔바텍 미노출</t>
-        </is>
-      </c>
-      <c r="I34" s="25" t="n">
-        <v>500</v>
-      </c>
-      <c r="J34" s="26">
-        <f>VLOOKUP(H34,$A$3:$B$8,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="K34" s="25">
-        <f>IF(J34=0,I34,MAX(I34,MIN($B$10,ROUNDUP(I34*(1+J34),-1))))</f>
-        <v/>
-      </c>
-      <c r="L34" s="21" t="n"/>
-      <c r="M34" s="27">
-        <f>IF(L34&lt;&gt;"",MIN($B$10,L34),K34)</f>
-        <v/>
-      </c>
-      <c r="N34" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" s="23" t="inlineStr">
-        <is>
-          <t>0원</t>
-        </is>
-      </c>
+      <c r="C34" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" s="17" t="n">
+        <v>70</v>
+      </c>
+      <c r="E34" s="17" t="n"/>
+      <c r="F34" s="17" t="n"/>
+      <c r="G34" s="9" t="n"/>
+      <c r="H34" s="9" t="n"/>
+      <c r="I34" s="9" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>바코드발행기</t>
-        </is>
-      </c>
-      <c r="B35" s="23" t="inlineStr">
-        <is>
-          <t>노출가능</t>
-        </is>
-      </c>
-      <c r="C35" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="D35" s="23" t="n"/>
-      <c r="E35" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="F35" s="23" t="n"/>
-      <c r="G35" s="24" t="inlineStr">
+          <t>빅솔론프린터</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
         <is>
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H35" s="23" t="inlineStr">
-        <is>
-          <t>솔바텍 미노출</t>
-        </is>
-      </c>
-      <c r="I35" s="25" t="n">
-        <v>400</v>
-      </c>
-      <c r="J35" s="26">
-        <f>VLOOKUP(H35,$A$3:$B$8,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="K35" s="25">
-        <f>IF(J35=0,I35,MAX(I35,MIN($B$10,ROUNDUP(I35*(1+J35),-1))))</f>
-        <v/>
-      </c>
-      <c r="L35" s="21" t="n"/>
-      <c r="M35" s="27">
-        <f>IF(L35&lt;&gt;"",MIN($B$10,L35),K35)</f>
-        <v/>
-      </c>
-      <c r="N35" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" s="23" t="inlineStr">
-        <is>
-          <t>0원</t>
-        </is>
-      </c>
+      <c r="C35" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="D35" s="17" t="n">
+        <v>940</v>
+      </c>
+      <c r="E35" s="17" t="n"/>
+      <c r="F35" s="17" t="n"/>
+      <c r="G35" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="H35" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" s="9" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="inlineStr">
-        <is>
-          <t>바코드인쇄기</t>
-        </is>
-      </c>
-      <c r="B36" s="23" t="inlineStr">
-        <is>
-          <t>노출가능</t>
-        </is>
-      </c>
-      <c r="C36" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="D36" s="23" t="n"/>
-      <c r="E36" s="23" t="n"/>
-      <c r="F36" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="G36" s="24" t="inlineStr">
-        <is>
-          <t>수정필요</t>
-        </is>
-      </c>
-      <c r="H36" s="23" t="inlineStr">
-        <is>
-          <t>솔바텍 미노출</t>
-        </is>
-      </c>
-      <c r="I36" s="25" t="n">
-        <v>3300</v>
-      </c>
-      <c r="J36" s="26">
-        <f>VLOOKUP(H36,$A$3:$B$8,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="K36" s="25">
-        <f>IF(J36=0,I36,MAX(I36,MIN($B$10,ROUNDUP(I36*(1+J36),-1))))</f>
-        <v/>
-      </c>
-      <c r="L36" s="21" t="n"/>
-      <c r="M36" s="27">
-        <f>IF(L36&lt;&gt;"",MIN($B$10,L36),K36)</f>
-        <v/>
-      </c>
-      <c r="N36" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="O36" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" s="23" t="inlineStr">
-        <is>
-          <t>0원</t>
-        </is>
-      </c>
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>산업용라벨프린터</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="n"/>
+      <c r="C36" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D36" s="16" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E36" s="16" t="n"/>
+      <c r="F36" s="16" t="n"/>
+      <c r="G36" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="H36" s="7" t="n"/>
+      <c r="I36" s="7" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>바코드출력기</t>
-        </is>
-      </c>
-      <c r="B37" s="23" t="inlineStr">
-        <is>
-          <t>노출가능</t>
-        </is>
-      </c>
-      <c r="C37" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="D37" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="E37" s="23" t="n">
-        <v>6</v>
-      </c>
-      <c r="F37" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" s="24" t="inlineStr">
+          <t>산업용바코드프린터</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
         <is>
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H37" s="23" t="inlineStr">
-        <is>
-          <t>순위 차이 큼</t>
-        </is>
-      </c>
-      <c r="I37" s="25" t="n">
-        <v>2500</v>
-      </c>
-      <c r="J37" s="26">
-        <f>VLOOKUP(H37,$A$3:$B$8,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="K37" s="25">
-        <f>IF(J37=0,I37,MAX(I37,MIN($B$10,ROUNDUP(I37*(1+J37),-1))))</f>
-        <v/>
-      </c>
-      <c r="L37" s="21" t="n"/>
-      <c r="M37" s="27">
-        <f>IF(L37&lt;&gt;"",MIN($B$10,L37),K37)</f>
-        <v/>
-      </c>
-      <c r="N37" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="O37" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" s="23" t="inlineStr">
-        <is>
-          <t>0원</t>
-        </is>
-      </c>
+      <c r="C37" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="D37" s="17" t="n">
+        <v>800</v>
+      </c>
+      <c r="E37" s="17" t="n"/>
+      <c r="F37" s="17" t="n"/>
+      <c r="G37" s="9" t="n"/>
+      <c r="H37" s="9" t="n"/>
+      <c r="I37" s="9" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>바코드프린터기</t>
-        </is>
-      </c>
-      <c r="B38" s="23" t="inlineStr">
-        <is>
-          <t>노출가능</t>
-        </is>
-      </c>
-      <c r="C38" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="D38" s="23" t="n"/>
-      <c r="E38" s="23" t="n">
+          <t>산업용프린터</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="D38" s="17" t="n">
+        <v>6500</v>
+      </c>
+      <c r="E38" s="17" t="n"/>
+      <c r="F38" s="17" t="n"/>
+      <c r="G38" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F38" s="23" t="n"/>
-      <c r="G38" s="24" t="inlineStr">
-        <is>
-          <t>수정필요</t>
-        </is>
-      </c>
-      <c r="H38" s="23" t="inlineStr">
-        <is>
-          <t>솔바텍 미노출</t>
-        </is>
-      </c>
-      <c r="I38" s="25" t="n">
-        <v>4000</v>
-      </c>
-      <c r="J38" s="26">
-        <f>VLOOKUP(H38,$A$3:$B$8,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="K38" s="25">
-        <f>IF(J38=0,I38,MAX(I38,MIN($B$10,ROUNDUP(I38*(1+J38),-1))))</f>
-        <v/>
-      </c>
-      <c r="L38" s="21" t="n"/>
-      <c r="M38" s="27">
-        <f>IF(L38&lt;&gt;"",MIN($B$10,L38),K38)</f>
-        <v/>
-      </c>
-      <c r="N38" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="O38" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" s="23" t="inlineStr">
-        <is>
-          <t>0원</t>
-        </is>
-      </c>
+      <c r="H38" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I38" s="9" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>바코드프린터라벨</t>
-        </is>
-      </c>
-      <c r="B39" s="23" t="inlineStr">
-        <is>
-          <t>노출가능</t>
-        </is>
-      </c>
-      <c r="C39" s="23" t="n">
+          <t>소형바코드프린터</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="D39" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="E39" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="F39" s="23" t="n"/>
-      <c r="G39" s="24" t="inlineStr">
-        <is>
-          <t>수정필요</t>
-        </is>
-      </c>
-      <c r="H39" s="23" t="inlineStr">
-        <is>
-          <t>순위 차이 큼</t>
-        </is>
-      </c>
-      <c r="I39" s="25" t="n">
-        <v>1100</v>
-      </c>
-      <c r="J39" s="26">
-        <f>VLOOKUP(H39,$A$3:$B$8,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="K39" s="25">
-        <f>IF(J39=0,I39,MAX(I39,MIN($B$10,ROUNDUP(I39*(1+J39),-1))))</f>
-        <v/>
-      </c>
-      <c r="L39" s="21" t="n"/>
-      <c r="M39" s="27">
-        <f>IF(L39&lt;&gt;"",MIN($B$10,L39),K39)</f>
-        <v/>
-      </c>
-      <c r="N39" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="O39" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" s="23" t="inlineStr">
-        <is>
-          <t>0원</t>
-        </is>
-      </c>
+      <c r="D39" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E39" s="17" t="n"/>
+      <c r="F39" s="17" t="n"/>
+      <c r="G39" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="H39" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="I39" s="9" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>바코드프린터전문업체</t>
-        </is>
-      </c>
-      <c r="B40" s="23" t="inlineStr">
-        <is>
-          <t>노출가능</t>
-        </is>
-      </c>
-      <c r="C40" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="D40" s="23" t="n"/>
-      <c r="E40" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="F40" s="23" t="n"/>
-      <c r="G40" s="24" t="inlineStr">
+          <t>스티커라벨기</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="inlineStr">
         <is>
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H40" s="23" t="inlineStr">
-        <is>
-          <t>솔바텍 미노출</t>
-        </is>
-      </c>
-      <c r="I40" s="25" t="n">
-        <v>700</v>
-      </c>
-      <c r="J40" s="26">
-        <f>VLOOKUP(H40,$A$3:$B$8,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="K40" s="25">
-        <f>IF(J40=0,I40,MAX(I40,MIN($B$10,ROUNDUP(I40*(1+J40),-1))))</f>
-        <v/>
-      </c>
-      <c r="L40" s="21" t="n"/>
-      <c r="M40" s="27">
-        <f>IF(L40&lt;&gt;"",MIN($B$10,L40),K40)</f>
-        <v/>
-      </c>
-      <c r="N40" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" s="23" t="inlineStr">
-        <is>
-          <t>0원</t>
-        </is>
-      </c>
+      <c r="C40" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="D40" s="17" t="n">
+        <v>2300</v>
+      </c>
+      <c r="E40" s="17" t="n"/>
+      <c r="F40" s="17" t="n"/>
+      <c r="G40" s="9" t="n"/>
+      <c r="H40" s="9" t="n"/>
+      <c r="I40" s="9" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="8" t="inlineStr">
-        <is>
-          <t>바코드프린터추천</t>
-        </is>
-      </c>
-      <c r="B41" s="23" t="inlineStr">
-        <is>
-          <t>노출가능</t>
-        </is>
-      </c>
-      <c r="C41" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="D41" s="23" t="n"/>
-      <c r="E41" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="F41" s="23" t="n">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>스티커인쇄기</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="n"/>
+      <c r="C41" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D41" s="16" t="n">
+        <v>800</v>
+      </c>
+      <c r="E41" s="16" t="n"/>
+      <c r="F41" s="16" t="n"/>
+      <c r="G41" s="7" t="n"/>
+      <c r="H41" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="I41" s="7" t="n">
         <v>1</v>
-      </c>
-      <c r="G41" s="24" t="inlineStr">
-        <is>
-          <t>수정필요</t>
-        </is>
-      </c>
-      <c r="H41" s="23" t="inlineStr">
-        <is>
-          <t>솔바텍 미노출</t>
-        </is>
-      </c>
-      <c r="I41" s="25" t="n">
-        <v>1700</v>
-      </c>
-      <c r="J41" s="26">
-        <f>VLOOKUP(H41,$A$3:$B$8,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="K41" s="25">
-        <f>IF(J41=0,I41,MAX(I41,MIN($B$10,ROUNDUP(I41*(1+J41),-1))))</f>
-        <v/>
-      </c>
-      <c r="L41" s="21" t="n"/>
-      <c r="M41" s="27">
-        <f>IF(L41&lt;&gt;"",MIN($B$10,L41),K41)</f>
-        <v/>
-      </c>
-      <c r="N41" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" s="23" t="inlineStr">
-        <is>
-          <t>0원</t>
-        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>바코드프린터판매</t>
-        </is>
-      </c>
-      <c r="B42" s="23" t="inlineStr">
-        <is>
-          <t>노출가능</t>
-        </is>
-      </c>
-      <c r="C42" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="D42" s="23" t="n"/>
-      <c r="E42" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="F42" s="23" t="n"/>
-      <c r="G42" s="24" t="inlineStr">
+          <t>스티커출력기</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="inlineStr">
         <is>
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H42" s="23" t="inlineStr">
-        <is>
-          <t>솔바텍 미노출</t>
-        </is>
-      </c>
-      <c r="I42" s="25" t="n">
-        <v>280</v>
-      </c>
-      <c r="J42" s="26">
-        <f>VLOOKUP(H42,$A$3:$B$8,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="K42" s="25">
-        <f>IF(J42=0,I42,MAX(I42,MIN($B$10,ROUNDUP(I42*(1+J42),-1))))</f>
-        <v/>
-      </c>
-      <c r="L42" s="21" t="n"/>
-      <c r="M42" s="27">
-        <f>IF(L42&lt;&gt;"",MIN($B$10,L42),K42)</f>
-        <v/>
-      </c>
-      <c r="N42" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" s="23" t="inlineStr">
-        <is>
-          <t>0원</t>
-        </is>
-      </c>
+      <c r="C42" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D42" s="17" t="n">
+        <v>400</v>
+      </c>
+      <c r="E42" s="17" t="n"/>
+      <c r="F42" s="17" t="n"/>
+      <c r="G42" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="H42" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" s="9" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>바코드프린터프로그램</t>
-        </is>
-      </c>
-      <c r="B43" s="18" t="inlineStr">
-        <is>
-          <t>노출가능</t>
-        </is>
-      </c>
-      <c r="C43" s="18" t="n">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>스티커프린터</t>
+        </is>
+      </c>
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D43" s="17" t="n">
+        <v>1340</v>
+      </c>
+      <c r="E43" s="17" t="n"/>
+      <c r="F43" s="17" t="n"/>
+      <c r="G43" s="9" t="n"/>
+      <c r="H43" s="9" t="n"/>
+      <c r="I43" s="9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>열전사프린터</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="D43" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="E43" s="18" t="n"/>
-      <c r="F43" s="18" t="n"/>
-      <c r="G43" s="18" t="n"/>
-      <c r="H43" s="18" t="inlineStr">
-        <is>
-          <t>유지</t>
-        </is>
-      </c>
-      <c r="I43" s="19" t="n">
-        <v>2750</v>
-      </c>
-      <c r="J43" s="20">
-        <f>VLOOKUP(H43,$A$3:$B$8,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="K43" s="19">
-        <f>IF(J43=0,I43,MAX(I43,MIN($B$10,ROUNDUP(I43*(1+J43),-1))))</f>
-        <v/>
-      </c>
-      <c r="L43" s="21" t="n"/>
-      <c r="M43" s="22">
-        <f>IF(L43&lt;&gt;"",MIN($B$10,L43),K43)</f>
-        <v/>
-      </c>
-      <c r="N43" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="O43" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" s="18" t="inlineStr">
-        <is>
-          <t>0원</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>빅솔론</t>
-        </is>
-      </c>
-      <c r="B44" s="18" t="inlineStr">
-        <is>
-          <t>노출가능</t>
-        </is>
-      </c>
-      <c r="C44" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="D44" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="E44" s="18" t="n"/>
-      <c r="F44" s="18" t="n"/>
-      <c r="G44" s="18" t="n"/>
-      <c r="H44" s="18" t="inlineStr">
-        <is>
-          <t>유지</t>
-        </is>
-      </c>
-      <c r="I44" s="19" t="n">
-        <v>800</v>
-      </c>
-      <c r="J44" s="20">
-        <f>VLOOKUP(H44,$A$3:$B$8,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="K44" s="19">
-        <f>IF(J44=0,I44,MAX(I44,MIN($B$10,ROUNDUP(I44*(1+J44),-1))))</f>
-        <v/>
-      </c>
-      <c r="L44" s="21" t="n"/>
-      <c r="M44" s="22">
-        <f>IF(L44&lt;&gt;"",MIN($B$10,L44),K44)</f>
-        <v/>
-      </c>
-      <c r="N44" s="18" t="n">
-        <v>562</v>
-      </c>
-      <c r="O44" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" s="18" t="inlineStr">
-        <is>
-          <t>0원</t>
-        </is>
-      </c>
+      <c r="D44" s="17" t="n">
+        <v>5500</v>
+      </c>
+      <c r="E44" s="17" t="n"/>
+      <c r="F44" s="17" t="n"/>
+      <c r="G44" s="9" t="n"/>
+      <c r="H44" s="9" t="n"/>
+      <c r="I44" s="9" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>빅솔론총판</t>
-        </is>
-      </c>
-      <c r="B45" s="23" t="inlineStr">
-        <is>
-          <t>노출가능</t>
-        </is>
-      </c>
-      <c r="C45" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="D45" s="23" t="n"/>
-      <c r="E45" s="23" t="n"/>
-      <c r="F45" s="23" t="n"/>
-      <c r="G45" s="24" t="inlineStr">
+          <t>열전사프린터기</t>
+        </is>
+      </c>
+      <c r="B45" s="10" t="inlineStr">
         <is>
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H45" s="23" t="inlineStr">
-        <is>
-          <t>솔바텍 미노출</t>
-        </is>
-      </c>
-      <c r="I45" s="25" t="n">
-        <v>70</v>
-      </c>
-      <c r="J45" s="26">
-        <f>VLOOKUP(H45,$A$3:$B$8,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="K45" s="25">
-        <f>IF(J45=0,I45,MAX(I45,MIN($B$10,ROUNDUP(I45*(1+J45),-1))))</f>
-        <v/>
-      </c>
-      <c r="L45" s="21" t="n"/>
-      <c r="M45" s="27">
-        <f>IF(L45&lt;&gt;"",MIN($B$10,L45),K45)</f>
-        <v/>
-      </c>
-      <c r="N45" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" s="23" t="inlineStr">
-        <is>
-          <t>0원</t>
-        </is>
+      <c r="C45" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="D45" s="17" t="n">
+        <v>450</v>
+      </c>
+      <c r="E45" s="17" t="n"/>
+      <c r="F45" s="17" t="n"/>
+      <c r="G45" s="9" t="n"/>
+      <c r="H45" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="I45" s="9" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>빅솔론프린터</t>
-        </is>
-      </c>
-      <c r="B46" s="23" t="inlineStr">
-        <is>
-          <t>노출가능</t>
-        </is>
-      </c>
-      <c r="C46" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="D46" s="23" t="n">
-        <v>6</v>
-      </c>
-      <c r="E46" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="F46" s="23" t="n"/>
-      <c r="G46" s="24" t="inlineStr">
+          <t>영수증프린터</t>
+        </is>
+      </c>
+      <c r="B46" s="10" t="inlineStr">
         <is>
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H46" s="23" t="inlineStr">
-        <is>
-          <t>순위 차이 큼</t>
-        </is>
-      </c>
-      <c r="I46" s="25" t="n">
-        <v>940</v>
-      </c>
-      <c r="J46" s="26">
-        <f>VLOOKUP(H46,$A$3:$B$8,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="K46" s="25">
-        <f>IF(J46=0,I46,MAX(I46,MIN($B$10,ROUNDUP(I46*(1+J46),-1))))</f>
-        <v/>
-      </c>
-      <c r="L46" s="21" t="n"/>
-      <c r="M46" s="27">
-        <f>IF(L46&lt;&gt;"",MIN($B$10,L46),K46)</f>
-        <v/>
-      </c>
-      <c r="N46" s="23" t="n">
-        <v>43</v>
-      </c>
-      <c r="O46" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" s="23" t="inlineStr">
-        <is>
-          <t>0원</t>
-        </is>
-      </c>
+      <c r="C46" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D46" s="17" t="n">
+        <v>1070</v>
+      </c>
+      <c r="E46" s="17" t="n"/>
+      <c r="F46" s="17" t="n"/>
+      <c r="G46" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H46" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="I46" s="9" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>산업용라벨프린터</t>
-        </is>
-      </c>
-      <c r="B47" s="18" t="inlineStr">
-        <is>
-          <t>노출가능</t>
-        </is>
-      </c>
-      <c r="C47" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="D47" s="18" t="n">
-        <v>6</v>
-      </c>
-      <c r="E47" s="18" t="n"/>
-      <c r="F47" s="18" t="n"/>
-      <c r="G47" s="18" t="n"/>
-      <c r="H47" s="18" t="inlineStr">
-        <is>
-          <t>유지</t>
-        </is>
-      </c>
-      <c r="I47" s="19" t="n">
-        <v>5000</v>
-      </c>
-      <c r="J47" s="20">
-        <f>VLOOKUP(H47,$A$3:$B$8,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="K47" s="19">
-        <f>IF(J47=0,I47,MAX(I47,MIN($B$10,ROUNDUP(I47*(1+J47),-1))))</f>
-        <v/>
-      </c>
-      <c r="L47" s="21" t="n"/>
-      <c r="M47" s="22">
-        <f>IF(L47&lt;&gt;"",MIN($B$10,L47),K47)</f>
-        <v/>
-      </c>
-      <c r="N47" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="O47" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="P47" s="18" t="inlineStr">
-        <is>
-          <t>4,970원</t>
-        </is>
-      </c>
+          <t>제브라</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="n"/>
+      <c r="C47" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="D47" s="16" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E47" s="16" t="n"/>
+      <c r="F47" s="16" t="n"/>
+      <c r="G47" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H47" s="7" t="n"/>
+      <c r="I47" s="7" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>산업용바코드프린터</t>
-        </is>
-      </c>
-      <c r="B48" s="23" t="inlineStr">
-        <is>
-          <t>노출가능</t>
-        </is>
-      </c>
-      <c r="C48" s="23" t="n">
+          <t>제브라라벨프린터</t>
+        </is>
+      </c>
+      <c r="B48" s="10" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D48" s="23" t="n"/>
-      <c r="E48" s="23" t="n"/>
-      <c r="F48" s="23" t="n"/>
-      <c r="G48" s="24" t="inlineStr">
-        <is>
-          <t>수정필요</t>
-        </is>
-      </c>
-      <c r="H48" s="23" t="inlineStr">
-        <is>
-          <t>솔바텍 미노출</t>
-        </is>
-      </c>
-      <c r="I48" s="25" t="n">
-        <v>800</v>
-      </c>
-      <c r="J48" s="26">
-        <f>VLOOKUP(H48,$A$3:$B$8,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="K48" s="25">
-        <f>IF(J48=0,I48,MAX(I48,MIN($B$10,ROUNDUP(I48*(1+J48),-1))))</f>
-        <v/>
-      </c>
-      <c r="L48" s="21" t="n"/>
-      <c r="M48" s="27">
-        <f>IF(L48&lt;&gt;"",MIN($B$10,L48),K48)</f>
-        <v/>
-      </c>
-      <c r="N48" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" s="23" t="inlineStr">
-        <is>
-          <t>0원</t>
-        </is>
-      </c>
+      <c r="D48" s="17" t="n">
+        <v>700</v>
+      </c>
+      <c r="E48" s="17" t="n"/>
+      <c r="F48" s="17" t="n"/>
+      <c r="G48" s="9" t="n"/>
+      <c r="H48" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="I48" s="9" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>산업용프린터</t>
-        </is>
-      </c>
-      <c r="B49" s="23" t="inlineStr">
-        <is>
-          <t>노출가능</t>
-        </is>
-      </c>
-      <c r="C49" s="23" t="n">
+          <t>제브라바코드프린터</t>
+        </is>
+      </c>
+      <c r="B49" s="10" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D49" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E49" s="17" t="n"/>
+      <c r="F49" s="17" t="n"/>
+      <c r="G49" s="9" t="n"/>
+      <c r="H49" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="D49" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E49" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="F49" s="23" t="n"/>
-      <c r="G49" s="24" t="inlineStr">
-        <is>
-          <t>수정필요</t>
-        </is>
-      </c>
-      <c r="H49" s="23" t="inlineStr">
-        <is>
-          <t>붙어있음(위)</t>
-        </is>
-      </c>
-      <c r="I49" s="25" t="n">
-        <v>6500</v>
-      </c>
-      <c r="J49" s="26">
-        <f>VLOOKUP(H49,$A$3:$B$8,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="K49" s="25">
-        <f>IF(J49=0,I49,MAX(I49,MIN($B$10,ROUNDUP(I49*(1+J49),-1))))</f>
-        <v/>
-      </c>
-      <c r="L49" s="21" t="n"/>
-      <c r="M49" s="27">
-        <f>IF(L49&lt;&gt;"",MIN($B$10,L49),K49)</f>
-        <v/>
-      </c>
-      <c r="N49" s="23" t="n">
-        <v>6</v>
-      </c>
-      <c r="O49" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="P49" s="23" t="inlineStr">
-        <is>
-          <t>6,578원</t>
-        </is>
-      </c>
+      <c r="I49" s="9" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>소형바코드프린터</t>
-        </is>
-      </c>
-      <c r="B50" s="23" t="inlineStr">
-        <is>
-          <t>노출가능</t>
-        </is>
-      </c>
-      <c r="C50" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="D50" s="23" t="n">
-        <v>6</v>
-      </c>
-      <c r="E50" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="F50" s="23" t="n"/>
-      <c r="G50" s="24" t="inlineStr">
+          <t>제브라프린터</t>
+        </is>
+      </c>
+      <c r="B50" s="10" t="inlineStr">
         <is>
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H50" s="23" t="inlineStr">
-        <is>
-          <t>붙어있음(아래)</t>
-        </is>
-      </c>
-      <c r="I50" s="25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J50" s="26">
-        <f>VLOOKUP(H50,$A$3:$B$8,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="K50" s="25">
-        <f>IF(J50=0,I50,MAX(I50,MIN($B$10,ROUNDUP(I50*(1+J50),-1))))</f>
-        <v/>
-      </c>
-      <c r="L50" s="21" t="n"/>
-      <c r="M50" s="27">
-        <f>IF(L50&lt;&gt;"",MIN($B$10,L50),K50)</f>
-        <v/>
-      </c>
-      <c r="N50" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" s="23" t="inlineStr">
-        <is>
-          <t>0원</t>
-        </is>
-      </c>
+      <c r="C50" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="D50" s="17" t="n">
+        <v>1410</v>
+      </c>
+      <c r="E50" s="17" t="n"/>
+      <c r="F50" s="17" t="n"/>
+      <c r="G50" s="9" t="n"/>
+      <c r="H50" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I50" s="9" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>스티커라벨기</t>
-        </is>
-      </c>
-      <c r="B51" s="23" t="inlineStr">
-        <is>
-          <t>노출가능</t>
-        </is>
-      </c>
-      <c r="C51" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="D51" s="23" t="n"/>
-      <c r="E51" s="23" t="n"/>
-      <c r="F51" s="23" t="n"/>
-      <c r="G51" s="24" t="inlineStr">
+          <t>카드프린터기</t>
+        </is>
+      </c>
+      <c r="B51" s="10" t="inlineStr">
         <is>
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H51" s="23" t="inlineStr">
-        <is>
-          <t>솔바텍 미노출</t>
-        </is>
-      </c>
-      <c r="I51" s="25" t="n">
-        <v>2300</v>
-      </c>
-      <c r="J51" s="26">
-        <f>VLOOKUP(H51,$A$3:$B$8,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="K51" s="25">
-        <f>IF(J51=0,I51,MAX(I51,MIN($B$10,ROUNDUP(I51*(1+J51),-1))))</f>
-        <v/>
-      </c>
-      <c r="L51" s="21" t="n"/>
-      <c r="M51" s="27">
-        <f>IF(L51&lt;&gt;"",MIN($B$10,L51),K51)</f>
-        <v/>
-      </c>
-      <c r="N51" s="23" t="n">
-        <v>21</v>
-      </c>
-      <c r="O51" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" s="23" t="inlineStr">
-        <is>
-          <t>0원</t>
-        </is>
-      </c>
+      <c r="C51" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D51" s="17" t="n">
+        <v>70</v>
+      </c>
+      <c r="E51" s="17" t="n"/>
+      <c r="F51" s="17" t="n"/>
+      <c r="G51" s="9" t="n"/>
+      <c r="H51" s="9" t="n"/>
+      <c r="I51" s="9" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>스티커인쇄기</t>
-        </is>
-      </c>
-      <c r="B52" s="18" t="inlineStr">
-        <is>
-          <t>노출가능</t>
-        </is>
-      </c>
-      <c r="C52" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="D52" s="18" t="n"/>
-      <c r="E52" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="F52" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G52" s="18" t="n"/>
-      <c r="H52" s="18" t="inlineStr">
-        <is>
-          <t>유지</t>
-        </is>
-      </c>
-      <c r="I52" s="19" t="n">
-        <v>800</v>
-      </c>
-      <c r="J52" s="20">
-        <f>VLOOKUP(H52,$A$3:$B$8,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="K52" s="19">
-        <f>IF(J52=0,I52,MAX(I52,MIN($B$10,ROUNDUP(I52*(1+J52),-1))))</f>
-        <v/>
-      </c>
-      <c r="L52" s="21" t="n"/>
-      <c r="M52" s="22">
-        <f>IF(L52&lt;&gt;"",MIN($B$10,L52),K52)</f>
-        <v/>
-      </c>
-      <c r="N52" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="O52" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" s="18" t="inlineStr">
-        <is>
-          <t>0원</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="8" t="inlineStr">
-        <is>
-          <t>스티커출력기</t>
-        </is>
-      </c>
-      <c r="B53" s="23" t="inlineStr">
-        <is>
-          <t>노출가능</t>
-        </is>
-      </c>
-      <c r="C53" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="D53" s="23" t="n">
+          <t>프린터관리</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="n"/>
+      <c r="C52" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="E53" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="F53" s="23" t="n"/>
-      <c r="G53" s="24" t="inlineStr">
-        <is>
-          <t>수정필요</t>
-        </is>
-      </c>
-      <c r="H53" s="23" t="inlineStr">
-        <is>
-          <t>순위 차이 큼</t>
-        </is>
-      </c>
-      <c r="I53" s="25" t="n">
-        <v>400</v>
-      </c>
-      <c r="J53" s="26">
-        <f>VLOOKUP(H53,$A$3:$B$8,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="K53" s="25">
-        <f>IF(J53=0,I53,MAX(I53,MIN($B$10,ROUNDUP(I53*(1+J53),-1))))</f>
-        <v/>
-      </c>
-      <c r="L53" s="21" t="n"/>
-      <c r="M53" s="27">
-        <f>IF(L53&lt;&gt;"",MIN($B$10,L53),K53)</f>
-        <v/>
-      </c>
-      <c r="N53" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="O53" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" s="23" t="inlineStr">
-        <is>
-          <t>0원</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="8" t="inlineStr">
-        <is>
-          <t>스티커프린터</t>
-        </is>
-      </c>
-      <c r="B54" s="23" t="inlineStr">
-        <is>
-          <t>노출가능</t>
-        </is>
-      </c>
-      <c r="C54" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="D54" s="23" t="n"/>
-      <c r="E54" s="23" t="n"/>
-      <c r="F54" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="G54" s="24" t="inlineStr">
-        <is>
-          <t>수정필요</t>
-        </is>
-      </c>
-      <c r="H54" s="23" t="inlineStr">
-        <is>
-          <t>솔바텍 미노출</t>
-        </is>
-      </c>
-      <c r="I54" s="25" t="n">
-        <v>1340</v>
-      </c>
-      <c r="J54" s="26">
-        <f>VLOOKUP(H54,$A$3:$B$8,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="K54" s="25">
-        <f>IF(J54=0,I54,MAX(I54,MIN($B$10,ROUNDUP(I54*(1+J54),-1))))</f>
-        <v/>
-      </c>
-      <c r="L54" s="21" t="n"/>
-      <c r="M54" s="27">
-        <f>IF(L54&lt;&gt;"",MIN($B$10,L54),K54)</f>
-        <v/>
-      </c>
-      <c r="N54" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="O54" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" s="23" t="inlineStr">
-        <is>
-          <t>0원</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="8" t="inlineStr">
-        <is>
-          <t>열전사프린터</t>
-        </is>
-      </c>
-      <c r="B55" s="23" t="inlineStr">
-        <is>
-          <t>노출가능</t>
-        </is>
-      </c>
-      <c r="C55" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="D55" s="23" t="n"/>
-      <c r="E55" s="23" t="n"/>
-      <c r="F55" s="23" t="n"/>
-      <c r="G55" s="24" t="inlineStr">
-        <is>
-          <t>수정필요</t>
-        </is>
-      </c>
-      <c r="H55" s="23" t="inlineStr">
-        <is>
-          <t>솔바텍 미노출</t>
-        </is>
-      </c>
-      <c r="I55" s="25" t="n">
-        <v>5500</v>
-      </c>
-      <c r="J55" s="26">
-        <f>VLOOKUP(H55,$A$3:$B$8,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="K55" s="25">
-        <f>IF(J55=0,I55,MAX(I55,MIN($B$10,ROUNDUP(I55*(1+J55),-1))))</f>
-        <v/>
-      </c>
-      <c r="L55" s="21" t="n"/>
-      <c r="M55" s="27">
-        <f>IF(L55&lt;&gt;"",MIN($B$10,L55),K55)</f>
-        <v/>
-      </c>
-      <c r="N55" s="23" t="n">
-        <v>13</v>
-      </c>
-      <c r="O55" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" s="23" t="inlineStr">
-        <is>
-          <t>0원</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="8" t="inlineStr">
-        <is>
-          <t>열전사프린터기</t>
-        </is>
-      </c>
-      <c r="B56" s="23" t="inlineStr">
-        <is>
-          <t>노출가능</t>
-        </is>
-      </c>
-      <c r="C56" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="D56" s="23" t="n"/>
-      <c r="E56" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="F56" s="23" t="n">
-        <v>9</v>
-      </c>
-      <c r="G56" s="24" t="inlineStr">
-        <is>
-          <t>수정필요</t>
-        </is>
-      </c>
-      <c r="H56" s="23" t="inlineStr">
-        <is>
-          <t>솔바텍 미노출</t>
-        </is>
-      </c>
-      <c r="I56" s="25" t="n">
-        <v>450</v>
-      </c>
-      <c r="J56" s="26">
-        <f>VLOOKUP(H56,$A$3:$B$8,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="K56" s="25">
-        <f>IF(J56=0,I56,MAX(I56,MIN($B$10,ROUNDUP(I56*(1+J56),-1))))</f>
-        <v/>
-      </c>
-      <c r="L56" s="21" t="n"/>
-      <c r="M56" s="27">
-        <f>IF(L56&lt;&gt;"",MIN($B$10,L56),K56)</f>
-        <v/>
-      </c>
-      <c r="N56" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" s="23" t="inlineStr">
-        <is>
-          <t>0원</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="8" t="inlineStr">
-        <is>
-          <t>영수증프린터</t>
-        </is>
-      </c>
-      <c r="B57" s="23" t="inlineStr">
-        <is>
-          <t>노출가능</t>
-        </is>
-      </c>
-      <c r="C57" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="D57" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="E57" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="F57" s="23" t="n"/>
-      <c r="G57" s="24" t="inlineStr">
-        <is>
-          <t>수정필요</t>
-        </is>
-      </c>
-      <c r="H57" s="23" t="inlineStr">
-        <is>
-          <t>붙어있음(위)</t>
-        </is>
-      </c>
-      <c r="I57" s="25" t="n">
-        <v>1070</v>
-      </c>
-      <c r="J57" s="26">
-        <f>VLOOKUP(H57,$A$3:$B$8,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="K57" s="25">
-        <f>IF(J57=0,I57,MAX(I57,MIN($B$10,ROUNDUP(I57*(1+J57),-1))))</f>
-        <v/>
-      </c>
-      <c r="L57" s="21" t="n"/>
-      <c r="M57" s="27">
-        <f>IF(L57&lt;&gt;"",MIN($B$10,L57),K57)</f>
-        <v/>
-      </c>
-      <c r="N57" s="23" t="n">
-        <v>85</v>
-      </c>
-      <c r="O57" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" s="23" t="inlineStr">
-        <is>
-          <t>0원</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="6" t="inlineStr">
-        <is>
-          <t>제브라</t>
-        </is>
-      </c>
-      <c r="B58" s="18" t="inlineStr">
-        <is>
-          <t>노출가능</t>
-        </is>
-      </c>
-      <c r="C58" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="D58" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="E58" s="18" t="n"/>
-      <c r="F58" s="18" t="n"/>
-      <c r="G58" s="18" t="n"/>
-      <c r="H58" s="18" t="inlineStr">
-        <is>
-          <t>유지</t>
-        </is>
-      </c>
-      <c r="I58" s="19" t="n">
-        <v>1500</v>
-      </c>
-      <c r="J58" s="20">
-        <f>VLOOKUP(H58,$A$3:$B$8,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="K58" s="19">
-        <f>IF(J58=0,I58,MAX(I58,MIN($B$10,ROUNDUP(I58*(1+J58),-1))))</f>
-        <v/>
-      </c>
-      <c r="L58" s="21" t="n"/>
-      <c r="M58" s="22">
-        <f>IF(L58&lt;&gt;"",MIN($B$10,L58),K58)</f>
-        <v/>
-      </c>
-      <c r="N58" s="18" t="n">
-        <v>115</v>
-      </c>
-      <c r="O58" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="P58" s="18" t="inlineStr">
-        <is>
-          <t>1,464원</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="8" t="inlineStr">
-        <is>
-          <t>제브라라벨프린터</t>
-        </is>
-      </c>
-      <c r="B59" s="23" t="inlineStr">
-        <is>
-          <t>노출가능</t>
-        </is>
-      </c>
-      <c r="C59" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="D59" s="23" t="n"/>
-      <c r="E59" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="F59" s="23" t="n"/>
-      <c r="G59" s="24" t="inlineStr">
-        <is>
-          <t>수정필요</t>
-        </is>
-      </c>
-      <c r="H59" s="23" t="inlineStr">
-        <is>
-          <t>솔바텍 미노출</t>
-        </is>
-      </c>
-      <c r="I59" s="25" t="n">
-        <v>700</v>
-      </c>
-      <c r="J59" s="26">
-        <f>VLOOKUP(H59,$A$3:$B$8,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="K59" s="25">
-        <f>IF(J59=0,I59,MAX(I59,MIN($B$10,ROUNDUP(I59*(1+J59),-1))))</f>
-        <v/>
-      </c>
-      <c r="L59" s="21" t="n"/>
-      <c r="M59" s="27">
-        <f>IF(L59&lt;&gt;"",MIN($B$10,L59),K59)</f>
-        <v/>
-      </c>
-      <c r="N59" s="23" t="n">
-        <v>6</v>
-      </c>
-      <c r="O59" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P59" s="23" t="inlineStr">
-        <is>
-          <t>0원</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="8" t="inlineStr">
-        <is>
-          <t>제브라바코드프린터</t>
-        </is>
-      </c>
-      <c r="B60" s="23" t="inlineStr">
-        <is>
-          <t>노출가능</t>
-        </is>
-      </c>
-      <c r="C60" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="D60" s="23" t="n"/>
-      <c r="E60" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="F60" s="23" t="n"/>
-      <c r="G60" s="24" t="inlineStr">
-        <is>
-          <t>수정필요</t>
-        </is>
-      </c>
-      <c r="H60" s="23" t="inlineStr">
-        <is>
-          <t>솔바텍 미노출</t>
-        </is>
-      </c>
-      <c r="I60" s="25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J60" s="26">
-        <f>VLOOKUP(H60,$A$3:$B$8,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="K60" s="25">
-        <f>IF(J60=0,I60,MAX(I60,MIN($B$10,ROUNDUP(I60*(1+J60),-1))))</f>
-        <v/>
-      </c>
-      <c r="L60" s="21" t="n"/>
-      <c r="M60" s="27">
-        <f>IF(L60&lt;&gt;"",MIN($B$10,L60),K60)</f>
-        <v/>
-      </c>
-      <c r="N60" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="O60" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P60" s="23" t="inlineStr">
-        <is>
-          <t>0원</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="8" t="inlineStr">
-        <is>
-          <t>제브라프린터</t>
-        </is>
-      </c>
-      <c r="B61" s="23" t="inlineStr">
-        <is>
-          <t>노출가능</t>
-        </is>
-      </c>
-      <c r="C61" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="D61" s="23" t="n"/>
-      <c r="E61" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="F61" s="23" t="n"/>
-      <c r="G61" s="24" t="inlineStr">
-        <is>
-          <t>수정필요</t>
-        </is>
-      </c>
-      <c r="H61" s="23" t="inlineStr">
-        <is>
-          <t>솔바텍 미노출</t>
-        </is>
-      </c>
-      <c r="I61" s="25" t="n">
-        <v>1410</v>
-      </c>
-      <c r="J61" s="26">
-        <f>VLOOKUP(H61,$A$3:$B$8,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="K61" s="25">
-        <f>IF(J61=0,I61,MAX(I61,MIN($B$10,ROUNDUP(I61*(1+J61),-1))))</f>
-        <v/>
-      </c>
-      <c r="L61" s="21" t="n"/>
-      <c r="M61" s="27">
-        <f>IF(L61&lt;&gt;"",MIN($B$10,L61),K61)</f>
-        <v/>
-      </c>
-      <c r="N61" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="O61" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P61" s="23" t="inlineStr">
-        <is>
-          <t>0원</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="8" t="inlineStr">
-        <is>
-          <t>카드프린터기</t>
-        </is>
-      </c>
-      <c r="B62" s="23" t="inlineStr">
-        <is>
-          <t>중지: 키워드 OFF</t>
-        </is>
-      </c>
-      <c r="C62" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="D62" s="23" t="n"/>
-      <c r="E62" s="23" t="n"/>
-      <c r="F62" s="23" t="n"/>
-      <c r="G62" s="24" t="inlineStr">
-        <is>
-          <t>수정필요</t>
-        </is>
-      </c>
-      <c r="H62" s="23" t="inlineStr">
-        <is>
-          <t>솔바텍 미노출</t>
-        </is>
-      </c>
-      <c r="I62" s="25" t="n">
-        <v>70</v>
-      </c>
-      <c r="J62" s="26">
-        <f>VLOOKUP(H62,$A$3:$B$8,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="K62" s="25">
-        <f>IF(J62=0,I62,MAX(I62,MIN($B$10,ROUNDUP(I62*(1+J62),-1))))</f>
-        <v/>
-      </c>
-      <c r="L62" s="21" t="n"/>
-      <c r="M62" s="27">
-        <f>IF(L62&lt;&gt;"",MIN($B$10,L62),K62)</f>
-        <v/>
-      </c>
-      <c r="N62" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O62" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" s="23" t="inlineStr">
-        <is>
-          <t>0원</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="6" t="inlineStr">
-        <is>
-          <t>프린터관리</t>
-        </is>
-      </c>
-      <c r="B63" s="18" t="inlineStr">
-        <is>
-          <t>중지: 키워드 OFF</t>
-        </is>
-      </c>
-      <c r="C63" s="18" t="n">
-        <v>7</v>
-      </c>
-      <c r="D63" s="18" t="n"/>
-      <c r="E63" s="18" t="n"/>
-      <c r="F63" s="18" t="n"/>
-      <c r="G63" s="18" t="n"/>
-      <c r="H63" s="18" t="inlineStr">
-        <is>
-          <t>유지</t>
-        </is>
-      </c>
-      <c r="I63" s="19" t="n">
+      <c r="D52" s="16" t="n">
         <v>200</v>
       </c>
-      <c r="J63" s="20">
-        <f>VLOOKUP(H63,$A$3:$B$8,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="K63" s="19">
-        <f>IF(J63=0,I63,MAX(I63,MIN($B$10,ROUNDUP(I63*(1+J63),-1))))</f>
-        <v/>
-      </c>
-      <c r="L63" s="21" t="n"/>
-      <c r="M63" s="22">
-        <f>IF(L63&lt;&gt;"",MIN($B$10,L63),K63)</f>
-        <v/>
-      </c>
-      <c r="N63" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O63" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P63" s="18" t="inlineStr">
-        <is>
-          <t>0원</t>
-        </is>
-      </c>
+      <c r="E52" s="16" t="n"/>
+      <c r="F52" s="16" t="n"/>
+      <c r="G52" s="7" t="n"/>
+      <c r="H52" s="7" t="n"/>
+      <c r="I52" s="7" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A13:P63"/>
-  <mergeCells count="8">
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="C3:F3"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="C2:F2"/>
+  <autoFilter ref="A2:I52"/>
+  <mergeCells count="5">
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="A1:A2"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="H14:H63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>=$A$3:$A$8</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3767,23 +1947,23 @@
           <t>입찰가 변경 전</t>
         </is>
       </c>
-      <c r="C1" s="28" t="n"/>
-      <c r="D1" s="28" t="n"/>
-      <c r="E1" s="28" t="n"/>
-      <c r="F1" s="28" t="n"/>
-      <c r="G1" s="29" t="n"/>
+      <c r="C1" s="18" t="n"/>
+      <c r="D1" s="18" t="n"/>
+      <c r="E1" s="18" t="n"/>
+      <c r="F1" s="18" t="n"/>
+      <c r="G1" s="19" t="n"/>
       <c r="H1" s="4" t="inlineStr">
         <is>
           <t>입찰가 변경 후</t>
         </is>
       </c>
-      <c r="I1" s="28" t="n"/>
-      <c r="J1" s="28" t="n"/>
-      <c r="K1" s="28" t="n"/>
-      <c r="L1" s="29" t="n"/>
+      <c r="I1" s="18" t="n"/>
+      <c r="J1" s="18" t="n"/>
+      <c r="K1" s="18" t="n"/>
+      <c r="L1" s="19" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="30" t="n"/>
+      <c r="A2" s="20" t="n"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>현재 입찰가</t>
@@ -9306,10 +7486,7 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H305" s="31">
-        <f>'프린터 입찰가'!M21</f>
-        <v/>
-      </c>
+      <c r="H305" s="9" t="n"/>
       <c r="I305" s="9" t="n"/>
       <c r="J305" s="9" t="n"/>
       <c r="K305" s="9" t="n"/>
@@ -9337,10 +7514,7 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H306" s="31">
-        <f>'프린터 입찰가'!M23</f>
-        <v/>
-      </c>
+      <c r="H306" s="9" t="n"/>
       <c r="I306" s="9" t="n"/>
       <c r="J306" s="9" t="n"/>
       <c r="K306" s="9" t="n"/>
@@ -9368,10 +7542,7 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H307" s="31">
-        <f>'프린터 입찰가'!M24</f>
-        <v/>
-      </c>
+      <c r="H307" s="9" t="n"/>
       <c r="I307" s="9" t="n"/>
       <c r="J307" s="9" t="n"/>
       <c r="K307" s="9" t="n"/>
@@ -9399,10 +7570,7 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H308" s="31">
-        <f>'프린터 입찰가'!M26</f>
-        <v/>
-      </c>
+      <c r="H308" s="9" t="n"/>
       <c r="I308" s="9" t="n"/>
       <c r="J308" s="9" t="n"/>
       <c r="K308" s="9" t="n"/>
@@ -9432,10 +7600,7 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H309" s="31">
-        <f>'프린터 입찰가'!M27</f>
-        <v/>
-      </c>
+      <c r="H309" s="9" t="n"/>
       <c r="I309" s="9" t="n"/>
       <c r="J309" s="9" t="n"/>
       <c r="K309" s="9" t="n"/>
@@ -9463,10 +7628,7 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H310" s="31">
-        <f>'프린터 입찰가'!M31</f>
-        <v/>
-      </c>
+      <c r="H310" s="9" t="n"/>
       <c r="I310" s="9" t="n"/>
       <c r="J310" s="9" t="n"/>
       <c r="K310" s="9" t="n"/>
@@ -9494,10 +7656,7 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H311" s="31">
-        <f>'프린터 입찰가'!M36</f>
-        <v/>
-      </c>
+      <c r="H311" s="9" t="n"/>
       <c r="I311" s="9" t="n"/>
       <c r="J311" s="9" t="n"/>
       <c r="K311" s="9" t="n"/>
@@ -9527,10 +7686,7 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H312" s="31">
-        <f>'프린터 입찰가'!M41</f>
-        <v/>
-      </c>
+      <c r="H312" s="9" t="n"/>
       <c r="I312" s="9" t="n"/>
       <c r="J312" s="9" t="n"/>
       <c r="K312" s="9" t="n"/>
@@ -9582,10 +7738,7 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H314" s="31">
-        <f>'프린터 입찰가'!M59</f>
-        <v/>
-      </c>
+      <c r="H314" s="9" t="n"/>
       <c r="I314" s="9" t="n"/>
       <c r="J314" s="9" t="n"/>
       <c r="K314" s="9" t="n"/>
@@ -9613,10 +7766,7 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H315" s="31">
-        <f>'프린터 입찰가'!M60</f>
-        <v/>
-      </c>
+      <c r="H315" s="9" t="n"/>
       <c r="I315" s="9" t="n"/>
       <c r="J315" s="9" t="n"/>
       <c r="K315" s="9" t="n"/>
@@ -9644,10 +7794,7 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H316" s="31">
-        <f>'프린터 입찰가'!M33</f>
-        <v/>
-      </c>
+      <c r="H316" s="9" t="n"/>
       <c r="I316" s="9" t="n"/>
       <c r="J316" s="9" t="n"/>
       <c r="K316" s="9" t="n"/>
@@ -9675,10 +7822,7 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H317" s="31">
-        <f>'프린터 입찰가'!M40</f>
-        <v/>
-      </c>
+      <c r="H317" s="9" t="n"/>
       <c r="I317" s="9" t="n"/>
       <c r="J317" s="9" t="n"/>
       <c r="K317" s="9" t="n"/>
@@ -9752,10 +7896,7 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H320" s="31">
-        <f>'프린터 입찰가'!M20</f>
-        <v/>
-      </c>
+      <c r="H320" s="9" t="n"/>
       <c r="I320" s="9" t="n"/>
       <c r="J320" s="9" t="n"/>
       <c r="K320" s="9" t="n"/>
@@ -9783,10 +7924,7 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H321" s="31">
-        <f>'프린터 입찰가'!M35</f>
-        <v/>
-      </c>
+      <c r="H321" s="9" t="n"/>
       <c r="I321" s="9" t="n"/>
       <c r="J321" s="9" t="n"/>
       <c r="K321" s="9" t="n"/>
@@ -9814,10 +7952,7 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H322" s="31">
-        <f>'프린터 입찰가'!M42</f>
-        <v/>
-      </c>
+      <c r="H322" s="9" t="n"/>
       <c r="I322" s="9" t="n"/>
       <c r="J322" s="9" t="n"/>
       <c r="K322" s="9" t="n"/>
@@ -9847,10 +7982,7 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H323" s="31">
-        <f>'프린터 입찰가'!M46</f>
-        <v/>
-      </c>
+      <c r="H323" s="9" t="n"/>
       <c r="I323" s="9" t="n"/>
       <c r="J323" s="9" t="n"/>
       <c r="K323" s="9" t="n"/>
@@ -9880,10 +8012,7 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H324" s="31">
-        <f>'프린터 입찰가'!M50</f>
-        <v/>
-      </c>
+      <c r="H324" s="9" t="n"/>
       <c r="I324" s="9" t="n"/>
       <c r="J324" s="9" t="n"/>
       <c r="K324" s="9" t="n"/>
@@ -9935,10 +8064,7 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H326" s="31">
-        <f>'프린터 입찰가'!M61</f>
-        <v/>
-      </c>
+      <c r="H326" s="9" t="n"/>
       <c r="I326" s="9" t="n"/>
       <c r="J326" s="9" t="n"/>
       <c r="K326" s="9" t="n"/>
@@ -9988,10 +8114,7 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H328" s="31">
-        <f>'프린터 입찰가'!M45</f>
-        <v/>
-      </c>
+      <c r="H328" s="9" t="n"/>
       <c r="I328" s="9" t="n"/>
       <c r="J328" s="9" t="n"/>
       <c r="K328" s="9" t="n"/>
@@ -10017,10 +8140,7 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H329" s="31">
-        <f>'프린터 입찰가'!M48</f>
-        <v/>
-      </c>
+      <c r="H329" s="9" t="n"/>
       <c r="I329" s="9" t="n"/>
       <c r="J329" s="9" t="n"/>
       <c r="K329" s="9" t="n"/>
@@ -10050,10 +8170,7 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H330" s="31">
-        <f>'프린터 입찰가'!M49</f>
-        <v/>
-      </c>
+      <c r="H330" s="9" t="n"/>
       <c r="I330" s="9" t="n"/>
       <c r="J330" s="9" t="n"/>
       <c r="K330" s="9" t="n"/>
@@ -10079,10 +8196,7 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H331" s="31">
-        <f>'프린터 입찰가'!M51</f>
-        <v/>
-      </c>
+      <c r="H331" s="9" t="n"/>
       <c r="I331" s="9" t="n"/>
       <c r="J331" s="9" t="n"/>
       <c r="K331" s="9" t="n"/>
@@ -10110,10 +8224,7 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H332" s="31">
-        <f>'프린터 입찰가'!M54</f>
-        <v/>
-      </c>
+      <c r="H332" s="9" t="n"/>
       <c r="I332" s="9" t="n"/>
       <c r="J332" s="9" t="n"/>
       <c r="K332" s="9" t="n"/>
@@ -10169,10 +8280,7 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H334" s="31">
-        <f>'프린터 입찰가'!M53</f>
-        <v/>
-      </c>
+      <c r="H334" s="9" t="n"/>
       <c r="I334" s="9" t="n"/>
       <c r="J334" s="9" t="n"/>
       <c r="K334" s="9" t="n"/>
@@ -10200,10 +8308,7 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H335" s="31">
-        <f>'프린터 입찰가'!M30</f>
-        <v/>
-      </c>
+      <c r="H335" s="9" t="n"/>
       <c r="I335" s="9" t="n"/>
       <c r="J335" s="9" t="n"/>
       <c r="K335" s="9" t="n"/>
@@ -10231,10 +8336,7 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H336" s="31">
-        <f>'프린터 입찰가'!M29</f>
-        <v/>
-      </c>
+      <c r="H336" s="9" t="n"/>
       <c r="I336" s="9" t="n"/>
       <c r="J336" s="9" t="n"/>
       <c r="K336" s="9" t="n"/>
@@ -10262,10 +8364,7 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H337" s="31">
-        <f>'프린터 입찰가'!M28</f>
-        <v/>
-      </c>
+      <c r="H337" s="9" t="n"/>
       <c r="I337" s="9" t="n"/>
       <c r="J337" s="9" t="n"/>
       <c r="K337" s="9" t="n"/>
@@ -10295,10 +8394,7 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H338" s="31">
-        <f>'프린터 입찰가'!M57</f>
-        <v/>
-      </c>
+      <c r="H338" s="9" t="n"/>
       <c r="I338" s="9" t="n"/>
       <c r="J338" s="9" t="n"/>
       <c r="K338" s="9" t="n"/>
@@ -10330,10 +8426,7 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H339" s="31">
-        <f>'프린터 입찰가'!M16</f>
-        <v/>
-      </c>
+      <c r="H339" s="9" t="n"/>
       <c r="I339" s="9" t="n"/>
       <c r="J339" s="9" t="n"/>
       <c r="K339" s="9" t="n"/>
@@ -10363,10 +8456,7 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H340" s="31">
-        <f>'프린터 입찰가'!M56</f>
-        <v/>
-      </c>
+      <c r="H340" s="9" t="n"/>
       <c r="I340" s="9" t="n"/>
       <c r="J340" s="9" t="n"/>
       <c r="K340" s="9" t="n"/>
@@ -10392,10 +8482,7 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H341" s="31">
-        <f>'프린터 입찰가'!M55</f>
-        <v/>
-      </c>
+      <c r="H341" s="9" t="n"/>
       <c r="I341" s="9" t="n"/>
       <c r="J341" s="9" t="n"/>
       <c r="K341" s="9" t="n"/>
@@ -10447,10 +8534,7 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H343" s="31">
-        <f>'프린터 입찰가'!M19</f>
-        <v/>
-      </c>
+      <c r="H343" s="9" t="n"/>
       <c r="I343" s="9" t="n"/>
       <c r="J343" s="9" t="n"/>
       <c r="K343" s="9" t="n"/>
@@ -10482,10 +8566,7 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H344" s="31">
-        <f>'프린터 입찰가'!M37</f>
-        <v/>
-      </c>
+      <c r="H344" s="9" t="n"/>
       <c r="I344" s="9" t="n"/>
       <c r="J344" s="9" t="n"/>
       <c r="K344" s="9" t="n"/>
@@ -10515,10 +8596,7 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H345" s="31">
-        <f>'프린터 입찰가'!M25</f>
-        <v/>
-      </c>
+      <c r="H345" s="9" t="n"/>
       <c r="I345" s="9" t="n"/>
       <c r="J345" s="9" t="n"/>
       <c r="K345" s="9" t="n"/>
@@ -10548,10 +8626,7 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H346" s="31">
-        <f>'프린터 입찰가'!M39</f>
-        <v/>
-      </c>
+      <c r="H346" s="9" t="n"/>
       <c r="I346" s="9" t="n"/>
       <c r="J346" s="9" t="n"/>
       <c r="K346" s="9" t="n"/>
@@ -10579,10 +8654,7 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H347" s="31">
-        <f>'프린터 입찰가'!M18</f>
-        <v/>
-      </c>
+      <c r="H347" s="9" t="n"/>
       <c r="I347" s="9" t="n"/>
       <c r="J347" s="9" t="n"/>
       <c r="K347" s="9" t="n"/>
@@ -10610,10 +8682,7 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H348" s="31">
-        <f>'프린터 입찰가'!M38</f>
-        <v/>
-      </c>
+      <c r="H348" s="9" t="n"/>
       <c r="I348" s="9" t="n"/>
       <c r="J348" s="9" t="n"/>
       <c r="K348" s="9" t="n"/>
@@ -10643,10 +8712,7 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H349" s="31">
-        <f>'프린터 입찰가'!M32</f>
-        <v/>
-      </c>
+      <c r="H349" s="9" t="n"/>
       <c r="I349" s="9" t="n"/>
       <c r="J349" s="9" t="n"/>
       <c r="K349" s="9" t="n"/>
@@ -10674,10 +8740,7 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H350" s="31">
-        <f>'프린터 입찰가'!M22</f>
-        <v/>
-      </c>
+      <c r="H350" s="9" t="n"/>
       <c r="I350" s="9" t="n"/>
       <c r="J350" s="9" t="n"/>
       <c r="K350" s="9" t="n"/>
@@ -12125,10 +10188,7 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H430" s="31">
-        <f>'프린터 입찰가'!M34</f>
-        <v/>
-      </c>
+      <c r="H430" s="9" t="n"/>
       <c r="I430" s="9" t="n"/>
       <c r="J430" s="9" t="n"/>
       <c r="K430" s="9" t="n"/>
@@ -12154,10 +10214,7 @@
           <t>수정필요</t>
         </is>
       </c>
-      <c r="H431" s="31">
-        <f>'프린터 입찰가'!M62</f>
-        <v/>
-      </c>
+      <c r="H431" s="9" t="n"/>
       <c r="I431" s="9" t="n"/>
       <c r="J431" s="9" t="n"/>
       <c r="K431" s="9" t="n"/>

--- a/솔바텍_URL도메인변경완료_순위반영_20261029.xlsx
+++ b/솔바텍_URL도메인변경완료_순위반영_20261029.xlsx
@@ -49,7 +49,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -74,6 +74,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFE5E5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -180,7 +185,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -217,10 +222,25 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -591,7 +611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:K75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -603,6 +623,7 @@
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -635,6 +656,11 @@
       </c>
       <c r="H1" s="5" t="n"/>
       <c r="I1" s="5" t="n"/>
+      <c r="K1" s="16" t="inlineStr">
+        <is>
+          <t>범례</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="D2" s="14" t="inlineStr">
@@ -667,107 +693,82 @@
           <t>sb렌탈</t>
         </is>
       </c>
+      <c r="K2" s="17" t="inlineStr">
+        <is>
+          <t>회색 칸 = 키워드 OFF(중지)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="K3" s="16" t="inlineStr">
+        <is>
+          <t>굵은 글씨 = 3개 사이트 중 최고 입찰가</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="K4" s="18" t="inlineStr">
+        <is>
+          <t>빨간 글씨 = 입찰가 수정 대상</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>감열식프린터</t>
         </is>
       </c>
-      <c r="B3" s="7" t="n"/>
-      <c r="C3" s="7" t="n">
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="D3" s="16" t="n">
+      <c r="D5" s="19" t="n">
         <v>800</v>
       </c>
-      <c r="E3" s="16" t="n"/>
-      <c r="F3" s="16" t="n"/>
-      <c r="G3" s="7" t="n">
+      <c r="E5" s="20" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F5" s="19" t="n"/>
+      <c r="G5" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="H3" s="7" t="n">
+      <c r="H5" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="I3" s="7" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>감열프린터</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="n"/>
-      <c r="C4" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="D4" s="16" t="n">
-        <v>2000</v>
-      </c>
-      <c r="E4" s="16" t="n"/>
-      <c r="F4" s="16" t="n"/>
-      <c r="G4" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="H4" s="7" t="n"/>
-      <c r="I4" s="7" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>감열프린터기</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>수정필요</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="D5" s="17" t="n">
-        <v>650</v>
-      </c>
-      <c r="E5" s="17" t="n"/>
-      <c r="F5" s="17" t="n"/>
-      <c r="G5" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="H5" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="I5" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="I5" s="7" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>도시바프린터</t>
+          <t>감열프린터</t>
         </is>
       </c>
       <c r="B6" s="7" t="n"/>
       <c r="C6" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="D6" s="20" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E6" s="19" t="n">
         <v>1500</v>
       </c>
-      <c r="E6" s="16" t="n"/>
-      <c r="F6" s="16" t="n"/>
+      <c r="F6" s="19" t="n">
+        <v>1330</v>
+      </c>
       <c r="G6" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H6" s="7" t="n"/>
-      <c r="I6" s="7" t="n"/>
+      <c r="I6" s="7" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>라밸프린터</t>
+          <t>감열프린터기</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
@@ -778,44 +779,50 @@
       <c r="C7" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="D7" s="17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E7" s="17" t="n"/>
-      <c r="F7" s="17" t="n"/>
-      <c r="G7" s="9" t="n"/>
-      <c r="H7" s="9" t="n"/>
+      <c r="D7" s="21" t="n">
+        <v>650</v>
+      </c>
+      <c r="E7" s="21" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F7" s="22" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="H7" s="9" t="n">
+        <v>7</v>
+      </c>
       <c r="I7" s="9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>도시바프린터</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="D8" s="19" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E8" s="19" t="n"/>
+      <c r="F8" s="19" t="n"/>
+      <c r="G8" s="7" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>라벨기</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>수정필요</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="D8" s="17" t="n">
-        <v>2000</v>
-      </c>
-      <c r="E8" s="17" t="n"/>
-      <c r="F8" s="17" t="n"/>
-      <c r="G8" s="9" t="n"/>
-      <c r="H8" s="9" t="n"/>
-      <c r="I8" s="9" t="n"/>
+      <c r="H8" s="7" t="n"/>
+      <c r="I8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>라벨기계</t>
+          <t>라밸프린터</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
@@ -826,19 +833,23 @@
       <c r="C9" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="D9" s="17" t="n">
-        <v>890</v>
-      </c>
-      <c r="E9" s="17" t="n"/>
-      <c r="F9" s="17" t="n"/>
+      <c r="D9" s="21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E9" s="22" t="n">
+        <v>1700</v>
+      </c>
+      <c r="F9" s="21" t="n"/>
       <c r="G9" s="9" t="n"/>
       <c r="H9" s="9" t="n"/>
-      <c r="I9" s="9" t="n"/>
+      <c r="I9" s="9" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>라벨용지프린터</t>
+          <t>라벨기</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
@@ -847,23 +858,23 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="D10" s="17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E10" s="17" t="n"/>
-      <c r="F10" s="17" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="D10" s="21" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E10" s="21" t="n"/>
+      <c r="F10" s="22" t="n">
+        <v>5000</v>
+      </c>
       <c r="G10" s="9" t="n"/>
-      <c r="H10" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="H10" s="9" t="n"/>
       <c r="I10" s="9" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>라벨인쇄기</t>
+          <t>라벨기계</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
@@ -874,21 +885,19 @@
       <c r="C11" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="D11" s="17" t="n">
-        <v>3500</v>
-      </c>
-      <c r="E11" s="17" t="n"/>
-      <c r="F11" s="17" t="n"/>
+      <c r="D11" s="21" t="n">
+        <v>890</v>
+      </c>
+      <c r="E11" s="21" t="n"/>
+      <c r="F11" s="21" t="n"/>
       <c r="G11" s="9" t="n"/>
       <c r="H11" s="9" t="n"/>
-      <c r="I11" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="I11" s="9" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>라벨인쇄기계</t>
+          <t>라벨용지프린터</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
@@ -897,23 +906,23 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="D12" s="17" t="n">
-        <v>600</v>
-      </c>
-      <c r="E12" s="17" t="n"/>
-      <c r="F12" s="17" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="D12" s="21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E12" s="21" t="n"/>
+      <c r="F12" s="21" t="n"/>
       <c r="G12" s="9" t="n"/>
-      <c r="H12" s="9" t="n"/>
-      <c r="I12" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="H12" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I12" s="9" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>라벨지프린터</t>
+          <t>라벨인쇄기</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
@@ -924,21 +933,23 @@
       <c r="C13" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="D13" s="17" t="n">
-        <v>800</v>
-      </c>
-      <c r="E13" s="17" t="n"/>
-      <c r="F13" s="17" t="n"/>
+      <c r="D13" s="21" t="n">
+        <v>3500</v>
+      </c>
+      <c r="E13" s="22" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F13" s="21" t="n"/>
       <c r="G13" s="9" t="n"/>
-      <c r="H13" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="I13" s="9" t="n"/>
+      <c r="H13" s="9" t="n"/>
+      <c r="I13" s="9" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>라벨출력기</t>
+          <t>라벨인쇄기계</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
@@ -949,23 +960,21 @@
       <c r="C14" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="D14" s="17" t="n">
-        <v>1110</v>
-      </c>
-      <c r="E14" s="17" t="n"/>
-      <c r="F14" s="17" t="n"/>
-      <c r="G14" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="H14" s="9" t="n">
+      <c r="D14" s="21" t="n">
+        <v>600</v>
+      </c>
+      <c r="E14" s="21" t="n"/>
+      <c r="F14" s="21" t="n"/>
+      <c r="G14" s="9" t="n"/>
+      <c r="H14" s="9" t="n"/>
+      <c r="I14" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I14" s="9" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>라벨프린터업체</t>
+          <t>라벨지프린터</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -976,21 +985,23 @@
       <c r="C15" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="D15" s="17" t="n">
-        <v>530</v>
-      </c>
-      <c r="E15" s="17" t="n"/>
-      <c r="F15" s="17" t="n"/>
+      <c r="D15" s="21" t="n">
+        <v>800</v>
+      </c>
+      <c r="E15" s="22" t="n">
+        <v>1790</v>
+      </c>
+      <c r="F15" s="21" t="n"/>
       <c r="G15" s="9" t="n"/>
       <c r="H15" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I15" s="9" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>라벨프린터추천</t>
+          <t>라벨출력기</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
@@ -1001,23 +1012,23 @@
       <c r="C16" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="D16" s="17" t="n">
-        <v>1580</v>
-      </c>
-      <c r="E16" s="17" t="n"/>
-      <c r="F16" s="17" t="n"/>
+      <c r="D16" s="21" t="n">
+        <v>1110</v>
+      </c>
+      <c r="E16" s="21" t="n"/>
+      <c r="F16" s="21" t="n"/>
       <c r="G16" s="9" t="n">
         <v>7</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I16" s="9" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>롤라벨인쇄기</t>
+          <t>라벨프린터업체</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
@@ -1028,21 +1039,21 @@
       <c r="C17" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="D17" s="17" t="n">
-        <v>70</v>
-      </c>
-      <c r="E17" s="17" t="n"/>
-      <c r="F17" s="17" t="n"/>
+      <c r="D17" s="21" t="n">
+        <v>530</v>
+      </c>
+      <c r="E17" s="21" t="n"/>
+      <c r="F17" s="21" t="n"/>
       <c r="G17" s="9" t="n"/>
       <c r="H17" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I17" s="9" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>롤라벨출력기</t>
+          <t>라벨프린터추천</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -1051,23 +1062,25 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="D18" s="17" t="n">
-        <v>100</v>
-      </c>
-      <c r="E18" s="17" t="n"/>
-      <c r="F18" s="17" t="n"/>
-      <c r="G18" s="9" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="D18" s="21" t="n">
+        <v>1580</v>
+      </c>
+      <c r="E18" s="21" t="n"/>
+      <c r="F18" s="21" t="n"/>
+      <c r="G18" s="9" t="n">
+        <v>7</v>
+      </c>
       <c r="H18" s="9" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I18" s="9" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>롤라벨프린터</t>
+          <t>롤라벨인쇄기</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
@@ -1078,21 +1091,23 @@
       <c r="C19" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="D19" s="17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E19" s="17" t="n"/>
-      <c r="F19" s="17" t="n"/>
-      <c r="G19" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="H19" s="9" t="n"/>
+      <c r="D19" s="21" t="n">
+        <v>70</v>
+      </c>
+      <c r="E19" s="22" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F19" s="21" t="n"/>
+      <c r="G19" s="9" t="n"/>
+      <c r="H19" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="I19" s="9" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>바코드라벨인쇄기</t>
+          <t>롤라벨출력기</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
@@ -1101,13 +1116,15 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="D20" s="17" t="n">
-        <v>400</v>
-      </c>
-      <c r="E20" s="17" t="n"/>
-      <c r="F20" s="17" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="D20" s="21" t="n">
+        <v>100</v>
+      </c>
+      <c r="E20" s="22" t="n">
+        <v>500</v>
+      </c>
+      <c r="F20" s="21" t="n"/>
       <c r="G20" s="9" t="n"/>
       <c r="H20" s="9" t="n">
         <v>3</v>
@@ -1117,7 +1134,7 @@
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>바코드라벨프린터</t>
+          <t>롤라벨프린터</t>
         </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
@@ -1128,23 +1145,23 @@
       <c r="C21" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="D21" s="17" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E21" s="17" t="n"/>
-      <c r="F21" s="17" t="n"/>
+      <c r="D21" s="21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E21" s="22" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F21" s="21" t="n"/>
       <c r="G21" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="H21" s="9" t="n">
-        <v>4</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="H21" s="9" t="n"/>
       <c r="I21" s="9" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>바코드라벨프린터업체</t>
+          <t>바코드라벨인쇄기</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
@@ -1153,13 +1170,13 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="D22" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="E22" s="17" t="n"/>
-      <c r="F22" s="17" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="D22" s="21" t="n">
+        <v>400</v>
+      </c>
+      <c r="E22" s="21" t="n"/>
+      <c r="F22" s="21" t="n"/>
       <c r="G22" s="9" t="n"/>
       <c r="H22" s="9" t="n">
         <v>3</v>
@@ -1169,7 +1186,7 @@
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>바코드만들기</t>
+          <t>바코드라벨프린터</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
@@ -1178,21 +1195,29 @@
         </is>
       </c>
       <c r="C23" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="D23" s="17" t="n">
-        <v>500</v>
-      </c>
-      <c r="E23" s="17" t="n"/>
-      <c r="F23" s="17" t="n"/>
-      <c r="G23" s="9" t="n"/>
-      <c r="H23" s="9" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="D23" s="21" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E23" s="21" t="n">
+        <v>4460</v>
+      </c>
+      <c r="F23" s="22" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G23" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="H23" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="I23" s="9" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>바코드발행기</t>
+          <t>바코드라벨프린터업체</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
@@ -1201,13 +1226,13 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="D24" s="17" t="n">
-        <v>400</v>
-      </c>
-      <c r="E24" s="17" t="n"/>
-      <c r="F24" s="17" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="D24" s="21" t="n">
+        <v>300</v>
+      </c>
+      <c r="E24" s="21" t="n"/>
+      <c r="F24" s="21" t="n"/>
       <c r="G24" s="9" t="n"/>
       <c r="H24" s="9" t="n">
         <v>3</v>
@@ -1217,7 +1242,7 @@
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>바코드인쇄기</t>
+          <t>바코드만들기</t>
         </is>
       </c>
       <c r="B25" s="10" t="inlineStr">
@@ -1226,23 +1251,23 @@
         </is>
       </c>
       <c r="C25" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="D25" s="17" t="n">
-        <v>3300</v>
-      </c>
-      <c r="E25" s="17" t="n"/>
-      <c r="F25" s="17" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="D25" s="23" t="n">
+        <v>500</v>
+      </c>
+      <c r="E25" s="24" t="n">
+        <v>910</v>
+      </c>
+      <c r="F25" s="21" t="n"/>
       <c r="G25" s="9" t="n"/>
       <c r="H25" s="9" t="n"/>
-      <c r="I25" s="9" t="n">
-        <v>7</v>
-      </c>
+      <c r="I25" s="9" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>바코드출력기</t>
+          <t>바코드발행기</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
@@ -1251,27 +1276,25 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="D26" s="17" t="n">
-        <v>2500</v>
-      </c>
-      <c r="E26" s="17" t="n"/>
-      <c r="F26" s="17" t="n"/>
-      <c r="G26" s="9" t="n">
-        <v>8</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="D26" s="21" t="n">
+        <v>400</v>
+      </c>
+      <c r="E26" s="22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F26" s="21" t="n"/>
+      <c r="G26" s="9" t="n"/>
       <c r="H26" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="I26" s="9" t="n">
-        <v>1</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="I26" s="9" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>바코드프린터기</t>
+          <t>바코드인쇄기</t>
         </is>
       </c>
       <c r="B27" s="10" t="inlineStr">
@@ -1280,23 +1303,27 @@
         </is>
       </c>
       <c r="C27" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="D27" s="17" t="n">
-        <v>4000</v>
-      </c>
-      <c r="E27" s="17" t="n"/>
-      <c r="F27" s="17" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="D27" s="21" t="n">
+        <v>3300</v>
+      </c>
+      <c r="E27" s="21" t="n">
+        <v>4500</v>
+      </c>
+      <c r="F27" s="22" t="n">
+        <v>5000</v>
+      </c>
       <c r="G27" s="9" t="n"/>
-      <c r="H27" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="I27" s="9" t="n"/>
+      <c r="H27" s="9" t="n"/>
+      <c r="I27" s="9" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>바코드프린터라벨</t>
+          <t>바코드출력기</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
@@ -1305,25 +1332,31 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="D28" s="17" t="n">
-        <v>1100</v>
-      </c>
-      <c r="E28" s="17" t="n"/>
-      <c r="F28" s="17" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="D28" s="21" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E28" s="21" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F28" s="22" t="n">
+        <v>4000</v>
+      </c>
       <c r="G28" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="I28" s="9" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="I28" s="9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>바코드프린터전문업체</t>
+          <t>바코드프린터기</t>
         </is>
       </c>
       <c r="B29" s="10" t="inlineStr">
@@ -1332,23 +1365,25 @@
         </is>
       </c>
       <c r="C29" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="D29" s="17" t="n">
-        <v>700</v>
-      </c>
-      <c r="E29" s="17" t="n"/>
-      <c r="F29" s="17" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="D29" s="21" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E29" s="22" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F29" s="21" t="n"/>
       <c r="G29" s="9" t="n"/>
       <c r="H29" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I29" s="9" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>바코드프린터추천</t>
+          <t>바코드프린터라벨</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
@@ -1359,23 +1394,23 @@
       <c r="C30" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="D30" s="17" t="n">
-        <v>1700</v>
-      </c>
-      <c r="E30" s="17" t="n"/>
-      <c r="F30" s="17" t="n"/>
-      <c r="G30" s="9" t="n"/>
+      <c r="D30" s="21" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E30" s="21" t="n"/>
+      <c r="F30" s="21" t="n"/>
+      <c r="G30" s="9" t="n">
+        <v>7</v>
+      </c>
       <c r="H30" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="I30" s="9" t="n">
-        <v>1</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="I30" s="9" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>바코드프린터판매</t>
+          <t>바코드프린터전문업체</t>
         </is>
       </c>
       <c r="B31" s="10" t="inlineStr">
@@ -1386,11 +1421,13 @@
       <c r="C31" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D31" s="17" t="n">
-        <v>280</v>
-      </c>
-      <c r="E31" s="17" t="n"/>
-      <c r="F31" s="17" t="n"/>
+      <c r="D31" s="21" t="n">
+        <v>700</v>
+      </c>
+      <c r="E31" s="22" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F31" s="21" t="n"/>
       <c r="G31" s="9" t="n"/>
       <c r="H31" s="9" t="n">
         <v>2</v>
@@ -1398,122 +1435,132 @@
       <c r="I31" s="9" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>바코드프린터추천</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="D32" s="21" t="n">
+        <v>1700</v>
+      </c>
+      <c r="E32" s="22" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F32" s="21" t="n"/>
+      <c r="G32" s="9" t="n"/>
+      <c r="H32" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="I32" s="9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>바코드프린터판매</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D33" s="21" t="n">
+        <v>280</v>
+      </c>
+      <c r="E33" s="22" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F33" s="21" t="n"/>
+      <c r="G33" s="9" t="n"/>
+      <c r="H33" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I33" s="9" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>바코드프린터프로그램</t>
         </is>
       </c>
-      <c r="B32" s="7" t="n"/>
-      <c r="C32" s="7" t="n">
+      <c r="B34" s="7" t="n"/>
+      <c r="C34" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="D32" s="16" t="n">
+      <c r="D34" s="19" t="n">
         <v>2750</v>
       </c>
-      <c r="E32" s="16" t="n"/>
-      <c r="F32" s="16" t="n"/>
-      <c r="G32" s="7" t="n">
+      <c r="E34" s="19" t="n"/>
+      <c r="F34" s="19" t="n"/>
+      <c r="G34" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="H32" s="7" t="n"/>
-      <c r="I32" s="7" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+      <c r="H34" s="7" t="n"/>
+      <c r="I34" s="7" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>빅솔론</t>
         </is>
       </c>
-      <c r="B33" s="7" t="n"/>
-      <c r="C33" s="7" t="n">
+      <c r="B35" s="7" t="n"/>
+      <c r="C35" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="D33" s="16" t="n">
+      <c r="D35" s="20" t="n">
         <v>800</v>
       </c>
-      <c r="E33" s="16" t="n"/>
-      <c r="F33" s="16" t="n"/>
-      <c r="G33" s="7" t="n">
+      <c r="E35" s="23" t="n">
+        <v>300</v>
+      </c>
+      <c r="F35" s="19" t="n"/>
+      <c r="G35" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="H33" s="7" t="n"/>
-      <c r="I33" s="7" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="H35" s="7" t="n"/>
+      <c r="I35" s="7" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>빅솔론총판</t>
         </is>
       </c>
-      <c r="B34" s="10" t="inlineStr">
+      <c r="B36" s="10" t="inlineStr">
         <is>
           <t>수정필요</t>
         </is>
       </c>
-      <c r="C34" s="9" t="n">
+      <c r="C36" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D34" s="17" t="n">
+      <c r="D36" s="21" t="n">
         <v>70</v>
       </c>
-      <c r="E34" s="17" t="n"/>
-      <c r="F34" s="17" t="n"/>
-      <c r="G34" s="9" t="n"/>
-      <c r="H34" s="9" t="n"/>
-      <c r="I34" s="9" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="8" t="inlineStr">
-        <is>
-          <t>빅솔론프린터</t>
-        </is>
-      </c>
-      <c r="B35" s="10" t="inlineStr">
-        <is>
-          <t>수정필요</t>
-        </is>
-      </c>
-      <c r="C35" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="D35" s="17" t="n">
-        <v>940</v>
-      </c>
-      <c r="E35" s="17" t="n"/>
-      <c r="F35" s="17" t="n"/>
-      <c r="G35" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="H35" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="I35" s="9" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>산업용라벨프린터</t>
-        </is>
-      </c>
-      <c r="B36" s="7" t="n"/>
-      <c r="C36" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="D36" s="16" t="n">
-        <v>5000</v>
-      </c>
-      <c r="E36" s="16" t="n"/>
-      <c r="F36" s="16" t="n"/>
-      <c r="G36" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="H36" s="7" t="n"/>
-      <c r="I36" s="7" t="n"/>
+      <c r="E36" s="21" t="n"/>
+      <c r="F36" s="21" t="n"/>
+      <c r="G36" s="9" t="n"/>
+      <c r="H36" s="9" t="n"/>
+      <c r="I36" s="9" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>산업용바코드프린터</t>
+          <t>빅솔론프린터</t>
         </is>
       </c>
       <c r="B37" s="10" t="inlineStr">
@@ -1524,46 +1571,48 @@
       <c r="C37" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D37" s="17" t="n">
-        <v>800</v>
-      </c>
-      <c r="E37" s="17" t="n"/>
-      <c r="F37" s="17" t="n"/>
-      <c r="G37" s="9" t="n"/>
-      <c r="H37" s="9" t="n"/>
+      <c r="D37" s="21" t="n">
+        <v>940</v>
+      </c>
+      <c r="E37" s="22" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F37" s="21" t="n"/>
+      <c r="G37" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="H37" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="I37" s="9" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="8" t="inlineStr">
-        <is>
-          <t>산업용프린터</t>
-        </is>
-      </c>
-      <c r="B38" s="10" t="inlineStr">
-        <is>
-          <t>수정필요</t>
-        </is>
-      </c>
-      <c r="C38" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="D38" s="17" t="n">
-        <v>6500</v>
-      </c>
-      <c r="E38" s="17" t="n"/>
-      <c r="F38" s="17" t="n"/>
-      <c r="G38" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="I38" s="9" t="n"/>
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>산업용라벨프린터</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="n"/>
+      <c r="C38" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D38" s="19" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E38" s="20" t="n">
+        <v>8500</v>
+      </c>
+      <c r="F38" s="19" t="n"/>
+      <c r="G38" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="H38" s="7" t="n"/>
+      <c r="I38" s="7" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>소형바코드프린터</t>
+          <t>산업용바코드프린터</t>
         </is>
       </c>
       <c r="B39" s="10" t="inlineStr">
@@ -1572,25 +1621,23 @@
         </is>
       </c>
       <c r="C39" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="D39" s="17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E39" s="17" t="n"/>
-      <c r="F39" s="17" t="n"/>
-      <c r="G39" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="H39" s="9" t="n">
-        <v>5</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="D39" s="21" t="n">
+        <v>800</v>
+      </c>
+      <c r="E39" s="22" t="n">
+        <v>3500</v>
+      </c>
+      <c r="F39" s="21" t="n"/>
+      <c r="G39" s="9" t="n"/>
+      <c r="H39" s="9" t="n"/>
       <c r="I39" s="9" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>스티커라벨기</t>
+          <t>산업용프린터</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
@@ -1599,44 +1646,56 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="D40" s="17" t="n">
-        <v>2300</v>
-      </c>
-      <c r="E40" s="17" t="n"/>
-      <c r="F40" s="17" t="n"/>
-      <c r="G40" s="9" t="n"/>
-      <c r="H40" s="9" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="D40" s="21" t="n">
+        <v>6500</v>
+      </c>
+      <c r="E40" s="22" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F40" s="21" t="n"/>
+      <c r="G40" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="I40" s="9" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>스티커인쇄기</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="n"/>
-      <c r="C41" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="D41" s="16" t="n">
-        <v>800</v>
-      </c>
-      <c r="E41" s="16" t="n"/>
-      <c r="F41" s="16" t="n"/>
-      <c r="G41" s="7" t="n"/>
-      <c r="H41" s="7" t="n">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>소형바코드프린터</t>
+        </is>
+      </c>
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="D41" s="21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E41" s="22" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F41" s="21" t="n"/>
+      <c r="G41" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="H41" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="I41" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="I41" s="9" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>스티커출력기</t>
+          <t>스티커라벨기</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
@@ -1645,50 +1704,48 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="D42" s="17" t="n">
-        <v>400</v>
-      </c>
-      <c r="E42" s="17" t="n"/>
-      <c r="F42" s="17" t="n"/>
-      <c r="G42" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="H42" s="9" t="n">
-        <v>1</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="D42" s="22" t="n">
+        <v>2300</v>
+      </c>
+      <c r="E42" s="21" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="9" t="n"/>
+      <c r="H42" s="9" t="n"/>
       <c r="I42" s="9" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="8" t="inlineStr">
-        <is>
-          <t>스티커프린터</t>
-        </is>
-      </c>
-      <c r="B43" s="10" t="inlineStr">
-        <is>
-          <t>수정필요</t>
-        </is>
-      </c>
-      <c r="C43" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="D43" s="17" t="n">
-        <v>1340</v>
-      </c>
-      <c r="E43" s="17" t="n"/>
-      <c r="F43" s="17" t="n"/>
-      <c r="G43" s="9" t="n"/>
-      <c r="H43" s="9" t="n"/>
-      <c r="I43" s="9" t="n">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>스티커인쇄기</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="n"/>
+      <c r="C43" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D43" s="19" t="n">
+        <v>800</v>
+      </c>
+      <c r="E43" s="20" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F43" s="19" t="n"/>
+      <c r="G43" s="7" t="n"/>
+      <c r="H43" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="I43" s="7" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>열전사프린터</t>
+          <t>스티커출력기</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
@@ -1697,21 +1754,27 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D44" s="21" t="n">
+        <v>400</v>
+      </c>
+      <c r="E44" s="22" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F44" s="21" t="n"/>
+      <c r="G44" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="D44" s="17" t="n">
-        <v>5500</v>
-      </c>
-      <c r="E44" s="17" t="n"/>
-      <c r="F44" s="17" t="n"/>
-      <c r="G44" s="9" t="n"/>
-      <c r="H44" s="9" t="n"/>
+      <c r="H44" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="I44" s="9" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>열전사프린터기</t>
+          <t>스티커프린터</t>
         </is>
       </c>
       <c r="B45" s="10" t="inlineStr">
@@ -1720,25 +1783,25 @@
         </is>
       </c>
       <c r="C45" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="D45" s="17" t="n">
-        <v>450</v>
-      </c>
-      <c r="E45" s="17" t="n"/>
-      <c r="F45" s="17" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="D45" s="21" t="n">
+        <v>1340</v>
+      </c>
+      <c r="E45" s="22" t="n">
+        <v>3500</v>
+      </c>
+      <c r="F45" s="21" t="n"/>
       <c r="G45" s="9" t="n"/>
-      <c r="H45" s="9" t="n">
-        <v>8</v>
-      </c>
+      <c r="H45" s="9" t="n"/>
       <c r="I45" s="9" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>영수증프린터</t>
+          <t>열전사프린터</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
@@ -1747,46 +1810,56 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="D46" s="21" t="n">
+        <v>5500</v>
+      </c>
+      <c r="E46" s="22" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F46" s="21" t="n">
+        <v>4550</v>
+      </c>
+      <c r="G46" s="9" t="n"/>
+      <c r="H46" s="9" t="n"/>
+      <c r="I46" s="9" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>열전사프린터기</t>
+        </is>
+      </c>
+      <c r="B47" s="10" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="D47" s="21" t="n">
+        <v>450</v>
+      </c>
+      <c r="E47" s="22" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F47" s="21" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G47" s="9" t="n"/>
+      <c r="H47" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="D46" s="17" t="n">
-        <v>1070</v>
-      </c>
-      <c r="E46" s="17" t="n"/>
-      <c r="F46" s="17" t="n"/>
-      <c r="G46" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H46" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="I46" s="9" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>제브라</t>
-        </is>
-      </c>
-      <c r="B47" s="7" t="n"/>
-      <c r="C47" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="D47" s="16" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E47" s="16" t="n"/>
-      <c r="F47" s="16" t="n"/>
-      <c r="G47" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="H47" s="7" t="n"/>
-      <c r="I47" s="7" t="n"/>
+      <c r="I47" s="9" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>제브라라벨프린터</t>
+          <t>영수증프린터</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
@@ -1795,48 +1868,48 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="D48" s="17" t="n">
-        <v>700</v>
-      </c>
-      <c r="E48" s="17" t="n"/>
-      <c r="F48" s="17" t="n"/>
-      <c r="G48" s="9" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="D48" s="21" t="n">
+        <v>1070</v>
+      </c>
+      <c r="E48" s="22" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F48" s="21" t="n"/>
+      <c r="G48" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="H48" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I48" s="9" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="8" t="inlineStr">
-        <is>
-          <t>제브라바코드프린터</t>
-        </is>
-      </c>
-      <c r="B49" s="10" t="inlineStr">
-        <is>
-          <t>수정필요</t>
-        </is>
-      </c>
-      <c r="C49" s="9" t="n">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>제브라</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="n"/>
+      <c r="C49" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="D49" s="17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E49" s="17" t="n"/>
-      <c r="F49" s="17" t="n"/>
-      <c r="G49" s="9" t="n"/>
-      <c r="H49" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="I49" s="9" t="n"/>
+      <c r="D49" s="19" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E49" s="19" t="n"/>
+      <c r="F49" s="19" t="n"/>
+      <c r="G49" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H49" s="7" t="n"/>
+      <c r="I49" s="7" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>제브라프린터</t>
+          <t>제브라라벨프린터</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
@@ -1847,21 +1920,23 @@
       <c r="C50" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D50" s="17" t="n">
-        <v>1410</v>
-      </c>
-      <c r="E50" s="17" t="n"/>
-      <c r="F50" s="17" t="n"/>
+      <c r="D50" s="21" t="n">
+        <v>700</v>
+      </c>
+      <c r="E50" s="22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F50" s="21" t="n"/>
       <c r="G50" s="9" t="n"/>
       <c r="H50" s="9" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I50" s="9" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>카드프린터기</t>
+          <t>제브라바코드프린터</t>
         </is>
       </c>
       <c r="B51" s="10" t="inlineStr">
@@ -1872,33 +1947,434 @@
       <c r="C51" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="D51" s="17" t="n">
+      <c r="D51" s="21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E51" s="22" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F51" s="21" t="n"/>
+      <c r="G51" s="9" t="n"/>
+      <c r="H51" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="I51" s="9" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>제브라프린터</t>
+        </is>
+      </c>
+      <c r="B52" s="10" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="D52" s="21" t="n">
+        <v>1410</v>
+      </c>
+      <c r="E52" s="22" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F52" s="21" t="n"/>
+      <c r="G52" s="9" t="n"/>
+      <c r="H52" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I52" s="9" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>카드프린터기</t>
+        </is>
+      </c>
+      <c r="B53" s="10" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D53" s="23" t="n">
         <v>70</v>
       </c>
-      <c r="E51" s="17" t="n"/>
-      <c r="F51" s="17" t="n"/>
-      <c r="G51" s="9" t="n"/>
-      <c r="H51" s="9" t="n"/>
-      <c r="I51" s="9" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="6" t="inlineStr">
+      <c r="E53" s="21" t="n"/>
+      <c r="F53" s="21" t="n"/>
+      <c r="G53" s="9" t="n"/>
+      <c r="H53" s="9" t="n"/>
+      <c r="I53" s="9" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
         <is>
           <t>프린터관리</t>
         </is>
       </c>
-      <c r="B52" s="7" t="n"/>
-      <c r="C52" s="7" t="n">
+      <c r="B54" s="7" t="n"/>
+      <c r="C54" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="D52" s="16" t="n">
+      <c r="D54" s="23" t="n">
         <v>200</v>
       </c>
-      <c r="E52" s="16" t="n"/>
-      <c r="F52" s="16" t="n"/>
-      <c r="G52" s="7" t="n"/>
-      <c r="H52" s="7" t="n"/>
-      <c r="I52" s="7" t="n"/>
+      <c r="E54" s="19" t="n"/>
+      <c r="F54" s="19" t="n"/>
+      <c r="G54" s="7" t="n"/>
+      <c r="H54" s="7" t="n"/>
+      <c r="I54" s="7" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="16" t="inlineStr">
+        <is>
+          <t>솔바텍에 없는 키워드 (20개)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>B-FV4T</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="n"/>
+      <c r="C56" s="7" t="n"/>
+      <c r="D56" s="19" t="n"/>
+      <c r="E56" s="19" t="n"/>
+      <c r="F56" s="19" t="n">
+        <v>850</v>
+      </c>
+      <c r="G56" s="7" t="n"/>
+      <c r="H56" s="7" t="n"/>
+      <c r="I56" s="7" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>B-FV4T-GS</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="n"/>
+      <c r="C57" s="7" t="n"/>
+      <c r="D57" s="19" t="n"/>
+      <c r="E57" s="19" t="n"/>
+      <c r="F57" s="19" t="n">
+        <v>90</v>
+      </c>
+      <c r="G57" s="7" t="n"/>
+      <c r="H57" s="7" t="n"/>
+      <c r="I57" s="7" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>B-FV4T-TS</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="n"/>
+      <c r="C58" s="7" t="n"/>
+      <c r="D58" s="19" t="n"/>
+      <c r="E58" s="19" t="n"/>
+      <c r="F58" s="19" t="n">
+        <v>70</v>
+      </c>
+      <c r="G58" s="7" t="n"/>
+      <c r="H58" s="7" t="n"/>
+      <c r="I58" s="7" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>G530+</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="n"/>
+      <c r="C59" s="7" t="n"/>
+      <c r="D59" s="19" t="n"/>
+      <c r="E59" s="19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F59" s="19" t="n"/>
+      <c r="G59" s="7" t="n"/>
+      <c r="H59" s="7" t="n"/>
+      <c r="I59" s="7" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>SLPTX400</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="n"/>
+      <c r="C60" s="7" t="n"/>
+      <c r="D60" s="19" t="n"/>
+      <c r="E60" s="19" t="n"/>
+      <c r="F60" s="19" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G60" s="7" t="n"/>
+      <c r="H60" s="7" t="n"/>
+      <c r="I60" s="7" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>SLPTX403</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="n"/>
+      <c r="C61" s="7" t="n"/>
+      <c r="D61" s="19" t="n"/>
+      <c r="E61" s="19" t="n"/>
+      <c r="F61" s="19" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G61" s="7" t="n"/>
+      <c r="H61" s="7" t="n"/>
+      <c r="I61" s="7" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>TSC프린터</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="n"/>
+      <c r="C62" s="7" t="n"/>
+      <c r="D62" s="19" t="n"/>
+      <c r="E62" s="23" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F62" s="19" t="n"/>
+      <c r="G62" s="7" t="n"/>
+      <c r="H62" s="7" t="n"/>
+      <c r="I62" s="7" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>고덱스</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="n"/>
+      <c r="C63" s="7" t="n"/>
+      <c r="D63" s="19" t="n"/>
+      <c r="E63" s="19" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F63" s="19" t="n"/>
+      <c r="G63" s="7" t="n"/>
+      <c r="H63" s="7" t="n"/>
+      <c r="I63" s="7" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>라벨발행기</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="n"/>
+      <c r="C64" s="7" t="n"/>
+      <c r="D64" s="19" t="n"/>
+      <c r="E64" s="19" t="n">
+        <v>2620</v>
+      </c>
+      <c r="F64" s="19" t="n"/>
+      <c r="G64" s="7" t="n"/>
+      <c r="H64" s="7" t="n"/>
+      <c r="I64" s="7" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>라벨프린터기</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="n"/>
+      <c r="C65" s="7" t="n"/>
+      <c r="D65" s="19" t="n"/>
+      <c r="E65" s="19" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F65" s="19" t="n"/>
+      <c r="G65" s="7" t="n"/>
+      <c r="H65" s="7" t="n"/>
+      <c r="I65" s="7" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>라벨프린터용지</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="n"/>
+      <c r="C66" s="7" t="n"/>
+      <c r="D66" s="19" t="n"/>
+      <c r="E66" s="19" t="n">
+        <v>2100</v>
+      </c>
+      <c r="F66" s="19" t="n"/>
+      <c r="G66" s="7" t="n"/>
+      <c r="H66" s="7" t="n"/>
+      <c r="I66" s="7" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>롤프린터</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="n"/>
+      <c r="C67" s="7" t="n"/>
+      <c r="D67" s="19" t="n"/>
+      <c r="E67" s="19" t="n">
+        <v>1100</v>
+      </c>
+      <c r="F67" s="19" t="n"/>
+      <c r="G67" s="7" t="n"/>
+      <c r="H67" s="7" t="n"/>
+      <c r="I67" s="7" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>바코드구입</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="n"/>
+      <c r="C68" s="7" t="n"/>
+      <c r="D68" s="19" t="n"/>
+      <c r="E68" s="19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F68" s="19" t="n"/>
+      <c r="G68" s="7" t="n"/>
+      <c r="H68" s="7" t="n"/>
+      <c r="I68" s="7" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>바코드등록</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="n"/>
+      <c r="C69" s="7" t="n"/>
+      <c r="D69" s="19" t="n"/>
+      <c r="E69" s="19" t="n">
+        <v>2200</v>
+      </c>
+      <c r="F69" s="19" t="n"/>
+      <c r="G69" s="7" t="n"/>
+      <c r="H69" s="7" t="n"/>
+      <c r="I69" s="7" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>바코드라벨프린터기</t>
+        </is>
+      </c>
+      <c r="B70" s="7" t="n"/>
+      <c r="C70" s="7" t="n"/>
+      <c r="D70" s="19" t="n"/>
+      <c r="E70" s="19" t="n">
+        <v>1700</v>
+      </c>
+      <c r="F70" s="19" t="n"/>
+      <c r="G70" s="7" t="n"/>
+      <c r="H70" s="7" t="n"/>
+      <c r="I70" s="7" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>바코드생성</t>
+        </is>
+      </c>
+      <c r="B71" s="7" t="n"/>
+      <c r="C71" s="7" t="n"/>
+      <c r="D71" s="19" t="n"/>
+      <c r="E71" s="19" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F71" s="19" t="n"/>
+      <c r="G71" s="7" t="n"/>
+      <c r="H71" s="7" t="n"/>
+      <c r="I71" s="7" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>바코드프린트</t>
+        </is>
+      </c>
+      <c r="B72" s="7" t="n"/>
+      <c r="C72" s="7" t="n"/>
+      <c r="D72" s="19" t="n"/>
+      <c r="E72" s="19" t="n">
+        <v>1520</v>
+      </c>
+      <c r="F72" s="19" t="n"/>
+      <c r="G72" s="7" t="n"/>
+      <c r="H72" s="7" t="n"/>
+      <c r="I72" s="7" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>산업용바코드</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="n"/>
+      <c r="C73" s="7" t="n"/>
+      <c r="D73" s="19" t="n"/>
+      <c r="E73" s="19" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F73" s="19" t="n"/>
+      <c r="G73" s="7" t="n"/>
+      <c r="H73" s="7" t="n"/>
+      <c r="I73" s="7" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>소형라벨프린터</t>
+        </is>
+      </c>
+      <c r="B74" s="7" t="n"/>
+      <c r="C74" s="7" t="n"/>
+      <c r="D74" s="19" t="n"/>
+      <c r="E74" s="19" t="n">
+        <v>3500</v>
+      </c>
+      <c r="F74" s="19" t="n"/>
+      <c r="G74" s="7" t="n"/>
+      <c r="H74" s="7" t="n"/>
+      <c r="I74" s="7" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>지브라프린터</t>
+        </is>
+      </c>
+      <c r="B75" s="7" t="n"/>
+      <c r="C75" s="7" t="n"/>
+      <c r="D75" s="19" t="n"/>
+      <c r="E75" s="19" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F75" s="19" t="n"/>
+      <c r="G75" s="7" t="n"/>
+      <c r="H75" s="7" t="n"/>
+      <c r="I75" s="7" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:I52"/>
@@ -1947,23 +2423,23 @@
           <t>입찰가 변경 전</t>
         </is>
       </c>
-      <c r="C1" s="18" t="n"/>
-      <c r="D1" s="18" t="n"/>
-      <c r="E1" s="18" t="n"/>
-      <c r="F1" s="18" t="n"/>
-      <c r="G1" s="19" t="n"/>
+      <c r="C1" s="25" t="n"/>
+      <c r="D1" s="25" t="n"/>
+      <c r="E1" s="25" t="n"/>
+      <c r="F1" s="25" t="n"/>
+      <c r="G1" s="26" t="n"/>
       <c r="H1" s="4" t="inlineStr">
         <is>
           <t>입찰가 변경 후</t>
         </is>
       </c>
-      <c r="I1" s="18" t="n"/>
-      <c r="J1" s="18" t="n"/>
-      <c r="K1" s="18" t="n"/>
-      <c r="L1" s="19" t="n"/>
+      <c r="I1" s="25" t="n"/>
+      <c r="J1" s="25" t="n"/>
+      <c r="K1" s="25" t="n"/>
+      <c r="L1" s="26" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="20" t="n"/>
+      <c r="A2" s="27" t="n"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>현재 입찰가</t>

--- a/솔바텍_URL도메인변경완료_순위반영_20261029.xlsx
+++ b/솔바텍_URL도메인변경완료_순위반영_20261029.xlsx
@@ -224,13 +224,13 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -611,7 +611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K75"/>
+  <dimension ref="A1:K73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -700,6 +700,29 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>감열식프린터</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="n"/>
+      <c r="C3" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="D3" s="18" t="n">
+        <v>800</v>
+      </c>
+      <c r="E3" s="19" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F3" s="18" t="n"/>
+      <c r="G3" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="I3" s="7" t="n"/>
       <c r="K3" s="16" t="inlineStr">
         <is>
           <t>굵은 글씨 = 3개 사이트 중 최고 입찰가</t>
@@ -707,68 +730,95 @@
       </c>
     </row>
     <row r="4">
-      <c r="K4" s="18" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>감열프린터</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n"/>
+      <c r="C4" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="D4" s="19" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E4" s="18" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F4" s="18" t="n">
+        <v>1330</v>
+      </c>
+      <c r="G4" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" s="7" t="n"/>
+      <c r="I4" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K4" s="20" t="inlineStr">
         <is>
           <t>빨간 글씨 = 입찰가 수정 대상</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>감열식프린터</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>감열프린터기</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="D5" s="19" t="n">
-        <v>800</v>
-      </c>
-      <c r="E5" s="20" t="n">
+      <c r="D5" s="21" t="n">
+        <v>650</v>
+      </c>
+      <c r="E5" s="21" t="n">
         <v>1500</v>
       </c>
-      <c r="F5" s="19" t="n"/>
-      <c r="G5" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="H5" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="I5" s="7" t="n"/>
+      <c r="F5" s="22" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G5" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="H5" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="I5" s="9" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>감열프린터</t>
+          <t>도시바프린터</t>
         </is>
       </c>
       <c r="B6" s="7" t="n"/>
       <c r="C6" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="D6" s="20" t="n">
-        <v>2000</v>
-      </c>
-      <c r="E6" s="19" t="n">
+      <c r="D6" s="18" t="n">
         <v>1500</v>
       </c>
-      <c r="F6" s="19" t="n">
-        <v>1330</v>
-      </c>
+      <c r="E6" s="18" t="n"/>
+      <c r="F6" s="18" t="n"/>
       <c r="G6" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H6" s="7" t="n"/>
-      <c r="I6" s="7" t="n">
-        <v>5</v>
-      </c>
+      <c r="I6" s="7" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>감열프린터기</t>
+          <t>라밸프린터</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
@@ -780,49 +830,47 @@
         <v>8</v>
       </c>
       <c r="D7" s="21" t="n">
-        <v>650</v>
-      </c>
-      <c r="E7" s="21" t="n">
-        <v>1500</v>
-      </c>
-      <c r="F7" s="22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E7" s="22" t="n">
+        <v>1700</v>
+      </c>
+      <c r="F7" s="21" t="n"/>
+      <c r="G7" s="9" t="n"/>
+      <c r="H7" s="9" t="n"/>
+      <c r="I7" s="9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>라벨기</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D8" s="21" t="n">
         <v>2000</v>
       </c>
-      <c r="G7" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="H7" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="I7" s="9" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>도시바프린터</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="n"/>
-      <c r="C8" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="D8" s="19" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E8" s="19" t="n"/>
-      <c r="F8" s="19" t="n"/>
-      <c r="G8" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="H8" s="7" t="n"/>
-      <c r="I8" s="7" t="n"/>
+      <c r="E8" s="21" t="n"/>
+      <c r="F8" s="22" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G8" s="9" t="n"/>
+      <c r="H8" s="9" t="n"/>
+      <c r="I8" s="9" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>라밸프린터</t>
+          <t>라벨기계</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
@@ -834,22 +882,18 @@
         <v>8</v>
       </c>
       <c r="D9" s="21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E9" s="22" t="n">
-        <v>1700</v>
-      </c>
+        <v>890</v>
+      </c>
+      <c r="E9" s="21" t="n"/>
       <c r="F9" s="21" t="n"/>
       <c r="G9" s="9" t="n"/>
       <c r="H9" s="9" t="n"/>
-      <c r="I9" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="I9" s="9" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>라벨기</t>
+          <t>라벨용지프린터</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
@@ -858,23 +902,23 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D10" s="21" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="E10" s="21" t="n"/>
-      <c r="F10" s="22" t="n">
-        <v>5000</v>
-      </c>
+      <c r="F10" s="21" t="n"/>
       <c r="G10" s="9" t="n"/>
-      <c r="H10" s="9" t="n"/>
+      <c r="H10" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="I10" s="9" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>라벨기계</t>
+          <t>라벨인쇄기</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
@@ -886,18 +930,22 @@
         <v>8</v>
       </c>
       <c r="D11" s="21" t="n">
-        <v>890</v>
-      </c>
-      <c r="E11" s="21" t="n"/>
+        <v>3500</v>
+      </c>
+      <c r="E11" s="22" t="n">
+        <v>5000</v>
+      </c>
       <c r="F11" s="21" t="n"/>
       <c r="G11" s="9" t="n"/>
       <c r="H11" s="9" t="n"/>
-      <c r="I11" s="9" t="n"/>
+      <c r="I11" s="9" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>라벨용지프린터</t>
+          <t>라벨인쇄기계</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
@@ -906,23 +954,23 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D12" s="21" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="E12" s="21" t="n"/>
       <c r="F12" s="21" t="n"/>
       <c r="G12" s="9" t="n"/>
-      <c r="H12" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="I12" s="9" t="n"/>
+      <c r="H12" s="9" t="n"/>
+      <c r="I12" s="9" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>라벨인쇄기</t>
+          <t>라벨지프린터</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
@@ -934,22 +982,22 @@
         <v>8</v>
       </c>
       <c r="D13" s="21" t="n">
-        <v>3500</v>
+        <v>800</v>
       </c>
       <c r="E13" s="22" t="n">
-        <v>5000</v>
+        <v>1790</v>
       </c>
       <c r="F13" s="21" t="n"/>
       <c r="G13" s="9" t="n"/>
-      <c r="H13" s="9" t="n"/>
-      <c r="I13" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="H13" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="I13" s="9" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>라벨인쇄기계</t>
+          <t>라벨출력기</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
@@ -961,20 +1009,22 @@
         <v>8</v>
       </c>
       <c r="D14" s="21" t="n">
-        <v>600</v>
+        <v>1110</v>
       </c>
       <c r="E14" s="21" t="n"/>
       <c r="F14" s="21" t="n"/>
-      <c r="G14" s="9" t="n"/>
-      <c r="H14" s="9" t="n"/>
-      <c r="I14" s="9" t="n">
+      <c r="G14" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="H14" s="9" t="n">
         <v>2</v>
       </c>
+      <c r="I14" s="9" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>라벨지프린터</t>
+          <t>라벨프린터업체</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -986,22 +1036,20 @@
         <v>8</v>
       </c>
       <c r="D15" s="21" t="n">
-        <v>800</v>
-      </c>
-      <c r="E15" s="22" t="n">
-        <v>1790</v>
-      </c>
+        <v>530</v>
+      </c>
+      <c r="E15" s="21" t="n"/>
       <c r="F15" s="21" t="n"/>
       <c r="G15" s="9" t="n"/>
       <c r="H15" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I15" s="9" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>라벨출력기</t>
+          <t>라벨프린터추천</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
@@ -1013,7 +1061,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="21" t="n">
-        <v>1110</v>
+        <v>1580</v>
       </c>
       <c r="E16" s="21" t="n"/>
       <c r="F16" s="21" t="n"/>
@@ -1021,14 +1069,14 @@
         <v>7</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I16" s="9" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>라벨프린터업체</t>
+          <t>롤라벨인쇄기</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
@@ -1040,20 +1088,22 @@
         <v>8</v>
       </c>
       <c r="D17" s="21" t="n">
-        <v>530</v>
-      </c>
-      <c r="E17" s="21" t="n"/>
+        <v>70</v>
+      </c>
+      <c r="E17" s="22" t="n">
+        <v>4000</v>
+      </c>
       <c r="F17" s="21" t="n"/>
       <c r="G17" s="9" t="n"/>
       <c r="H17" s="9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I17" s="9" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>라벨프린터추천</t>
+          <t>롤라벨출력기</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -1062,25 +1112,25 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D18" s="21" t="n">
-        <v>1580</v>
-      </c>
-      <c r="E18" s="21" t="n"/>
+        <v>100</v>
+      </c>
+      <c r="E18" s="22" t="n">
+        <v>500</v>
+      </c>
       <c r="F18" s="21" t="n"/>
-      <c r="G18" s="9" t="n">
-        <v>7</v>
-      </c>
+      <c r="G18" s="9" t="n"/>
       <c r="H18" s="9" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I18" s="9" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>롤라벨인쇄기</t>
+          <t>롤라벨프린터</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
@@ -1092,22 +1142,22 @@
         <v>8</v>
       </c>
       <c r="D19" s="21" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="E19" s="22" t="n">
-        <v>4000</v>
+        <v>1500</v>
       </c>
       <c r="F19" s="21" t="n"/>
-      <c r="G19" s="9" t="n"/>
-      <c r="H19" s="9" t="n">
-        <v>1</v>
-      </c>
+      <c r="G19" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="H19" s="9" t="n"/>
       <c r="I19" s="9" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>롤라벨출력기</t>
+          <t>바코드라벨인쇄기</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
@@ -1116,14 +1166,12 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D20" s="21" t="n">
-        <v>100</v>
-      </c>
-      <c r="E20" s="22" t="n">
-        <v>500</v>
-      </c>
+        <v>400</v>
+      </c>
+      <c r="E20" s="21" t="n"/>
       <c r="F20" s="21" t="n"/>
       <c r="G20" s="9" t="n"/>
       <c r="H20" s="9" t="n">
@@ -1134,7 +1182,7 @@
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>롤라벨프린터</t>
+          <t>바코드라벨프린터</t>
         </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
@@ -1146,22 +1194,26 @@
         <v>8</v>
       </c>
       <c r="D21" s="21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E21" s="22" t="n">
-        <v>1500</v>
-      </c>
-      <c r="F21" s="21" t="n"/>
+        <v>3000</v>
+      </c>
+      <c r="E21" s="21" t="n">
+        <v>4460</v>
+      </c>
+      <c r="F21" s="22" t="n">
+        <v>5000</v>
+      </c>
       <c r="G21" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="H21" s="9" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="H21" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="I21" s="9" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>바코드라벨인쇄기</t>
+          <t>바코드라벨프린터업체</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
@@ -1170,10 +1222,10 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D22" s="21" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E22" s="21" t="n"/>
       <c r="F22" s="21" t="n"/>
@@ -1186,7 +1238,7 @@
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>바코드라벨프린터</t>
+          <t>바코드만들기</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
@@ -1195,29 +1247,23 @@
         </is>
       </c>
       <c r="C23" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="D23" s="21" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E23" s="21" t="n">
-        <v>4460</v>
-      </c>
-      <c r="F23" s="22" t="n">
-        <v>5000</v>
-      </c>
-      <c r="G23" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="H23" s="9" t="n">
-        <v>4</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="D23" s="23" t="n">
+        <v>500</v>
+      </c>
+      <c r="E23" s="24" t="n">
+        <v>910</v>
+      </c>
+      <c r="F23" s="21" t="n"/>
+      <c r="G23" s="9" t="n"/>
+      <c r="H23" s="9" t="n"/>
       <c r="I23" s="9" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>바코드라벨프린터업체</t>
+          <t>바코드발행기</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
@@ -1226,12 +1272,14 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D24" s="21" t="n">
-        <v>300</v>
-      </c>
-      <c r="E24" s="21" t="n"/>
+        <v>400</v>
+      </c>
+      <c r="E24" s="22" t="n">
+        <v>1000</v>
+      </c>
       <c r="F24" s="21" t="n"/>
       <c r="G24" s="9" t="n"/>
       <c r="H24" s="9" t="n">
@@ -1242,7 +1290,7 @@
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>바코드만들기</t>
+          <t>바코드인쇄기</t>
         </is>
       </c>
       <c r="B25" s="10" t="inlineStr">
@@ -1251,23 +1299,27 @@
         </is>
       </c>
       <c r="C25" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="D25" s="23" t="n">
-        <v>500</v>
-      </c>
-      <c r="E25" s="24" t="n">
-        <v>910</v>
-      </c>
-      <c r="F25" s="21" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="D25" s="21" t="n">
+        <v>3300</v>
+      </c>
+      <c r="E25" s="21" t="n">
+        <v>4500</v>
+      </c>
+      <c r="F25" s="22" t="n">
+        <v>5000</v>
+      </c>
       <c r="G25" s="9" t="n"/>
       <c r="H25" s="9" t="n"/>
-      <c r="I25" s="9" t="n"/>
+      <c r="I25" s="9" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>바코드발행기</t>
+          <t>바코드출력기</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
@@ -1276,25 +1328,31 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D26" s="21" t="n">
-        <v>400</v>
-      </c>
-      <c r="E26" s="22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F26" s="21" t="n"/>
-      <c r="G26" s="9" t="n"/>
+        <v>2500</v>
+      </c>
+      <c r="E26" s="21" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F26" s="22" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G26" s="9" t="n">
+        <v>8</v>
+      </c>
       <c r="H26" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="I26" s="9" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="I26" s="9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>바코드인쇄기</t>
+          <t>바코드프린터기</t>
         </is>
       </c>
       <c r="B27" s="10" t="inlineStr">
@@ -1303,27 +1361,25 @@
         </is>
       </c>
       <c r="C27" s="9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D27" s="21" t="n">
-        <v>3300</v>
-      </c>
-      <c r="E27" s="21" t="n">
-        <v>4500</v>
-      </c>
-      <c r="F27" s="22" t="n">
-        <v>5000</v>
-      </c>
+        <v>4000</v>
+      </c>
+      <c r="E27" s="22" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F27" s="21" t="n"/>
       <c r="G27" s="9" t="n"/>
-      <c r="H27" s="9" t="n"/>
-      <c r="I27" s="9" t="n">
-        <v>7</v>
-      </c>
+      <c r="H27" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="9" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>바코드출력기</t>
+          <t>바코드프린터라벨</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
@@ -1332,31 +1388,25 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D28" s="21" t="n">
-        <v>2500</v>
-      </c>
-      <c r="E28" s="21" t="n">
-        <v>3000</v>
-      </c>
-      <c r="F28" s="22" t="n">
-        <v>4000</v>
-      </c>
+        <v>1100</v>
+      </c>
+      <c r="E28" s="21" t="n"/>
+      <c r="F28" s="21" t="n"/>
       <c r="G28" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="I28" s="9" t="n">
-        <v>1</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="I28" s="9" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>바코드프린터기</t>
+          <t>바코드프린터전문업체</t>
         </is>
       </c>
       <c r="B29" s="10" t="inlineStr">
@@ -1365,25 +1415,25 @@
         </is>
       </c>
       <c r="C29" s="9" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D29" s="21" t="n">
-        <v>4000</v>
+        <v>700</v>
       </c>
       <c r="E29" s="22" t="n">
-        <v>15000</v>
+        <v>2000</v>
       </c>
       <c r="F29" s="21" t="n"/>
       <c r="G29" s="9" t="n"/>
       <c r="H29" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I29" s="9" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>바코드프린터라벨</t>
+          <t>바코드프린터추천</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
@@ -1395,22 +1445,24 @@
         <v>7</v>
       </c>
       <c r="D30" s="21" t="n">
-        <v>1100</v>
-      </c>
-      <c r="E30" s="21" t="n"/>
+        <v>1700</v>
+      </c>
+      <c r="E30" s="22" t="n">
+        <v>2000</v>
+      </c>
       <c r="F30" s="21" t="n"/>
-      <c r="G30" s="9" t="n">
+      <c r="G30" s="9" t="n"/>
+      <c r="H30" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="H30" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="I30" s="9" t="n"/>
+      <c r="I30" s="9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>바코드프린터전문업체</t>
+          <t>바코드프린터판매</t>
         </is>
       </c>
       <c r="B31" s="10" t="inlineStr">
@@ -1422,7 +1474,7 @@
         <v>3</v>
       </c>
       <c r="D31" s="21" t="n">
-        <v>700</v>
+        <v>280</v>
       </c>
       <c r="E31" s="22" t="n">
         <v>2000</v>
@@ -1435,132 +1487,128 @@
       <c r="I31" s="9" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t>바코드프린터추천</t>
-        </is>
-      </c>
-      <c r="B32" s="10" t="inlineStr">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>바코드프린터프로그램</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="n"/>
+      <c r="C32" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D32" s="18" t="n">
+        <v>2750</v>
+      </c>
+      <c r="E32" s="18" t="n"/>
+      <c r="F32" s="18" t="n"/>
+      <c r="G32" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H32" s="7" t="n"/>
+      <c r="I32" s="7" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>빅솔론</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="n"/>
+      <c r="C33" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D33" s="19" t="n">
+        <v>800</v>
+      </c>
+      <c r="E33" s="23" t="n">
+        <v>300</v>
+      </c>
+      <c r="F33" s="18" t="n"/>
+      <c r="G33" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H33" s="7" t="n"/>
+      <c r="I33" s="7" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>빅솔론총판</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
         <is>
           <t>수정필요</t>
         </is>
       </c>
-      <c r="C32" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="D32" s="21" t="n">
-        <v>1700</v>
-      </c>
-      <c r="E32" s="22" t="n">
-        <v>2000</v>
-      </c>
-      <c r="F32" s="21" t="n"/>
-      <c r="G32" s="9" t="n"/>
-      <c r="H32" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="I32" s="9" t="n">
+      <c r="C34" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" s="21" t="n">
+        <v>70</v>
+      </c>
+      <c r="E34" s="21" t="n"/>
+      <c r="F34" s="21" t="n"/>
+      <c r="G34" s="9" t="n"/>
+      <c r="H34" s="9" t="n"/>
+      <c r="I34" s="9" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>빅솔론프린터</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="D35" s="21" t="n">
+        <v>940</v>
+      </c>
+      <c r="E35" s="22" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F35" s="21" t="n"/>
+      <c r="G35" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="H35" s="9" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="8" t="inlineStr">
-        <is>
-          <t>바코드프린터판매</t>
-        </is>
-      </c>
-      <c r="B33" s="10" t="inlineStr">
-        <is>
-          <t>수정필요</t>
-        </is>
-      </c>
-      <c r="C33" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="D33" s="21" t="n">
-        <v>280</v>
-      </c>
-      <c r="E33" s="22" t="n">
-        <v>2000</v>
-      </c>
-      <c r="F33" s="21" t="n"/>
-      <c r="G33" s="9" t="n"/>
-      <c r="H33" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="I33" s="9" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>바코드프린터프로그램</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="n"/>
-      <c r="C34" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="D34" s="19" t="n">
-        <v>2750</v>
-      </c>
-      <c r="E34" s="19" t="n"/>
-      <c r="F34" s="19" t="n"/>
-      <c r="G34" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="H34" s="7" t="n"/>
-      <c r="I34" s="7" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>빅솔론</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="n"/>
-      <c r="C35" s="7" t="n">
+      <c r="I35" s="9" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>산업용라벨프린터</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="n"/>
+      <c r="C36" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="D35" s="20" t="n">
-        <v>800</v>
-      </c>
-      <c r="E35" s="23" t="n">
-        <v>300</v>
-      </c>
-      <c r="F35" s="19" t="n"/>
-      <c r="G35" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="H35" s="7" t="n"/>
-      <c r="I35" s="7" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="8" t="inlineStr">
-        <is>
-          <t>빅솔론총판</t>
-        </is>
-      </c>
-      <c r="B36" s="10" t="inlineStr">
-        <is>
-          <t>수정필요</t>
-        </is>
-      </c>
-      <c r="C36" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="D36" s="21" t="n">
-        <v>70</v>
-      </c>
-      <c r="E36" s="21" t="n"/>
-      <c r="F36" s="21" t="n"/>
-      <c r="G36" s="9" t="n"/>
-      <c r="H36" s="9" t="n"/>
-      <c r="I36" s="9" t="n"/>
+      <c r="D36" s="18" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E36" s="19" t="n">
+        <v>8500</v>
+      </c>
+      <c r="F36" s="18" t="n"/>
+      <c r="G36" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="H36" s="7" t="n"/>
+      <c r="I36" s="7" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>빅솔론프린터</t>
+          <t>산업용바코드프린터</t>
         </is>
       </c>
       <c r="B37" s="10" t="inlineStr">
@@ -1572,47 +1620,49 @@
         <v>10</v>
       </c>
       <c r="D37" s="21" t="n">
-        <v>940</v>
+        <v>800</v>
       </c>
       <c r="E37" s="22" t="n">
-        <v>4000</v>
+        <v>3500</v>
       </c>
       <c r="F37" s="21" t="n"/>
-      <c r="G37" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="H37" s="9" t="n">
+      <c r="G37" s="9" t="n"/>
+      <c r="H37" s="9" t="n"/>
+      <c r="I37" s="9" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>산업용프린터</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="D38" s="21" t="n">
+        <v>6500</v>
+      </c>
+      <c r="E38" s="22" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F38" s="21" t="n"/>
+      <c r="G38" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I37" s="9" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>산업용라벨프린터</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="n"/>
-      <c r="C38" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="D38" s="19" t="n">
-        <v>5000</v>
-      </c>
-      <c r="E38" s="20" t="n">
-        <v>8500</v>
-      </c>
-      <c r="F38" s="19" t="n"/>
-      <c r="G38" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="H38" s="7" t="n"/>
-      <c r="I38" s="7" t="n"/>
+      <c r="H38" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I38" s="9" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>산업용바코드프린터</t>
+          <t>소형바코드프린터</t>
         </is>
       </c>
       <c r="B39" s="10" t="inlineStr">
@@ -1621,23 +1671,27 @@
         </is>
       </c>
       <c r="C39" s="9" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D39" s="21" t="n">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="E39" s="22" t="n">
-        <v>3500</v>
+        <v>1500</v>
       </c>
       <c r="F39" s="21" t="n"/>
-      <c r="G39" s="9" t="n"/>
-      <c r="H39" s="9" t="n"/>
+      <c r="G39" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="H39" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="I39" s="9" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>산업용프린터</t>
+          <t>스티커라벨기</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
@@ -1646,56 +1700,48 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="D40" s="21" t="n">
-        <v>6500</v>
-      </c>
-      <c r="E40" s="22" t="n">
-        <v>15000</v>
+        <v>10</v>
+      </c>
+      <c r="D40" s="22" t="n">
+        <v>2300</v>
+      </c>
+      <c r="E40" s="21" t="n">
+        <v>2000</v>
       </c>
       <c r="F40" s="21" t="n"/>
-      <c r="G40" s="9" t="n">
+      <c r="G40" s="9" t="n"/>
+      <c r="H40" s="9" t="n"/>
+      <c r="I40" s="9" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>스티커인쇄기</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="n"/>
+      <c r="C41" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D41" s="18" t="n">
+        <v>800</v>
+      </c>
+      <c r="E41" s="19" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F41" s="18" t="n"/>
+      <c r="G41" s="7" t="n"/>
+      <c r="H41" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="I41" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="H40" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="I40" s="9" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="8" t="inlineStr">
-        <is>
-          <t>소형바코드프린터</t>
-        </is>
-      </c>
-      <c r="B41" s="10" t="inlineStr">
-        <is>
-          <t>수정필요</t>
-        </is>
-      </c>
-      <c r="C41" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="D41" s="21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E41" s="22" t="n">
-        <v>1500</v>
-      </c>
-      <c r="F41" s="21" t="n"/>
-      <c r="G41" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="H41" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="I41" s="9" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>스티커라벨기</t>
+          <t>스티커출력기</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
@@ -1704,48 +1750,54 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="D42" s="22" t="n">
-        <v>2300</v>
-      </c>
-      <c r="E42" s="21" t="n">
-        <v>2000</v>
+        <v>8</v>
+      </c>
+      <c r="D42" s="21" t="n">
+        <v>400</v>
+      </c>
+      <c r="E42" s="22" t="n">
+        <v>4000</v>
       </c>
       <c r="F42" s="21" t="n"/>
-      <c r="G42" s="9" t="n"/>
-      <c r="H42" s="9" t="n"/>
+      <c r="G42" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="H42" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="I42" s="9" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>스티커인쇄기</t>
-        </is>
-      </c>
-      <c r="B43" s="7" t="n"/>
-      <c r="C43" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="D43" s="19" t="n">
-        <v>800</v>
-      </c>
-      <c r="E43" s="20" t="n">
-        <v>3000</v>
-      </c>
-      <c r="F43" s="19" t="n"/>
-      <c r="G43" s="7" t="n"/>
-      <c r="H43" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="I43" s="7" t="n">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>스티커프린터</t>
+        </is>
+      </c>
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D43" s="21" t="n">
+        <v>1340</v>
+      </c>
+      <c r="E43" s="22" t="n">
+        <v>3500</v>
+      </c>
+      <c r="F43" s="21" t="n"/>
+      <c r="G43" s="9" t="n"/>
+      <c r="H43" s="9" t="n"/>
+      <c r="I43" s="9" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>스티커출력기</t>
+          <t>열전사프린터</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
@@ -1754,27 +1806,25 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D44" s="21" t="n">
-        <v>400</v>
+        <v>5500</v>
       </c>
       <c r="E44" s="22" t="n">
-        <v>4000</v>
-      </c>
-      <c r="F44" s="21" t="n"/>
-      <c r="G44" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="H44" s="9" t="n">
-        <v>1</v>
-      </c>
+        <v>6000</v>
+      </c>
+      <c r="F44" s="21" t="n">
+        <v>4550</v>
+      </c>
+      <c r="G44" s="9" t="n"/>
+      <c r="H44" s="9" t="n"/>
       <c r="I44" s="9" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>스티커프린터</t>
+          <t>열전사프린터기</t>
         </is>
       </c>
       <c r="B45" s="10" t="inlineStr">
@@ -1783,25 +1833,29 @@
         </is>
       </c>
       <c r="C45" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="D45" s="21" t="n">
+        <v>450</v>
+      </c>
+      <c r="E45" s="22" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F45" s="21" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G45" s="9" t="n"/>
+      <c r="H45" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="D45" s="21" t="n">
-        <v>1340</v>
-      </c>
-      <c r="E45" s="22" t="n">
-        <v>3500</v>
-      </c>
-      <c r="F45" s="21" t="n"/>
-      <c r="G45" s="9" t="n"/>
-      <c r="H45" s="9" t="n"/>
       <c r="I45" s="9" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>열전사프린터</t>
+          <t>영수증프린터</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
@@ -1810,56 +1864,48 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D46" s="21" t="n">
-        <v>5500</v>
+        <v>1070</v>
       </c>
       <c r="E46" s="22" t="n">
-        <v>6000</v>
-      </c>
-      <c r="F46" s="21" t="n">
-        <v>4550</v>
-      </c>
-      <c r="G46" s="9" t="n"/>
-      <c r="H46" s="9" t="n"/>
+        <v>1300</v>
+      </c>
+      <c r="F46" s="21" t="n"/>
+      <c r="G46" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H46" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="I46" s="9" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="8" t="inlineStr">
-        <is>
-          <t>열전사프린터기</t>
-        </is>
-      </c>
-      <c r="B47" s="10" t="inlineStr">
-        <is>
-          <t>수정필요</t>
-        </is>
-      </c>
-      <c r="C47" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="D47" s="21" t="n">
-        <v>450</v>
-      </c>
-      <c r="E47" s="22" t="n">
-        <v>5000</v>
-      </c>
-      <c r="F47" s="21" t="n">
-        <v>4000</v>
-      </c>
-      <c r="G47" s="9" t="n"/>
-      <c r="H47" s="9" t="n">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>제브라</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="n"/>
+      <c r="C47" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="I47" s="9" t="n">
-        <v>9</v>
-      </c>
+      <c r="D47" s="18" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E47" s="18" t="n"/>
+      <c r="F47" s="18" t="n"/>
+      <c r="G47" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H47" s="7" t="n"/>
+      <c r="I47" s="7" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>영수증프린터</t>
+          <t>제브라라벨프린터</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
@@ -1868,48 +1914,52 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="D48" s="21" t="n">
+        <v>700</v>
+      </c>
+      <c r="E48" s="22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F48" s="21" t="n"/>
+      <c r="G48" s="9" t="n"/>
+      <c r="H48" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="I48" s="9" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>제브라바코드프린터</t>
+        </is>
+      </c>
+      <c r="B49" s="10" t="inlineStr">
+        <is>
+          <t>수정필요</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="D48" s="21" t="n">
-        <v>1070</v>
-      </c>
-      <c r="E48" s="22" t="n">
-        <v>1300</v>
-      </c>
-      <c r="F48" s="21" t="n"/>
-      <c r="G48" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H48" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="I48" s="9" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>제브라</t>
-        </is>
-      </c>
-      <c r="B49" s="7" t="n"/>
-      <c r="C49" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="D49" s="19" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E49" s="19" t="n"/>
-      <c r="F49" s="19" t="n"/>
-      <c r="G49" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="H49" s="7" t="n"/>
-      <c r="I49" s="7" t="n"/>
+      <c r="D49" s="21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E49" s="22" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F49" s="21" t="n"/>
+      <c r="G49" s="9" t="n"/>
+      <c r="H49" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="I49" s="9" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>제브라라벨프린터</t>
+          <t>제브라프린터</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
@@ -1921,22 +1971,22 @@
         <v>10</v>
       </c>
       <c r="D50" s="21" t="n">
-        <v>700</v>
+        <v>1410</v>
       </c>
       <c r="E50" s="22" t="n">
-        <v>1000</v>
+        <v>6000</v>
       </c>
       <c r="F50" s="21" t="n"/>
       <c r="G50" s="9" t="n"/>
       <c r="H50" s="9" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I50" s="9" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>제브라바코드프린터</t>
+          <t>카드프린터기</t>
         </is>
       </c>
       <c r="B51" s="10" t="inlineStr">
@@ -1947,107 +1997,87 @@
       <c r="C51" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="D51" s="21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E51" s="22" t="n">
-        <v>2000</v>
-      </c>
+      <c r="D51" s="23" t="n">
+        <v>70</v>
+      </c>
+      <c r="E51" s="21" t="n"/>
       <c r="F51" s="21" t="n"/>
       <c r="G51" s="9" t="n"/>
-      <c r="H51" s="9" t="n">
+      <c r="H51" s="9" t="n"/>
+      <c r="I51" s="9" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>프린터관리</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="n"/>
+      <c r="C52" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="I51" s="9" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="8" t="inlineStr">
-        <is>
-          <t>제브라프린터</t>
-        </is>
-      </c>
-      <c r="B52" s="10" t="inlineStr">
-        <is>
-          <t>수정필요</t>
-        </is>
-      </c>
-      <c r="C52" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="D52" s="21" t="n">
-        <v>1410</v>
-      </c>
-      <c r="E52" s="22" t="n">
-        <v>6000</v>
-      </c>
-      <c r="F52" s="21" t="n"/>
-      <c r="G52" s="9" t="n"/>
-      <c r="H52" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="I52" s="9" t="n"/>
+      <c r="D52" s="23" t="n">
+        <v>200</v>
+      </c>
+      <c r="E52" s="18" t="n"/>
+      <c r="F52" s="18" t="n"/>
+      <c r="G52" s="7" t="n"/>
+      <c r="H52" s="7" t="n"/>
+      <c r="I52" s="7" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="8" t="inlineStr">
-        <is>
-          <t>카드프린터기</t>
-        </is>
-      </c>
-      <c r="B53" s="10" t="inlineStr">
-        <is>
-          <t>수정필요</t>
-        </is>
-      </c>
-      <c r="C53" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="D53" s="23" t="n">
-        <v>70</v>
-      </c>
-      <c r="E53" s="21" t="n"/>
-      <c r="F53" s="21" t="n"/>
-      <c r="G53" s="9" t="n"/>
-      <c r="H53" s="9" t="n"/>
-      <c r="I53" s="9" t="n"/>
+      <c r="A53" s="16" t="inlineStr">
+        <is>
+          <t>솔바텍에 없는 키워드 (20개)</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>프린터관리</t>
+          <t>B-FV4T</t>
         </is>
       </c>
       <c r="B54" s="7" t="n"/>
-      <c r="C54" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="D54" s="23" t="n">
-        <v>200</v>
-      </c>
-      <c r="E54" s="19" t="n"/>
-      <c r="F54" s="19" t="n"/>
+      <c r="C54" s="7" t="n"/>
+      <c r="D54" s="18" t="n"/>
+      <c r="E54" s="18" t="n"/>
+      <c r="F54" s="18" t="n">
+        <v>850</v>
+      </c>
       <c r="G54" s="7" t="n"/>
       <c r="H54" s="7" t="n"/>
       <c r="I54" s="7" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="16" t="inlineStr">
-        <is>
-          <t>솔바텍에 없는 키워드 (20개)</t>
-        </is>
-      </c>
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>B-FV4T-GS</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="n"/>
+      <c r="C55" s="7" t="n"/>
+      <c r="D55" s="18" t="n"/>
+      <c r="E55" s="18" t="n"/>
+      <c r="F55" s="18" t="n">
+        <v>90</v>
+      </c>
+      <c r="G55" s="7" t="n"/>
+      <c r="H55" s="7" t="n"/>
+      <c r="I55" s="7" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>B-FV4T</t>
+          <t>B-FV4T-TS</t>
         </is>
       </c>
       <c r="B56" s="7" t="n"/>
       <c r="C56" s="7" t="n"/>
-      <c r="D56" s="19" t="n"/>
-      <c r="E56" s="19" t="n"/>
-      <c r="F56" s="19" t="n">
-        <v>850</v>
+      <c r="D56" s="18" t="n"/>
+      <c r="E56" s="18" t="n"/>
+      <c r="F56" s="18" t="n">
+        <v>70</v>
       </c>
       <c r="G56" s="7" t="n"/>
       <c r="H56" s="7" t="n"/>
@@ -2056,16 +2086,16 @@
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>B-FV4T-GS</t>
+          <t>G530+</t>
         </is>
       </c>
       <c r="B57" s="7" t="n"/>
       <c r="C57" s="7" t="n"/>
-      <c r="D57" s="19" t="n"/>
-      <c r="E57" s="19" t="n"/>
-      <c r="F57" s="19" t="n">
-        <v>90</v>
-      </c>
+      <c r="D57" s="18" t="n"/>
+      <c r="E57" s="18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F57" s="18" t="n"/>
       <c r="G57" s="7" t="n"/>
       <c r="H57" s="7" t="n"/>
       <c r="I57" s="7" t="n"/>
@@ -2073,15 +2103,15 @@
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>B-FV4T-TS</t>
+          <t>SLPTX400</t>
         </is>
       </c>
       <c r="B58" s="7" t="n"/>
       <c r="C58" s="7" t="n"/>
-      <c r="D58" s="19" t="n"/>
-      <c r="E58" s="19" t="n"/>
-      <c r="F58" s="19" t="n">
-        <v>70</v>
+      <c r="D58" s="18" t="n"/>
+      <c r="E58" s="18" t="n"/>
+      <c r="F58" s="18" t="n">
+        <v>1500</v>
       </c>
       <c r="G58" s="7" t="n"/>
       <c r="H58" s="7" t="n"/>
@@ -2090,16 +2120,16 @@
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>G530+</t>
+          <t>SLPTX403</t>
         </is>
       </c>
       <c r="B59" s="7" t="n"/>
       <c r="C59" s="7" t="n"/>
-      <c r="D59" s="19" t="n"/>
-      <c r="E59" s="19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F59" s="19" t="n"/>
+      <c r="D59" s="18" t="n"/>
+      <c r="E59" s="18" t="n"/>
+      <c r="F59" s="18" t="n">
+        <v>1500</v>
+      </c>
       <c r="G59" s="7" t="n"/>
       <c r="H59" s="7" t="n"/>
       <c r="I59" s="7" t="n"/>
@@ -2107,16 +2137,16 @@
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>SLPTX400</t>
+          <t>TSC프린터</t>
         </is>
       </c>
       <c r="B60" s="7" t="n"/>
       <c r="C60" s="7" t="n"/>
-      <c r="D60" s="19" t="n"/>
-      <c r="E60" s="19" t="n"/>
-      <c r="F60" s="19" t="n">
-        <v>1500</v>
-      </c>
+      <c r="D60" s="18" t="n"/>
+      <c r="E60" s="23" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F60" s="18" t="n"/>
       <c r="G60" s="7" t="n"/>
       <c r="H60" s="7" t="n"/>
       <c r="I60" s="7" t="n"/>
@@ -2124,16 +2154,16 @@
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>SLPTX403</t>
+          <t>고덱스</t>
         </is>
       </c>
       <c r="B61" s="7" t="n"/>
       <c r="C61" s="7" t="n"/>
-      <c r="D61" s="19" t="n"/>
-      <c r="E61" s="19" t="n"/>
-      <c r="F61" s="19" t="n">
-        <v>1500</v>
-      </c>
+      <c r="D61" s="18" t="n"/>
+      <c r="E61" s="18" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F61" s="18" t="n"/>
       <c r="G61" s="7" t="n"/>
       <c r="H61" s="7" t="n"/>
       <c r="I61" s="7" t="n"/>
@@ -2141,16 +2171,16 @@
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>TSC프린터</t>
+          <t>라벨발행기</t>
         </is>
       </c>
       <c r="B62" s="7" t="n"/>
       <c r="C62" s="7" t="n"/>
-      <c r="D62" s="19" t="n"/>
-      <c r="E62" s="23" t="n">
-        <v>2500</v>
-      </c>
-      <c r="F62" s="19" t="n"/>
+      <c r="D62" s="18" t="n"/>
+      <c r="E62" s="18" t="n">
+        <v>2620</v>
+      </c>
+      <c r="F62" s="18" t="n"/>
       <c r="G62" s="7" t="n"/>
       <c r="H62" s="7" t="n"/>
       <c r="I62" s="7" t="n"/>
@@ -2158,16 +2188,16 @@
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>고덱스</t>
+          <t>라벨프린터기</t>
         </is>
       </c>
       <c r="B63" s="7" t="n"/>
       <c r="C63" s="7" t="n"/>
-      <c r="D63" s="19" t="n"/>
-      <c r="E63" s="19" t="n">
-        <v>2500</v>
-      </c>
-      <c r="F63" s="19" t="n"/>
+      <c r="D63" s="18" t="n"/>
+      <c r="E63" s="18" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F63" s="18" t="n"/>
       <c r="G63" s="7" t="n"/>
       <c r="H63" s="7" t="n"/>
       <c r="I63" s="7" t="n"/>
@@ -2175,16 +2205,16 @@
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>라벨발행기</t>
+          <t>라벨프린터용지</t>
         </is>
       </c>
       <c r="B64" s="7" t="n"/>
       <c r="C64" s="7" t="n"/>
-      <c r="D64" s="19" t="n"/>
-      <c r="E64" s="19" t="n">
-        <v>2620</v>
-      </c>
-      <c r="F64" s="19" t="n"/>
+      <c r="D64" s="18" t="n"/>
+      <c r="E64" s="18" t="n">
+        <v>2100</v>
+      </c>
+      <c r="F64" s="18" t="n"/>
       <c r="G64" s="7" t="n"/>
       <c r="H64" s="7" t="n"/>
       <c r="I64" s="7" t="n"/>
@@ -2192,16 +2222,16 @@
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>라벨프린터기</t>
+          <t>롤프린터</t>
         </is>
       </c>
       <c r="B65" s="7" t="n"/>
       <c r="C65" s="7" t="n"/>
-      <c r="D65" s="19" t="n"/>
-      <c r="E65" s="19" t="n">
-        <v>4000</v>
-      </c>
-      <c r="F65" s="19" t="n"/>
+      <c r="D65" s="18" t="n"/>
+      <c r="E65" s="18" t="n">
+        <v>1100</v>
+      </c>
+      <c r="F65" s="18" t="n"/>
       <c r="G65" s="7" t="n"/>
       <c r="H65" s="7" t="n"/>
       <c r="I65" s="7" t="n"/>
@@ -2209,16 +2239,16 @@
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>라벨프린터용지</t>
+          <t>바코드구입</t>
         </is>
       </c>
       <c r="B66" s="7" t="n"/>
       <c r="C66" s="7" t="n"/>
-      <c r="D66" s="19" t="n"/>
-      <c r="E66" s="19" t="n">
-        <v>2100</v>
-      </c>
-      <c r="F66" s="19" t="n"/>
+      <c r="D66" s="18" t="n"/>
+      <c r="E66" s="18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F66" s="18" t="n"/>
       <c r="G66" s="7" t="n"/>
       <c r="H66" s="7" t="n"/>
       <c r="I66" s="7" t="n"/>
@@ -2226,16 +2256,16 @@
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>롤프린터</t>
+          <t>바코드등록</t>
         </is>
       </c>
       <c r="B67" s="7" t="n"/>
       <c r="C67" s="7" t="n"/>
-      <c r="D67" s="19" t="n"/>
-      <c r="E67" s="19" t="n">
-        <v>1100</v>
-      </c>
-      <c r="F67" s="19" t="n"/>
+      <c r="D67" s="18" t="n"/>
+      <c r="E67" s="18" t="n">
+        <v>2200</v>
+      </c>
+      <c r="F67" s="18" t="n"/>
       <c r="G67" s="7" t="n"/>
       <c r="H67" s="7" t="n"/>
       <c r="I67" s="7" t="n"/>
@@ -2243,16 +2273,16 @@
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>바코드구입</t>
+          <t>바코드라벨프린터기</t>
         </is>
       </c>
       <c r="B68" s="7" t="n"/>
       <c r="C68" s="7" t="n"/>
-      <c r="D68" s="19" t="n"/>
-      <c r="E68" s="19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F68" s="19" t="n"/>
+      <c r="D68" s="18" t="n"/>
+      <c r="E68" s="18" t="n">
+        <v>1700</v>
+      </c>
+      <c r="F68" s="18" t="n"/>
       <c r="G68" s="7" t="n"/>
       <c r="H68" s="7" t="n"/>
       <c r="I68" s="7" t="n"/>
@@ -2260,16 +2290,16 @@
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>바코드등록</t>
+          <t>바코드생성</t>
         </is>
       </c>
       <c r="B69" s="7" t="n"/>
       <c r="C69" s="7" t="n"/>
-      <c r="D69" s="19" t="n"/>
-      <c r="E69" s="19" t="n">
-        <v>2200</v>
-      </c>
-      <c r="F69" s="19" t="n"/>
+      <c r="D69" s="18" t="n"/>
+      <c r="E69" s="18" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F69" s="18" t="n"/>
       <c r="G69" s="7" t="n"/>
       <c r="H69" s="7" t="n"/>
       <c r="I69" s="7" t="n"/>
@@ -2277,16 +2307,16 @@
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>바코드라벨프린터기</t>
+          <t>바코드프린트</t>
         </is>
       </c>
       <c r="B70" s="7" t="n"/>
       <c r="C70" s="7" t="n"/>
-      <c r="D70" s="19" t="n"/>
-      <c r="E70" s="19" t="n">
-        <v>1700</v>
-      </c>
-      <c r="F70" s="19" t="n"/>
+      <c r="D70" s="18" t="n"/>
+      <c r="E70" s="18" t="n">
+        <v>1520</v>
+      </c>
+      <c r="F70" s="18" t="n"/>
       <c r="G70" s="7" t="n"/>
       <c r="H70" s="7" t="n"/>
       <c r="I70" s="7" t="n"/>
@@ -2294,16 +2324,16 @@
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>바코드생성</t>
+          <t>산업용바코드</t>
         </is>
       </c>
       <c r="B71" s="7" t="n"/>
       <c r="C71" s="7" t="n"/>
-      <c r="D71" s="19" t="n"/>
-      <c r="E71" s="19" t="n">
-        <v>2500</v>
-      </c>
-      <c r="F71" s="19" t="n"/>
+      <c r="D71" s="18" t="n"/>
+      <c r="E71" s="18" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F71" s="18" t="n"/>
       <c r="G71" s="7" t="n"/>
       <c r="H71" s="7" t="n"/>
       <c r="I71" s="7" t="n"/>
@@ -2311,16 +2341,16 @@
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>바코드프린트</t>
+          <t>소형라벨프린터</t>
         </is>
       </c>
       <c r="B72" s="7" t="n"/>
       <c r="C72" s="7" t="n"/>
-      <c r="D72" s="19" t="n"/>
-      <c r="E72" s="19" t="n">
-        <v>1520</v>
-      </c>
-      <c r="F72" s="19" t="n"/>
+      <c r="D72" s="18" t="n"/>
+      <c r="E72" s="18" t="n">
+        <v>3500</v>
+      </c>
+      <c r="F72" s="18" t="n"/>
       <c r="G72" s="7" t="n"/>
       <c r="H72" s="7" t="n"/>
       <c r="I72" s="7" t="n"/>
@@ -2328,53 +2358,19 @@
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>산업용바코드</t>
+          <t>지브라프린터</t>
         </is>
       </c>
       <c r="B73" s="7" t="n"/>
       <c r="C73" s="7" t="n"/>
-      <c r="D73" s="19" t="n"/>
-      <c r="E73" s="19" t="n">
-        <v>4000</v>
-      </c>
-      <c r="F73" s="19" t="n"/>
+      <c r="D73" s="18" t="n"/>
+      <c r="E73" s="18" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F73" s="18" t="n"/>
       <c r="G73" s="7" t="n"/>
       <c r="H73" s="7" t="n"/>
       <c r="I73" s="7" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="6" t="inlineStr">
-        <is>
-          <t>소형라벨프린터</t>
-        </is>
-      </c>
-      <c r="B74" s="7" t="n"/>
-      <c r="C74" s="7" t="n"/>
-      <c r="D74" s="19" t="n"/>
-      <c r="E74" s="19" t="n">
-        <v>3500</v>
-      </c>
-      <c r="F74" s="19" t="n"/>
-      <c r="G74" s="7" t="n"/>
-      <c r="H74" s="7" t="n"/>
-      <c r="I74" s="7" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="6" t="inlineStr">
-        <is>
-          <t>지브라프린터</t>
-        </is>
-      </c>
-      <c r="B75" s="7" t="n"/>
-      <c r="C75" s="7" t="n"/>
-      <c r="D75" s="19" t="n"/>
-      <c r="E75" s="19" t="n">
-        <v>5000</v>
-      </c>
-      <c r="F75" s="19" t="n"/>
-      <c r="G75" s="7" t="n"/>
-      <c r="H75" s="7" t="n"/>
-      <c r="I75" s="7" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:I52"/>

--- a/솔바텍_URL도메인변경완료_순위반영_20261029.xlsx
+++ b/솔바텍_URL도메인변경완료_순위반영_20261029.xlsx
@@ -7,20 +7,25 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="입찰가 변경 전후" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="광고 기본 정보" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="키워드ID·링크" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분류 기준" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="직접 확인 목록" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="입찰가 변경 전후" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="광고 기본 정보" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="키워드ID·링크" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분류 기준" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'직접 확인 목록'!$A$5:$V$160</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="9">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="+0;-0;0"/>
+  </numFmts>
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -61,8 +66,15 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="FF595959"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -114,8 +126,13 @@
         <fgColor rgb="FFFFE5E5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -153,11 +170,108 @@
       </top>
       <bottom/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -246,10 +360,47 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF008000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -1016,6 +1167,7863 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:V162"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="9.5" customWidth="1" min="5" max="5"/>
+    <col width="9.5" customWidth="1" min="6" max="6"/>
+    <col width="9.5" customWidth="1" min="7" max="7"/>
+    <col width="9.5" customWidth="1" min="8" max="8"/>
+    <col width="9.5" customWidth="1" min="9" max="9"/>
+    <col width="9.5" customWidth="1" min="10" max="10"/>
+    <col width="9.5" customWidth="1" min="11" max="11"/>
+    <col width="9.5" customWidth="1" min="12" max="12"/>
+    <col width="9.5" customWidth="1" min="13" max="13"/>
+    <col width="9.5" customWidth="1" min="14" max="14"/>
+    <col width="9.5" customWidth="1" min="15" max="15"/>
+    <col width="9.5" customWidth="1" min="16" max="16"/>
+    <col width="9.5" customWidth="1" min="17" max="17"/>
+    <col width="9.5" customWidth="1" min="18" max="18"/>
+    <col width="9.5" customWidth="1" min="19" max="19"/>
+    <col width="9.5" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
+    <col width="24" customWidth="1" min="22" max="22"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="38" t="inlineStr">
+        <is>
+          <t>입찰가 조정 키워드 직접 확인 목록 (155개)  —  3사이트 7일 비용이 큰 순서</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="39" t="inlineStr">
+        <is>
+          <t>확인 방법: PC 시크릿 창에서 키워드 검색 → 파워링크 순위 기록 (안 보이면 비워 두기) → 입찰가 변경 → 30분쯤 뒤 다시 검색해서 "변경 후"에 기록.  노란 칸만 입력하면 됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>기본</t>
+        </is>
+      </c>
+      <c r="B4" s="40" t="n"/>
+      <c r="C4" s="40" t="n"/>
+      <c r="D4" s="40" t="n"/>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>7일 평균순위 (보고서)</t>
+        </is>
+      </c>
+      <c r="F4" s="41" t="n"/>
+      <c r="G4" s="41" t="n"/>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>변경 전 직접 확인 순위</t>
+        </is>
+      </c>
+      <c r="I4" s="42" t="n"/>
+      <c r="J4" s="42" t="n"/>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>현재 입찰가</t>
+        </is>
+      </c>
+      <c r="L4" s="43" t="n"/>
+      <c r="M4" s="43" t="n"/>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>변경 입찰가 (바꾼 사이트만)</t>
+        </is>
+      </c>
+      <c r="O4" s="44" t="n"/>
+      <c r="P4" s="44" t="n"/>
+      <c r="Q4" s="8" t="inlineStr">
+        <is>
+          <t>변경 후 직접 확인 순위</t>
+        </is>
+      </c>
+      <c r="R4" s="42" t="n"/>
+      <c r="S4" s="42" t="n"/>
+      <c r="T4" s="45" t="inlineStr">
+        <is>
+          <t>결과</t>
+        </is>
+      </c>
+      <c r="U4" s="46" t="n"/>
+      <c r="V4" s="46" t="n"/>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>순서</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>그룹</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>키워드</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>조치</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>솔바텍</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>코스모스몰</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>SB렌탈</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>솔바텍</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>코스모스몰</t>
+        </is>
+      </c>
+      <c r="J5" s="8" t="inlineStr">
+        <is>
+          <t>SB렌탈</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>솔바텍</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>코스모스몰</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>SB렌탈</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>솔바텍</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>코스모스몰</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>SB렌탈</t>
+        </is>
+      </c>
+      <c r="Q5" s="8" t="inlineStr">
+        <is>
+          <t>솔바텍</t>
+        </is>
+      </c>
+      <c r="R5" s="8" t="inlineStr">
+        <is>
+          <t>코스모스몰</t>
+        </is>
+      </c>
+      <c r="S5" s="8" t="inlineStr">
+        <is>
+          <t>SB렌탈</t>
+        </is>
+      </c>
+      <c r="T5" s="45" t="inlineStr">
+        <is>
+          <t>솔바텍
+순위 변화</t>
+        </is>
+      </c>
+      <c r="U5" s="45" t="inlineStr">
+        <is>
+          <t>확인 시각</t>
+        </is>
+      </c>
+      <c r="V5" s="45" t="inlineStr">
+        <is>
+          <t>메모</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>3.라벨</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>바코드라벨</t>
+        </is>
+      </c>
+      <c r="D6" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F6" s="13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G6" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="H6" s="48" t="n"/>
+      <c r="I6" s="48" t="n"/>
+      <c r="J6" s="48" t="n"/>
+      <c r="K6" s="15" t="n">
+        <v>6680</v>
+      </c>
+      <c r="L6" s="15" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M6" s="15" t="n">
+        <v>3180</v>
+      </c>
+      <c r="N6" s="16" t="n"/>
+      <c r="O6" s="16" t="n"/>
+      <c r="P6" s="16" t="n"/>
+      <c r="Q6" s="48" t="n"/>
+      <c r="R6" s="48" t="n"/>
+      <c r="S6" s="48" t="n"/>
+      <c r="T6" s="49">
+        <f>IF(AND(H6&lt;&gt;"",Q6&lt;&gt;""),H6-Q6,"")</f>
+        <v/>
+      </c>
+      <c r="U6" s="48" t="n"/>
+      <c r="V6" s="48" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>2.프린터-1</t>
+        </is>
+      </c>
+      <c r="C7" s="34" t="inlineStr">
+        <is>
+          <t>바코드프린터기</t>
+        </is>
+      </c>
+      <c r="D7" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="F7" s="13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G7" s="13" t="n"/>
+      <c r="H7" s="48" t="n"/>
+      <c r="I7" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="48" t="n"/>
+      <c r="K7" s="15" t="n">
+        <v>4000</v>
+      </c>
+      <c r="L7" s="15" t="n">
+        <v>15000</v>
+      </c>
+      <c r="M7" s="15" t="n"/>
+      <c r="N7" s="16" t="n"/>
+      <c r="O7" s="16" t="n"/>
+      <c r="P7" s="16" t="n"/>
+      <c r="Q7" s="48" t="n"/>
+      <c r="R7" s="48" t="n"/>
+      <c r="S7" s="48" t="n"/>
+      <c r="T7" s="49">
+        <f>IF(AND(H7&lt;&gt;"",Q7&lt;&gt;""),H7-Q7,"")</f>
+        <v/>
+      </c>
+      <c r="U7" s="48" t="n"/>
+      <c r="V7" s="48" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>1.스캐너-1</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>무선바코드스캐너</t>
+        </is>
+      </c>
+      <c r="D8" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F8" s="13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G8" s="13" t="n"/>
+      <c r="H8" s="48" t="n"/>
+      <c r="I8" s="48" t="n"/>
+      <c r="J8" s="48" t="n"/>
+      <c r="K8" s="15" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L8" s="15" t="n">
+        <v>12000</v>
+      </c>
+      <c r="M8" s="15" t="n"/>
+      <c r="N8" s="16" t="n"/>
+      <c r="O8" s="16" t="n"/>
+      <c r="P8" s="16" t="n"/>
+      <c r="Q8" s="48" t="n"/>
+      <c r="R8" s="48" t="n"/>
+      <c r="S8" s="48" t="n"/>
+      <c r="T8" s="49">
+        <f>IF(AND(H8&lt;&gt;"",Q8&lt;&gt;""),H8-Q8,"")</f>
+        <v/>
+      </c>
+      <c r="U8" s="48" t="n"/>
+      <c r="V8" s="48" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>1.스캐너-1</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>바코드리더기</t>
+        </is>
+      </c>
+      <c r="D9" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="F9" s="13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G9" s="13" t="n"/>
+      <c r="H9" s="48" t="n"/>
+      <c r="I9" s="48" t="n"/>
+      <c r="J9" s="48" t="n"/>
+      <c r="K9" s="15" t="n">
+        <v>8000</v>
+      </c>
+      <c r="L9" s="15" t="n">
+        <v>15000</v>
+      </c>
+      <c r="M9" s="15" t="n"/>
+      <c r="N9" s="16" t="n"/>
+      <c r="O9" s="16" t="n"/>
+      <c r="P9" s="16" t="n"/>
+      <c r="Q9" s="48" t="n"/>
+      <c r="R9" s="48" t="n"/>
+      <c r="S9" s="48" t="n"/>
+      <c r="T9" s="49">
+        <f>IF(AND(H9&lt;&gt;"",Q9&lt;&gt;""),H9-Q9,"")</f>
+        <v/>
+      </c>
+      <c r="U9" s="48" t="n"/>
+      <c r="V9" s="48" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>2.프린터-1</t>
+        </is>
+      </c>
+      <c r="C10" s="34" t="inlineStr">
+        <is>
+          <t>바코드출력기</t>
+        </is>
+      </c>
+      <c r="D10" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하 / SB렌탈 인하</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="F10" s="13" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G10" s="13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H10" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="I10" s="48" t="n">
+        <v>6</v>
+      </c>
+      <c r="J10" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="15" t="n">
+        <v>2500</v>
+      </c>
+      <c r="L10" s="15" t="n">
+        <v>3000</v>
+      </c>
+      <c r="M10" s="15" t="n">
+        <v>4000</v>
+      </c>
+      <c r="N10" s="16" t="n"/>
+      <c r="O10" s="16" t="n"/>
+      <c r="P10" s="16" t="n"/>
+      <c r="Q10" s="48" t="n"/>
+      <c r="R10" s="48" t="n"/>
+      <c r="S10" s="48" t="n"/>
+      <c r="T10" s="49">
+        <f>IF(AND(H10&lt;&gt;"",Q10&lt;&gt;""),H10-Q10,"")</f>
+        <v/>
+      </c>
+      <c r="U10" s="48" t="n"/>
+      <c r="V10" s="48" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>2.프린터-1</t>
+        </is>
+      </c>
+      <c r="C11" s="34" t="inlineStr">
+        <is>
+          <t>라벨출력기</t>
+        </is>
+      </c>
+      <c r="D11" s="50" t="inlineStr">
+        <is>
+          <t>솔바텍 미노출 (다른 사이트는 노출됨) → 인상 또는 품질 확인</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="n"/>
+      <c r="F11" s="13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G11" s="13" t="n"/>
+      <c r="H11" s="48" t="n">
+        <v>7</v>
+      </c>
+      <c r="I11" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" s="48" t="n"/>
+      <c r="K11" s="15" t="n">
+        <v>1110</v>
+      </c>
+      <c r="L11" s="15" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M11" s="15" t="n"/>
+      <c r="N11" s="16" t="n"/>
+      <c r="O11" s="16" t="n"/>
+      <c r="P11" s="16" t="n"/>
+      <c r="Q11" s="48" t="n"/>
+      <c r="R11" s="48" t="n"/>
+      <c r="S11" s="48" t="n"/>
+      <c r="T11" s="49">
+        <f>IF(AND(H11&lt;&gt;"",Q11&lt;&gt;""),H11-Q11,"")</f>
+        <v/>
+      </c>
+      <c r="U11" s="48" t="n"/>
+      <c r="V11" s="48" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>2.프린터-1</t>
+        </is>
+      </c>
+      <c r="C12" s="34" t="inlineStr">
+        <is>
+          <t>스티커프린터</t>
+        </is>
+      </c>
+      <c r="D12" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하 / SB렌탈 인하</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="F12" s="13" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G12" s="13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H12" s="48" t="n"/>
+      <c r="I12" s="48" t="n"/>
+      <c r="J12" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" s="15" t="n">
+        <v>1340</v>
+      </c>
+      <c r="L12" s="15" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M12" s="15" t="n">
+        <v>3400</v>
+      </c>
+      <c r="N12" s="16" t="n"/>
+      <c r="O12" s="16" t="n"/>
+      <c r="P12" s="16" t="n"/>
+      <c r="Q12" s="48" t="n"/>
+      <c r="R12" s="48" t="n"/>
+      <c r="S12" s="48" t="n"/>
+      <c r="T12" s="49">
+        <f>IF(AND(H12&lt;&gt;"",Q12&lt;&gt;""),H12-Q12,"")</f>
+        <v/>
+      </c>
+      <c r="U12" s="48" t="n"/>
+      <c r="V12" s="48" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>2.프린터-1</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>스티커인쇄기</t>
+        </is>
+      </c>
+      <c r="D13" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하 / SB렌탈 인하</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F13" s="13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="G13" s="13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H13" s="48" t="n"/>
+      <c r="I13" s="48" t="n">
+        <v>5</v>
+      </c>
+      <c r="J13" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" s="15" t="n">
+        <v>800</v>
+      </c>
+      <c r="L13" s="15" t="n">
+        <v>3000</v>
+      </c>
+      <c r="M13" s="15" t="n">
+        <v>3500</v>
+      </c>
+      <c r="N13" s="16" t="n"/>
+      <c r="O13" s="16" t="n"/>
+      <c r="P13" s="16" t="n"/>
+      <c r="Q13" s="48" t="n"/>
+      <c r="R13" s="48" t="n"/>
+      <c r="S13" s="48" t="n"/>
+      <c r="T13" s="49">
+        <f>IF(AND(H13&lt;&gt;"",Q13&lt;&gt;""),H13-Q13,"")</f>
+        <v/>
+      </c>
+      <c r="U13" s="48" t="n"/>
+      <c r="V13" s="48" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>2.프린터-1</t>
+        </is>
+      </c>
+      <c r="C14" s="34" t="inlineStr">
+        <is>
+          <t>라벨기</t>
+        </is>
+      </c>
+      <c r="D14" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하 / SB렌탈 인하</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="F14" s="13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G14" s="13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H14" s="48" t="n"/>
+      <c r="I14" s="48" t="n"/>
+      <c r="J14" s="48" t="n"/>
+      <c r="K14" s="15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="L14" s="15" t="n">
+        <v>8000</v>
+      </c>
+      <c r="M14" s="15" t="n">
+        <v>5000</v>
+      </c>
+      <c r="N14" s="16" t="n"/>
+      <c r="O14" s="16" t="n"/>
+      <c r="P14" s="16" t="n"/>
+      <c r="Q14" s="48" t="n"/>
+      <c r="R14" s="48" t="n"/>
+      <c r="S14" s="48" t="n"/>
+      <c r="T14" s="49">
+        <f>IF(AND(H14&lt;&gt;"",Q14&lt;&gt;""),H14-Q14,"")</f>
+        <v/>
+      </c>
+      <c r="U14" s="48" t="n"/>
+      <c r="V14" s="48" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>3.라벨</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>바코드라벨제작</t>
+        </is>
+      </c>
+      <c r="D15" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="F15" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="G15" s="13" t="n"/>
+      <c r="H15" s="48" t="n"/>
+      <c r="I15" s="48" t="n"/>
+      <c r="J15" s="48" t="n"/>
+      <c r="K15" s="15" t="n">
+        <v>3000</v>
+      </c>
+      <c r="L15" s="15" t="n">
+        <v>7000</v>
+      </c>
+      <c r="M15" s="15" t="n">
+        <v>1500</v>
+      </c>
+      <c r="N15" s="16" t="n"/>
+      <c r="O15" s="16" t="n"/>
+      <c r="P15" s="16" t="n"/>
+      <c r="Q15" s="48" t="n"/>
+      <c r="R15" s="48" t="n"/>
+      <c r="S15" s="48" t="n"/>
+      <c r="T15" s="49">
+        <f>IF(AND(H15&lt;&gt;"",Q15&lt;&gt;""),H15-Q15,"")</f>
+        <v/>
+      </c>
+      <c r="U15" s="48" t="n"/>
+      <c r="V15" s="48" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>2.프린터-1</t>
+        </is>
+      </c>
+      <c r="C16" s="34" t="inlineStr">
+        <is>
+          <t>제브라프린터</t>
+        </is>
+      </c>
+      <c r="D16" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="F16" s="13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G16" s="13" t="n"/>
+      <c r="H16" s="48" t="n"/>
+      <c r="I16" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="J16" s="48" t="n"/>
+      <c r="K16" s="15" t="n">
+        <v>1410</v>
+      </c>
+      <c r="L16" s="15" t="n">
+        <v>6000</v>
+      </c>
+      <c r="M16" s="15" t="n"/>
+      <c r="N16" s="16" t="n"/>
+      <c r="O16" s="16" t="n"/>
+      <c r="P16" s="16" t="n"/>
+      <c r="Q16" s="48" t="n"/>
+      <c r="R16" s="48" t="n"/>
+      <c r="S16" s="48" t="n"/>
+      <c r="T16" s="49">
+        <f>IF(AND(H16&lt;&gt;"",Q16&lt;&gt;""),H16-Q16,"")</f>
+        <v/>
+      </c>
+      <c r="U16" s="48" t="n"/>
+      <c r="V16" s="48" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>4.솔루션SW-2</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>바코드재고관리</t>
+        </is>
+      </c>
+      <c r="D17" s="50" t="inlineStr">
+        <is>
+          <t>솔바텍 인상</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="F17" s="13" t="n"/>
+      <c r="G17" s="13" t="n"/>
+      <c r="H17" s="48" t="n"/>
+      <c r="I17" s="48" t="n"/>
+      <c r="J17" s="48" t="n"/>
+      <c r="K17" s="15" t="n">
+        <v>6000</v>
+      </c>
+      <c r="L17" s="15" t="n">
+        <v>3950</v>
+      </c>
+      <c r="M17" s="15" t="n"/>
+      <c r="N17" s="16" t="n"/>
+      <c r="O17" s="16" t="n"/>
+      <c r="P17" s="16" t="n"/>
+      <c r="Q17" s="48" t="n"/>
+      <c r="R17" s="48" t="n"/>
+      <c r="S17" s="48" t="n"/>
+      <c r="T17" s="49">
+        <f>IF(AND(H17&lt;&gt;"",Q17&lt;&gt;""),H17-Q17,"")</f>
+        <v/>
+      </c>
+      <c r="U17" s="48" t="n"/>
+      <c r="V17" s="48" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>1.스캐너-1</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>무선바코드</t>
+        </is>
+      </c>
+      <c r="D18" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="F18" s="13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G18" s="13" t="n"/>
+      <c r="H18" s="48" t="n"/>
+      <c r="I18" s="48" t="n"/>
+      <c r="J18" s="48" t="n"/>
+      <c r="K18" s="15" t="n">
+        <v>620</v>
+      </c>
+      <c r="L18" s="15" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M18" s="15" t="n"/>
+      <c r="N18" s="16" t="n"/>
+      <c r="O18" s="16" t="n"/>
+      <c r="P18" s="16" t="n"/>
+      <c r="Q18" s="48" t="n"/>
+      <c r="R18" s="48" t="n"/>
+      <c r="S18" s="48" t="n"/>
+      <c r="T18" s="49">
+        <f>IF(AND(H18&lt;&gt;"",Q18&lt;&gt;""),H18-Q18,"")</f>
+        <v/>
+      </c>
+      <c r="U18" s="48" t="n"/>
+      <c r="V18" s="48" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>2.프린터-1</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>산업용라벨프린터</t>
+        </is>
+      </c>
+      <c r="D19" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하 (간격 벌리기)</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F19" s="13" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="G19" s="13" t="n"/>
+      <c r="H19" s="48" t="n">
+        <v>6</v>
+      </c>
+      <c r="I19" s="48" t="n"/>
+      <c r="J19" s="48" t="n"/>
+      <c r="K19" s="15" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L19" s="15" t="n">
+        <v>8500</v>
+      </c>
+      <c r="M19" s="15" t="n"/>
+      <c r="N19" s="16" t="n"/>
+      <c r="O19" s="16" t="n"/>
+      <c r="P19" s="16" t="n"/>
+      <c r="Q19" s="48" t="n"/>
+      <c r="R19" s="48" t="n"/>
+      <c r="S19" s="48" t="n"/>
+      <c r="T19" s="49">
+        <f>IF(AND(H19&lt;&gt;"",Q19&lt;&gt;""),H19-Q19,"")</f>
+        <v/>
+      </c>
+      <c r="U19" s="48" t="n"/>
+      <c r="V19" s="48" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>2.프린터-1</t>
+        </is>
+      </c>
+      <c r="C20" s="34" t="inlineStr">
+        <is>
+          <t>열전사프린터</t>
+        </is>
+      </c>
+      <c r="D20" s="50" t="inlineStr">
+        <is>
+          <t>SB렌탈 인하 / 솔바텍 인상</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="F20" s="13" t="n"/>
+      <c r="G20" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="H20" s="48" t="n"/>
+      <c r="I20" s="48" t="n"/>
+      <c r="J20" s="48" t="n"/>
+      <c r="K20" s="15" t="n">
+        <v>5500</v>
+      </c>
+      <c r="L20" s="15" t="n">
+        <v>6000</v>
+      </c>
+      <c r="M20" s="15" t="n">
+        <v>4550</v>
+      </c>
+      <c r="N20" s="16" t="n"/>
+      <c r="O20" s="16" t="n"/>
+      <c r="P20" s="16" t="n"/>
+      <c r="Q20" s="48" t="n"/>
+      <c r="R20" s="48" t="n"/>
+      <c r="S20" s="48" t="n"/>
+      <c r="T20" s="49">
+        <f>IF(AND(H20&lt;&gt;"",Q20&lt;&gt;""),H20-Q20,"")</f>
+        <v/>
+      </c>
+      <c r="U20" s="48" t="n"/>
+      <c r="V20" s="48" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>1.스캐너-1</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>QR코드스캐너</t>
+        </is>
+      </c>
+      <c r="D21" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="F21" s="13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G21" s="13" t="n"/>
+      <c r="H21" s="48" t="n"/>
+      <c r="I21" s="48" t="n"/>
+      <c r="J21" s="48" t="n"/>
+      <c r="K21" s="15" t="n">
+        <v>1500</v>
+      </c>
+      <c r="L21" s="15" t="n">
+        <v>4000</v>
+      </c>
+      <c r="M21" s="15" t="n"/>
+      <c r="N21" s="16" t="n"/>
+      <c r="O21" s="16" t="n"/>
+      <c r="P21" s="16" t="n"/>
+      <c r="Q21" s="48" t="n"/>
+      <c r="R21" s="48" t="n"/>
+      <c r="S21" s="48" t="n"/>
+      <c r="T21" s="49">
+        <f>IF(AND(H21&lt;&gt;"",Q21&lt;&gt;""),H21-Q21,"")</f>
+        <v/>
+      </c>
+      <c r="U21" s="48" t="n"/>
+      <c r="V21" s="48" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>6.산업용PDA-1</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>안드로이드PDA</t>
+        </is>
+      </c>
+      <c r="D22" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="F22" s="13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G22" s="13" t="n"/>
+      <c r="H22" s="48" t="n"/>
+      <c r="I22" s="48" t="n"/>
+      <c r="J22" s="48" t="n"/>
+      <c r="K22" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L22" s="15" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M22" s="15" t="n"/>
+      <c r="N22" s="16" t="n"/>
+      <c r="O22" s="16" t="n"/>
+      <c r="P22" s="16" t="n"/>
+      <c r="Q22" s="48" t="n"/>
+      <c r="R22" s="48" t="n"/>
+      <c r="S22" s="48" t="n"/>
+      <c r="T22" s="49">
+        <f>IF(AND(H22&lt;&gt;"",Q22&lt;&gt;""),H22-Q22,"")</f>
+        <v/>
+      </c>
+      <c r="U22" s="48" t="n"/>
+      <c r="V22" s="48" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>2.프린터-1</t>
+        </is>
+      </c>
+      <c r="C23" s="34" t="inlineStr">
+        <is>
+          <t>바코드라벨프린터</t>
+        </is>
+      </c>
+      <c r="D23" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하 / SB렌탈 인하</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="F23" s="13" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="G23" s="13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H23" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="I23" s="48" t="n">
+        <v>4</v>
+      </c>
+      <c r="J23" s="48" t="n"/>
+      <c r="K23" s="15" t="n">
+        <v>3000</v>
+      </c>
+      <c r="L23" s="15" t="n">
+        <v>4460</v>
+      </c>
+      <c r="M23" s="15" t="n">
+        <v>5000</v>
+      </c>
+      <c r="N23" s="16" t="n"/>
+      <c r="O23" s="16" t="n"/>
+      <c r="P23" s="16" t="n"/>
+      <c r="Q23" s="48" t="n"/>
+      <c r="R23" s="48" t="n"/>
+      <c r="S23" s="48" t="n"/>
+      <c r="T23" s="49">
+        <f>IF(AND(H23&lt;&gt;"",Q23&lt;&gt;""),H23-Q23,"")</f>
+        <v/>
+      </c>
+      <c r="U23" s="48" t="n"/>
+      <c r="V23" s="48" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>3.라벨</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>아트지</t>
+        </is>
+      </c>
+      <c r="D24" s="47" t="inlineStr">
+        <is>
+          <t>솔바텍 인하</t>
+        </is>
+      </c>
+      <c r="E24" s="13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F24" s="13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="G24" s="13" t="n"/>
+      <c r="H24" s="48" t="n"/>
+      <c r="I24" s="48" t="n"/>
+      <c r="J24" s="48" t="n"/>
+      <c r="K24" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L24" s="15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="M24" s="15" t="n"/>
+      <c r="N24" s="16" t="n"/>
+      <c r="O24" s="16" t="n"/>
+      <c r="P24" s="16" t="n"/>
+      <c r="Q24" s="48" t="n"/>
+      <c r="R24" s="48" t="n"/>
+      <c r="S24" s="48" t="n"/>
+      <c r="T24" s="49">
+        <f>IF(AND(H24&lt;&gt;"",Q24&lt;&gt;""),H24-Q24,"")</f>
+        <v/>
+      </c>
+      <c r="U24" s="48" t="n"/>
+      <c r="V24" s="48" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>6.산업용PDA-1</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>산업용태블릿</t>
+        </is>
+      </c>
+      <c r="D25" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="F25" s="13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G25" s="13" t="n"/>
+      <c r="H25" s="48" t="n"/>
+      <c r="I25" s="48" t="n"/>
+      <c r="J25" s="48" t="n"/>
+      <c r="K25" s="15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="L25" s="15" t="n">
+        <v>10000</v>
+      </c>
+      <c r="M25" s="15" t="n"/>
+      <c r="N25" s="16" t="n"/>
+      <c r="O25" s="16" t="n"/>
+      <c r="P25" s="16" t="n"/>
+      <c r="Q25" s="48" t="n"/>
+      <c r="R25" s="48" t="n"/>
+      <c r="S25" s="48" t="n"/>
+      <c r="T25" s="49">
+        <f>IF(AND(H25&lt;&gt;"",Q25&lt;&gt;""),H25-Q25,"")</f>
+        <v/>
+      </c>
+      <c r="U25" s="48" t="n"/>
+      <c r="V25" s="48" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>3.라벨</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>바코드생성기</t>
+        </is>
+      </c>
+      <c r="D26" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하 / SB렌탈 인하</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="F26" s="13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="G26" s="13" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="H26" s="48" t="n"/>
+      <c r="I26" s="48" t="n"/>
+      <c r="J26" s="48" t="n"/>
+      <c r="K26" s="15" t="n">
+        <v>1500</v>
+      </c>
+      <c r="L26" s="15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="M26" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N26" s="16" t="n"/>
+      <c r="O26" s="16" t="n"/>
+      <c r="P26" s="16" t="n"/>
+      <c r="Q26" s="48" t="n"/>
+      <c r="R26" s="48" t="n"/>
+      <c r="S26" s="48" t="n"/>
+      <c r="T26" s="49">
+        <f>IF(AND(H26&lt;&gt;"",Q26&lt;&gt;""),H26-Q26,"")</f>
+        <v/>
+      </c>
+      <c r="U26" s="48" t="n"/>
+      <c r="V26" s="48" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>2.프린터-1</t>
+        </is>
+      </c>
+      <c r="C27" s="34" t="inlineStr">
+        <is>
+          <t>감열프린터기</t>
+        </is>
+      </c>
+      <c r="D27" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하 / SB렌탈 인하</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="F27" s="13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="G27" s="13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H27" s="48" t="n">
+        <v>9</v>
+      </c>
+      <c r="I27" s="48" t="n">
+        <v>7</v>
+      </c>
+      <c r="J27" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="K27" s="15" t="n">
+        <v>650</v>
+      </c>
+      <c r="L27" s="15" t="n">
+        <v>1500</v>
+      </c>
+      <c r="M27" s="15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="N27" s="16" t="n"/>
+      <c r="O27" s="16" t="n"/>
+      <c r="P27" s="16" t="n"/>
+      <c r="Q27" s="48" t="n"/>
+      <c r="R27" s="48" t="n"/>
+      <c r="S27" s="48" t="n"/>
+      <c r="T27" s="49">
+        <f>IF(AND(H27&lt;&gt;"",Q27&lt;&gt;""),H27-Q27,"")</f>
+        <v/>
+      </c>
+      <c r="U27" s="48" t="n"/>
+      <c r="V27" s="48" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="n">
+        <v>23</v>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>1.스캐너-1</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>모바일바코드스캐너</t>
+        </is>
+      </c>
+      <c r="D28" s="50" t="inlineStr">
+        <is>
+          <t>솔바텍 미노출 (다른 사이트는 노출됨) → 인상 또는 품질 확인</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="n"/>
+      <c r="F28" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="13" t="n"/>
+      <c r="H28" s="48" t="n"/>
+      <c r="I28" s="48" t="n"/>
+      <c r="J28" s="48" t="n"/>
+      <c r="K28" s="15" t="n">
+        <v>800</v>
+      </c>
+      <c r="L28" s="15" t="n">
+        <v>1500</v>
+      </c>
+      <c r="M28" s="15" t="n"/>
+      <c r="N28" s="16" t="n"/>
+      <c r="O28" s="16" t="n"/>
+      <c r="P28" s="16" t="n"/>
+      <c r="Q28" s="48" t="n"/>
+      <c r="R28" s="48" t="n"/>
+      <c r="S28" s="48" t="n"/>
+      <c r="T28" s="49">
+        <f>IF(AND(H28&lt;&gt;"",Q28&lt;&gt;""),H28-Q28,"")</f>
+        <v/>
+      </c>
+      <c r="U28" s="48" t="n"/>
+      <c r="V28" s="48" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="n">
+        <v>24</v>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>1.스캐너-1</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>바코드스캔</t>
+        </is>
+      </c>
+      <c r="D29" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="F29" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="G29" s="13" t="n"/>
+      <c r="H29" s="48" t="n"/>
+      <c r="I29" s="48" t="n"/>
+      <c r="J29" s="48" t="n"/>
+      <c r="K29" s="15" t="n">
+        <v>700</v>
+      </c>
+      <c r="L29" s="15" t="n">
+        <v>1500</v>
+      </c>
+      <c r="M29" s="15" t="n"/>
+      <c r="N29" s="16" t="n"/>
+      <c r="O29" s="16" t="n"/>
+      <c r="P29" s="16" t="n"/>
+      <c r="Q29" s="48" t="n"/>
+      <c r="R29" s="48" t="n"/>
+      <c r="S29" s="48" t="n"/>
+      <c r="T29" s="49">
+        <f>IF(AND(H29&lt;&gt;"",Q29&lt;&gt;""),H29-Q29,"")</f>
+        <v/>
+      </c>
+      <c r="U29" s="48" t="n"/>
+      <c r="V29" s="48" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>1.스캐너-1</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>미니스캐너</t>
+        </is>
+      </c>
+      <c r="D30" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F30" s="13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G30" s="13" t="n"/>
+      <c r="H30" s="48" t="n"/>
+      <c r="I30" s="48" t="n"/>
+      <c r="J30" s="48" t="n"/>
+      <c r="K30" s="15" t="n">
+        <v>150</v>
+      </c>
+      <c r="L30" s="15" t="n">
+        <v>500</v>
+      </c>
+      <c r="M30" s="15" t="n"/>
+      <c r="N30" s="16" t="n"/>
+      <c r="O30" s="16" t="n"/>
+      <c r="P30" s="16" t="n"/>
+      <c r="Q30" s="48" t="n"/>
+      <c r="R30" s="48" t="n"/>
+      <c r="S30" s="48" t="n"/>
+      <c r="T30" s="49">
+        <f>IF(AND(H30&lt;&gt;"",Q30&lt;&gt;""),H30-Q30,"")</f>
+        <v/>
+      </c>
+      <c r="U30" s="48" t="n"/>
+      <c r="V30" s="48" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="13" t="n">
+        <v>26</v>
+      </c>
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>6.산업용PDA-1</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>PDA</t>
+        </is>
+      </c>
+      <c r="D31" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="F31" s="13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G31" s="13" t="n"/>
+      <c r="H31" s="48" t="n"/>
+      <c r="I31" s="48" t="n"/>
+      <c r="J31" s="48" t="n"/>
+      <c r="K31" s="15" t="n">
+        <v>2800</v>
+      </c>
+      <c r="L31" s="15" t="n">
+        <v>15000</v>
+      </c>
+      <c r="M31" s="15" t="n"/>
+      <c r="N31" s="16" t="n"/>
+      <c r="O31" s="16" t="n"/>
+      <c r="P31" s="16" t="n"/>
+      <c r="Q31" s="48" t="n"/>
+      <c r="R31" s="48" t="n"/>
+      <c r="S31" s="48" t="n"/>
+      <c r="T31" s="49">
+        <f>IF(AND(H31&lt;&gt;"",Q31&lt;&gt;""),H31-Q31,"")</f>
+        <v/>
+      </c>
+      <c r="U31" s="48" t="n"/>
+      <c r="V31" s="48" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="n">
+        <v>27</v>
+      </c>
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>3.라벨</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>바코드생성</t>
+        </is>
+      </c>
+      <c r="D32" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하</t>
+        </is>
+      </c>
+      <c r="E32" s="13" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="F32" s="13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="G32" s="13" t="n"/>
+      <c r="H32" s="48" t="n"/>
+      <c r="I32" s="48" t="n"/>
+      <c r="J32" s="48" t="n"/>
+      <c r="K32" s="15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="L32" s="15" t="n">
+        <v>2500</v>
+      </c>
+      <c r="M32" s="15" t="n"/>
+      <c r="N32" s="16" t="n"/>
+      <c r="O32" s="16" t="n"/>
+      <c r="P32" s="16" t="n"/>
+      <c r="Q32" s="48" t="n"/>
+      <c r="R32" s="48" t="n"/>
+      <c r="S32" s="48" t="n"/>
+      <c r="T32" s="49">
+        <f>IF(AND(H32&lt;&gt;"",Q32&lt;&gt;""),H32-Q32,"")</f>
+        <v/>
+      </c>
+      <c r="U32" s="48" t="n"/>
+      <c r="V32" s="48" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="13" t="n">
+        <v>28</v>
+      </c>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>4.솔루션SW-3</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>고정자산관리프로그램</t>
+        </is>
+      </c>
+      <c r="D33" s="50" t="inlineStr">
+        <is>
+          <t>솔바텍 인상</t>
+        </is>
+      </c>
+      <c r="E33" s="13" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="F33" s="13" t="n"/>
+      <c r="G33" s="13" t="n"/>
+      <c r="H33" s="48" t="n"/>
+      <c r="I33" s="48" t="n"/>
+      <c r="J33" s="48" t="n"/>
+      <c r="K33" s="15" t="n">
+        <v>3970</v>
+      </c>
+      <c r="L33" s="15" t="n">
+        <v>3800</v>
+      </c>
+      <c r="M33" s="15" t="n"/>
+      <c r="N33" s="16" t="n"/>
+      <c r="O33" s="16" t="n"/>
+      <c r="P33" s="16" t="n"/>
+      <c r="Q33" s="48" t="n"/>
+      <c r="R33" s="48" t="n"/>
+      <c r="S33" s="48" t="n"/>
+      <c r="T33" s="49">
+        <f>IF(AND(H33&lt;&gt;"",Q33&lt;&gt;""),H33-Q33,"")</f>
+        <v/>
+      </c>
+      <c r="U33" s="48" t="n"/>
+      <c r="V33" s="48" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="n">
+        <v>29</v>
+      </c>
+      <c r="B34" s="12" t="inlineStr">
+        <is>
+          <t>2.프린터-1</t>
+        </is>
+      </c>
+      <c r="C34" s="34" t="inlineStr">
+        <is>
+          <t>영수증프린터</t>
+        </is>
+      </c>
+      <c r="D34" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하 (간격 벌리기)</t>
+        </is>
+      </c>
+      <c r="E34" s="13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="F34" s="13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="G34" s="13" t="n"/>
+      <c r="H34" s="48" t="n">
+        <v>4</v>
+      </c>
+      <c r="I34" s="48" t="n">
+        <v>5</v>
+      </c>
+      <c r="J34" s="48" t="n"/>
+      <c r="K34" s="15" t="n">
+        <v>1070</v>
+      </c>
+      <c r="L34" s="15" t="n">
+        <v>1300</v>
+      </c>
+      <c r="M34" s="15" t="n"/>
+      <c r="N34" s="16" t="n"/>
+      <c r="O34" s="16" t="n"/>
+      <c r="P34" s="16" t="n"/>
+      <c r="Q34" s="48" t="n"/>
+      <c r="R34" s="48" t="n"/>
+      <c r="S34" s="48" t="n"/>
+      <c r="T34" s="49">
+        <f>IF(AND(H34&lt;&gt;"",Q34&lt;&gt;""),H34-Q34,"")</f>
+        <v/>
+      </c>
+      <c r="U34" s="48" t="n"/>
+      <c r="V34" s="48" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>2.프린터모델-2</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>BIXOLON</t>
+        </is>
+      </c>
+      <c r="D35" s="50" t="inlineStr">
+        <is>
+          <t>솔바텍 인상</t>
+        </is>
+      </c>
+      <c r="E35" s="13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="F35" s="13" t="n"/>
+      <c r="G35" s="13" t="n"/>
+      <c r="H35" s="48" t="n"/>
+      <c r="I35" s="48" t="n"/>
+      <c r="J35" s="48" t="n"/>
+      <c r="K35" s="15" t="n">
+        <v>370</v>
+      </c>
+      <c r="L35" s="15" t="n"/>
+      <c r="M35" s="15" t="n"/>
+      <c r="N35" s="16" t="n"/>
+      <c r="O35" s="16" t="n"/>
+      <c r="P35" s="16" t="n"/>
+      <c r="Q35" s="48" t="n"/>
+      <c r="R35" s="48" t="n"/>
+      <c r="S35" s="48" t="n"/>
+      <c r="T35" s="49">
+        <f>IF(AND(H35&lt;&gt;"",Q35&lt;&gt;""),H35-Q35,"")</f>
+        <v/>
+      </c>
+      <c r="U35" s="48" t="n"/>
+      <c r="V35" s="48" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="13" t="n">
+        <v>31</v>
+      </c>
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>2.프린터-1</t>
+        </is>
+      </c>
+      <c r="C36" s="34" t="inlineStr">
+        <is>
+          <t>빅솔론프린터</t>
+        </is>
+      </c>
+      <c r="D36" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하</t>
+        </is>
+      </c>
+      <c r="E36" s="13" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="F36" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="13" t="n"/>
+      <c r="H36" s="48" t="n">
+        <v>6</v>
+      </c>
+      <c r="I36" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" s="48" t="n"/>
+      <c r="K36" s="15" t="n">
+        <v>940</v>
+      </c>
+      <c r="L36" s="15" t="n">
+        <v>4000</v>
+      </c>
+      <c r="M36" s="15" t="n"/>
+      <c r="N36" s="16" t="n"/>
+      <c r="O36" s="16" t="n"/>
+      <c r="P36" s="16" t="n"/>
+      <c r="Q36" s="48" t="n"/>
+      <c r="R36" s="48" t="n"/>
+      <c r="S36" s="48" t="n"/>
+      <c r="T36" s="49">
+        <f>IF(AND(H36&lt;&gt;"",Q36&lt;&gt;""),H36-Q36,"")</f>
+        <v/>
+      </c>
+      <c r="U36" s="48" t="n"/>
+      <c r="V36" s="48" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="13" t="n">
+        <v>32</v>
+      </c>
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>4.솔루션SW-1</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="inlineStr">
+        <is>
+          <t>고정자산프로그램</t>
+        </is>
+      </c>
+      <c r="D37" s="50" t="inlineStr">
+        <is>
+          <t>솔바텍 인상</t>
+        </is>
+      </c>
+      <c r="E37" s="13" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="F37" s="13" t="n"/>
+      <c r="G37" s="13" t="n"/>
+      <c r="H37" s="48" t="n"/>
+      <c r="I37" s="48" t="n"/>
+      <c r="J37" s="48" t="n"/>
+      <c r="K37" s="15" t="n">
+        <v>2040</v>
+      </c>
+      <c r="L37" s="15" t="n">
+        <v>1200</v>
+      </c>
+      <c r="M37" s="15" t="n"/>
+      <c r="N37" s="16" t="n"/>
+      <c r="O37" s="16" t="n"/>
+      <c r="P37" s="16" t="n"/>
+      <c r="Q37" s="48" t="n"/>
+      <c r="R37" s="48" t="n"/>
+      <c r="S37" s="48" t="n"/>
+      <c r="T37" s="49">
+        <f>IF(AND(H37&lt;&gt;"",Q37&lt;&gt;""),H37-Q37,"")</f>
+        <v/>
+      </c>
+      <c r="U37" s="48" t="n"/>
+      <c r="V37" s="48" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="13" t="n">
+        <v>33</v>
+      </c>
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t>1.스캐너-1</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>핸드스캐너</t>
+        </is>
+      </c>
+      <c r="D38" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하</t>
+        </is>
+      </c>
+      <c r="E38" s="13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="F38" s="13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G38" s="13" t="n"/>
+      <c r="H38" s="48" t="n"/>
+      <c r="I38" s="48" t="n"/>
+      <c r="J38" s="48" t="n"/>
+      <c r="K38" s="15" t="n">
+        <v>6590</v>
+      </c>
+      <c r="L38" s="15" t="n">
+        <v>8000</v>
+      </c>
+      <c r="M38" s="15" t="n"/>
+      <c r="N38" s="16" t="n"/>
+      <c r="O38" s="16" t="n"/>
+      <c r="P38" s="16" t="n"/>
+      <c r="Q38" s="48" t="n"/>
+      <c r="R38" s="48" t="n"/>
+      <c r="S38" s="48" t="n"/>
+      <c r="T38" s="49">
+        <f>IF(AND(H38&lt;&gt;"",Q38&lt;&gt;""),H38-Q38,"")</f>
+        <v/>
+      </c>
+      <c r="U38" s="48" t="n"/>
+      <c r="V38" s="48" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="13" t="n">
+        <v>34</v>
+      </c>
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>1.스캐너모델-2</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="inlineStr">
+        <is>
+          <t>PM3</t>
+        </is>
+      </c>
+      <c r="D39" s="47" t="inlineStr">
+        <is>
+          <t>솔바텍 인하</t>
+        </is>
+      </c>
+      <c r="E39" s="13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F39" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G39" s="13" t="n"/>
+      <c r="H39" s="48" t="n"/>
+      <c r="I39" s="48" t="n"/>
+      <c r="J39" s="48" t="n"/>
+      <c r="K39" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L39" s="15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="M39" s="15" t="n"/>
+      <c r="N39" s="16" t="n"/>
+      <c r="O39" s="16" t="n"/>
+      <c r="P39" s="16" t="n"/>
+      <c r="Q39" s="48" t="n"/>
+      <c r="R39" s="48" t="n"/>
+      <c r="S39" s="48" t="n"/>
+      <c r="T39" s="49">
+        <f>IF(AND(H39&lt;&gt;"",Q39&lt;&gt;""),H39-Q39,"")</f>
+        <v/>
+      </c>
+      <c r="U39" s="48" t="n"/>
+      <c r="V39" s="48" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="13" t="n">
+        <v>35</v>
+      </c>
+      <c r="B40" s="12" t="inlineStr">
+        <is>
+          <t>2.프린터-1</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="inlineStr">
+        <is>
+          <t>감열식프린터</t>
+        </is>
+      </c>
+      <c r="D40" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하</t>
+        </is>
+      </c>
+      <c r="E40" s="13" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="F40" s="13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G40" s="13" t="n"/>
+      <c r="H40" s="48" t="n">
+        <v>4</v>
+      </c>
+      <c r="I40" s="48" t="n">
+        <v>6</v>
+      </c>
+      <c r="J40" s="48" t="n"/>
+      <c r="K40" s="15" t="n">
+        <v>800</v>
+      </c>
+      <c r="L40" s="15" t="n">
+        <v>1500</v>
+      </c>
+      <c r="M40" s="15" t="n"/>
+      <c r="N40" s="16" t="n"/>
+      <c r="O40" s="16" t="n"/>
+      <c r="P40" s="16" t="n"/>
+      <c r="Q40" s="48" t="n"/>
+      <c r="R40" s="48" t="n"/>
+      <c r="S40" s="48" t="n"/>
+      <c r="T40" s="49">
+        <f>IF(AND(H40&lt;&gt;"",Q40&lt;&gt;""),H40-Q40,"")</f>
+        <v/>
+      </c>
+      <c r="U40" s="48" t="n"/>
+      <c r="V40" s="48" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="13" t="n">
+        <v>36</v>
+      </c>
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>2.프린터모델-2</t>
+        </is>
+      </c>
+      <c r="C41" s="12" t="inlineStr">
+        <is>
+          <t>SLP-DX420</t>
+        </is>
+      </c>
+      <c r="D41" s="47" t="inlineStr">
+        <is>
+          <t>솔바텍 인하</t>
+        </is>
+      </c>
+      <c r="E41" s="13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="F41" s="13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G41" s="13" t="n"/>
+      <c r="H41" s="48" t="n"/>
+      <c r="I41" s="48" t="n"/>
+      <c r="J41" s="48" t="n"/>
+      <c r="K41" s="15" t="n">
+        <v>700</v>
+      </c>
+      <c r="L41" s="15" t="n">
+        <v>1500</v>
+      </c>
+      <c r="M41" s="15" t="n"/>
+      <c r="N41" s="16" t="n"/>
+      <c r="O41" s="16" t="n"/>
+      <c r="P41" s="16" t="n"/>
+      <c r="Q41" s="48" t="n"/>
+      <c r="R41" s="48" t="n"/>
+      <c r="S41" s="48" t="n"/>
+      <c r="T41" s="49">
+        <f>IF(AND(H41&lt;&gt;"",Q41&lt;&gt;""),H41-Q41,"")</f>
+        <v/>
+      </c>
+      <c r="U41" s="48" t="n"/>
+      <c r="V41" s="48" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="13" t="n">
+        <v>37</v>
+      </c>
+      <c r="B42" s="12" t="inlineStr">
+        <is>
+          <t>4.솔루션SW-2</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="inlineStr">
+        <is>
+          <t>재고관리</t>
+        </is>
+      </c>
+      <c r="D42" s="50" t="inlineStr">
+        <is>
+          <t>솔바텍 인상</t>
+        </is>
+      </c>
+      <c r="E42" s="13" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="F42" s="13" t="n"/>
+      <c r="G42" s="13" t="n"/>
+      <c r="H42" s="48" t="n"/>
+      <c r="I42" s="48" t="n"/>
+      <c r="J42" s="48" t="n"/>
+      <c r="K42" s="15" t="n">
+        <v>14000</v>
+      </c>
+      <c r="L42" s="15" t="n">
+        <v>10190</v>
+      </c>
+      <c r="M42" s="15" t="n"/>
+      <c r="N42" s="16" t="n"/>
+      <c r="O42" s="16" t="n"/>
+      <c r="P42" s="16" t="n"/>
+      <c r="Q42" s="48" t="n"/>
+      <c r="R42" s="48" t="n"/>
+      <c r="S42" s="48" t="n"/>
+      <c r="T42" s="49">
+        <f>IF(AND(H42&lt;&gt;"",Q42&lt;&gt;""),H42-Q42,"")</f>
+        <v/>
+      </c>
+      <c r="U42" s="48" t="n"/>
+      <c r="V42" s="48" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="13" t="n">
+        <v>38</v>
+      </c>
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>2.프린터-1</t>
+        </is>
+      </c>
+      <c r="C43" s="34" t="inlineStr">
+        <is>
+          <t>스티커라벨기</t>
+        </is>
+      </c>
+      <c r="D43" s="50" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하 / 솔바텍 인상</t>
+        </is>
+      </c>
+      <c r="E43" s="13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="F43" s="13" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="G43" s="13" t="n"/>
+      <c r="H43" s="48" t="n"/>
+      <c r="I43" s="48" t="n"/>
+      <c r="J43" s="48" t="n"/>
+      <c r="K43" s="15" t="n">
+        <v>2300</v>
+      </c>
+      <c r="L43" s="15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="M43" s="15" t="n"/>
+      <c r="N43" s="16" t="n"/>
+      <c r="O43" s="16" t="n"/>
+      <c r="P43" s="16" t="n"/>
+      <c r="Q43" s="48" t="n"/>
+      <c r="R43" s="48" t="n"/>
+      <c r="S43" s="48" t="n"/>
+      <c r="T43" s="49">
+        <f>IF(AND(H43&lt;&gt;"",Q43&lt;&gt;""),H43-Q43,"")</f>
+        <v/>
+      </c>
+      <c r="U43" s="48" t="n"/>
+      <c r="V43" s="48" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="13" t="n">
+        <v>39</v>
+      </c>
+      <c r="B44" s="12" t="inlineStr">
+        <is>
+          <t>1.스캐너모델-2</t>
+        </is>
+      </c>
+      <c r="C44" s="12" t="inlineStr">
+        <is>
+          <t>DS8178</t>
+        </is>
+      </c>
+      <c r="D44" s="47" t="inlineStr">
+        <is>
+          <t>솔바텍 인하</t>
+        </is>
+      </c>
+      <c r="E44" s="13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="F44" s="13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G44" s="13" t="n"/>
+      <c r="H44" s="48" t="n"/>
+      <c r="I44" s="48" t="n"/>
+      <c r="J44" s="48" t="n"/>
+      <c r="K44" s="15" t="n">
+        <v>800</v>
+      </c>
+      <c r="L44" s="15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="M44" s="15" t="n"/>
+      <c r="N44" s="16" t="n"/>
+      <c r="O44" s="16" t="n"/>
+      <c r="P44" s="16" t="n"/>
+      <c r="Q44" s="48" t="n"/>
+      <c r="R44" s="48" t="n"/>
+      <c r="S44" s="48" t="n"/>
+      <c r="T44" s="49">
+        <f>IF(AND(H44&lt;&gt;"",Q44&lt;&gt;""),H44-Q44,"")</f>
+        <v/>
+      </c>
+      <c r="U44" s="48" t="n"/>
+      <c r="V44" s="48" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="B45" s="12" t="inlineStr">
+        <is>
+          <t>3.라벨</t>
+        </is>
+      </c>
+      <c r="C45" s="12" t="inlineStr">
+        <is>
+          <t>라벨프로그램</t>
+        </is>
+      </c>
+      <c r="D45" s="50" t="inlineStr">
+        <is>
+          <t>솔바텍 인상</t>
+        </is>
+      </c>
+      <c r="E45" s="13" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="F45" s="13" t="n"/>
+      <c r="G45" s="13" t="n"/>
+      <c r="H45" s="48" t="n"/>
+      <c r="I45" s="48" t="n"/>
+      <c r="J45" s="48" t="n"/>
+      <c r="K45" s="15" t="n">
+        <v>1130</v>
+      </c>
+      <c r="L45" s="15" t="n"/>
+      <c r="M45" s="15" t="n"/>
+      <c r="N45" s="16" t="n"/>
+      <c r="O45" s="16" t="n"/>
+      <c r="P45" s="16" t="n"/>
+      <c r="Q45" s="48" t="n"/>
+      <c r="R45" s="48" t="n"/>
+      <c r="S45" s="48" t="n"/>
+      <c r="T45" s="49">
+        <f>IF(AND(H45&lt;&gt;"",Q45&lt;&gt;""),H45-Q45,"")</f>
+        <v/>
+      </c>
+      <c r="U45" s="48" t="n"/>
+      <c r="V45" s="48" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="13" t="n">
+        <v>41</v>
+      </c>
+      <c r="B46" s="12" t="inlineStr">
+        <is>
+          <t>5.리본</t>
+        </is>
+      </c>
+      <c r="C46" s="12" t="inlineStr">
+        <is>
+          <t>레진리본</t>
+        </is>
+      </c>
+      <c r="D46" s="47" t="inlineStr">
+        <is>
+          <t>솔바텍 인하 (간격 벌리기)</t>
+        </is>
+      </c>
+      <c r="E46" s="13" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="F46" s="13" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="G46" s="13" t="n"/>
+      <c r="H46" s="48" t="n"/>
+      <c r="I46" s="48" t="n"/>
+      <c r="J46" s="48" t="n"/>
+      <c r="K46" s="15" t="n">
+        <v>1470</v>
+      </c>
+      <c r="L46" s="15" t="n">
+        <v>2500</v>
+      </c>
+      <c r="M46" s="15" t="n"/>
+      <c r="N46" s="16" t="n"/>
+      <c r="O46" s="16" t="n"/>
+      <c r="P46" s="16" t="n"/>
+      <c r="Q46" s="48" t="n"/>
+      <c r="R46" s="48" t="n"/>
+      <c r="S46" s="48" t="n"/>
+      <c r="T46" s="49">
+        <f>IF(AND(H46&lt;&gt;"",Q46&lt;&gt;""),H46-Q46,"")</f>
+        <v/>
+      </c>
+      <c r="U46" s="48" t="n"/>
+      <c r="V46" s="48" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="13" t="n">
+        <v>42</v>
+      </c>
+      <c r="B47" s="12" t="inlineStr">
+        <is>
+          <t>1.스캐너모델-2</t>
+        </is>
+      </c>
+      <c r="C47" s="12" t="inlineStr">
+        <is>
+          <t>LS2208</t>
+        </is>
+      </c>
+      <c r="D47" s="47" t="inlineStr">
+        <is>
+          <t>솔바텍 인하</t>
+        </is>
+      </c>
+      <c r="E47" s="13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F47" s="13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G47" s="13" t="n"/>
+      <c r="H47" s="48" t="n"/>
+      <c r="I47" s="48" t="n"/>
+      <c r="J47" s="48" t="n"/>
+      <c r="K47" s="15" t="n">
+        <v>1800</v>
+      </c>
+      <c r="L47" s="15" t="n">
+        <v>3000</v>
+      </c>
+      <c r="M47" s="15" t="n"/>
+      <c r="N47" s="16" t="n"/>
+      <c r="O47" s="16" t="n"/>
+      <c r="P47" s="16" t="n"/>
+      <c r="Q47" s="48" t="n"/>
+      <c r="R47" s="48" t="n"/>
+      <c r="S47" s="48" t="n"/>
+      <c r="T47" s="49">
+        <f>IF(AND(H47&lt;&gt;"",Q47&lt;&gt;""),H47-Q47,"")</f>
+        <v/>
+      </c>
+      <c r="U47" s="48" t="n"/>
+      <c r="V47" s="48" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="13" t="n">
+        <v>43</v>
+      </c>
+      <c r="B48" s="12" t="inlineStr">
+        <is>
+          <t>1.스캐너모델-2</t>
+        </is>
+      </c>
+      <c r="C48" s="12" t="inlineStr">
+        <is>
+          <t>DS2278</t>
+        </is>
+      </c>
+      <c r="D48" s="47" t="inlineStr">
+        <is>
+          <t>솔바텍 인하 (간격 벌리기)</t>
+        </is>
+      </c>
+      <c r="E48" s="13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F48" s="13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="G48" s="13" t="n"/>
+      <c r="H48" s="48" t="n"/>
+      <c r="I48" s="48" t="n"/>
+      <c r="J48" s="48" t="n"/>
+      <c r="K48" s="15" t="n">
+        <v>800</v>
+      </c>
+      <c r="L48" s="15" t="n">
+        <v>2500</v>
+      </c>
+      <c r="M48" s="15" t="n"/>
+      <c r="N48" s="16" t="n"/>
+      <c r="O48" s="16" t="n"/>
+      <c r="P48" s="16" t="n"/>
+      <c r="Q48" s="48" t="n"/>
+      <c r="R48" s="48" t="n"/>
+      <c r="S48" s="48" t="n"/>
+      <c r="T48" s="49">
+        <f>IF(AND(H48&lt;&gt;"",Q48&lt;&gt;""),H48-Q48,"")</f>
+        <v/>
+      </c>
+      <c r="U48" s="48" t="n"/>
+      <c r="V48" s="48" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="13" t="n">
+        <v>44</v>
+      </c>
+      <c r="B49" s="12" t="inlineStr">
+        <is>
+          <t>3.라벨</t>
+        </is>
+      </c>
+      <c r="C49" s="12" t="inlineStr">
+        <is>
+          <t>스티커라벨</t>
+        </is>
+      </c>
+      <c r="D49" s="47" t="inlineStr">
+        <is>
+          <t>솔바텍 인하</t>
+        </is>
+      </c>
+      <c r="E49" s="13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="F49" s="13" t="n">
+        <v>29</v>
+      </c>
+      <c r="G49" s="13" t="n"/>
+      <c r="H49" s="48" t="n"/>
+      <c r="I49" s="48" t="n"/>
+      <c r="J49" s="48" t="n"/>
+      <c r="K49" s="15" t="n">
+        <v>3500</v>
+      </c>
+      <c r="L49" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="M49" s="15" t="n"/>
+      <c r="N49" s="16" t="n"/>
+      <c r="O49" s="16" t="n"/>
+      <c r="P49" s="16" t="n"/>
+      <c r="Q49" s="48" t="n"/>
+      <c r="R49" s="48" t="n"/>
+      <c r="S49" s="48" t="n"/>
+      <c r="T49" s="49">
+        <f>IF(AND(H49&lt;&gt;"",Q49&lt;&gt;""),H49-Q49,"")</f>
+        <v/>
+      </c>
+      <c r="U49" s="48" t="n"/>
+      <c r="V49" s="48" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="13" t="n">
+        <v>45</v>
+      </c>
+      <c r="B50" s="12" t="inlineStr">
+        <is>
+          <t>1.스캐너모델-2</t>
+        </is>
+      </c>
+      <c r="C50" s="12" t="inlineStr">
+        <is>
+          <t>LI4278</t>
+        </is>
+      </c>
+      <c r="D50" s="47" t="inlineStr">
+        <is>
+          <t>솔바텍 인하</t>
+        </is>
+      </c>
+      <c r="E50" s="13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="F50" s="13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G50" s="13" t="n"/>
+      <c r="H50" s="48" t="n"/>
+      <c r="I50" s="48" t="n"/>
+      <c r="J50" s="48" t="n"/>
+      <c r="K50" s="15" t="n">
+        <v>700</v>
+      </c>
+      <c r="L50" s="15" t="n">
+        <v>1500</v>
+      </c>
+      <c r="M50" s="15" t="n"/>
+      <c r="N50" s="16" t="n"/>
+      <c r="O50" s="16" t="n"/>
+      <c r="P50" s="16" t="n"/>
+      <c r="Q50" s="48" t="n"/>
+      <c r="R50" s="48" t="n"/>
+      <c r="S50" s="48" t="n"/>
+      <c r="T50" s="49">
+        <f>IF(AND(H50&lt;&gt;"",Q50&lt;&gt;""),H50-Q50,"")</f>
+        <v/>
+      </c>
+      <c r="U50" s="48" t="n"/>
+      <c r="V50" s="48" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="13" t="n">
+        <v>46</v>
+      </c>
+      <c r="B51" s="12" t="inlineStr">
+        <is>
+          <t>1.스캐너-1</t>
+        </is>
+      </c>
+      <c r="C51" s="12" t="inlineStr">
+        <is>
+          <t>2D바코드</t>
+        </is>
+      </c>
+      <c r="D51" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하 (간격 벌리기)</t>
+        </is>
+      </c>
+      <c r="E51" s="13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F51" s="13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G51" s="13" t="n"/>
+      <c r="H51" s="48" t="n"/>
+      <c r="I51" s="48" t="n"/>
+      <c r="J51" s="48" t="n"/>
+      <c r="K51" s="15" t="n">
+        <v>5500</v>
+      </c>
+      <c r="L51" s="15" t="n">
+        <v>5650</v>
+      </c>
+      <c r="M51" s="15" t="n"/>
+      <c r="N51" s="16" t="n"/>
+      <c r="O51" s="16" t="n"/>
+      <c r="P51" s="16" t="n"/>
+      <c r="Q51" s="48" t="n"/>
+      <c r="R51" s="48" t="n"/>
+      <c r="S51" s="48" t="n"/>
+      <c r="T51" s="49">
+        <f>IF(AND(H51&lt;&gt;"",Q51&lt;&gt;""),H51-Q51,"")</f>
+        <v/>
+      </c>
+      <c r="U51" s="48" t="n"/>
+      <c r="V51" s="48" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="13" t="n">
+        <v>47</v>
+      </c>
+      <c r="B52" s="12" t="inlineStr">
+        <is>
+          <t>1.스캐너-1</t>
+        </is>
+      </c>
+      <c r="C52" s="12" t="inlineStr">
+        <is>
+          <t>블루투스스캐너</t>
+        </is>
+      </c>
+      <c r="D52" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하</t>
+        </is>
+      </c>
+      <c r="E52" s="13" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="F52" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="13" t="n"/>
+      <c r="H52" s="48" t="n"/>
+      <c r="I52" s="48" t="n"/>
+      <c r="J52" s="48" t="n"/>
+      <c r="K52" s="15" t="n">
+        <v>430</v>
+      </c>
+      <c r="L52" s="15" t="n">
+        <v>3000</v>
+      </c>
+      <c r="M52" s="15" t="n"/>
+      <c r="N52" s="16" t="n"/>
+      <c r="O52" s="16" t="n"/>
+      <c r="P52" s="16" t="n"/>
+      <c r="Q52" s="48" t="n"/>
+      <c r="R52" s="48" t="n"/>
+      <c r="S52" s="48" t="n"/>
+      <c r="T52" s="49">
+        <f>IF(AND(H52&lt;&gt;"",Q52&lt;&gt;""),H52-Q52,"")</f>
+        <v/>
+      </c>
+      <c r="U52" s="48" t="n"/>
+      <c r="V52" s="48" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="13" t="n">
+        <v>48</v>
+      </c>
+      <c r="B53" s="12" t="inlineStr">
+        <is>
+          <t>1.스캐너-1</t>
+        </is>
+      </c>
+      <c r="C53" s="12" t="inlineStr">
+        <is>
+          <t>QR코드리더기</t>
+        </is>
+      </c>
+      <c r="D53" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하</t>
+        </is>
+      </c>
+      <c r="E53" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="F53" s="13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G53" s="13" t="n"/>
+      <c r="H53" s="48" t="n"/>
+      <c r="I53" s="48" t="n"/>
+      <c r="J53" s="48" t="n"/>
+      <c r="K53" s="15" t="n">
+        <v>600</v>
+      </c>
+      <c r="L53" s="15" t="n">
+        <v>4000</v>
+      </c>
+      <c r="M53" s="15" t="n"/>
+      <c r="N53" s="16" t="n"/>
+      <c r="O53" s="16" t="n"/>
+      <c r="P53" s="16" t="n"/>
+      <c r="Q53" s="48" t="n"/>
+      <c r="R53" s="48" t="n"/>
+      <c r="S53" s="48" t="n"/>
+      <c r="T53" s="49">
+        <f>IF(AND(H53&lt;&gt;"",Q53&lt;&gt;""),H53-Q53,"")</f>
+        <v/>
+      </c>
+      <c r="U53" s="48" t="n"/>
+      <c r="V53" s="48" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="13" t="n">
+        <v>49</v>
+      </c>
+      <c r="B54" s="12" t="inlineStr">
+        <is>
+          <t>1.스캐너모델-2</t>
+        </is>
+      </c>
+      <c r="C54" s="12" t="inlineStr">
+        <is>
+          <t>바코드스캐너거치대</t>
+        </is>
+      </c>
+      <c r="D54" s="50" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하 / 솔바텍 인상</t>
+        </is>
+      </c>
+      <c r="E54" s="13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F54" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="G54" s="13" t="n"/>
+      <c r="H54" s="48" t="n"/>
+      <c r="I54" s="48" t="n"/>
+      <c r="J54" s="48" t="n"/>
+      <c r="K54" s="15" t="n">
+        <v>300</v>
+      </c>
+      <c r="L54" s="15" t="n">
+        <v>300</v>
+      </c>
+      <c r="M54" s="15" t="n"/>
+      <c r="N54" s="16" t="n"/>
+      <c r="O54" s="16" t="n"/>
+      <c r="P54" s="16" t="n"/>
+      <c r="Q54" s="48" t="n"/>
+      <c r="R54" s="48" t="n"/>
+      <c r="S54" s="48" t="n"/>
+      <c r="T54" s="49">
+        <f>IF(AND(H54&lt;&gt;"",Q54&lt;&gt;""),H54-Q54,"")</f>
+        <v/>
+      </c>
+      <c r="U54" s="48" t="n"/>
+      <c r="V54" s="48" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="B55" s="12" t="inlineStr">
+        <is>
+          <t>1.스캐너-1</t>
+        </is>
+      </c>
+      <c r="C55" s="12" t="inlineStr">
+        <is>
+          <t>바코드종류</t>
+        </is>
+      </c>
+      <c r="D55" s="50" t="inlineStr">
+        <is>
+          <t>SB렌탈 인하 / 솔바텍 인상</t>
+        </is>
+      </c>
+      <c r="E55" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F55" s="13" t="n"/>
+      <c r="G55" s="13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H55" s="48" t="n"/>
+      <c r="I55" s="48" t="n"/>
+      <c r="J55" s="48" t="n"/>
+      <c r="K55" s="15" t="n">
+        <v>300</v>
+      </c>
+      <c r="L55" s="15" t="n">
+        <v>500</v>
+      </c>
+      <c r="M55" s="15" t="n">
+        <v>260</v>
+      </c>
+      <c r="N55" s="16" t="n"/>
+      <c r="O55" s="16" t="n"/>
+      <c r="P55" s="16" t="n"/>
+      <c r="Q55" s="48" t="n"/>
+      <c r="R55" s="48" t="n"/>
+      <c r="S55" s="48" t="n"/>
+      <c r="T55" s="49">
+        <f>IF(AND(H55&lt;&gt;"",Q55&lt;&gt;""),H55-Q55,"")</f>
+        <v/>
+      </c>
+      <c r="U55" s="48" t="n"/>
+      <c r="V55" s="48" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="13" t="n">
+        <v>51</v>
+      </c>
+      <c r="B56" s="12" t="inlineStr">
+        <is>
+          <t>1.스캐너모델-2</t>
+        </is>
+      </c>
+      <c r="C56" s="12" t="inlineStr">
+        <is>
+          <t>DS9908</t>
+        </is>
+      </c>
+      <c r="D56" s="47" t="inlineStr">
+        <is>
+          <t>솔바텍 인하</t>
+        </is>
+      </c>
+      <c r="E56" s="13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F56" s="13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G56" s="13" t="n"/>
+      <c r="H56" s="48" t="n"/>
+      <c r="I56" s="48" t="n"/>
+      <c r="J56" s="48" t="n"/>
+      <c r="K56" s="15" t="n">
+        <v>1500</v>
+      </c>
+      <c r="L56" s="15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="M56" s="15" t="n"/>
+      <c r="N56" s="16" t="n"/>
+      <c r="O56" s="16" t="n"/>
+      <c r="P56" s="16" t="n"/>
+      <c r="Q56" s="48" t="n"/>
+      <c r="R56" s="48" t="n"/>
+      <c r="S56" s="48" t="n"/>
+      <c r="T56" s="49">
+        <f>IF(AND(H56&lt;&gt;"",Q56&lt;&gt;""),H56-Q56,"")</f>
+        <v/>
+      </c>
+      <c r="U56" s="48" t="n"/>
+      <c r="V56" s="48" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="13" t="n">
+        <v>52</v>
+      </c>
+      <c r="B57" s="12" t="inlineStr">
+        <is>
+          <t>1.스캐너모델-2</t>
+        </is>
+      </c>
+      <c r="C57" s="12" t="inlineStr">
+        <is>
+          <t>DS9308</t>
+        </is>
+      </c>
+      <c r="D57" s="47" t="inlineStr">
+        <is>
+          <t>솔바텍 인하 (간격 벌리기)</t>
+        </is>
+      </c>
+      <c r="E57" s="13" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="F57" s="13" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G57" s="13" t="n"/>
+      <c r="H57" s="48" t="n"/>
+      <c r="I57" s="48" t="n"/>
+      <c r="J57" s="48" t="n"/>
+      <c r="K57" s="15" t="n">
+        <v>500</v>
+      </c>
+      <c r="L57" s="15" t="n">
+        <v>2100</v>
+      </c>
+      <c r="M57" s="15" t="n"/>
+      <c r="N57" s="16" t="n"/>
+      <c r="O57" s="16" t="n"/>
+      <c r="P57" s="16" t="n"/>
+      <c r="Q57" s="48" t="n"/>
+      <c r="R57" s="48" t="n"/>
+      <c r="S57" s="48" t="n"/>
+      <c r="T57" s="49">
+        <f>IF(AND(H57&lt;&gt;"",Q57&lt;&gt;""),H57-Q57,"")</f>
+        <v/>
+      </c>
+      <c r="U57" s="48" t="n"/>
+      <c r="V57" s="48" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="13" t="n">
+        <v>53</v>
+      </c>
+      <c r="B58" s="12" t="inlineStr">
+        <is>
+          <t>6.산업용PDA-1</t>
+        </is>
+      </c>
+      <c r="C58" s="12" t="inlineStr">
+        <is>
+          <t>산업용PDA</t>
+        </is>
+      </c>
+      <c r="D58" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하</t>
+        </is>
+      </c>
+      <c r="E58" s="13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="F58" s="13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G58" s="13" t="n"/>
+      <c r="H58" s="48" t="n"/>
+      <c r="I58" s="48" t="n"/>
+      <c r="J58" s="48" t="n"/>
+      <c r="K58" s="15" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L58" s="15" t="n">
+        <v>10000</v>
+      </c>
+      <c r="M58" s="15" t="n"/>
+      <c r="N58" s="16" t="n"/>
+      <c r="O58" s="16" t="n"/>
+      <c r="P58" s="16" t="n"/>
+      <c r="Q58" s="48" t="n"/>
+      <c r="R58" s="48" t="n"/>
+      <c r="S58" s="48" t="n"/>
+      <c r="T58" s="49">
+        <f>IF(AND(H58&lt;&gt;"",Q58&lt;&gt;""),H58-Q58,"")</f>
+        <v/>
+      </c>
+      <c r="U58" s="48" t="n"/>
+      <c r="V58" s="48" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="13" t="n">
+        <v>54</v>
+      </c>
+      <c r="B59" s="12" t="inlineStr">
+        <is>
+          <t>1.스캐너-1</t>
+        </is>
+      </c>
+      <c r="C59" s="12" t="inlineStr">
+        <is>
+          <t>큐알코드스캐너</t>
+        </is>
+      </c>
+      <c r="D59" s="50" t="inlineStr">
+        <is>
+          <t>솔바텍 인상</t>
+        </is>
+      </c>
+      <c r="E59" s="13" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="F59" s="13" t="n"/>
+      <c r="G59" s="13" t="n"/>
+      <c r="H59" s="48" t="n"/>
+      <c r="I59" s="48" t="n"/>
+      <c r="J59" s="48" t="n"/>
+      <c r="K59" s="15" t="n">
+        <v>490</v>
+      </c>
+      <c r="L59" s="15" t="n">
+        <v>130</v>
+      </c>
+      <c r="M59" s="15" t="n"/>
+      <c r="N59" s="16" t="n"/>
+      <c r="O59" s="16" t="n"/>
+      <c r="P59" s="16" t="n"/>
+      <c r="Q59" s="48" t="n"/>
+      <c r="R59" s="48" t="n"/>
+      <c r="S59" s="48" t="n"/>
+      <c r="T59" s="49">
+        <f>IF(AND(H59&lt;&gt;"",Q59&lt;&gt;""),H59-Q59,"")</f>
+        <v/>
+      </c>
+      <c r="U59" s="48" t="n"/>
+      <c r="V59" s="48" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="13" t="n">
+        <v>55</v>
+      </c>
+      <c r="B60" s="12" t="inlineStr">
+        <is>
+          <t>3.라벨</t>
+        </is>
+      </c>
+      <c r="C60" s="12" t="inlineStr">
+        <is>
+          <t>바코드라벨지</t>
+        </is>
+      </c>
+      <c r="D60" s="47" t="inlineStr">
+        <is>
+          <t>솔바텍 인하 (간격 벌리기) / SB렌탈 인하</t>
+        </is>
+      </c>
+      <c r="E60" s="13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="F60" s="13" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G60" s="13" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="H60" s="48" t="n"/>
+      <c r="I60" s="48" t="n"/>
+      <c r="J60" s="48" t="n"/>
+      <c r="K60" s="15" t="n">
+        <v>4000</v>
+      </c>
+      <c r="L60" s="15" t="n">
+        <v>6000</v>
+      </c>
+      <c r="M60" s="15" t="n">
+        <v>1600</v>
+      </c>
+      <c r="N60" s="16" t="n"/>
+      <c r="O60" s="16" t="n"/>
+      <c r="P60" s="16" t="n"/>
+      <c r="Q60" s="48" t="n"/>
+      <c r="R60" s="48" t="n"/>
+      <c r="S60" s="48" t="n"/>
+      <c r="T60" s="49">
+        <f>IF(AND(H60&lt;&gt;"",Q60&lt;&gt;""),H60-Q60,"")</f>
+        <v/>
+      </c>
+      <c r="U60" s="48" t="n"/>
+      <c r="V60" s="48" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="13" t="n">
+        <v>56</v>
+      </c>
+      <c r="B61" s="12" t="inlineStr">
+        <is>
+          <t>1.스캐너-1</t>
+        </is>
+      </c>
+      <c r="C61" s="12" t="inlineStr">
+        <is>
+          <t>무선바코드리더기</t>
+        </is>
+      </c>
+      <c r="D61" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하</t>
+        </is>
+      </c>
+      <c r="E61" s="13" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F61" s="13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G61" s="13" t="n"/>
+      <c r="H61" s="48" t="n"/>
+      <c r="I61" s="48" t="n"/>
+      <c r="J61" s="48" t="n"/>
+      <c r="K61" s="15" t="n">
+        <v>500</v>
+      </c>
+      <c r="L61" s="15" t="n">
+        <v>2500</v>
+      </c>
+      <c r="M61" s="15" t="n"/>
+      <c r="N61" s="16" t="n"/>
+      <c r="O61" s="16" t="n"/>
+      <c r="P61" s="16" t="n"/>
+      <c r="Q61" s="48" t="n"/>
+      <c r="R61" s="48" t="n"/>
+      <c r="S61" s="48" t="n"/>
+      <c r="T61" s="49">
+        <f>IF(AND(H61&lt;&gt;"",Q61&lt;&gt;""),H61-Q61,"")</f>
+        <v/>
+      </c>
+      <c r="U61" s="48" t="n"/>
+      <c r="V61" s="48" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="13" t="n">
+        <v>57</v>
+      </c>
+      <c r="B62" s="12" t="inlineStr">
+        <is>
+          <t>2.프린터모델-2</t>
+        </is>
+      </c>
+      <c r="C62" s="12" t="inlineStr">
+        <is>
+          <t>SLP-DX220</t>
+        </is>
+      </c>
+      <c r="D62" s="47" t="inlineStr">
+        <is>
+          <t>솔바텍 인하 (간격 벌리기)</t>
+        </is>
+      </c>
+      <c r="E62" s="13" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="F62" s="13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G62" s="13" t="n"/>
+      <c r="H62" s="48" t="n"/>
+      <c r="I62" s="48" t="n"/>
+      <c r="J62" s="48" t="n"/>
+      <c r="K62" s="15" t="n">
+        <v>300</v>
+      </c>
+      <c r="L62" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="M62" s="15" t="n"/>
+      <c r="N62" s="16" t="n"/>
+      <c r="O62" s="16" t="n"/>
+      <c r="P62" s="16" t="n"/>
+      <c r="Q62" s="48" t="n"/>
+      <c r="R62" s="48" t="n"/>
+      <c r="S62" s="48" t="n"/>
+      <c r="T62" s="49">
+        <f>IF(AND(H62&lt;&gt;"",Q62&lt;&gt;""),H62-Q62,"")</f>
+        <v/>
+      </c>
+      <c r="U62" s="48" t="n"/>
+      <c r="V62" s="48" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="13" t="n">
+        <v>58</v>
+      </c>
+      <c r="B63" s="12" t="inlineStr">
+        <is>
+          <t>3.라벨</t>
+        </is>
+      </c>
+      <c r="C63" s="12" t="inlineStr">
+        <is>
+          <t>감열지라벨</t>
+        </is>
+      </c>
+      <c r="D63" s="47" t="inlineStr">
+        <is>
+          <t>솔바텍 인하</t>
+        </is>
+      </c>
+      <c r="E63" s="13" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="F63" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="G63" s="13" t="n"/>
+      <c r="H63" s="48" t="n"/>
+      <c r="I63" s="48" t="n"/>
+      <c r="J63" s="48" t="n"/>
+      <c r="K63" s="15" t="n">
+        <v>1650</v>
+      </c>
+      <c r="L63" s="15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="M63" s="15" t="n"/>
+      <c r="N63" s="16" t="n"/>
+      <c r="O63" s="16" t="n"/>
+      <c r="P63" s="16" t="n"/>
+      <c r="Q63" s="48" t="n"/>
+      <c r="R63" s="48" t="n"/>
+      <c r="S63" s="48" t="n"/>
+      <c r="T63" s="49">
+        <f>IF(AND(H63&lt;&gt;"",Q63&lt;&gt;""),H63-Q63,"")</f>
+        <v/>
+      </c>
+      <c r="U63" s="48" t="n"/>
+      <c r="V63" s="48" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="13" t="n">
+        <v>59</v>
+      </c>
+      <c r="B64" s="12" t="inlineStr">
+        <is>
+          <t>2.프린터-1</t>
+        </is>
+      </c>
+      <c r="C64" s="34" t="inlineStr">
+        <is>
+          <t>라벨지프린터</t>
+        </is>
+      </c>
+      <c r="D64" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하</t>
+        </is>
+      </c>
+      <c r="E64" s="13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="F64" s="13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="G64" s="13" t="n"/>
+      <c r="H64" s="48" t="n"/>
+      <c r="I64" s="48" t="n">
+        <v>6</v>
+      </c>
+      <c r="J64" s="48" t="n"/>
+      <c r="K64" s="15" t="n">
+        <v>800</v>
+      </c>
+      <c r="L64" s="15" t="n">
+        <v>1790</v>
+      </c>
+      <c r="M64" s="15" t="n"/>
+      <c r="N64" s="16" t="n"/>
+      <c r="O64" s="16" t="n"/>
+      <c r="P64" s="16" t="n"/>
+      <c r="Q64" s="48" t="n"/>
+      <c r="R64" s="48" t="n"/>
+      <c r="S64" s="48" t="n"/>
+      <c r="T64" s="49">
+        <f>IF(AND(H64&lt;&gt;"",Q64&lt;&gt;""),H64-Q64,"")</f>
+        <v/>
+      </c>
+      <c r="U64" s="48" t="n"/>
+      <c r="V64" s="48" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="B65" s="12" t="inlineStr">
+        <is>
+          <t>2.프린터-1</t>
+        </is>
+      </c>
+      <c r="C65" s="34" t="inlineStr">
+        <is>
+          <t>스티커출력기</t>
+        </is>
+      </c>
+      <c r="D65" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하</t>
+        </is>
+      </c>
+      <c r="E65" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="F65" s="13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G65" s="13" t="n"/>
+      <c r="H65" s="48" t="n">
+        <v>7</v>
+      </c>
+      <c r="I65" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="J65" s="48" t="n"/>
+      <c r="K65" s="15" t="n">
+        <v>400</v>
+      </c>
+      <c r="L65" s="15" t="n">
+        <v>4000</v>
+      </c>
+      <c r="M65" s="15" t="n"/>
+      <c r="N65" s="16" t="n"/>
+      <c r="O65" s="16" t="n"/>
+      <c r="P65" s="16" t="n"/>
+      <c r="Q65" s="48" t="n"/>
+      <c r="R65" s="48" t="n"/>
+      <c r="S65" s="48" t="n"/>
+      <c r="T65" s="49">
+        <f>IF(AND(H65&lt;&gt;"",Q65&lt;&gt;""),H65-Q65,"")</f>
+        <v/>
+      </c>
+      <c r="U65" s="48" t="n"/>
+      <c r="V65" s="48" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="13" t="n">
+        <v>61</v>
+      </c>
+      <c r="B66" s="12" t="inlineStr">
+        <is>
+          <t>3.라벨</t>
+        </is>
+      </c>
+      <c r="C66" s="12" t="inlineStr">
+        <is>
+          <t>바코드제작</t>
+        </is>
+      </c>
+      <c r="D66" s="50" t="inlineStr">
+        <is>
+          <t>SB렌탈 인하 / 솔바텍 인상</t>
+        </is>
+      </c>
+      <c r="E66" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="F66" s="13" t="n"/>
+      <c r="G66" s="13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H66" s="48" t="n"/>
+      <c r="I66" s="48" t="n"/>
+      <c r="J66" s="48" t="n"/>
+      <c r="K66" s="15" t="n">
+        <v>1540</v>
+      </c>
+      <c r="L66" s="15" t="n"/>
+      <c r="M66" s="15" t="n">
+        <v>1030</v>
+      </c>
+      <c r="N66" s="16" t="n"/>
+      <c r="O66" s="16" t="n"/>
+      <c r="P66" s="16" t="n"/>
+      <c r="Q66" s="48" t="n"/>
+      <c r="R66" s="48" t="n"/>
+      <c r="S66" s="48" t="n"/>
+      <c r="T66" s="49">
+        <f>IF(AND(H66&lt;&gt;"",Q66&lt;&gt;""),H66-Q66,"")</f>
+        <v/>
+      </c>
+      <c r="U66" s="48" t="n"/>
+      <c r="V66" s="48" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="13" t="n">
+        <v>62</v>
+      </c>
+      <c r="B67" s="12" t="inlineStr">
+        <is>
+          <t>3.라벨</t>
+        </is>
+      </c>
+      <c r="C67" s="12" t="inlineStr">
+        <is>
+          <t>바코드용지</t>
+        </is>
+      </c>
+      <c r="D67" s="47" t="inlineStr">
+        <is>
+          <t>솔바텍 인하</t>
+        </is>
+      </c>
+      <c r="E67" s="13" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="F67" s="13" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G67" s="13" t="n"/>
+      <c r="H67" s="48" t="n"/>
+      <c r="I67" s="48" t="n"/>
+      <c r="J67" s="48" t="n"/>
+      <c r="K67" s="15" t="n">
+        <v>1500</v>
+      </c>
+      <c r="L67" s="15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="M67" s="15" t="n"/>
+      <c r="N67" s="16" t="n"/>
+      <c r="O67" s="16" t="n"/>
+      <c r="P67" s="16" t="n"/>
+      <c r="Q67" s="48" t="n"/>
+      <c r="R67" s="48" t="n"/>
+      <c r="S67" s="48" t="n"/>
+      <c r="T67" s="49">
+        <f>IF(AND(H67&lt;&gt;"",Q67&lt;&gt;""),H67-Q67,"")</f>
+        <v/>
+      </c>
+      <c r="U67" s="48" t="n"/>
+      <c r="V67" s="48" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="13" t="n">
+        <v>63</v>
+      </c>
+      <c r="B68" s="12" t="inlineStr">
+        <is>
+          <t>1.스캐너-1</t>
+        </is>
+      </c>
+      <c r="C68" s="12" t="inlineStr">
+        <is>
+          <t>2차원바코드</t>
+        </is>
+      </c>
+      <c r="D68" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하</t>
+        </is>
+      </c>
+      <c r="E68" s="13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F68" s="13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G68" s="13" t="n"/>
+      <c r="H68" s="48" t="n"/>
+      <c r="I68" s="48" t="n"/>
+      <c r="J68" s="48" t="n"/>
+      <c r="K68" s="15" t="n">
+        <v>2900</v>
+      </c>
+      <c r="L68" s="15" t="n">
+        <v>3200</v>
+      </c>
+      <c r="M68" s="15" t="n"/>
+      <c r="N68" s="16" t="n"/>
+      <c r="O68" s="16" t="n"/>
+      <c r="P68" s="16" t="n"/>
+      <c r="Q68" s="48" t="n"/>
+      <c r="R68" s="48" t="n"/>
+      <c r="S68" s="48" t="n"/>
+      <c r="T68" s="49">
+        <f>IF(AND(H68&lt;&gt;"",Q68&lt;&gt;""),H68-Q68,"")</f>
+        <v/>
+      </c>
+      <c r="U68" s="48" t="n"/>
+      <c r="V68" s="48" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="13" t="n">
+        <v>64</v>
+      </c>
+      <c r="B69" s="12" t="inlineStr">
+        <is>
+          <t>2.프린터-1</t>
+        </is>
+      </c>
+      <c r="C69" s="34" t="inlineStr">
+        <is>
+          <t>제브라라벨프린터</t>
+        </is>
+      </c>
+      <c r="D69" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하 (간격 벌리기)</t>
+        </is>
+      </c>
+      <c r="E69" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="F69" s="13" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="G69" s="13" t="n"/>
+      <c r="H69" s="48" t="n"/>
+      <c r="I69" s="48" t="n">
+        <v>10</v>
+      </c>
+      <c r="J69" s="48" t="n"/>
+      <c r="K69" s="15" t="n">
+        <v>700</v>
+      </c>
+      <c r="L69" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="M69" s="15" t="n"/>
+      <c r="N69" s="16" t="n"/>
+      <c r="O69" s="16" t="n"/>
+      <c r="P69" s="16" t="n"/>
+      <c r="Q69" s="48" t="n"/>
+      <c r="R69" s="48" t="n"/>
+      <c r="S69" s="48" t="n"/>
+      <c r="T69" s="49">
+        <f>IF(AND(H69&lt;&gt;"",Q69&lt;&gt;""),H69-Q69,"")</f>
+        <v/>
+      </c>
+      <c r="U69" s="48" t="n"/>
+      <c r="V69" s="48" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="13" t="n">
+        <v>65</v>
+      </c>
+      <c r="B70" s="12" t="inlineStr">
+        <is>
+          <t>3.라벨</t>
+        </is>
+      </c>
+      <c r="C70" s="12" t="inlineStr">
+        <is>
+          <t>바코드생성프로그램</t>
+        </is>
+      </c>
+      <c r="D70" s="50" t="inlineStr">
+        <is>
+          <t>솔바텍 인상</t>
+        </is>
+      </c>
+      <c r="E70" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="F70" s="13" t="n"/>
+      <c r="G70" s="13" t="n"/>
+      <c r="H70" s="48" t="n"/>
+      <c r="I70" s="48" t="n"/>
+      <c r="J70" s="48" t="n"/>
+      <c r="K70" s="15" t="n">
+        <v>3000</v>
+      </c>
+      <c r="L70" s="15" t="n"/>
+      <c r="M70" s="15" t="n"/>
+      <c r="N70" s="16" t="n"/>
+      <c r="O70" s="16" t="n"/>
+      <c r="P70" s="16" t="n"/>
+      <c r="Q70" s="48" t="n"/>
+      <c r="R70" s="48" t="n"/>
+      <c r="S70" s="48" t="n"/>
+      <c r="T70" s="49">
+        <f>IF(AND(H70&lt;&gt;"",Q70&lt;&gt;""),H70-Q70,"")</f>
+        <v/>
+      </c>
+      <c r="U70" s="48" t="n"/>
+      <c r="V70" s="48" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="13" t="n">
+        <v>66</v>
+      </c>
+      <c r="B71" s="12" t="inlineStr">
+        <is>
+          <t>5.리본</t>
+        </is>
+      </c>
+      <c r="C71" s="12" t="inlineStr">
+        <is>
+          <t>라벨먹지</t>
+        </is>
+      </c>
+      <c r="D71" s="50" t="inlineStr">
+        <is>
+          <t>솔바텍 인상</t>
+        </is>
+      </c>
+      <c r="E71" s="13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="F71" s="13" t="n"/>
+      <c r="G71" s="13" t="n"/>
+      <c r="H71" s="48" t="n"/>
+      <c r="I71" s="48" t="n"/>
+      <c r="J71" s="48" t="n"/>
+      <c r="K71" s="15" t="n">
+        <v>1810</v>
+      </c>
+      <c r="L71" s="15" t="n"/>
+      <c r="M71" s="15" t="n"/>
+      <c r="N71" s="16" t="n"/>
+      <c r="O71" s="16" t="n"/>
+      <c r="P71" s="16" t="n"/>
+      <c r="Q71" s="48" t="n"/>
+      <c r="R71" s="48" t="n"/>
+      <c r="S71" s="48" t="n"/>
+      <c r="T71" s="49">
+        <f>IF(AND(H71&lt;&gt;"",Q71&lt;&gt;""),H71-Q71,"")</f>
+        <v/>
+      </c>
+      <c r="U71" s="48" t="n"/>
+      <c r="V71" s="48" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="13" t="n">
+        <v>67</v>
+      </c>
+      <c r="B72" s="12" t="inlineStr">
+        <is>
+          <t>5.리본</t>
+        </is>
+      </c>
+      <c r="C72" s="12" t="inlineStr">
+        <is>
+          <t>왁스레진리본</t>
+        </is>
+      </c>
+      <c r="D72" s="47" t="inlineStr">
+        <is>
+          <t>솔바텍 인하</t>
+        </is>
+      </c>
+      <c r="E72" s="13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F72" s="13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G72" s="13" t="n"/>
+      <c r="H72" s="48" t="n"/>
+      <c r="I72" s="48" t="n"/>
+      <c r="J72" s="48" t="n"/>
+      <c r="K72" s="15" t="n">
+        <v>1500</v>
+      </c>
+      <c r="L72" s="15" t="n">
+        <v>4000</v>
+      </c>
+      <c r="M72" s="15" t="n"/>
+      <c r="N72" s="16" t="n"/>
+      <c r="O72" s="16" t="n"/>
+      <c r="P72" s="16" t="n"/>
+      <c r="Q72" s="48" t="n"/>
+      <c r="R72" s="48" t="n"/>
+      <c r="S72" s="48" t="n"/>
+      <c r="T72" s="49">
+        <f>IF(AND(H72&lt;&gt;"",Q72&lt;&gt;""),H72-Q72,"")</f>
+        <v/>
+      </c>
+      <c r="U72" s="48" t="n"/>
+      <c r="V72" s="48" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="13" t="n">
+        <v>68</v>
+      </c>
+      <c r="B73" s="12" t="inlineStr">
+        <is>
+          <t>1.스캐너-1</t>
+        </is>
+      </c>
+      <c r="C73" s="12" t="inlineStr">
+        <is>
+          <t>평판스캐너</t>
+        </is>
+      </c>
+      <c r="D73" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하</t>
+        </is>
+      </c>
+      <c r="E73" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="F73" s="13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G73" s="13" t="n"/>
+      <c r="H73" s="48" t="n"/>
+      <c r="I73" s="48" t="n"/>
+      <c r="J73" s="48" t="n"/>
+      <c r="K73" s="15" t="n">
+        <v>470</v>
+      </c>
+      <c r="L73" s="15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="M73" s="15" t="n"/>
+      <c r="N73" s="16" t="n"/>
+      <c r="O73" s="16" t="n"/>
+      <c r="P73" s="16" t="n"/>
+      <c r="Q73" s="48" t="n"/>
+      <c r="R73" s="48" t="n"/>
+      <c r="S73" s="48" t="n"/>
+      <c r="T73" s="49">
+        <f>IF(AND(H73&lt;&gt;"",Q73&lt;&gt;""),H73-Q73,"")</f>
+        <v/>
+      </c>
+      <c r="U73" s="48" t="n"/>
+      <c r="V73" s="48" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="13" t="n">
+        <v>69</v>
+      </c>
+      <c r="B74" s="12" t="inlineStr">
+        <is>
+          <t>1.스캐너-1</t>
+        </is>
+      </c>
+      <c r="C74" s="12" t="inlineStr">
+        <is>
+          <t>고정식스캐너</t>
+        </is>
+      </c>
+      <c r="D74" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하</t>
+        </is>
+      </c>
+      <c r="E74" s="13" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="F74" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="13" t="n"/>
+      <c r="H74" s="48" t="n"/>
+      <c r="I74" s="48" t="n"/>
+      <c r="J74" s="48" t="n"/>
+      <c r="K74" s="15" t="n">
+        <v>3500</v>
+      </c>
+      <c r="L74" s="15" t="n">
+        <v>10000</v>
+      </c>
+      <c r="M74" s="15" t="n"/>
+      <c r="N74" s="16" t="n"/>
+      <c r="O74" s="16" t="n"/>
+      <c r="P74" s="16" t="n"/>
+      <c r="Q74" s="48" t="n"/>
+      <c r="R74" s="48" t="n"/>
+      <c r="S74" s="48" t="n"/>
+      <c r="T74" s="49">
+        <f>IF(AND(H74&lt;&gt;"",Q74&lt;&gt;""),H74-Q74,"")</f>
+        <v/>
+      </c>
+      <c r="U74" s="48" t="n"/>
+      <c r="V74" s="48" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="13" t="n">
+        <v>70</v>
+      </c>
+      <c r="B75" s="12" t="inlineStr">
+        <is>
+          <t>2.프린터-1</t>
+        </is>
+      </c>
+      <c r="C75" s="34" t="inlineStr">
+        <is>
+          <t>라벨프린터추천</t>
+        </is>
+      </c>
+      <c r="D75" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하 (간격 벌리기)</t>
+        </is>
+      </c>
+      <c r="E75" s="13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="F75" s="13" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="G75" s="13" t="n"/>
+      <c r="H75" s="48" t="n">
+        <v>7</v>
+      </c>
+      <c r="I75" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="J75" s="48" t="n"/>
+      <c r="K75" s="15" t="n">
+        <v>1580</v>
+      </c>
+      <c r="L75" s="15" t="n">
+        <v>3000</v>
+      </c>
+      <c r="M75" s="15" t="n"/>
+      <c r="N75" s="16" t="n"/>
+      <c r="O75" s="16" t="n"/>
+      <c r="P75" s="16" t="n"/>
+      <c r="Q75" s="48" t="n"/>
+      <c r="R75" s="48" t="n"/>
+      <c r="S75" s="48" t="n"/>
+      <c r="T75" s="49">
+        <f>IF(AND(H75&lt;&gt;"",Q75&lt;&gt;""),H75-Q75,"")</f>
+        <v/>
+      </c>
+      <c r="U75" s="48" t="n"/>
+      <c r="V75" s="48" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="13" t="n">
+        <v>71</v>
+      </c>
+      <c r="B76" s="12" t="inlineStr">
+        <is>
+          <t>6.PDA모델-3</t>
+        </is>
+      </c>
+      <c r="C76" s="12" t="inlineStr">
+        <is>
+          <t>M3SL20</t>
+        </is>
+      </c>
+      <c r="D76" s="50" t="inlineStr">
+        <is>
+          <t>솔바텍 인상</t>
+        </is>
+      </c>
+      <c r="E76" s="13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="F76" s="13" t="n"/>
+      <c r="G76" s="13" t="n"/>
+      <c r="H76" s="48" t="n"/>
+      <c r="I76" s="48" t="n"/>
+      <c r="J76" s="48" t="n"/>
+      <c r="K76" s="15" t="n">
+        <v>70</v>
+      </c>
+      <c r="L76" s="15" t="n"/>
+      <c r="M76" s="15" t="n"/>
+      <c r="N76" s="16" t="n"/>
+      <c r="O76" s="16" t="n"/>
+      <c r="P76" s="16" t="n"/>
+      <c r="Q76" s="48" t="n"/>
+      <c r="R76" s="48" t="n"/>
+      <c r="S76" s="48" t="n"/>
+      <c r="T76" s="49">
+        <f>IF(AND(H76&lt;&gt;"",Q76&lt;&gt;""),H76-Q76,"")</f>
+        <v/>
+      </c>
+      <c r="U76" s="48" t="n"/>
+      <c r="V76" s="48" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="13" t="n">
+        <v>72</v>
+      </c>
+      <c r="B77" s="12" t="inlineStr">
+        <is>
+          <t>1.스캐너-1</t>
+        </is>
+      </c>
+      <c r="C77" s="12" t="inlineStr">
+        <is>
+          <t>모바일스캐너</t>
+        </is>
+      </c>
+      <c r="D77" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하</t>
+        </is>
+      </c>
+      <c r="E77" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F77" s="13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G77" s="13" t="n"/>
+      <c r="H77" s="48" t="n"/>
+      <c r="I77" s="48" t="n"/>
+      <c r="J77" s="48" t="n"/>
+      <c r="K77" s="15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="L77" s="15" t="n">
+        <v>3000</v>
+      </c>
+      <c r="M77" s="15" t="n"/>
+      <c r="N77" s="16" t="n"/>
+      <c r="O77" s="16" t="n"/>
+      <c r="P77" s="16" t="n"/>
+      <c r="Q77" s="48" t="n"/>
+      <c r="R77" s="48" t="n"/>
+      <c r="S77" s="48" t="n"/>
+      <c r="T77" s="49">
+        <f>IF(AND(H77&lt;&gt;"",Q77&lt;&gt;""),H77-Q77,"")</f>
+        <v/>
+      </c>
+      <c r="U77" s="48" t="n"/>
+      <c r="V77" s="48" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="13" t="n">
+        <v>73</v>
+      </c>
+      <c r="B78" s="12" t="inlineStr">
+        <is>
+          <t>1.스캐너-1</t>
+        </is>
+      </c>
+      <c r="C78" s="12" t="inlineStr">
+        <is>
+          <t>데이타로직</t>
+        </is>
+      </c>
+      <c r="D78" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하</t>
+        </is>
+      </c>
+      <c r="E78" s="13" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F78" s="13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G78" s="13" t="n"/>
+      <c r="H78" s="48" t="n"/>
+      <c r="I78" s="48" t="n"/>
+      <c r="J78" s="48" t="n"/>
+      <c r="K78" s="15" t="n">
+        <v>500</v>
+      </c>
+      <c r="L78" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="M78" s="15" t="n"/>
+      <c r="N78" s="16" t="n"/>
+      <c r="O78" s="16" t="n"/>
+      <c r="P78" s="16" t="n"/>
+      <c r="Q78" s="48" t="n"/>
+      <c r="R78" s="48" t="n"/>
+      <c r="S78" s="48" t="n"/>
+      <c r="T78" s="49">
+        <f>IF(AND(H78&lt;&gt;"",Q78&lt;&gt;""),H78-Q78,"")</f>
+        <v/>
+      </c>
+      <c r="U78" s="48" t="n"/>
+      <c r="V78" s="48" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="13" t="n">
+        <v>74</v>
+      </c>
+      <c r="B79" s="12" t="inlineStr">
+        <is>
+          <t>1.스캐너-1</t>
+        </is>
+      </c>
+      <c r="C79" s="12" t="inlineStr">
+        <is>
+          <t>바코드리더</t>
+        </is>
+      </c>
+      <c r="D79" s="50" t="inlineStr">
+        <is>
+          <t>솔바텍 인상</t>
+        </is>
+      </c>
+      <c r="E79" s="13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="F79" s="13" t="n"/>
+      <c r="G79" s="13" t="n"/>
+      <c r="H79" s="48" t="n"/>
+      <c r="I79" s="48" t="n"/>
+      <c r="J79" s="48" t="n"/>
+      <c r="K79" s="15" t="n">
+        <v>2800</v>
+      </c>
+      <c r="L79" s="15" t="n">
+        <v>1990</v>
+      </c>
+      <c r="M79" s="15" t="n"/>
+      <c r="N79" s="16" t="n"/>
+      <c r="O79" s="16" t="n"/>
+      <c r="P79" s="16" t="n"/>
+      <c r="Q79" s="48" t="n"/>
+      <c r="R79" s="48" t="n"/>
+      <c r="S79" s="48" t="n"/>
+      <c r="T79" s="49">
+        <f>IF(AND(H79&lt;&gt;"",Q79&lt;&gt;""),H79-Q79,"")</f>
+        <v/>
+      </c>
+      <c r="U79" s="48" t="n"/>
+      <c r="V79" s="48" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="13" t="n">
+        <v>75</v>
+      </c>
+      <c r="B80" s="12" t="inlineStr">
+        <is>
+          <t>1.스캐너-1</t>
+        </is>
+      </c>
+      <c r="C80" s="12" t="inlineStr">
+        <is>
+          <t>2D스캐너</t>
+        </is>
+      </c>
+      <c r="D80" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하</t>
+        </is>
+      </c>
+      <c r="E80" s="13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="F80" s="13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G80" s="13" t="n"/>
+      <c r="H80" s="48" t="n"/>
+      <c r="I80" s="48" t="n"/>
+      <c r="J80" s="48" t="n"/>
+      <c r="K80" s="15" t="n">
+        <v>2730</v>
+      </c>
+      <c r="L80" s="15" t="n">
+        <v>6000</v>
+      </c>
+      <c r="M80" s="15" t="n"/>
+      <c r="N80" s="16" t="n"/>
+      <c r="O80" s="16" t="n"/>
+      <c r="P80" s="16" t="n"/>
+      <c r="Q80" s="48" t="n"/>
+      <c r="R80" s="48" t="n"/>
+      <c r="S80" s="48" t="n"/>
+      <c r="T80" s="49">
+        <f>IF(AND(H80&lt;&gt;"",Q80&lt;&gt;""),H80-Q80,"")</f>
+        <v/>
+      </c>
+      <c r="U80" s="48" t="n"/>
+      <c r="V80" s="48" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="13" t="n">
+        <v>76</v>
+      </c>
+      <c r="B81" s="12" t="inlineStr">
+        <is>
+          <t>1.스캐너-1</t>
+        </is>
+      </c>
+      <c r="C81" s="12" t="inlineStr">
+        <is>
+          <t>무선스캐너</t>
+        </is>
+      </c>
+      <c r="D81" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하</t>
+        </is>
+      </c>
+      <c r="E81" s="13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="F81" s="13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G81" s="13" t="n"/>
+      <c r="H81" s="48" t="n"/>
+      <c r="I81" s="48" t="n"/>
+      <c r="J81" s="48" t="n"/>
+      <c r="K81" s="15" t="n">
+        <v>2500</v>
+      </c>
+      <c r="L81" s="15" t="n">
+        <v>10000</v>
+      </c>
+      <c r="M81" s="15" t="n"/>
+      <c r="N81" s="16" t="n"/>
+      <c r="O81" s="16" t="n"/>
+      <c r="P81" s="16" t="n"/>
+      <c r="Q81" s="48" t="n"/>
+      <c r="R81" s="48" t="n"/>
+      <c r="S81" s="48" t="n"/>
+      <c r="T81" s="49">
+        <f>IF(AND(H81&lt;&gt;"",Q81&lt;&gt;""),H81-Q81,"")</f>
+        <v/>
+      </c>
+      <c r="U81" s="48" t="n"/>
+      <c r="V81" s="48" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="13" t="n">
+        <v>77</v>
+      </c>
+      <c r="B82" s="12" t="inlineStr">
+        <is>
+          <t>1.스캐너모델-2</t>
+        </is>
+      </c>
+      <c r="C82" s="12" t="inlineStr">
+        <is>
+          <t>DS2208</t>
+        </is>
+      </c>
+      <c r="D82" s="47" t="inlineStr">
+        <is>
+          <t>솔바텍 인하</t>
+        </is>
+      </c>
+      <c r="E82" s="13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F82" s="13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G82" s="13" t="n"/>
+      <c r="H82" s="48" t="n"/>
+      <c r="I82" s="48" t="n"/>
+      <c r="J82" s="48" t="n"/>
+      <c r="K82" s="15" t="n">
+        <v>800</v>
+      </c>
+      <c r="L82" s="15" t="n">
+        <v>3000</v>
+      </c>
+      <c r="M82" s="15" t="n"/>
+      <c r="N82" s="16" t="n"/>
+      <c r="O82" s="16" t="n"/>
+      <c r="P82" s="16" t="n"/>
+      <c r="Q82" s="48" t="n"/>
+      <c r="R82" s="48" t="n"/>
+      <c r="S82" s="48" t="n"/>
+      <c r="T82" s="49">
+        <f>IF(AND(H82&lt;&gt;"",Q82&lt;&gt;""),H82-Q82,"")</f>
+        <v/>
+      </c>
+      <c r="U82" s="48" t="n"/>
+      <c r="V82" s="48" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="13" t="n">
+        <v>78</v>
+      </c>
+      <c r="B83" s="12" t="inlineStr">
+        <is>
+          <t>3.라벨</t>
+        </is>
+      </c>
+      <c r="C83" s="12" t="inlineStr">
+        <is>
+          <t>감열라벨</t>
+        </is>
+      </c>
+      <c r="D83" s="47" t="inlineStr">
+        <is>
+          <t>솔바텍 인하 (간격 벌리기)</t>
+        </is>
+      </c>
+      <c r="E83" s="13" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F83" s="13" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G83" s="13" t="n"/>
+      <c r="H83" s="48" t="n"/>
+      <c r="I83" s="48" t="n"/>
+      <c r="J83" s="48" t="n"/>
+      <c r="K83" s="15" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L83" s="15" t="n">
+        <v>2500</v>
+      </c>
+      <c r="M83" s="15" t="n"/>
+      <c r="N83" s="16" t="n"/>
+      <c r="O83" s="16" t="n"/>
+      <c r="P83" s="16" t="n"/>
+      <c r="Q83" s="48" t="n"/>
+      <c r="R83" s="48" t="n"/>
+      <c r="S83" s="48" t="n"/>
+      <c r="T83" s="49">
+        <f>IF(AND(H83&lt;&gt;"",Q83&lt;&gt;""),H83-Q83,"")</f>
+        <v/>
+      </c>
+      <c r="U83" s="48" t="n"/>
+      <c r="V83" s="48" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="13" t="n">
+        <v>79</v>
+      </c>
+      <c r="B84" s="12" t="inlineStr">
+        <is>
+          <t>3.라벨</t>
+        </is>
+      </c>
+      <c r="C84" s="12" t="inlineStr">
+        <is>
+          <t>유포지라벨</t>
+        </is>
+      </c>
+      <c r="D84" s="47" t="inlineStr">
+        <is>
+          <t>솔바텍 인하 (간격 벌리기)</t>
+        </is>
+      </c>
+      <c r="E84" s="13" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="F84" s="13" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="G84" s="13" t="n"/>
+      <c r="H84" s="48" t="n"/>
+      <c r="I84" s="48" t="n"/>
+      <c r="J84" s="48" t="n"/>
+      <c r="K84" s="15" t="n">
+        <v>1430</v>
+      </c>
+      <c r="L84" s="15" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M84" s="15" t="n"/>
+      <c r="N84" s="16" t="n"/>
+      <c r="O84" s="16" t="n"/>
+      <c r="P84" s="16" t="n"/>
+      <c r="Q84" s="48" t="n"/>
+      <c r="R84" s="48" t="n"/>
+      <c r="S84" s="48" t="n"/>
+      <c r="T84" s="49">
+        <f>IF(AND(H84&lt;&gt;"",Q84&lt;&gt;""),H84-Q84,"")</f>
+        <v/>
+      </c>
+      <c r="U84" s="48" t="n"/>
+      <c r="V84" s="48" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="13" t="n">
+        <v>80</v>
+      </c>
+      <c r="B85" s="12" t="inlineStr">
+        <is>
+          <t>3.라벨</t>
+        </is>
+      </c>
+      <c r="C85" s="12" t="inlineStr">
+        <is>
+          <t>라벨지제작</t>
+        </is>
+      </c>
+      <c r="D85" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하 / SB렌탈 인하</t>
+        </is>
+      </c>
+      <c r="E85" s="13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="F85" s="13" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="G85" s="13" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="H85" s="48" t="n"/>
+      <c r="I85" s="48" t="n"/>
+      <c r="J85" s="48" t="n"/>
+      <c r="K85" s="15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="L85" s="15" t="n">
+        <v>3000</v>
+      </c>
+      <c r="M85" s="15" t="n">
+        <v>1110</v>
+      </c>
+      <c r="N85" s="16" t="n"/>
+      <c r="O85" s="16" t="n"/>
+      <c r="P85" s="16" t="n"/>
+      <c r="Q85" s="48" t="n"/>
+      <c r="R85" s="48" t="n"/>
+      <c r="S85" s="48" t="n"/>
+      <c r="T85" s="49">
+        <f>IF(AND(H85&lt;&gt;"",Q85&lt;&gt;""),H85-Q85,"")</f>
+        <v/>
+      </c>
+      <c r="U85" s="48" t="n"/>
+      <c r="V85" s="48" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="13" t="n">
+        <v>81</v>
+      </c>
+      <c r="B86" s="12" t="inlineStr">
+        <is>
+          <t>3.라벨</t>
+        </is>
+      </c>
+      <c r="C86" s="12" t="inlineStr">
+        <is>
+          <t>라벨프린트</t>
+        </is>
+      </c>
+      <c r="D86" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하 (간격 벌리기)</t>
+        </is>
+      </c>
+      <c r="E86" s="13" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="F86" s="13" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G86" s="13" t="n"/>
+      <c r="H86" s="48" t="n"/>
+      <c r="I86" s="48" t="n"/>
+      <c r="J86" s="48" t="n"/>
+      <c r="K86" s="15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="L86" s="15" t="n">
+        <v>2500</v>
+      </c>
+      <c r="M86" s="15" t="n"/>
+      <c r="N86" s="16" t="n"/>
+      <c r="O86" s="16" t="n"/>
+      <c r="P86" s="16" t="n"/>
+      <c r="Q86" s="48" t="n"/>
+      <c r="R86" s="48" t="n"/>
+      <c r="S86" s="48" t="n"/>
+      <c r="T86" s="49">
+        <f>IF(AND(H86&lt;&gt;"",Q86&lt;&gt;""),H86-Q86,"")</f>
+        <v/>
+      </c>
+      <c r="U86" s="48" t="n"/>
+      <c r="V86" s="48" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="13" t="n">
+        <v>82</v>
+      </c>
+      <c r="B87" s="12" t="inlineStr">
+        <is>
+          <t>6.PDA모델-3</t>
+        </is>
+      </c>
+      <c r="C87" s="12" t="inlineStr">
+        <is>
+          <t>OX10</t>
+        </is>
+      </c>
+      <c r="D87" s="47" t="inlineStr">
+        <is>
+          <t>솔바텍 인하 (간격 벌리기)</t>
+        </is>
+      </c>
+      <c r="E87" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F87" s="13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G87" s="13" t="n"/>
+      <c r="H87" s="48" t="n"/>
+      <c r="I87" s="48" t="n"/>
+      <c r="J87" s="48" t="n"/>
+      <c r="K87" s="15" t="n">
+        <v>600</v>
+      </c>
+      <c r="L87" s="15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="M87" s="15" t="n"/>
+      <c r="N87" s="16" t="n"/>
+      <c r="O87" s="16" t="n"/>
+      <c r="P87" s="16" t="n"/>
+      <c r="Q87" s="48" t="n"/>
+      <c r="R87" s="48" t="n"/>
+      <c r="S87" s="48" t="n"/>
+      <c r="T87" s="49">
+        <f>IF(AND(H87&lt;&gt;"",Q87&lt;&gt;""),H87-Q87,"")</f>
+        <v/>
+      </c>
+      <c r="U87" s="48" t="n"/>
+      <c r="V87" s="48" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="13" t="n">
+        <v>83</v>
+      </c>
+      <c r="B88" s="12" t="inlineStr">
+        <is>
+          <t>1.스캐너-1</t>
+        </is>
+      </c>
+      <c r="C88" s="12" t="inlineStr">
+        <is>
+          <t>2D바코드스캐너</t>
+        </is>
+      </c>
+      <c r="D88" s="50" t="inlineStr">
+        <is>
+          <t>솔바텍 인상</t>
+        </is>
+      </c>
+      <c r="E88" s="13" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="F88" s="13" t="n"/>
+      <c r="G88" s="13" t="n"/>
+      <c r="H88" s="48" t="n"/>
+      <c r="I88" s="48" t="n"/>
+      <c r="J88" s="48" t="n"/>
+      <c r="K88" s="15" t="n">
+        <v>2500</v>
+      </c>
+      <c r="L88" s="15" t="n">
+        <v>1640</v>
+      </c>
+      <c r="M88" s="15" t="n"/>
+      <c r="N88" s="16" t="n"/>
+      <c r="O88" s="16" t="n"/>
+      <c r="P88" s="16" t="n"/>
+      <c r="Q88" s="48" t="n"/>
+      <c r="R88" s="48" t="n"/>
+      <c r="S88" s="48" t="n"/>
+      <c r="T88" s="49">
+        <f>IF(AND(H88&lt;&gt;"",Q88&lt;&gt;""),H88-Q88,"")</f>
+        <v/>
+      </c>
+      <c r="U88" s="48" t="n"/>
+      <c r="V88" s="48" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="13" t="n">
+        <v>84</v>
+      </c>
+      <c r="B89" s="12" t="inlineStr">
+        <is>
+          <t>1.스캐너-1</t>
+        </is>
+      </c>
+      <c r="C89" s="12" t="inlineStr">
+        <is>
+          <t>블루투스바코드</t>
+        </is>
+      </c>
+      <c r="D89" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하</t>
+        </is>
+      </c>
+      <c r="E89" s="13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F89" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" s="13" t="n"/>
+      <c r="H89" s="48" t="n"/>
+      <c r="I89" s="48" t="n"/>
+      <c r="J89" s="48" t="n"/>
+      <c r="K89" s="15" t="n">
+        <v>300</v>
+      </c>
+      <c r="L89" s="15" t="n">
+        <v>1500</v>
+      </c>
+      <c r="M89" s="15" t="n"/>
+      <c r="N89" s="16" t="n"/>
+      <c r="O89" s="16" t="n"/>
+      <c r="P89" s="16" t="n"/>
+      <c r="Q89" s="48" t="n"/>
+      <c r="R89" s="48" t="n"/>
+      <c r="S89" s="48" t="n"/>
+      <c r="T89" s="49">
+        <f>IF(AND(H89&lt;&gt;"",Q89&lt;&gt;""),H89-Q89,"")</f>
+        <v/>
+      </c>
+      <c r="U89" s="48" t="n"/>
+      <c r="V89" s="48" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="13" t="n">
+        <v>85</v>
+      </c>
+      <c r="B90" s="12" t="inlineStr">
+        <is>
+          <t>1.스캐너-1</t>
+        </is>
+      </c>
+      <c r="C90" s="12" t="inlineStr">
+        <is>
+          <t>바코드스캐너추천</t>
+        </is>
+      </c>
+      <c r="D90" s="50" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하 / 솔바텍 인상</t>
+        </is>
+      </c>
+      <c r="E90" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="F90" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="G90" s="13" t="n"/>
+      <c r="H90" s="48" t="n"/>
+      <c r="I90" s="48" t="n"/>
+      <c r="J90" s="48" t="n"/>
+      <c r="K90" s="15" t="n">
+        <v>1530</v>
+      </c>
+      <c r="L90" s="15" t="n">
+        <v>1500</v>
+      </c>
+      <c r="M90" s="15" t="n"/>
+      <c r="N90" s="16" t="n"/>
+      <c r="O90" s="16" t="n"/>
+      <c r="P90" s="16" t="n"/>
+      <c r="Q90" s="48" t="n"/>
+      <c r="R90" s="48" t="n"/>
+      <c r="S90" s="48" t="n"/>
+      <c r="T90" s="49">
+        <f>IF(AND(H90&lt;&gt;"",Q90&lt;&gt;""),H90-Q90,"")</f>
+        <v/>
+      </c>
+      <c r="U90" s="48" t="n"/>
+      <c r="V90" s="48" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="13" t="n">
+        <v>86</v>
+      </c>
+      <c r="B91" s="12" t="inlineStr">
+        <is>
+          <t>1.스캐너-1</t>
+        </is>
+      </c>
+      <c r="C91" s="12" t="inlineStr">
+        <is>
+          <t>물류바코드</t>
+        </is>
+      </c>
+      <c r="D91" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하</t>
+        </is>
+      </c>
+      <c r="E91" s="13" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="F91" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G91" s="13" t="n"/>
+      <c r="H91" s="48" t="n"/>
+      <c r="I91" s="48" t="n"/>
+      <c r="J91" s="48" t="n"/>
+      <c r="K91" s="15" t="n">
+        <v>1600</v>
+      </c>
+      <c r="L91" s="15" t="n">
+        <v>2140</v>
+      </c>
+      <c r="M91" s="15" t="n"/>
+      <c r="N91" s="16" t="n"/>
+      <c r="O91" s="16" t="n"/>
+      <c r="P91" s="16" t="n"/>
+      <c r="Q91" s="48" t="n"/>
+      <c r="R91" s="48" t="n"/>
+      <c r="S91" s="48" t="n"/>
+      <c r="T91" s="49">
+        <f>IF(AND(H91&lt;&gt;"",Q91&lt;&gt;""),H91-Q91,"")</f>
+        <v/>
+      </c>
+      <c r="U91" s="48" t="n"/>
+      <c r="V91" s="48" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="13" t="n">
+        <v>87</v>
+      </c>
+      <c r="B92" s="12" t="inlineStr">
+        <is>
+          <t>2.프린터모델-2</t>
+        </is>
+      </c>
+      <c r="C92" s="12" t="inlineStr">
+        <is>
+          <t>SLP-TX220</t>
+        </is>
+      </c>
+      <c r="D92" s="47" t="inlineStr">
+        <is>
+          <t>솔바텍 인하 (간격 벌리기)</t>
+        </is>
+      </c>
+      <c r="E92" s="13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F92" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" s="13" t="n"/>
+      <c r="H92" s="48" t="n"/>
+      <c r="I92" s="48" t="n"/>
+      <c r="J92" s="48" t="n"/>
+      <c r="K92" s="15" t="n">
+        <v>300</v>
+      </c>
+      <c r="L92" s="15" t="n">
+        <v>1500</v>
+      </c>
+      <c r="M92" s="15" t="n"/>
+      <c r="N92" s="16" t="n"/>
+      <c r="O92" s="16" t="n"/>
+      <c r="P92" s="16" t="n"/>
+      <c r="Q92" s="48" t="n"/>
+      <c r="R92" s="48" t="n"/>
+      <c r="S92" s="48" t="n"/>
+      <c r="T92" s="49">
+        <f>IF(AND(H92&lt;&gt;"",Q92&lt;&gt;""),H92-Q92,"")</f>
+        <v/>
+      </c>
+      <c r="U92" s="48" t="n"/>
+      <c r="V92" s="48" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="13" t="n">
+        <v>88</v>
+      </c>
+      <c r="B93" s="12" t="inlineStr">
+        <is>
+          <t>2.프린터모델-2</t>
+        </is>
+      </c>
+      <c r="C93" s="12" t="inlineStr">
+        <is>
+          <t>B-EX4T1</t>
+        </is>
+      </c>
+      <c r="D93" s="50" t="inlineStr">
+        <is>
+          <t>솔바텍 인상</t>
+        </is>
+      </c>
+      <c r="E93" s="13" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="F93" s="13" t="n"/>
+      <c r="G93" s="13" t="n"/>
+      <c r="H93" s="48" t="n"/>
+      <c r="I93" s="48" t="n"/>
+      <c r="J93" s="48" t="n"/>
+      <c r="K93" s="15" t="n">
+        <v>300</v>
+      </c>
+      <c r="L93" s="15" t="n">
+        <v>600</v>
+      </c>
+      <c r="M93" s="15" t="n"/>
+      <c r="N93" s="16" t="n"/>
+      <c r="O93" s="16" t="n"/>
+      <c r="P93" s="16" t="n"/>
+      <c r="Q93" s="48" t="n"/>
+      <c r="R93" s="48" t="n"/>
+      <c r="S93" s="48" t="n"/>
+      <c r="T93" s="49">
+        <f>IF(AND(H93&lt;&gt;"",Q93&lt;&gt;""),H93-Q93,"")</f>
+        <v/>
+      </c>
+      <c r="U93" s="48" t="n"/>
+      <c r="V93" s="48" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="13" t="n">
+        <v>89</v>
+      </c>
+      <c r="B94" s="12" t="inlineStr">
+        <is>
+          <t>8.산업자동화</t>
+        </is>
+      </c>
+      <c r="C94" s="12" t="inlineStr">
+        <is>
+          <t>생산자동화</t>
+        </is>
+      </c>
+      <c r="D94" s="50" t="inlineStr">
+        <is>
+          <t>솔바텍 인상</t>
+        </is>
+      </c>
+      <c r="E94" s="13" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="F94" s="13" t="n"/>
+      <c r="G94" s="13" t="n"/>
+      <c r="H94" s="48" t="n"/>
+      <c r="I94" s="48" t="n"/>
+      <c r="J94" s="48" t="n"/>
+      <c r="K94" s="15" t="n">
+        <v>1620</v>
+      </c>
+      <c r="L94" s="15" t="n"/>
+      <c r="M94" s="15" t="n"/>
+      <c r="N94" s="16" t="n"/>
+      <c r="O94" s="16" t="n"/>
+      <c r="P94" s="16" t="n"/>
+      <c r="Q94" s="48" t="n"/>
+      <c r="R94" s="48" t="n"/>
+      <c r="S94" s="48" t="n"/>
+      <c r="T94" s="49">
+        <f>IF(AND(H94&lt;&gt;"",Q94&lt;&gt;""),H94-Q94,"")</f>
+        <v/>
+      </c>
+      <c r="U94" s="48" t="n"/>
+      <c r="V94" s="48" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="13" t="n">
+        <v>90</v>
+      </c>
+      <c r="B95" s="12" t="inlineStr">
+        <is>
+          <t>1.스캐너-1</t>
+        </is>
+      </c>
+      <c r="C95" s="12" t="inlineStr">
+        <is>
+          <t>바코드스캐너프로그램</t>
+        </is>
+      </c>
+      <c r="D95" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하 (간격 벌리기)</t>
+        </is>
+      </c>
+      <c r="E95" s="13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F95" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G95" s="13" t="n"/>
+      <c r="H95" s="48" t="n"/>
+      <c r="I95" s="48" t="n"/>
+      <c r="J95" s="48" t="n"/>
+      <c r="K95" s="15" t="n">
+        <v>1020</v>
+      </c>
+      <c r="L95" s="15" t="n">
+        <v>700</v>
+      </c>
+      <c r="M95" s="15" t="n"/>
+      <c r="N95" s="16" t="n"/>
+      <c r="O95" s="16" t="n"/>
+      <c r="P95" s="16" t="n"/>
+      <c r="Q95" s="48" t="n"/>
+      <c r="R95" s="48" t="n"/>
+      <c r="S95" s="48" t="n"/>
+      <c r="T95" s="49">
+        <f>IF(AND(H95&lt;&gt;"",Q95&lt;&gt;""),H95-Q95,"")</f>
+        <v/>
+      </c>
+      <c r="U95" s="48" t="n"/>
+      <c r="V95" s="48" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="13" t="n">
+        <v>91</v>
+      </c>
+      <c r="B96" s="12" t="inlineStr">
+        <is>
+          <t>1.스캐너-1</t>
+        </is>
+      </c>
+      <c r="C96" s="12" t="inlineStr">
+        <is>
+          <t>핸드폰바코드스캐너</t>
+        </is>
+      </c>
+      <c r="D96" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하</t>
+        </is>
+      </c>
+      <c r="E96" s="13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F96" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" s="13" t="n"/>
+      <c r="H96" s="48" t="n"/>
+      <c r="I96" s="48" t="n"/>
+      <c r="J96" s="48" t="n"/>
+      <c r="K96" s="15" t="n">
+        <v>500</v>
+      </c>
+      <c r="L96" s="15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="M96" s="15" t="n"/>
+      <c r="N96" s="16" t="n"/>
+      <c r="O96" s="16" t="n"/>
+      <c r="P96" s="16" t="n"/>
+      <c r="Q96" s="48" t="n"/>
+      <c r="R96" s="48" t="n"/>
+      <c r="S96" s="48" t="n"/>
+      <c r="T96" s="49">
+        <f>IF(AND(H96&lt;&gt;"",Q96&lt;&gt;""),H96-Q96,"")</f>
+        <v/>
+      </c>
+      <c r="U96" s="48" t="n"/>
+      <c r="V96" s="48" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="13" t="n">
+        <v>92</v>
+      </c>
+      <c r="B97" s="12" t="inlineStr">
+        <is>
+          <t>1.스캐너-1</t>
+        </is>
+      </c>
+      <c r="C97" s="12" t="inlineStr">
+        <is>
+          <t>바코드기계</t>
+        </is>
+      </c>
+      <c r="D97" s="50" t="inlineStr">
+        <is>
+          <t>솔바텍 인상</t>
+        </is>
+      </c>
+      <c r="E97" s="13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F97" s="13" t="n"/>
+      <c r="G97" s="13" t="n"/>
+      <c r="H97" s="48" t="n"/>
+      <c r="I97" s="48" t="n"/>
+      <c r="J97" s="48" t="n"/>
+      <c r="K97" s="15" t="n">
+        <v>2700</v>
+      </c>
+      <c r="L97" s="15" t="n">
+        <v>1500</v>
+      </c>
+      <c r="M97" s="15" t="n"/>
+      <c r="N97" s="16" t="n"/>
+      <c r="O97" s="16" t="n"/>
+      <c r="P97" s="16" t="n"/>
+      <c r="Q97" s="48" t="n"/>
+      <c r="R97" s="48" t="n"/>
+      <c r="S97" s="48" t="n"/>
+      <c r="T97" s="49">
+        <f>IF(AND(H97&lt;&gt;"",Q97&lt;&gt;""),H97-Q97,"")</f>
+        <v/>
+      </c>
+      <c r="U97" s="48" t="n"/>
+      <c r="V97" s="48" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="13" t="n">
+        <v>93</v>
+      </c>
+      <c r="B98" s="12" t="inlineStr">
+        <is>
+          <t>1.스캐너-1</t>
+        </is>
+      </c>
+      <c r="C98" s="12" t="inlineStr">
+        <is>
+          <t>도서바코드</t>
+        </is>
+      </c>
+      <c r="D98" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하</t>
+        </is>
+      </c>
+      <c r="E98" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="F98" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="G98" s="13" t="n"/>
+      <c r="H98" s="48" t="n"/>
+      <c r="I98" s="48" t="n"/>
+      <c r="J98" s="48" t="n"/>
+      <c r="K98" s="15" t="n">
+        <v>490</v>
+      </c>
+      <c r="L98" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="M98" s="15" t="n"/>
+      <c r="N98" s="16" t="n"/>
+      <c r="O98" s="16" t="n"/>
+      <c r="P98" s="16" t="n"/>
+      <c r="Q98" s="48" t="n"/>
+      <c r="R98" s="48" t="n"/>
+      <c r="S98" s="48" t="n"/>
+      <c r="T98" s="49">
+        <f>IF(AND(H98&lt;&gt;"",Q98&lt;&gt;""),H98-Q98,"")</f>
+        <v/>
+      </c>
+      <c r="U98" s="48" t="n"/>
+      <c r="V98" s="48" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="13" t="n">
+        <v>94</v>
+      </c>
+      <c r="B99" s="12" t="inlineStr">
+        <is>
+          <t>1.스캐너모델-2</t>
+        </is>
+      </c>
+      <c r="C99" s="12" t="inlineStr">
+        <is>
+          <t>DS3608</t>
+        </is>
+      </c>
+      <c r="D99" s="47" t="inlineStr">
+        <is>
+          <t>솔바텍 인하</t>
+        </is>
+      </c>
+      <c r="E99" s="13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F99" s="13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G99" s="13" t="n"/>
+      <c r="H99" s="48" t="n"/>
+      <c r="I99" s="48" t="n"/>
+      <c r="J99" s="48" t="n"/>
+      <c r="K99" s="15" t="n">
+        <v>500</v>
+      </c>
+      <c r="L99" s="15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="M99" s="15" t="n"/>
+      <c r="N99" s="16" t="n"/>
+      <c r="O99" s="16" t="n"/>
+      <c r="P99" s="16" t="n"/>
+      <c r="Q99" s="48" t="n"/>
+      <c r="R99" s="48" t="n"/>
+      <c r="S99" s="48" t="n"/>
+      <c r="T99" s="49">
+        <f>IF(AND(H99&lt;&gt;"",Q99&lt;&gt;""),H99-Q99,"")</f>
+        <v/>
+      </c>
+      <c r="U99" s="48" t="n"/>
+      <c r="V99" s="48" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="13" t="n">
+        <v>95</v>
+      </c>
+      <c r="B100" s="12" t="inlineStr">
+        <is>
+          <t>1.스캐너모델-2</t>
+        </is>
+      </c>
+      <c r="C100" s="12" t="inlineStr">
+        <is>
+          <t>FA470</t>
+        </is>
+      </c>
+      <c r="D100" s="47" t="inlineStr">
+        <is>
+          <t>솔바텍 인하 (간격 벌리기)</t>
+        </is>
+      </c>
+      <c r="E100" s="13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F100" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G100" s="13" t="n"/>
+      <c r="H100" s="48" t="n"/>
+      <c r="I100" s="48" t="n"/>
+      <c r="J100" s="48" t="n"/>
+      <c r="K100" s="15" t="n">
+        <v>500</v>
+      </c>
+      <c r="L100" s="15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="M100" s="15" t="n"/>
+      <c r="N100" s="16" t="n"/>
+      <c r="O100" s="16" t="n"/>
+      <c r="P100" s="16" t="n"/>
+      <c r="Q100" s="48" t="n"/>
+      <c r="R100" s="48" t="n"/>
+      <c r="S100" s="48" t="n"/>
+      <c r="T100" s="49">
+        <f>IF(AND(H100&lt;&gt;"",Q100&lt;&gt;""),H100-Q100,"")</f>
+        <v/>
+      </c>
+      <c r="U100" s="48" t="n"/>
+      <c r="V100" s="48" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="13" t="n">
+        <v>96</v>
+      </c>
+      <c r="B101" s="12" t="inlineStr">
+        <is>
+          <t>2.프린터-1</t>
+        </is>
+      </c>
+      <c r="C101" s="34" t="inlineStr">
+        <is>
+          <t>바코드인쇄기</t>
+        </is>
+      </c>
+      <c r="D101" s="47" t="inlineStr">
+        <is>
+          <t>SB렌탈 인하</t>
+        </is>
+      </c>
+      <c r="E101" s="13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F101" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="G101" s="13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H101" s="48" t="n"/>
+      <c r="I101" s="48" t="n"/>
+      <c r="J101" s="48" t="n">
+        <v>7</v>
+      </c>
+      <c r="K101" s="15" t="n">
+        <v>3300</v>
+      </c>
+      <c r="L101" s="15" t="n">
+        <v>4500</v>
+      </c>
+      <c r="M101" s="15" t="n">
+        <v>5000</v>
+      </c>
+      <c r="N101" s="16" t="n"/>
+      <c r="O101" s="16" t="n"/>
+      <c r="P101" s="16" t="n"/>
+      <c r="Q101" s="48" t="n"/>
+      <c r="R101" s="48" t="n"/>
+      <c r="S101" s="48" t="n"/>
+      <c r="T101" s="49">
+        <f>IF(AND(H101&lt;&gt;"",Q101&lt;&gt;""),H101-Q101,"")</f>
+        <v/>
+      </c>
+      <c r="U101" s="48" t="n"/>
+      <c r="V101" s="48" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="13" t="n">
+        <v>97</v>
+      </c>
+      <c r="B102" s="12" t="inlineStr">
+        <is>
+          <t>2.프린터-1</t>
+        </is>
+      </c>
+      <c r="C102" s="34" t="inlineStr">
+        <is>
+          <t>라벨인쇄기</t>
+        </is>
+      </c>
+      <c r="D102" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하</t>
+        </is>
+      </c>
+      <c r="E102" s="13" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F102" s="13" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="G102" s="13" t="n"/>
+      <c r="H102" s="48" t="n"/>
+      <c r="I102" s="48" t="n"/>
+      <c r="J102" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="K102" s="15" t="n">
+        <v>3500</v>
+      </c>
+      <c r="L102" s="15" t="n">
+        <v>7000</v>
+      </c>
+      <c r="M102" s="15" t="n"/>
+      <c r="N102" s="16" t="n"/>
+      <c r="O102" s="16" t="n"/>
+      <c r="P102" s="16" t="n"/>
+      <c r="Q102" s="48" t="n"/>
+      <c r="R102" s="48" t="n"/>
+      <c r="S102" s="48" t="n"/>
+      <c r="T102" s="49">
+        <f>IF(AND(H102&lt;&gt;"",Q102&lt;&gt;""),H102-Q102,"")</f>
+        <v/>
+      </c>
+      <c r="U102" s="48" t="n"/>
+      <c r="V102" s="48" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="13" t="n">
+        <v>98</v>
+      </c>
+      <c r="B103" s="12" t="inlineStr">
+        <is>
+          <t>3.라벨</t>
+        </is>
+      </c>
+      <c r="C103" s="12" t="inlineStr">
+        <is>
+          <t>상품바코드</t>
+        </is>
+      </c>
+      <c r="D103" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하</t>
+        </is>
+      </c>
+      <c r="E103" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="F103" s="13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G103" s="13" t="n"/>
+      <c r="H103" s="48" t="n"/>
+      <c r="I103" s="48" t="n"/>
+      <c r="J103" s="48" t="n"/>
+      <c r="K103" s="15" t="n">
+        <v>850</v>
+      </c>
+      <c r="L103" s="15" t="n">
+        <v>1500</v>
+      </c>
+      <c r="M103" s="15" t="n"/>
+      <c r="N103" s="16" t="n"/>
+      <c r="O103" s="16" t="n"/>
+      <c r="P103" s="16" t="n"/>
+      <c r="Q103" s="48" t="n"/>
+      <c r="R103" s="48" t="n"/>
+      <c r="S103" s="48" t="n"/>
+      <c r="T103" s="49">
+        <f>IF(AND(H103&lt;&gt;"",Q103&lt;&gt;""),H103-Q103,"")</f>
+        <v/>
+      </c>
+      <c r="U103" s="48" t="n"/>
+      <c r="V103" s="48" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="13" t="n">
+        <v>99</v>
+      </c>
+      <c r="B104" s="12" t="inlineStr">
+        <is>
+          <t>3.라벨</t>
+        </is>
+      </c>
+      <c r="C104" s="12" t="inlineStr">
+        <is>
+          <t>라벨인쇄</t>
+        </is>
+      </c>
+      <c r="D104" s="50" t="inlineStr">
+        <is>
+          <t>솔바텍 인상</t>
+        </is>
+      </c>
+      <c r="E104" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F104" s="13" t="n"/>
+      <c r="G104" s="13" t="n"/>
+      <c r="H104" s="48" t="n"/>
+      <c r="I104" s="48" t="n"/>
+      <c r="J104" s="48" t="n"/>
+      <c r="K104" s="15" t="n">
+        <v>3500</v>
+      </c>
+      <c r="L104" s="15" t="n">
+        <v>4000</v>
+      </c>
+      <c r="M104" s="15" t="n">
+        <v>2170</v>
+      </c>
+      <c r="N104" s="16" t="n"/>
+      <c r="O104" s="16" t="n"/>
+      <c r="P104" s="16" t="n"/>
+      <c r="Q104" s="48" t="n"/>
+      <c r="R104" s="48" t="n"/>
+      <c r="S104" s="48" t="n"/>
+      <c r="T104" s="49">
+        <f>IF(AND(H104&lt;&gt;"",Q104&lt;&gt;""),H104-Q104,"")</f>
+        <v/>
+      </c>
+      <c r="U104" s="48" t="n"/>
+      <c r="V104" s="48" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B105" s="12" t="inlineStr">
+        <is>
+          <t>3.라벨</t>
+        </is>
+      </c>
+      <c r="C105" s="12" t="inlineStr">
+        <is>
+          <t>바코드프린터라벨지</t>
+        </is>
+      </c>
+      <c r="D105" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하</t>
+        </is>
+      </c>
+      <c r="E105" s="13" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F105" s="13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G105" s="13" t="n"/>
+      <c r="H105" s="48" t="n"/>
+      <c r="I105" s="48" t="n"/>
+      <c r="J105" s="48" t="n"/>
+      <c r="K105" s="15" t="n">
+        <v>910</v>
+      </c>
+      <c r="L105" s="15" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M105" s="15" t="n"/>
+      <c r="N105" s="16" t="n"/>
+      <c r="O105" s="16" t="n"/>
+      <c r="P105" s="16" t="n"/>
+      <c r="Q105" s="48" t="n"/>
+      <c r="R105" s="48" t="n"/>
+      <c r="S105" s="48" t="n"/>
+      <c r="T105" s="49">
+        <f>IF(AND(H105&lt;&gt;"",Q105&lt;&gt;""),H105-Q105,"")</f>
+        <v/>
+      </c>
+      <c r="U105" s="48" t="n"/>
+      <c r="V105" s="48" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="13" t="n">
+        <v>101</v>
+      </c>
+      <c r="B106" s="12" t="inlineStr">
+        <is>
+          <t>4.솔루션SW-1</t>
+        </is>
+      </c>
+      <c r="C106" s="12" t="inlineStr">
+        <is>
+          <t>재고프로그램</t>
+        </is>
+      </c>
+      <c r="D106" s="50" t="inlineStr">
+        <is>
+          <t>솔바텍 인상</t>
+        </is>
+      </c>
+      <c r="E106" s="13" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="F106" s="13" t="n"/>
+      <c r="G106" s="13" t="n"/>
+      <c r="H106" s="48" t="n"/>
+      <c r="I106" s="48" t="n"/>
+      <c r="J106" s="48" t="n"/>
+      <c r="K106" s="15" t="n">
+        <v>9000</v>
+      </c>
+      <c r="L106" s="15" t="n">
+        <v>5810</v>
+      </c>
+      <c r="M106" s="15" t="n"/>
+      <c r="N106" s="16" t="n"/>
+      <c r="O106" s="16" t="n"/>
+      <c r="P106" s="16" t="n"/>
+      <c r="Q106" s="48" t="n"/>
+      <c r="R106" s="48" t="n"/>
+      <c r="S106" s="48" t="n"/>
+      <c r="T106" s="49">
+        <f>IF(AND(H106&lt;&gt;"",Q106&lt;&gt;""),H106-Q106,"")</f>
+        <v/>
+      </c>
+      <c r="U106" s="48" t="n"/>
+      <c r="V106" s="48" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="13" t="n">
+        <v>102</v>
+      </c>
+      <c r="B107" s="12" t="inlineStr">
+        <is>
+          <t>4.솔루션SW-1</t>
+        </is>
+      </c>
+      <c r="C107" s="12" t="inlineStr">
+        <is>
+          <t>WMS시스템</t>
+        </is>
+      </c>
+      <c r="D107" s="50" t="inlineStr">
+        <is>
+          <t>솔바텍 인상</t>
+        </is>
+      </c>
+      <c r="E107" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="F107" s="13" t="n"/>
+      <c r="G107" s="13" t="n"/>
+      <c r="H107" s="48" t="n"/>
+      <c r="I107" s="48" t="n"/>
+      <c r="J107" s="48" t="n"/>
+      <c r="K107" s="15" t="n">
+        <v>7500</v>
+      </c>
+      <c r="L107" s="15" t="n"/>
+      <c r="M107" s="15" t="n"/>
+      <c r="N107" s="16" t="n"/>
+      <c r="O107" s="16" t="n"/>
+      <c r="P107" s="16" t="n"/>
+      <c r="Q107" s="48" t="n"/>
+      <c r="R107" s="48" t="n"/>
+      <c r="S107" s="48" t="n"/>
+      <c r="T107" s="49">
+        <f>IF(AND(H107&lt;&gt;"",Q107&lt;&gt;""),H107-Q107,"")</f>
+        <v/>
+      </c>
+      <c r="U107" s="48" t="n"/>
+      <c r="V107" s="48" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="13" t="n">
+        <v>103</v>
+      </c>
+      <c r="B108" s="12" t="inlineStr">
+        <is>
+          <t>5.리본</t>
+        </is>
+      </c>
+      <c r="C108" s="12" t="inlineStr">
+        <is>
+          <t>라벨리본</t>
+        </is>
+      </c>
+      <c r="D108" s="47" t="inlineStr">
+        <is>
+          <t>솔바텍 인하 (간격 벌리기)</t>
+        </is>
+      </c>
+      <c r="E108" s="13" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F108" s="13" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G108" s="13" t="n"/>
+      <c r="H108" s="48" t="n"/>
+      <c r="I108" s="48" t="n"/>
+      <c r="J108" s="48" t="n"/>
+      <c r="K108" s="15" t="n">
+        <v>2090</v>
+      </c>
+      <c r="L108" s="15" t="n">
+        <v>3000</v>
+      </c>
+      <c r="M108" s="15" t="n"/>
+      <c r="N108" s="16" t="n"/>
+      <c r="O108" s="16" t="n"/>
+      <c r="P108" s="16" t="n"/>
+      <c r="Q108" s="48" t="n"/>
+      <c r="R108" s="48" t="n"/>
+      <c r="S108" s="48" t="n"/>
+      <c r="T108" s="49">
+        <f>IF(AND(H108&lt;&gt;"",Q108&lt;&gt;""),H108-Q108,"")</f>
+        <v/>
+      </c>
+      <c r="U108" s="48" t="n"/>
+      <c r="V108" s="48" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="13" t="n">
+        <v>104</v>
+      </c>
+      <c r="B109" s="12" t="inlineStr">
+        <is>
+          <t>5.리본</t>
+        </is>
+      </c>
+      <c r="C109" s="12" t="inlineStr">
+        <is>
+          <t>프린터리본</t>
+        </is>
+      </c>
+      <c r="D109" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하</t>
+        </is>
+      </c>
+      <c r="E109" s="13" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F109" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="G109" s="13" t="n"/>
+      <c r="H109" s="48" t="n"/>
+      <c r="I109" s="48" t="n"/>
+      <c r="J109" s="48" t="n"/>
+      <c r="K109" s="15" t="n">
+        <v>1100</v>
+      </c>
+      <c r="L109" s="15" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M109" s="15" t="n"/>
+      <c r="N109" s="16" t="n"/>
+      <c r="O109" s="16" t="n"/>
+      <c r="P109" s="16" t="n"/>
+      <c r="Q109" s="48" t="n"/>
+      <c r="R109" s="48" t="n"/>
+      <c r="S109" s="48" t="n"/>
+      <c r="T109" s="49">
+        <f>IF(AND(H109&lt;&gt;"",Q109&lt;&gt;""),H109-Q109,"")</f>
+        <v/>
+      </c>
+      <c r="U109" s="48" t="n"/>
+      <c r="V109" s="48" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="13" t="n">
+        <v>105</v>
+      </c>
+      <c r="B110" s="12" t="inlineStr">
+        <is>
+          <t>6.PDA프로그램-2</t>
+        </is>
+      </c>
+      <c r="C110" s="12" t="inlineStr">
+        <is>
+          <t>PDA프로그램</t>
+        </is>
+      </c>
+      <c r="D110" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하 (간격 벌리기)</t>
+        </is>
+      </c>
+      <c r="E110" s="13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F110" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G110" s="13" t="n"/>
+      <c r="H110" s="48" t="n"/>
+      <c r="I110" s="48" t="n"/>
+      <c r="J110" s="48" t="n"/>
+      <c r="K110" s="15" t="n">
+        <v>1500</v>
+      </c>
+      <c r="L110" s="15" t="n">
+        <v>3000</v>
+      </c>
+      <c r="M110" s="15" t="n"/>
+      <c r="N110" s="16" t="n"/>
+      <c r="O110" s="16" t="n"/>
+      <c r="P110" s="16" t="n"/>
+      <c r="Q110" s="48" t="n"/>
+      <c r="R110" s="48" t="n"/>
+      <c r="S110" s="48" t="n"/>
+      <c r="T110" s="49">
+        <f>IF(AND(H110&lt;&gt;"",Q110&lt;&gt;""),H110-Q110,"")</f>
+        <v/>
+      </c>
+      <c r="U110" s="48" t="n"/>
+      <c r="V110" s="48" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="13" t="n">
+        <v>106</v>
+      </c>
+      <c r="B111" s="12" t="inlineStr">
+        <is>
+          <t>6.산업용PDA-1</t>
+        </is>
+      </c>
+      <c r="C111" s="12" t="inlineStr">
+        <is>
+          <t>바코드PDA</t>
+        </is>
+      </c>
+      <c r="D111" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하</t>
+        </is>
+      </c>
+      <c r="E111" s="13" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F111" s="13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G111" s="13" t="n"/>
+      <c r="H111" s="48" t="n"/>
+      <c r="I111" s="48" t="n"/>
+      <c r="J111" s="48" t="n"/>
+      <c r="K111" s="15" t="n">
+        <v>2300</v>
+      </c>
+      <c r="L111" s="15" t="n">
+        <v>4100</v>
+      </c>
+      <c r="M111" s="15" t="n"/>
+      <c r="N111" s="16" t="n"/>
+      <c r="O111" s="16" t="n"/>
+      <c r="P111" s="16" t="n"/>
+      <c r="Q111" s="48" t="n"/>
+      <c r="R111" s="48" t="n"/>
+      <c r="S111" s="48" t="n"/>
+      <c r="T111" s="49">
+        <f>IF(AND(H111&lt;&gt;"",Q111&lt;&gt;""),H111-Q111,"")</f>
+        <v/>
+      </c>
+      <c r="U111" s="48" t="n"/>
+      <c r="V111" s="48" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="13" t="n">
+        <v>107</v>
+      </c>
+      <c r="B112" s="12" t="inlineStr">
+        <is>
+          <t>8.산업자동화</t>
+        </is>
+      </c>
+      <c r="C112" s="12" t="inlineStr">
+        <is>
+          <t>산업자동화</t>
+        </is>
+      </c>
+      <c r="D112" s="50" t="inlineStr">
+        <is>
+          <t>솔바텍 인상</t>
+        </is>
+      </c>
+      <c r="E112" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="F112" s="13" t="n"/>
+      <c r="G112" s="13" t="n"/>
+      <c r="H112" s="48" t="n"/>
+      <c r="I112" s="48" t="n"/>
+      <c r="J112" s="48" t="n"/>
+      <c r="K112" s="15" t="n">
+        <v>1060</v>
+      </c>
+      <c r="L112" s="15" t="n"/>
+      <c r="M112" s="15" t="n"/>
+      <c r="N112" s="16" t="n"/>
+      <c r="O112" s="16" t="n"/>
+      <c r="P112" s="16" t="n"/>
+      <c r="Q112" s="48" t="n"/>
+      <c r="R112" s="48" t="n"/>
+      <c r="S112" s="48" t="n"/>
+      <c r="T112" s="49">
+        <f>IF(AND(H112&lt;&gt;"",Q112&lt;&gt;""),H112-Q112,"")</f>
+        <v/>
+      </c>
+      <c r="U112" s="48" t="n"/>
+      <c r="V112" s="48" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="13" t="n">
+        <v>108</v>
+      </c>
+      <c r="B113" s="12" t="inlineStr">
+        <is>
+          <t>1.스캐너-1</t>
+        </is>
+      </c>
+      <c r="C113" s="12" t="inlineStr">
+        <is>
+          <t>허니웰스캐너</t>
+        </is>
+      </c>
+      <c r="D113" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하</t>
+        </is>
+      </c>
+      <c r="E113" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="F113" s="13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G113" s="13" t="n"/>
+      <c r="H113" s="48" t="n"/>
+      <c r="I113" s="48" t="n"/>
+      <c r="J113" s="48" t="n"/>
+      <c r="K113" s="15" t="n">
+        <v>510</v>
+      </c>
+      <c r="L113" s="15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="M113" s="15" t="n"/>
+      <c r="N113" s="16" t="n"/>
+      <c r="O113" s="16" t="n"/>
+      <c r="P113" s="16" t="n"/>
+      <c r="Q113" s="48" t="n"/>
+      <c r="R113" s="48" t="n"/>
+      <c r="S113" s="48" t="n"/>
+      <c r="T113" s="49">
+        <f>IF(AND(H113&lt;&gt;"",Q113&lt;&gt;""),H113-Q113,"")</f>
+        <v/>
+      </c>
+      <c r="U113" s="48" t="n"/>
+      <c r="V113" s="48" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="13" t="n">
+        <v>109</v>
+      </c>
+      <c r="B114" s="12" t="inlineStr">
+        <is>
+          <t>1.스캐너-1</t>
+        </is>
+      </c>
+      <c r="C114" s="12" t="inlineStr">
+        <is>
+          <t>USB바코드스캐너</t>
+        </is>
+      </c>
+      <c r="D114" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하</t>
+        </is>
+      </c>
+      <c r="E114" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="F114" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="G114" s="13" t="n"/>
+      <c r="H114" s="48" t="n"/>
+      <c r="I114" s="48" t="n"/>
+      <c r="J114" s="48" t="n"/>
+      <c r="K114" s="15" t="n">
+        <v>400</v>
+      </c>
+      <c r="L114" s="15" t="n">
+        <v>750</v>
+      </c>
+      <c r="M114" s="15" t="n"/>
+      <c r="N114" s="16" t="n"/>
+      <c r="O114" s="16" t="n"/>
+      <c r="P114" s="16" t="n"/>
+      <c r="Q114" s="48" t="n"/>
+      <c r="R114" s="48" t="n"/>
+      <c r="S114" s="48" t="n"/>
+      <c r="T114" s="49">
+        <f>IF(AND(H114&lt;&gt;"",Q114&lt;&gt;""),H114-Q114,"")</f>
+        <v/>
+      </c>
+      <c r="U114" s="48" t="n"/>
+      <c r="V114" s="48" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="13" t="n">
+        <v>110</v>
+      </c>
+      <c r="B115" s="12" t="inlineStr">
+        <is>
+          <t>1.스캐너-1</t>
+        </is>
+      </c>
+      <c r="C115" s="12" t="inlineStr">
+        <is>
+          <t>SYMBOL스캐너</t>
+        </is>
+      </c>
+      <c r="D115" s="50" t="inlineStr">
+        <is>
+          <t>솔바텍 인상</t>
+        </is>
+      </c>
+      <c r="E115" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="F115" s="13" t="n"/>
+      <c r="G115" s="13" t="n"/>
+      <c r="H115" s="48" t="n"/>
+      <c r="I115" s="48" t="n"/>
+      <c r="J115" s="48" t="n"/>
+      <c r="K115" s="15" t="n">
+        <v>500</v>
+      </c>
+      <c r="L115" s="15" t="n">
+        <v>600</v>
+      </c>
+      <c r="M115" s="15" t="n"/>
+      <c r="N115" s="16" t="n"/>
+      <c r="O115" s="16" t="n"/>
+      <c r="P115" s="16" t="n"/>
+      <c r="Q115" s="48" t="n"/>
+      <c r="R115" s="48" t="n"/>
+      <c r="S115" s="48" t="n"/>
+      <c r="T115" s="49">
+        <f>IF(AND(H115&lt;&gt;"",Q115&lt;&gt;""),H115-Q115,"")</f>
+        <v/>
+      </c>
+      <c r="U115" s="48" t="n"/>
+      <c r="V115" s="48" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="13" t="n">
+        <v>111</v>
+      </c>
+      <c r="B116" s="12" t="inlineStr">
+        <is>
+          <t>1.스캐너-1</t>
+        </is>
+      </c>
+      <c r="C116" s="12" t="inlineStr">
+        <is>
+          <t>바코드기</t>
+        </is>
+      </c>
+      <c r="D116" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하</t>
+        </is>
+      </c>
+      <c r="E116" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="F116" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="G116" s="13" t="n"/>
+      <c r="H116" s="48" t="n"/>
+      <c r="I116" s="48" t="n"/>
+      <c r="J116" s="48" t="n"/>
+      <c r="K116" s="15" t="n">
+        <v>590</v>
+      </c>
+      <c r="L116" s="15" t="n">
+        <v>1200</v>
+      </c>
+      <c r="M116" s="15" t="n"/>
+      <c r="N116" s="16" t="n"/>
+      <c r="O116" s="16" t="n"/>
+      <c r="P116" s="16" t="n"/>
+      <c r="Q116" s="48" t="n"/>
+      <c r="R116" s="48" t="n"/>
+      <c r="S116" s="48" t="n"/>
+      <c r="T116" s="49">
+        <f>IF(AND(H116&lt;&gt;"",Q116&lt;&gt;""),H116-Q116,"")</f>
+        <v/>
+      </c>
+      <c r="U116" s="48" t="n"/>
+      <c r="V116" s="48" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="13" t="n">
+        <v>112</v>
+      </c>
+      <c r="B117" s="12" t="inlineStr">
+        <is>
+          <t>1.스캐너-1</t>
+        </is>
+      </c>
+      <c r="C117" s="12" t="inlineStr">
+        <is>
+          <t>바코드장비</t>
+        </is>
+      </c>
+      <c r="D117" s="50" t="inlineStr">
+        <is>
+          <t>솔바텍 인상</t>
+        </is>
+      </c>
+      <c r="E117" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="F117" s="13" t="n"/>
+      <c r="G117" s="13" t="n"/>
+      <c r="H117" s="48" t="n"/>
+      <c r="I117" s="48" t="n"/>
+      <c r="J117" s="48" t="n"/>
+      <c r="K117" s="15" t="n">
+        <v>3710</v>
+      </c>
+      <c r="L117" s="15" t="n">
+        <v>1800</v>
+      </c>
+      <c r="M117" s="15" t="n"/>
+      <c r="N117" s="16" t="n"/>
+      <c r="O117" s="16" t="n"/>
+      <c r="P117" s="16" t="n"/>
+      <c r="Q117" s="48" t="n"/>
+      <c r="R117" s="48" t="n"/>
+      <c r="S117" s="48" t="n"/>
+      <c r="T117" s="49">
+        <f>IF(AND(H117&lt;&gt;"",Q117&lt;&gt;""),H117-Q117,"")</f>
+        <v/>
+      </c>
+      <c r="U117" s="48" t="n"/>
+      <c r="V117" s="48" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="13" t="n">
+        <v>113</v>
+      </c>
+      <c r="B118" s="12" t="inlineStr">
+        <is>
+          <t>1.스캐너-1</t>
+        </is>
+      </c>
+      <c r="C118" s="12" t="inlineStr">
+        <is>
+          <t>바코드솔루션</t>
+        </is>
+      </c>
+      <c r="D118" s="50" t="inlineStr">
+        <is>
+          <t>솔바텍 인상</t>
+        </is>
+      </c>
+      <c r="E118" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="F118" s="13" t="n"/>
+      <c r="G118" s="13" t="n"/>
+      <c r="H118" s="48" t="n"/>
+      <c r="I118" s="48" t="n"/>
+      <c r="J118" s="48" t="n"/>
+      <c r="K118" s="15" t="n">
+        <v>3500</v>
+      </c>
+      <c r="L118" s="15" t="n">
+        <v>1850</v>
+      </c>
+      <c r="M118" s="15" t="n"/>
+      <c r="N118" s="16" t="n"/>
+      <c r="O118" s="16" t="n"/>
+      <c r="P118" s="16" t="n"/>
+      <c r="Q118" s="48" t="n"/>
+      <c r="R118" s="48" t="n"/>
+      <c r="S118" s="48" t="n"/>
+      <c r="T118" s="49">
+        <f>IF(AND(H118&lt;&gt;"",Q118&lt;&gt;""),H118-Q118,"")</f>
+        <v/>
+      </c>
+      <c r="U118" s="48" t="n"/>
+      <c r="V118" s="48" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="13" t="n">
+        <v>114</v>
+      </c>
+      <c r="B119" s="12" t="inlineStr">
+        <is>
+          <t>1.스캐너모델-2</t>
+        </is>
+      </c>
+      <c r="C119" s="12" t="inlineStr">
+        <is>
+          <t>SB7700</t>
+        </is>
+      </c>
+      <c r="D119" s="47" t="inlineStr">
+        <is>
+          <t>솔바텍 인하 (간격 벌리기)</t>
+        </is>
+      </c>
+      <c r="E119" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F119" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G119" s="13" t="n"/>
+      <c r="H119" s="48" t="n"/>
+      <c r="I119" s="48" t="n"/>
+      <c r="J119" s="48" t="n"/>
+      <c r="K119" s="15" t="n">
+        <v>150</v>
+      </c>
+      <c r="L119" s="15" t="n">
+        <v>320</v>
+      </c>
+      <c r="M119" s="15" t="n"/>
+      <c r="N119" s="16" t="n"/>
+      <c r="O119" s="16" t="n"/>
+      <c r="P119" s="16" t="n"/>
+      <c r="Q119" s="48" t="n"/>
+      <c r="R119" s="48" t="n"/>
+      <c r="S119" s="48" t="n"/>
+      <c r="T119" s="49">
+        <f>IF(AND(H119&lt;&gt;"",Q119&lt;&gt;""),H119-Q119,"")</f>
+        <v/>
+      </c>
+      <c r="U119" s="48" t="n"/>
+      <c r="V119" s="48" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="13" t="n">
+        <v>115</v>
+      </c>
+      <c r="B120" s="12" t="inlineStr">
+        <is>
+          <t>1.스캐너모델-2</t>
+        </is>
+      </c>
+      <c r="C120" s="12" t="inlineStr">
+        <is>
+          <t>LI3608</t>
+        </is>
+      </c>
+      <c r="D120" s="47" t="inlineStr">
+        <is>
+          <t>솔바텍 인하</t>
+        </is>
+      </c>
+      <c r="E120" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F120" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G120" s="13" t="n"/>
+      <c r="H120" s="48" t="n"/>
+      <c r="I120" s="48" t="n"/>
+      <c r="J120" s="48" t="n"/>
+      <c r="K120" s="15" t="n">
+        <v>900</v>
+      </c>
+      <c r="L120" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="M120" s="15" t="n"/>
+      <c r="N120" s="16" t="n"/>
+      <c r="O120" s="16" t="n"/>
+      <c r="P120" s="16" t="n"/>
+      <c r="Q120" s="48" t="n"/>
+      <c r="R120" s="48" t="n"/>
+      <c r="S120" s="48" t="n"/>
+      <c r="T120" s="49">
+        <f>IF(AND(H120&lt;&gt;"",Q120&lt;&gt;""),H120-Q120,"")</f>
+        <v/>
+      </c>
+      <c r="U120" s="48" t="n"/>
+      <c r="V120" s="48" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="13" t="n">
+        <v>116</v>
+      </c>
+      <c r="B121" s="12" t="inlineStr">
+        <is>
+          <t>2.프린터-1</t>
+        </is>
+      </c>
+      <c r="C121" s="34" t="inlineStr">
+        <is>
+          <t>제브라바코드프린터</t>
+        </is>
+      </c>
+      <c r="D121" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하 (간격 벌리기)</t>
+        </is>
+      </c>
+      <c r="E121" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="F121" s="13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="G121" s="13" t="n"/>
+      <c r="H121" s="48" t="n"/>
+      <c r="I121" s="48" t="n">
+        <v>7</v>
+      </c>
+      <c r="J121" s="48" t="n"/>
+      <c r="K121" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L121" s="15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="M121" s="15" t="n"/>
+      <c r="N121" s="16" t="n"/>
+      <c r="O121" s="16" t="n"/>
+      <c r="P121" s="16" t="n"/>
+      <c r="Q121" s="48" t="n"/>
+      <c r="R121" s="48" t="n"/>
+      <c r="S121" s="48" t="n"/>
+      <c r="T121" s="49">
+        <f>IF(AND(H121&lt;&gt;"",Q121&lt;&gt;""),H121-Q121,"")</f>
+        <v/>
+      </c>
+      <c r="U121" s="48" t="n"/>
+      <c r="V121" s="48" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="13" t="n">
+        <v>117</v>
+      </c>
+      <c r="B122" s="12" t="inlineStr">
+        <is>
+          <t>2.프린터-1</t>
+        </is>
+      </c>
+      <c r="C122" s="34" t="inlineStr">
+        <is>
+          <t>바코드프린터라벨</t>
+        </is>
+      </c>
+      <c r="D122" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하</t>
+        </is>
+      </c>
+      <c r="E122" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F122" s="13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G122" s="13" t="n"/>
+      <c r="H122" s="48" t="n">
+        <v>7</v>
+      </c>
+      <c r="I122" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="J122" s="48" t="n"/>
+      <c r="K122" s="15" t="n">
+        <v>1100</v>
+      </c>
+      <c r="L122" s="15" t="n">
+        <v>4000</v>
+      </c>
+      <c r="M122" s="15" t="n">
+        <v>1250</v>
+      </c>
+      <c r="N122" s="16" t="n"/>
+      <c r="O122" s="16" t="n"/>
+      <c r="P122" s="16" t="n"/>
+      <c r="Q122" s="48" t="n"/>
+      <c r="R122" s="48" t="n"/>
+      <c r="S122" s="48" t="n"/>
+      <c r="T122" s="49">
+        <f>IF(AND(H122&lt;&gt;"",Q122&lt;&gt;""),H122-Q122,"")</f>
+        <v/>
+      </c>
+      <c r="U122" s="48" t="n"/>
+      <c r="V122" s="48" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="13" t="n">
+        <v>118</v>
+      </c>
+      <c r="B123" s="12" t="inlineStr">
+        <is>
+          <t>2.프린터모델-2</t>
+        </is>
+      </c>
+      <c r="C123" s="12" t="inlineStr">
+        <is>
+          <t>MB-240T</t>
+        </is>
+      </c>
+      <c r="D123" s="47" t="inlineStr">
+        <is>
+          <t>솔바텍 인하 (간격 벌리기)</t>
+        </is>
+      </c>
+      <c r="E123" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F123" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G123" s="13" t="n"/>
+      <c r="H123" s="48" t="n"/>
+      <c r="I123" s="48" t="n"/>
+      <c r="J123" s="48" t="n"/>
+      <c r="K123" s="15" t="n">
+        <v>300</v>
+      </c>
+      <c r="L123" s="15" t="n">
+        <v>1500</v>
+      </c>
+      <c r="M123" s="15" t="n"/>
+      <c r="N123" s="16" t="n"/>
+      <c r="O123" s="16" t="n"/>
+      <c r="P123" s="16" t="n"/>
+      <c r="Q123" s="48" t="n"/>
+      <c r="R123" s="48" t="n"/>
+      <c r="S123" s="48" t="n"/>
+      <c r="T123" s="49">
+        <f>IF(AND(H123&lt;&gt;"",Q123&lt;&gt;""),H123-Q123,"")</f>
+        <v/>
+      </c>
+      <c r="U123" s="48" t="n"/>
+      <c r="V123" s="48" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="13" t="n">
+        <v>119</v>
+      </c>
+      <c r="B124" s="12" t="inlineStr">
+        <is>
+          <t>2.프린터모델-2</t>
+        </is>
+      </c>
+      <c r="C124" s="12" t="inlineStr">
+        <is>
+          <t>CL4NX</t>
+        </is>
+      </c>
+      <c r="D124" s="50" t="inlineStr">
+        <is>
+          <t>솔바텍 인상</t>
+        </is>
+      </c>
+      <c r="E124" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="F124" s="13" t="n"/>
+      <c r="G124" s="13" t="n"/>
+      <c r="H124" s="48" t="n"/>
+      <c r="I124" s="48" t="n"/>
+      <c r="J124" s="48" t="n"/>
+      <c r="K124" s="15" t="n">
+        <v>200</v>
+      </c>
+      <c r="L124" s="15" t="n">
+        <v>280</v>
+      </c>
+      <c r="M124" s="15" t="n"/>
+      <c r="N124" s="16" t="n"/>
+      <c r="O124" s="16" t="n"/>
+      <c r="P124" s="16" t="n"/>
+      <c r="Q124" s="48" t="n"/>
+      <c r="R124" s="48" t="n"/>
+      <c r="S124" s="48" t="n"/>
+      <c r="T124" s="49">
+        <f>IF(AND(H124&lt;&gt;"",Q124&lt;&gt;""),H124-Q124,"")</f>
+        <v/>
+      </c>
+      <c r="U124" s="48" t="n"/>
+      <c r="V124" s="48" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="13" t="n">
+        <v>120</v>
+      </c>
+      <c r="B125" s="12" t="inlineStr">
+        <is>
+          <t>3.라벨</t>
+        </is>
+      </c>
+      <c r="C125" s="12" t="inlineStr">
+        <is>
+          <t>라벨용지</t>
+        </is>
+      </c>
+      <c r="D125" s="47" t="inlineStr">
+        <is>
+          <t>솔바텍 인하 (간격 벌리기) / SB렌탈 인하</t>
+        </is>
+      </c>
+      <c r="E125" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="F125" s="13" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G125" s="13" t="n"/>
+      <c r="H125" s="48" t="n"/>
+      <c r="I125" s="48" t="n"/>
+      <c r="J125" s="48" t="n"/>
+      <c r="K125" s="15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="L125" s="15" t="n">
+        <v>4000</v>
+      </c>
+      <c r="M125" s="15" t="n">
+        <v>1450</v>
+      </c>
+      <c r="N125" s="16" t="n"/>
+      <c r="O125" s="16" t="n"/>
+      <c r="P125" s="16" t="n"/>
+      <c r="Q125" s="48" t="n"/>
+      <c r="R125" s="48" t="n"/>
+      <c r="S125" s="48" t="n"/>
+      <c r="T125" s="49">
+        <f>IF(AND(H125&lt;&gt;"",Q125&lt;&gt;""),H125-Q125,"")</f>
+        <v/>
+      </c>
+      <c r="U125" s="48" t="n"/>
+      <c r="V125" s="48" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="13" t="n">
+        <v>121</v>
+      </c>
+      <c r="B126" s="12" t="inlineStr">
+        <is>
+          <t>3.라벨</t>
+        </is>
+      </c>
+      <c r="C126" s="12" t="inlineStr">
+        <is>
+          <t>라벨출력</t>
+        </is>
+      </c>
+      <c r="D126" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하 (간격 벌리기)</t>
+        </is>
+      </c>
+      <c r="E126" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="F126" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="G126" s="13" t="n"/>
+      <c r="H126" s="48" t="n"/>
+      <c r="I126" s="48" t="n"/>
+      <c r="J126" s="48" t="n"/>
+      <c r="K126" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L126" s="15" t="n">
+        <v>1470</v>
+      </c>
+      <c r="M126" s="15" t="n"/>
+      <c r="N126" s="16" t="n"/>
+      <c r="O126" s="16" t="n"/>
+      <c r="P126" s="16" t="n"/>
+      <c r="Q126" s="48" t="n"/>
+      <c r="R126" s="48" t="n"/>
+      <c r="S126" s="48" t="n"/>
+      <c r="T126" s="49">
+        <f>IF(AND(H126&lt;&gt;"",Q126&lt;&gt;""),H126-Q126,"")</f>
+        <v/>
+      </c>
+      <c r="U126" s="48" t="n"/>
+      <c r="V126" s="48" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="13" t="n">
+        <v>122</v>
+      </c>
+      <c r="B127" s="12" t="inlineStr">
+        <is>
+          <t>3.라벨</t>
+        </is>
+      </c>
+      <c r="C127" s="12" t="inlineStr">
+        <is>
+          <t>바코드라벨출력</t>
+        </is>
+      </c>
+      <c r="D127" s="47" t="inlineStr">
+        <is>
+          <t>코스모스몰 인하</t>
+        </is>
+      </c>
+      <c r="E127" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="F127" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="G127" s="13" t="n"/>
+      <c r="H127" s="48" t="n"/>
+      <c r="I127" s="48" t="n"/>
+      <c r="J127" s="48" t="n"/>
+      <c r="K127" s="15" t="n">
+        <v>1080</v>
+      </c>
+      <c r="L127" s="15" t="n">
+        <v>1540</v>
+      </c>
+      <c r="M127" s="15" t="n"/>
+      <c r="N127" s="16" t="n"/>
+      <c r="O127" s="16" t="n"/>
+      <c r="P127" s="16" t="n"/>
+      <c r="Q127" s="48" t="n"/>
+      <c r="R127" s="48" t="n"/>
+      <c r="S127" s="48" t="n"/>
+      <c r="T127" s="49">
+        <f>IF(AND(H127&lt;&gt;"",Q127&lt;&gt;""),H127-Q127,"")</f>
+        <v/>
+      </c>
+      <c r="U127" s="48" t="n"/>
+      <c r="V127" s="48" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="13" t="n">
+        <v>123</v>
+      </c>
+      <c r="B128" s="12" t="inlineStr">
+        <is>
+          <t>3.라벨</t>
+        </is>
+      </c>
+      <c r="C128" s="12" t="inlineStr">
+        <is>
+          <t>감열용지</t>
+        </is>
+      </c>
+      <c r="D128" s="47" t="inlineStr">
+        <is>
+          <t>솔바텍 인하 (간격 벌리기)</t>
+        </is>
+      </c>
+      <c r="E128" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="F128" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="G128" s="13" t="n"/>
+      <c r="H128" s="48" t="n"/>
+      <c r="I128" s="48" t="n"/>
+      <c r="J128" s="48" t="n"/>
+      <c r="K128" s="15" t="n">
+        <v>560</v>
+      </c>
+      <c r="L128" s="15" t="n">
+        <v>740</v>
+      </c>
+      <c r="M128" s="15" t="n"/>
+      <c r="N128" s="16" t="n"/>
+      <c r="O128" s="16" t="n"/>
+      <c r="P128" s="16" t="n"/>
+      <c r="Q128" s="48" t="n"/>
+      <c r="R128" s="48" t="n"/>
+      <c r="S128" s="48" t="n"/>
+      <c r="T128" s="49">
+        <f>IF(AND(H128&lt;&gt;"",Q128&lt;&gt;""),H128-Q128,"")</f>
+        <v/>
+      </c>
+      <c r="U128" s="48" t="n"/>
+      <c r="V128" s="48" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="13" t="n">
+        <v>124</v>
+      </c>
+      <c r="B129" s="12" t="inlineStr">
+        <is>
+          <t>3.라벨</t>
+        </is>
+      </c>
+      <c r="C129" s="12" t="inlineStr">
+        <is>
+          <t>도서라벨</t>
+        </is>
+      </c>
+      <c r="D129" s="47" t="inlineStr">
+        <is>
+          <t>솔바텍 인하 (간격 벌리기)</t>
+        </is>
+      </c>
+      <c r="E129" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="F129" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="G129" s="13" t="n"/>
+      <c r="H129" s="48" t="n"/>
+      <c r="I129" s="48" t="n"/>
+      <c r="J129" s="48" t="n"/>
+      <c r="K129" s="15" t="n">
+        <v>670</v>
+      </c>
+      <c r="L129" s="15" t="n">
+        <v>910</v>
+      </c>
+      <c r="M129" s="15" t="n"/>
+      <c r="N129" s="16" t="n"/>
+      <c r="O129" s="16" t="n"/>
+      <c r="P129" s="16" t="n"/>
+      <c r="Q129" s="48" t="n"/>
+      <c r="R129" s="48" t="n"/>
+      <c r="S129" s="48" t="n"/>
+      <c r="T129" s="49">
+        <f>IF(AND(H129&lt;&gt;"",Q129&lt;&gt;""),H129-Q129,"")</f>
+        <v/>
+      </c>
+      <c r="U129" s="48" t="n"/>
+      <c r="V129" s="48" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="13" t="n">
+        <v>125</v>
+      </c>
+      <c r="B130" s="12" t="inlineStr">
+        <is>
+          <t>4.솔루션SW-1</t>
+        </is>
+      </c>
+      <c r="C130" s="12" t="inlineStr">
+        <is>
+          <t>창고재고관리</t>
+        </is>
+      </c>
+      <c r="D130" s="50" t="inlineStr">
+        <is>
+          <t>솔바텍 인상</t>
+        </is>
+      </c>
+      <c r="E130" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="F130" s="13" t="n"/>
+      <c r="G130" s="13" t="n"/>
+      <c r="H130" s="48" t="n"/>
+      <c r="I130" s="48" t="n"/>
+      <c r="J130" s="48" t="n"/>
+      <c r="K130" s="15" t="n">
+        <v>4890</v>
+      </c>
+      <c r="L130" s="15" t="n">
+        <v>2500</v>
+      </c>
+      <c r="M130" s="15" t="n"/>
+      <c r="N130" s="16" t="n"/>
+      <c r="O130" s="16" t="n"/>
+      <c r="P130" s="16" t="n"/>
+      <c r="Q130" s="48" t="n"/>
+      <c r="R130" s="48" t="n"/>
+      <c r="S130" s="48" t="n"/>
+      <c r="T130" s="49">
+        <f>IF(AND(H130&lt;&gt;"",Q130&lt;&gt;""),H130-Q130,"")</f>
+        <v/>
+      </c>
+      <c r="U130" s="48" t="n"/>
+      <c r="V130" s="48" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="13" t="n">
+        <v>126</v>
+      </c>
+      <c r="B131" s="12" t="inlineStr">
+        <is>
+          <t>5.리본</t>
+        </is>
+      </c>
+      <c r="C131" s="12" t="inlineStr">
+        <is>
+          <t>라벨지리본</t>
+        </is>
+      </c>
+      <c r="D131" s="50" t="inlineStr">
+        <is>
+          <t>솔바텍 인상</t>
+        </is>
+      </c>
+      <c r="E131" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="F131" s="13" t="n"/>
+      <c r="G131" s="13" t="n"/>
+      <c r="H131" s="48" t="n"/>
+      <c r="I131" s="48" t="n"/>
+      <c r="J131" s="48" t="n"/>
+      <c r="K131" s="15" t="n">
+        <v>540</v>
+      </c>
+      <c r="L131" s="15" t="n"/>
+      <c r="M131" s="15" t="n"/>
+      <c r="N131" s="16" t="n"/>
+      <c r="O131" s="16" t="n"/>
+      <c r="P131" s="16" t="n"/>
+      <c r="Q131" s="48" t="n"/>
+      <c r="R131" s="48" t="n"/>
+      <c r="S131" s="48" t="n"/>
+      <c r="T131" s="49">
+        <f>IF(AND(H131&lt;&gt;"",Q131&lt;&gt;""),H131-Q131,"")</f>
+        <v/>
+      </c>
+      <c r="U131" s="48" t="n"/>
+      <c r="V131" s="48" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="13" t="n">
+        <v>127</v>
+      </c>
+      <c r="B132" s="12" t="inlineStr">
+        <is>
+          <t>5.리본</t>
+        </is>
+      </c>
+      <c r="C132" s="12" t="inlineStr">
+        <is>
+          <t>제브라리본</t>
+        </is>
+      </c>
+      <c r="D132" s="50" t="inlineStr">
+        <is>
+          <t>솔바텍 인상</t>
+        </is>
+      </c>
+      <c r="E132" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="F132" s="13" t="n"/>
+      <c r="G132" s="13" t="n"/>
+      <c r="H132" s="48" t="n"/>
+      <c r="I132" s="48" t="n"/>
+      <c r="J132" s="48" t="n"/>
+      <c r="K132" s="15" t="n">
+        <v>830</v>
+      </c>
+      <c r="L132" s="15" t="n"/>
+      <c r="M132" s="15" t="n"/>
+      <c r="N132" s="16" t="n"/>
+      <c r="O132" s="16" t="n"/>
+      <c r="P132" s="16" t="n"/>
+      <c r="Q132" s="48" t="n"/>
+      <c r="R132" s="48" t="n"/>
+      <c r="S132" s="48" t="n"/>
+      <c r="T132" s="49">
+        <f>IF(AND(H132&lt;&gt;"",Q132&lt;&gt;""),H132-Q132,"")</f>
+        <v/>
+      </c>
+      <c r="U132" s="48" t="n"/>
+      <c r="V132" s="48" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="13" t="n">
+        <v>128</v>
+      </c>
+      <c r="B133" s="12" t="inlineStr">
+        <is>
+          <t>1.스캐너-1</t>
+        </is>
+      </c>
+      <c r="C133" s="12" t="inlineStr">
+        <is>
+          <t>저렴한스캐너</t>
+        </is>
+      </c>
+      <c r="D133" s="50" t="inlineStr">
+        <is>
+          <t>솔바텍 미노출 (다른 사이트는 노출됨) → 인상 또는 품질 확인</t>
+        </is>
+      </c>
+      <c r="E133" s="13" t="n"/>
+      <c r="F133" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G133" s="13" t="n"/>
+      <c r="H133" s="48" t="n"/>
+      <c r="I133" s="48" t="n"/>
+      <c r="J133" s="48" t="n"/>
+      <c r="K133" s="15" t="n">
+        <v>410</v>
+      </c>
+      <c r="L133" s="15" t="n">
+        <v>500</v>
+      </c>
+      <c r="M133" s="15" t="n"/>
+      <c r="N133" s="16" t="n"/>
+      <c r="O133" s="16" t="n"/>
+      <c r="P133" s="16" t="n"/>
+      <c r="Q133" s="48" t="n"/>
+      <c r="R133" s="48" t="n"/>
+      <c r="S133" s="48" t="n"/>
+      <c r="T133" s="49">
+        <f>IF(AND(H133&lt;&gt;"",Q133&lt;&gt;""),H133-Q133,"")</f>
+        <v/>
+      </c>
+      <c r="U133" s="48" t="n"/>
+      <c r="V133" s="48" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="13" t="n">
+        <v>129</v>
+      </c>
+      <c r="B134" s="12" t="inlineStr">
+        <is>
+          <t>1.스캐너-1</t>
+        </is>
+      </c>
+      <c r="C134" s="12" t="inlineStr">
+        <is>
+          <t>바코드판독기</t>
+        </is>
+      </c>
+      <c r="D134" s="50" t="inlineStr">
+        <is>
+          <t>솔바텍 미노출 (다른 사이트는 노출됨) → 인상 또는 품질 확인</t>
+        </is>
+      </c>
+      <c r="E134" s="13" t="n"/>
+      <c r="F134" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="G134" s="13" t="n"/>
+      <c r="H134" s="48" t="n"/>
+      <c r="I134" s="48" t="n"/>
+      <c r="J134" s="48" t="n"/>
+      <c r="K134" s="15" t="n">
+        <v>500</v>
+      </c>
+      <c r="L134" s="15" t="n">
+        <v>1300</v>
+      </c>
+      <c r="M134" s="15" t="n"/>
+      <c r="N134" s="16" t="n"/>
+      <c r="O134" s="16" t="n"/>
+      <c r="P134" s="16" t="n"/>
+      <c r="Q134" s="48" t="n"/>
+      <c r="R134" s="48" t="n"/>
+      <c r="S134" s="48" t="n"/>
+      <c r="T134" s="49">
+        <f>IF(AND(H134&lt;&gt;"",Q134&lt;&gt;""),H134-Q134,"")</f>
+        <v/>
+      </c>
+      <c r="U134" s="48" t="n"/>
+      <c r="V134" s="48" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="13" t="n">
+        <v>130</v>
+      </c>
+      <c r="B135" s="12" t="inlineStr">
+        <is>
+          <t>1.스캐너-1</t>
+        </is>
+      </c>
+      <c r="C135" s="12" t="inlineStr">
+        <is>
+          <t>바코드인식기</t>
+        </is>
+      </c>
+      <c r="D135" s="50" t="inlineStr">
+        <is>
+          <t>솔바텍 미노출 (다른 사이트는 노출됨) → 인상 또는 품질 확인</t>
+        </is>
+      </c>
+      <c r="E135" s="13" t="n"/>
+      <c r="F135" s="13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G135" s="13" t="n"/>
+      <c r="H135" s="48" t="n"/>
+      <c r="I135" s="48" t="n"/>
+      <c r="J135" s="48" t="n"/>
+      <c r="K135" s="15" t="n">
+        <v>2300</v>
+      </c>
+      <c r="L135" s="15" t="n">
+        <v>4500</v>
+      </c>
+      <c r="M135" s="15" t="n"/>
+      <c r="N135" s="16" t="n"/>
+      <c r="O135" s="16" t="n"/>
+      <c r="P135" s="16" t="n"/>
+      <c r="Q135" s="48" t="n"/>
+      <c r="R135" s="48" t="n"/>
+      <c r="S135" s="48" t="n"/>
+      <c r="T135" s="49">
+        <f>IF(AND(H135&lt;&gt;"",Q135&lt;&gt;""),H135-Q135,"")</f>
+        <v/>
+      </c>
+      <c r="U135" s="48" t="n"/>
+      <c r="V135" s="48" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="13" t="n">
+        <v>131</v>
+      </c>
+      <c r="B136" s="12" t="inlineStr">
+        <is>
+          <t>1.스캐너-1</t>
+        </is>
+      </c>
+      <c r="C136" s="12" t="inlineStr">
+        <is>
+          <t>바코드기기</t>
+        </is>
+      </c>
+      <c r="D136" s="50" t="inlineStr">
+        <is>
+          <t>솔바텍 미노출 (다른 사이트는 노출됨) → 인상 또는 품질 확인</t>
+        </is>
+      </c>
+      <c r="E136" s="13" t="n"/>
+      <c r="F136" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="G136" s="13" t="n"/>
+      <c r="H136" s="48" t="n"/>
+      <c r="I136" s="48" t="n"/>
+      <c r="J136" s="48" t="n"/>
+      <c r="K136" s="15" t="n">
+        <v>500</v>
+      </c>
+      <c r="L136" s="15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="M136" s="15" t="n"/>
+      <c r="N136" s="16" t="n"/>
+      <c r="O136" s="16" t="n"/>
+      <c r="P136" s="16" t="n"/>
+      <c r="Q136" s="48" t="n"/>
+      <c r="R136" s="48" t="n"/>
+      <c r="S136" s="48" t="n"/>
+      <c r="T136" s="49">
+        <f>IF(AND(H136&lt;&gt;"",Q136&lt;&gt;""),H136-Q136,"")</f>
+        <v/>
+      </c>
+      <c r="U136" s="48" t="n"/>
+      <c r="V136" s="48" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="13" t="n">
+        <v>132</v>
+      </c>
+      <c r="B137" s="12" t="inlineStr">
+        <is>
+          <t>1.스캐너-1</t>
+        </is>
+      </c>
+      <c r="C137" s="12" t="inlineStr">
+        <is>
+          <t>바코드모듈</t>
+        </is>
+      </c>
+      <c r="D137" s="50" t="inlineStr">
+        <is>
+          <t>솔바텍 미노출 (다른 사이트는 노출됨) → 인상 또는 품질 확인</t>
+        </is>
+      </c>
+      <c r="E137" s="13" t="n"/>
+      <c r="F137" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G137" s="13" t="n"/>
+      <c r="H137" s="48" t="n"/>
+      <c r="I137" s="48" t="n"/>
+      <c r="J137" s="48" t="n"/>
+      <c r="K137" s="15" t="n">
+        <v>200</v>
+      </c>
+      <c r="L137" s="15" t="n">
+        <v>600</v>
+      </c>
+      <c r="M137" s="15" t="n"/>
+      <c r="N137" s="16" t="n"/>
+      <c r="O137" s="16" t="n"/>
+      <c r="P137" s="16" t="n"/>
+      <c r="Q137" s="48" t="n"/>
+      <c r="R137" s="48" t="n"/>
+      <c r="S137" s="48" t="n"/>
+      <c r="T137" s="49">
+        <f>IF(AND(H137&lt;&gt;"",Q137&lt;&gt;""),H137-Q137,"")</f>
+        <v/>
+      </c>
+      <c r="U137" s="48" t="n"/>
+      <c r="V137" s="48" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="13" t="n">
+        <v>133</v>
+      </c>
+      <c r="B138" s="12" t="inlineStr">
+        <is>
+          <t>1.스캐너-1</t>
+        </is>
+      </c>
+      <c r="C138" s="12" t="inlineStr">
+        <is>
+          <t>산업용스캐너</t>
+        </is>
+      </c>
+      <c r="D138" s="50" t="inlineStr">
+        <is>
+          <t>솔바텍 미노출 (다른 사이트는 노출됨) → 인상 또는 품질 확인</t>
+        </is>
+      </c>
+      <c r="E138" s="13" t="n"/>
+      <c r="F138" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="G138" s="13" t="n"/>
+      <c r="H138" s="48" t="n"/>
+      <c r="I138" s="48" t="n"/>
+      <c r="J138" s="48" t="n"/>
+      <c r="K138" s="15" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L138" s="15" t="n">
+        <v>6000</v>
+      </c>
+      <c r="M138" s="15" t="n"/>
+      <c r="N138" s="16" t="n"/>
+      <c r="O138" s="16" t="n"/>
+      <c r="P138" s="16" t="n"/>
+      <c r="Q138" s="48" t="n"/>
+      <c r="R138" s="48" t="n"/>
+      <c r="S138" s="48" t="n"/>
+      <c r="T138" s="49">
+        <f>IF(AND(H138&lt;&gt;"",Q138&lt;&gt;""),H138-Q138,"")</f>
+        <v/>
+      </c>
+      <c r="U138" s="48" t="n"/>
+      <c r="V138" s="48" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="13" t="n">
+        <v>134</v>
+      </c>
+      <c r="B139" s="12" t="inlineStr">
+        <is>
+          <t>1.스캐너-1</t>
+        </is>
+      </c>
+      <c r="C139" s="12" t="inlineStr">
+        <is>
+          <t>CCD스캐너</t>
+        </is>
+      </c>
+      <c r="D139" s="50" t="inlineStr">
+        <is>
+          <t>솔바텍 미노출 (다른 사이트는 노출됨) → 인상 또는 품질 확인</t>
+        </is>
+      </c>
+      <c r="E139" s="13" t="n"/>
+      <c r="F139" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G139" s="13" t="n"/>
+      <c r="H139" s="48" t="n"/>
+      <c r="I139" s="48" t="n"/>
+      <c r="J139" s="48" t="n"/>
+      <c r="K139" s="15" t="n">
+        <v>1370</v>
+      </c>
+      <c r="L139" s="15" t="n">
+        <v>3000</v>
+      </c>
+      <c r="M139" s="15" t="n"/>
+      <c r="N139" s="16" t="n"/>
+      <c r="O139" s="16" t="n"/>
+      <c r="P139" s="16" t="n"/>
+      <c r="Q139" s="48" t="n"/>
+      <c r="R139" s="48" t="n"/>
+      <c r="S139" s="48" t="n"/>
+      <c r="T139" s="49">
+        <f>IF(AND(H139&lt;&gt;"",Q139&lt;&gt;""),H139-Q139,"")</f>
+        <v/>
+      </c>
+      <c r="U139" s="48" t="n"/>
+      <c r="V139" s="48" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="13" t="n">
+        <v>135</v>
+      </c>
+      <c r="B140" s="12" t="inlineStr">
+        <is>
+          <t>1.스캐너모델-2</t>
+        </is>
+      </c>
+      <c r="C140" s="12" t="inlineStr">
+        <is>
+          <t>XENON1950SR</t>
+        </is>
+      </c>
+      <c r="D140" s="47" t="inlineStr">
+        <is>
+          <t>솔바텍 인하</t>
+        </is>
+      </c>
+      <c r="E140" s="13" t="n"/>
+      <c r="F140" s="13" t="n"/>
+      <c r="G140" s="13" t="n"/>
+      <c r="H140" s="48" t="n"/>
+      <c r="I140" s="48" t="n"/>
+      <c r="J140" s="48" t="n"/>
+      <c r="K140" s="15" t="n">
+        <v>700</v>
+      </c>
+      <c r="L140" s="15" t="n">
+        <v>700</v>
+      </c>
+      <c r="M140" s="15" t="n"/>
+      <c r="N140" s="16" t="n"/>
+      <c r="O140" s="16" t="n"/>
+      <c r="P140" s="16" t="n"/>
+      <c r="Q140" s="48" t="n"/>
+      <c r="R140" s="48" t="n"/>
+      <c r="S140" s="48" t="n"/>
+      <c r="T140" s="49">
+        <f>IF(AND(H140&lt;&gt;"",Q140&lt;&gt;""),H140-Q140,"")</f>
+        <v/>
+      </c>
+      <c r="U140" s="48" t="n"/>
+      <c r="V140" s="48" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="13" t="n">
+        <v>136</v>
+      </c>
+      <c r="B141" s="12" t="inlineStr">
+        <is>
+          <t>2.프린터-1</t>
+        </is>
+      </c>
+      <c r="C141" s="34" t="inlineStr">
+        <is>
+          <t>라벨인쇄기계</t>
+        </is>
+      </c>
+      <c r="D141" s="50" t="inlineStr">
+        <is>
+          <t>솔바텍 미노출 (다른 사이트는 노출됨) → 인상 또는 품질 확인</t>
+        </is>
+      </c>
+      <c r="E141" s="13" t="n"/>
+      <c r="F141" s="13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G141" s="13" t="n"/>
+      <c r="H141" s="48" t="n"/>
+      <c r="I141" s="48" t="n"/>
+      <c r="J141" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="K141" s="15" t="n">
+        <v>600</v>
+      </c>
+      <c r="L141" s="15" t="n">
+        <v>1500</v>
+      </c>
+      <c r="M141" s="15" t="n"/>
+      <c r="N141" s="16" t="n"/>
+      <c r="O141" s="16" t="n"/>
+      <c r="P141" s="16" t="n"/>
+      <c r="Q141" s="48" t="n"/>
+      <c r="R141" s="48" t="n"/>
+      <c r="S141" s="48" t="n"/>
+      <c r="T141" s="49">
+        <f>IF(AND(H141&lt;&gt;"",Q141&lt;&gt;""),H141-Q141,"")</f>
+        <v/>
+      </c>
+      <c r="U141" s="48" t="n"/>
+      <c r="V141" s="48" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="13" t="n">
+        <v>137</v>
+      </c>
+      <c r="B142" s="12" t="inlineStr">
+        <is>
+          <t>2.프린터-1</t>
+        </is>
+      </c>
+      <c r="C142" s="34" t="inlineStr">
+        <is>
+          <t>바코드프린터추천</t>
+        </is>
+      </c>
+      <c r="D142" s="50" t="inlineStr">
+        <is>
+          <t>솔바텍 미노출 (다른 사이트는 노출됨) → 인상 또는 품질 확인</t>
+        </is>
+      </c>
+      <c r="E142" s="13" t="n"/>
+      <c r="F142" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="G142" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H142" s="48" t="n"/>
+      <c r="I142" s="48" t="n">
+        <v>7</v>
+      </c>
+      <c r="J142" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="K142" s="15" t="n">
+        <v>1700</v>
+      </c>
+      <c r="L142" s="15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="M142" s="15" t="n">
+        <v>3700</v>
+      </c>
+      <c r="N142" s="16" t="n"/>
+      <c r="O142" s="16" t="n"/>
+      <c r="P142" s="16" t="n"/>
+      <c r="Q142" s="48" t="n"/>
+      <c r="R142" s="48" t="n"/>
+      <c r="S142" s="48" t="n"/>
+      <c r="T142" s="49">
+        <f>IF(AND(H142&lt;&gt;"",Q142&lt;&gt;""),H142-Q142,"")</f>
+        <v/>
+      </c>
+      <c r="U142" s="48" t="n"/>
+      <c r="V142" s="48" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="13" t="n">
+        <v>138</v>
+      </c>
+      <c r="B143" s="12" t="inlineStr">
+        <is>
+          <t>2.프린터-1</t>
+        </is>
+      </c>
+      <c r="C143" s="34" t="inlineStr">
+        <is>
+          <t>바코드발행기</t>
+        </is>
+      </c>
+      <c r="D143" s="50" t="inlineStr">
+        <is>
+          <t>솔바텍 미노출 (다른 사이트는 노출됨) → 인상 또는 품질 확인</t>
+        </is>
+      </c>
+      <c r="E143" s="13" t="n"/>
+      <c r="F143" s="13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G143" s="13" t="n"/>
+      <c r="H143" s="48" t="n"/>
+      <c r="I143" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="J143" s="48" t="n"/>
+      <c r="K143" s="15" t="n">
+        <v>400</v>
+      </c>
+      <c r="L143" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="M143" s="15" t="n"/>
+      <c r="N143" s="16" t="n"/>
+      <c r="O143" s="16" t="n"/>
+      <c r="P143" s="16" t="n"/>
+      <c r="Q143" s="48" t="n"/>
+      <c r="R143" s="48" t="n"/>
+      <c r="S143" s="48" t="n"/>
+      <c r="T143" s="49">
+        <f>IF(AND(H143&lt;&gt;"",Q143&lt;&gt;""),H143-Q143,"")</f>
+        <v/>
+      </c>
+      <c r="U143" s="48" t="n"/>
+      <c r="V143" s="48" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="13" t="n">
+        <v>139</v>
+      </c>
+      <c r="B144" s="12" t="inlineStr">
+        <is>
+          <t>2.프린터-1</t>
+        </is>
+      </c>
+      <c r="C144" s="34" t="inlineStr">
+        <is>
+          <t>산업용바코드프린터</t>
+        </is>
+      </c>
+      <c r="D144" s="50" t="inlineStr">
+        <is>
+          <t>솔바텍 미노출 (다른 사이트는 노출됨) → 인상 또는 품질 확인</t>
+        </is>
+      </c>
+      <c r="E144" s="13" t="n"/>
+      <c r="F144" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="G144" s="13" t="n"/>
+      <c r="H144" s="48" t="n"/>
+      <c r="I144" s="48" t="n"/>
+      <c r="J144" s="48" t="n"/>
+      <c r="K144" s="15" t="n">
+        <v>800</v>
+      </c>
+      <c r="L144" s="15" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M144" s="15" t="n"/>
+      <c r="N144" s="16" t="n"/>
+      <c r="O144" s="16" t="n"/>
+      <c r="P144" s="16" t="n"/>
+      <c r="Q144" s="48" t="n"/>
+      <c r="R144" s="48" t="n"/>
+      <c r="S144" s="48" t="n"/>
+      <c r="T144" s="49">
+        <f>IF(AND(H144&lt;&gt;"",Q144&lt;&gt;""),H144-Q144,"")</f>
+        <v/>
+      </c>
+      <c r="U144" s="48" t="n"/>
+      <c r="V144" s="48" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="13" t="n">
+        <v>140</v>
+      </c>
+      <c r="B145" s="12" t="inlineStr">
+        <is>
+          <t>2.프린터-1</t>
+        </is>
+      </c>
+      <c r="C145" s="34" t="inlineStr">
+        <is>
+          <t>롤라벨인쇄기</t>
+        </is>
+      </c>
+      <c r="D145" s="50" t="inlineStr">
+        <is>
+          <t>솔바텍 미노출 (다른 사이트는 노출됨) → 인상 또는 품질 확인</t>
+        </is>
+      </c>
+      <c r="E145" s="13" t="n"/>
+      <c r="F145" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G145" s="13" t="n"/>
+      <c r="H145" s="48" t="n"/>
+      <c r="I145" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="J145" s="48" t="n"/>
+      <c r="K145" s="15" t="n">
+        <v>70</v>
+      </c>
+      <c r="L145" s="15" t="n">
+        <v>4000</v>
+      </c>
+      <c r="M145" s="15" t="n"/>
+      <c r="N145" s="16" t="n"/>
+      <c r="O145" s="16" t="n"/>
+      <c r="P145" s="16" t="n"/>
+      <c r="Q145" s="48" t="n"/>
+      <c r="R145" s="48" t="n"/>
+      <c r="S145" s="48" t="n"/>
+      <c r="T145" s="49">
+        <f>IF(AND(H145&lt;&gt;"",Q145&lt;&gt;""),H145-Q145,"")</f>
+        <v/>
+      </c>
+      <c r="U145" s="48" t="n"/>
+      <c r="V145" s="48" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="13" t="n">
+        <v>141</v>
+      </c>
+      <c r="B146" s="12" t="inlineStr">
+        <is>
+          <t>2.프린터-1</t>
+        </is>
+      </c>
+      <c r="C146" s="34" t="inlineStr">
+        <is>
+          <t>열전사프린터기</t>
+        </is>
+      </c>
+      <c r="D146" s="50" t="inlineStr">
+        <is>
+          <t>솔바텍 미노출 (다른 사이트는 노출됨) → 인상 또는 품질 확인</t>
+        </is>
+      </c>
+      <c r="E146" s="13" t="n"/>
+      <c r="F146" s="13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="G146" s="13" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H146" s="48" t="n"/>
+      <c r="I146" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="J146" s="48" t="n">
+        <v>9</v>
+      </c>
+      <c r="K146" s="15" t="n">
+        <v>450</v>
+      </c>
+      <c r="L146" s="15" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M146" s="15" t="n">
+        <v>4000</v>
+      </c>
+      <c r="N146" s="16" t="n"/>
+      <c r="O146" s="16" t="n"/>
+      <c r="P146" s="16" t="n"/>
+      <c r="Q146" s="48" t="n"/>
+      <c r="R146" s="48" t="n"/>
+      <c r="S146" s="48" t="n"/>
+      <c r="T146" s="49">
+        <f>IF(AND(H146&lt;&gt;"",Q146&lt;&gt;""),H146-Q146,"")</f>
+        <v/>
+      </c>
+      <c r="U146" s="48" t="n"/>
+      <c r="V146" s="48" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="13" t="n">
+        <v>142</v>
+      </c>
+      <c r="B147" s="12" t="inlineStr">
+        <is>
+          <t>3.라벨</t>
+        </is>
+      </c>
+      <c r="C147" s="12" t="inlineStr">
+        <is>
+          <t>바코드인쇄</t>
+        </is>
+      </c>
+      <c r="D147" s="50" t="inlineStr">
+        <is>
+          <t>솔바텍 미노출 (다른 사이트는 노출됨) → 인상 또는 품질 확인</t>
+        </is>
+      </c>
+      <c r="E147" s="13" t="n"/>
+      <c r="F147" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="G147" s="13" t="n"/>
+      <c r="H147" s="48" t="n"/>
+      <c r="I147" s="48" t="n"/>
+      <c r="J147" s="48" t="n"/>
+      <c r="K147" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L147" s="15" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M147" s="15" t="n">
+        <v>500</v>
+      </c>
+      <c r="N147" s="16" t="n"/>
+      <c r="O147" s="16" t="n"/>
+      <c r="P147" s="16" t="n"/>
+      <c r="Q147" s="48" t="n"/>
+      <c r="R147" s="48" t="n"/>
+      <c r="S147" s="48" t="n"/>
+      <c r="T147" s="49">
+        <f>IF(AND(H147&lt;&gt;"",Q147&lt;&gt;""),H147-Q147,"")</f>
+        <v/>
+      </c>
+      <c r="U147" s="48" t="n"/>
+      <c r="V147" s="48" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="13" t="n">
+        <v>143</v>
+      </c>
+      <c r="B148" s="12" t="inlineStr">
+        <is>
+          <t>3.라벨</t>
+        </is>
+      </c>
+      <c r="C148" s="12" t="inlineStr">
+        <is>
+          <t>감열지인쇄</t>
+        </is>
+      </c>
+      <c r="D148" s="50" t="inlineStr">
+        <is>
+          <t>솔바텍 미노출 (다른 사이트는 노출됨) → 인상 또는 품질 확인</t>
+        </is>
+      </c>
+      <c r="E148" s="13" t="n"/>
+      <c r="F148" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G148" s="13" t="n"/>
+      <c r="H148" s="48" t="n"/>
+      <c r="I148" s="48" t="n"/>
+      <c r="J148" s="48" t="n"/>
+      <c r="K148" s="15" t="n">
+        <v>540</v>
+      </c>
+      <c r="L148" s="15" t="n">
+        <v>760</v>
+      </c>
+      <c r="M148" s="15" t="n"/>
+      <c r="N148" s="16" t="n"/>
+      <c r="O148" s="16" t="n"/>
+      <c r="P148" s="16" t="n"/>
+      <c r="Q148" s="48" t="n"/>
+      <c r="R148" s="48" t="n"/>
+      <c r="S148" s="48" t="n"/>
+      <c r="T148" s="49">
+        <f>IF(AND(H148&lt;&gt;"",Q148&lt;&gt;""),H148-Q148,"")</f>
+        <v/>
+      </c>
+      <c r="U148" s="48" t="n"/>
+      <c r="V148" s="48" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="13" t="n">
+        <v>144</v>
+      </c>
+      <c r="B149" s="12" t="inlineStr">
+        <is>
+          <t>3.라벨</t>
+        </is>
+      </c>
+      <c r="C149" s="12" t="inlineStr">
+        <is>
+          <t>라벨바코드</t>
+        </is>
+      </c>
+      <c r="D149" s="50" t="inlineStr">
+        <is>
+          <t>솔바텍 미노출 (다른 사이트는 노출됨) → 인상 또는 품질 확인</t>
+        </is>
+      </c>
+      <c r="E149" s="13" t="n"/>
+      <c r="F149" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="G149" s="13" t="n"/>
+      <c r="H149" s="48" t="n"/>
+      <c r="I149" s="48" t="n"/>
+      <c r="J149" s="48" t="n"/>
+      <c r="K149" s="15" t="n">
+        <v>290</v>
+      </c>
+      <c r="L149" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="M149" s="15" t="n"/>
+      <c r="N149" s="16" t="n"/>
+      <c r="O149" s="16" t="n"/>
+      <c r="P149" s="16" t="n"/>
+      <c r="Q149" s="48" t="n"/>
+      <c r="R149" s="48" t="n"/>
+      <c r="S149" s="48" t="n"/>
+      <c r="T149" s="49">
+        <f>IF(AND(H149&lt;&gt;"",Q149&lt;&gt;""),H149-Q149,"")</f>
+        <v/>
+      </c>
+      <c r="U149" s="48" t="n"/>
+      <c r="V149" s="48" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="13" t="n">
+        <v>145</v>
+      </c>
+      <c r="B150" s="12" t="inlineStr">
+        <is>
+          <t>3.라벨</t>
+        </is>
+      </c>
+      <c r="C150" s="12" t="inlineStr">
+        <is>
+          <t>라벨제작업체</t>
+        </is>
+      </c>
+      <c r="D150" s="50" t="inlineStr">
+        <is>
+          <t>솔바텍 미노출 (다른 사이트는 노출됨) → 인상 또는 품질 확인</t>
+        </is>
+      </c>
+      <c r="E150" s="13" t="n"/>
+      <c r="F150" s="13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G150" s="13" t="n"/>
+      <c r="H150" s="48" t="n"/>
+      <c r="I150" s="48" t="n"/>
+      <c r="J150" s="48" t="n"/>
+      <c r="K150" s="15" t="n">
+        <v>650</v>
+      </c>
+      <c r="L150" s="15" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M150" s="15" t="n">
+        <v>430</v>
+      </c>
+      <c r="N150" s="16" t="n"/>
+      <c r="O150" s="16" t="n"/>
+      <c r="P150" s="16" t="n"/>
+      <c r="Q150" s="48" t="n"/>
+      <c r="R150" s="48" t="n"/>
+      <c r="S150" s="48" t="n"/>
+      <c r="T150" s="49">
+        <f>IF(AND(H150&lt;&gt;"",Q150&lt;&gt;""),H150-Q150,"")</f>
+        <v/>
+      </c>
+      <c r="U150" s="48" t="n"/>
+      <c r="V150" s="48" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="13" t="n">
+        <v>146</v>
+      </c>
+      <c r="B151" s="12" t="inlineStr">
+        <is>
+          <t>3.라벨</t>
+        </is>
+      </c>
+      <c r="C151" s="12" t="inlineStr">
+        <is>
+          <t>라벨주문제작</t>
+        </is>
+      </c>
+      <c r="D151" s="50" t="inlineStr">
+        <is>
+          <t>솔바텍 미노출 (다른 사이트는 노출됨) → 인상 또는 품질 확인</t>
+        </is>
+      </c>
+      <c r="E151" s="13" t="n"/>
+      <c r="F151" s="13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G151" s="13" t="n"/>
+      <c r="H151" s="48" t="n"/>
+      <c r="I151" s="48" t="n"/>
+      <c r="J151" s="48" t="n"/>
+      <c r="K151" s="15" t="n">
+        <v>1150</v>
+      </c>
+      <c r="L151" s="15" t="n">
+        <v>6000</v>
+      </c>
+      <c r="M151" s="15" t="n">
+        <v>900</v>
+      </c>
+      <c r="N151" s="16" t="n"/>
+      <c r="O151" s="16" t="n"/>
+      <c r="P151" s="16" t="n"/>
+      <c r="Q151" s="48" t="n"/>
+      <c r="R151" s="48" t="n"/>
+      <c r="S151" s="48" t="n"/>
+      <c r="T151" s="49">
+        <f>IF(AND(H151&lt;&gt;"",Q151&lt;&gt;""),H151-Q151,"")</f>
+        <v/>
+      </c>
+      <c r="U151" s="48" t="n"/>
+      <c r="V151" s="48" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="13" t="n">
+        <v>147</v>
+      </c>
+      <c r="B152" s="12" t="inlineStr">
+        <is>
+          <t>3.라벨</t>
+        </is>
+      </c>
+      <c r="C152" s="12" t="inlineStr">
+        <is>
+          <t>라벨지인쇄</t>
+        </is>
+      </c>
+      <c r="D152" s="50" t="inlineStr">
+        <is>
+          <t>솔바텍 미노출 (다른 사이트는 노출됨) → 인상 또는 품질 확인</t>
+        </is>
+      </c>
+      <c r="E152" s="13" t="n"/>
+      <c r="F152" s="13" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G152" s="13" t="n"/>
+      <c r="H152" s="48" t="n"/>
+      <c r="I152" s="48" t="n"/>
+      <c r="J152" s="48" t="n"/>
+      <c r="K152" s="15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="L152" s="15" t="n">
+        <v>3000</v>
+      </c>
+      <c r="M152" s="15" t="n"/>
+      <c r="N152" s="16" t="n"/>
+      <c r="O152" s="16" t="n"/>
+      <c r="P152" s="16" t="n"/>
+      <c r="Q152" s="48" t="n"/>
+      <c r="R152" s="48" t="n"/>
+      <c r="S152" s="48" t="n"/>
+      <c r="T152" s="49">
+        <f>IF(AND(H152&lt;&gt;"",Q152&lt;&gt;""),H152-Q152,"")</f>
+        <v/>
+      </c>
+      <c r="U152" s="48" t="n"/>
+      <c r="V152" s="48" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="13" t="n">
+        <v>148</v>
+      </c>
+      <c r="B153" s="12" t="inlineStr">
+        <is>
+          <t>3.라벨</t>
+        </is>
+      </c>
+      <c r="C153" s="12" t="inlineStr">
+        <is>
+          <t>라벨지출력</t>
+        </is>
+      </c>
+      <c r="D153" s="50" t="inlineStr">
+        <is>
+          <t>솔바텍 미노출 (다른 사이트는 노출됨) → 인상 또는 품질 확인</t>
+        </is>
+      </c>
+      <c r="E153" s="13" t="n"/>
+      <c r="F153" s="13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G153" s="13" t="n"/>
+      <c r="H153" s="48" t="n"/>
+      <c r="I153" s="48" t="n"/>
+      <c r="J153" s="48" t="n"/>
+      <c r="K153" s="15" t="n">
+        <v>810</v>
+      </c>
+      <c r="L153" s="15" t="n">
+        <v>2500</v>
+      </c>
+      <c r="M153" s="15" t="n"/>
+      <c r="N153" s="16" t="n"/>
+      <c r="O153" s="16" t="n"/>
+      <c r="P153" s="16" t="n"/>
+      <c r="Q153" s="48" t="n"/>
+      <c r="R153" s="48" t="n"/>
+      <c r="S153" s="48" t="n"/>
+      <c r="T153" s="49">
+        <f>IF(AND(H153&lt;&gt;"",Q153&lt;&gt;""),H153-Q153,"")</f>
+        <v/>
+      </c>
+      <c r="U153" s="48" t="n"/>
+      <c r="V153" s="48" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="13" t="n">
+        <v>149</v>
+      </c>
+      <c r="B154" s="12" t="inlineStr">
+        <is>
+          <t>3.라벨</t>
+        </is>
+      </c>
+      <c r="C154" s="12" t="inlineStr">
+        <is>
+          <t>바코드출력대행</t>
+        </is>
+      </c>
+      <c r="D154" s="50" t="inlineStr">
+        <is>
+          <t>솔바텍 미노출 (다른 사이트는 노출됨) → 인상 또는 품질 확인</t>
+        </is>
+      </c>
+      <c r="E154" s="13" t="n"/>
+      <c r="F154" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G154" s="13" t="n"/>
+      <c r="H154" s="48" t="n"/>
+      <c r="I154" s="48" t="n"/>
+      <c r="J154" s="48" t="n"/>
+      <c r="K154" s="15" t="n">
+        <v>520</v>
+      </c>
+      <c r="L154" s="15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="M154" s="15" t="n"/>
+      <c r="N154" s="16" t="n"/>
+      <c r="O154" s="16" t="n"/>
+      <c r="P154" s="16" t="n"/>
+      <c r="Q154" s="48" t="n"/>
+      <c r="R154" s="48" t="n"/>
+      <c r="S154" s="48" t="n"/>
+      <c r="T154" s="49">
+        <f>IF(AND(H154&lt;&gt;"",Q154&lt;&gt;""),H154-Q154,"")</f>
+        <v/>
+      </c>
+      <c r="U154" s="48" t="n"/>
+      <c r="V154" s="48" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="B155" s="12" t="inlineStr">
+        <is>
+          <t>3.라벨</t>
+        </is>
+      </c>
+      <c r="C155" s="12" t="inlineStr">
+        <is>
+          <t>바코드출력</t>
+        </is>
+      </c>
+      <c r="D155" s="50" t="inlineStr">
+        <is>
+          <t>솔바텍 미노출 (다른 사이트는 노출됨) → 인상 또는 품질 확인</t>
+        </is>
+      </c>
+      <c r="E155" s="13" t="n"/>
+      <c r="F155" s="13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G155" s="13" t="n"/>
+      <c r="H155" s="48" t="n"/>
+      <c r="I155" s="48" t="n"/>
+      <c r="J155" s="48" t="n"/>
+      <c r="K155" s="15" t="n">
+        <v>1660</v>
+      </c>
+      <c r="L155" s="15" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M155" s="15" t="n"/>
+      <c r="N155" s="16" t="n"/>
+      <c r="O155" s="16" t="n"/>
+      <c r="P155" s="16" t="n"/>
+      <c r="Q155" s="48" t="n"/>
+      <c r="R155" s="48" t="n"/>
+      <c r="S155" s="48" t="n"/>
+      <c r="T155" s="49">
+        <f>IF(AND(H155&lt;&gt;"",Q155&lt;&gt;""),H155-Q155,"")</f>
+        <v/>
+      </c>
+      <c r="U155" s="48" t="n"/>
+      <c r="V155" s="48" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="13" t="n">
+        <v>151</v>
+      </c>
+      <c r="B156" s="12" t="inlineStr">
+        <is>
+          <t>3.라벨</t>
+        </is>
+      </c>
+      <c r="C156" s="12" t="inlineStr">
+        <is>
+          <t>바코드프린터먹지</t>
+        </is>
+      </c>
+      <c r="D156" s="50" t="inlineStr">
+        <is>
+          <t>솔바텍 미노출 (다른 사이트는 노출됨) → 인상 또는 품질 확인</t>
+        </is>
+      </c>
+      <c r="E156" s="13" t="n"/>
+      <c r="F156" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="G156" s="13" t="n"/>
+      <c r="H156" s="48" t="n"/>
+      <c r="I156" s="48" t="n"/>
+      <c r="J156" s="48" t="n"/>
+      <c r="K156" s="15" t="n">
+        <v>490</v>
+      </c>
+      <c r="L156" s="15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="M156" s="15" t="n">
+        <v>290</v>
+      </c>
+      <c r="N156" s="16" t="n"/>
+      <c r="O156" s="16" t="n"/>
+      <c r="P156" s="16" t="n"/>
+      <c r="Q156" s="48" t="n"/>
+      <c r="R156" s="48" t="n"/>
+      <c r="S156" s="48" t="n"/>
+      <c r="T156" s="49">
+        <f>IF(AND(H156&lt;&gt;"",Q156&lt;&gt;""),H156-Q156,"")</f>
+        <v/>
+      </c>
+      <c r="U156" s="48" t="n"/>
+      <c r="V156" s="48" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="13" t="n">
+        <v>152</v>
+      </c>
+      <c r="B157" s="12" t="inlineStr">
+        <is>
+          <t>3.라벨</t>
+        </is>
+      </c>
+      <c r="C157" s="12" t="inlineStr">
+        <is>
+          <t>프린터라벨</t>
+        </is>
+      </c>
+      <c r="D157" s="50" t="inlineStr">
+        <is>
+          <t>솔바텍 미노출 (다른 사이트는 노출됨) → 인상 또는 품질 확인</t>
+        </is>
+      </c>
+      <c r="E157" s="13" t="n"/>
+      <c r="F157" s="13" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="G157" s="13" t="n"/>
+      <c r="H157" s="48" t="n"/>
+      <c r="I157" s="48" t="n"/>
+      <c r="J157" s="48" t="n"/>
+      <c r="K157" s="15" t="n">
+        <v>810</v>
+      </c>
+      <c r="L157" s="15" t="n">
+        <v>3000</v>
+      </c>
+      <c r="M157" s="15" t="n"/>
+      <c r="N157" s="16" t="n"/>
+      <c r="O157" s="16" t="n"/>
+      <c r="P157" s="16" t="n"/>
+      <c r="Q157" s="48" t="n"/>
+      <c r="R157" s="48" t="n"/>
+      <c r="S157" s="48" t="n"/>
+      <c r="T157" s="49">
+        <f>IF(AND(H157&lt;&gt;"",Q157&lt;&gt;""),H157-Q157,"")</f>
+        <v/>
+      </c>
+      <c r="U157" s="48" t="n"/>
+      <c r="V157" s="48" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="13" t="n">
+        <v>153</v>
+      </c>
+      <c r="B158" s="12" t="inlineStr">
+        <is>
+          <t>3.라벨</t>
+        </is>
+      </c>
+      <c r="C158" s="12" t="inlineStr">
+        <is>
+          <t>프린터라벨지</t>
+        </is>
+      </c>
+      <c r="D158" s="50" t="inlineStr">
+        <is>
+          <t>솔바텍 미노출 (다른 사이트는 노출됨) → 인상 또는 품질 확인</t>
+        </is>
+      </c>
+      <c r="E158" s="13" t="n"/>
+      <c r="F158" s="13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G158" s="13" t="n"/>
+      <c r="H158" s="48" t="n"/>
+      <c r="I158" s="48" t="n"/>
+      <c r="J158" s="48" t="n"/>
+      <c r="K158" s="15" t="n">
+        <v>500</v>
+      </c>
+      <c r="L158" s="15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="M158" s="15" t="n">
+        <v>400</v>
+      </c>
+      <c r="N158" s="16" t="n"/>
+      <c r="O158" s="16" t="n"/>
+      <c r="P158" s="16" t="n"/>
+      <c r="Q158" s="48" t="n"/>
+      <c r="R158" s="48" t="n"/>
+      <c r="S158" s="48" t="n"/>
+      <c r="T158" s="49">
+        <f>IF(AND(H158&lt;&gt;"",Q158&lt;&gt;""),H158-Q158,"")</f>
+        <v/>
+      </c>
+      <c r="U158" s="48" t="n"/>
+      <c r="V158" s="48" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="13" t="n">
+        <v>154</v>
+      </c>
+      <c r="B159" s="12" t="inlineStr">
+        <is>
+          <t>6.PDA모델-3</t>
+        </is>
+      </c>
+      <c r="C159" s="12" t="inlineStr">
+        <is>
+          <t>RFIDGUN</t>
+        </is>
+      </c>
+      <c r="D159" s="50" t="inlineStr">
+        <is>
+          <t>솔바텍 미노출 (다른 사이트는 노출됨) → 인상 또는 품질 확인</t>
+        </is>
+      </c>
+      <c r="E159" s="13" t="n"/>
+      <c r="F159" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G159" s="13" t="n"/>
+      <c r="H159" s="48" t="n"/>
+      <c r="I159" s="48" t="n"/>
+      <c r="J159" s="48" t="n"/>
+      <c r="K159" s="15" t="n">
+        <v>70</v>
+      </c>
+      <c r="L159" s="15" t="n">
+        <v>500</v>
+      </c>
+      <c r="M159" s="15" t="n"/>
+      <c r="N159" s="16" t="n"/>
+      <c r="O159" s="16" t="n"/>
+      <c r="P159" s="16" t="n"/>
+      <c r="Q159" s="48" t="n"/>
+      <c r="R159" s="48" t="n"/>
+      <c r="S159" s="48" t="n"/>
+      <c r="T159" s="49">
+        <f>IF(AND(H159&lt;&gt;"",Q159&lt;&gt;""),H159-Q159,"")</f>
+        <v/>
+      </c>
+      <c r="U159" s="48" t="n"/>
+      <c r="V159" s="48" t="n"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="13" t="n">
+        <v>155</v>
+      </c>
+      <c r="B160" s="12" t="inlineStr">
+        <is>
+          <t>6.PDA프로그램-2</t>
+        </is>
+      </c>
+      <c r="C160" s="12" t="inlineStr">
+        <is>
+          <t>PDA프로그램개발</t>
+        </is>
+      </c>
+      <c r="D160" s="50" t="inlineStr">
+        <is>
+          <t>솔바텍 미노출 (다른 사이트는 노출됨) → 인상 또는 품질 확인</t>
+        </is>
+      </c>
+      <c r="E160" s="13" t="n"/>
+      <c r="F160" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G160" s="13" t="n"/>
+      <c r="H160" s="48" t="n"/>
+      <c r="I160" s="48" t="n"/>
+      <c r="J160" s="48" t="n"/>
+      <c r="K160" s="15" t="n">
+        <v>300</v>
+      </c>
+      <c r="L160" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="M160" s="15" t="n"/>
+      <c r="N160" s="16" t="n"/>
+      <c r="O160" s="16" t="n"/>
+      <c r="P160" s="16" t="n"/>
+      <c r="Q160" s="48" t="n"/>
+      <c r="R160" s="48" t="n"/>
+      <c r="S160" s="48" t="n"/>
+      <c r="T160" s="49">
+        <f>IF(AND(H160&lt;&gt;"",Q160&lt;&gt;""),H160-Q160,"")</f>
+        <v/>
+      </c>
+      <c r="U160" s="48" t="n"/>
+      <c r="V160" s="48" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="39" t="inlineStr">
+        <is>
+          <t>순위 변화: +는 순위가 올라감(좋아짐), -는 내려감. 변경 전·후 솔바텍 순위를 모두 적으면 자동 계산.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A5:V160"/>
+  <mergeCells count="7">
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="Q4:S4"/>
+    <mergeCell ref="T4:V4"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="N4:P4"/>
+  </mergeCells>
+  <conditionalFormatting sqref="T6:T160">
+    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:V446"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1068,25 +9076,25 @@
           <t>입찰가 변경 전  (순위·노출·클릭·비용 = PC 캠페인 2026.10.22.~2026.10.28. 7일 합계/평균)</t>
         </is>
       </c>
-      <c r="F1" s="4" t="n"/>
-      <c r="G1" s="4" t="n"/>
-      <c r="H1" s="4" t="n"/>
-      <c r="I1" s="4" t="n"/>
-      <c r="J1" s="4" t="n"/>
-      <c r="K1" s="4" t="n"/>
-      <c r="L1" s="4" t="n"/>
-      <c r="M1" s="4" t="n"/>
-      <c r="N1" s="4" t="n"/>
-      <c r="O1" s="4" t="n"/>
+      <c r="F1" s="51" t="n"/>
+      <c r="G1" s="51" t="n"/>
+      <c r="H1" s="51" t="n"/>
+      <c r="I1" s="51" t="n"/>
+      <c r="J1" s="51" t="n"/>
+      <c r="K1" s="51" t="n"/>
+      <c r="L1" s="51" t="n"/>
+      <c r="M1" s="51" t="n"/>
+      <c r="N1" s="51" t="n"/>
+      <c r="O1" s="52" t="n"/>
       <c r="P1" s="5" t="inlineStr">
         <is>
           <t>입찰가 변경 후</t>
         </is>
       </c>
-      <c r="Q1" s="6" t="n"/>
-      <c r="R1" s="6" t="n"/>
-      <c r="S1" s="6" t="n"/>
-      <c r="T1" s="6" t="n"/>
+      <c r="Q1" s="51" t="n"/>
+      <c r="R1" s="51" t="n"/>
+      <c r="S1" s="51" t="n"/>
+      <c r="T1" s="52" t="n"/>
       <c r="V1" s="7" t="inlineStr">
         <is>
           <t>범례</t>
@@ -1094,6 +9102,10 @@
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="53" t="n"/>
+      <c r="B2" s="53" t="n"/>
+      <c r="C2" s="53" t="n"/>
+      <c r="D2" s="53" t="n"/>
       <c r="E2" s="3" t="inlineStr">
         <is>
           <t>광고업체수</t>
@@ -1200,25 +9212,25 @@
           <t>#. 자사명  (2개)   grp-a001-01-000000000071885</t>
         </is>
       </c>
-      <c r="B3" s="11" t="n"/>
-      <c r="C3" s="11" t="n"/>
-      <c r="D3" s="11" t="n"/>
-      <c r="E3" s="11" t="n"/>
-      <c r="F3" s="11" t="n"/>
-      <c r="G3" s="11" t="n"/>
-      <c r="H3" s="11" t="n"/>
-      <c r="I3" s="11" t="n"/>
-      <c r="J3" s="11" t="n"/>
-      <c r="K3" s="11" t="n"/>
-      <c r="L3" s="11" t="n"/>
-      <c r="M3" s="11" t="n"/>
-      <c r="N3" s="11" t="n"/>
-      <c r="O3" s="11" t="n"/>
-      <c r="P3" s="11" t="n"/>
-      <c r="Q3" s="11" t="n"/>
-      <c r="R3" s="11" t="n"/>
-      <c r="S3" s="11" t="n"/>
-      <c r="T3" s="11" t="n"/>
+      <c r="B3" s="54" t="n"/>
+      <c r="C3" s="54" t="n"/>
+      <c r="D3" s="54" t="n"/>
+      <c r="E3" s="54" t="n"/>
+      <c r="F3" s="54" t="n"/>
+      <c r="G3" s="54" t="n"/>
+      <c r="H3" s="54" t="n"/>
+      <c r="I3" s="54" t="n"/>
+      <c r="J3" s="54" t="n"/>
+      <c r="K3" s="54" t="n"/>
+      <c r="L3" s="54" t="n"/>
+      <c r="M3" s="54" t="n"/>
+      <c r="N3" s="54" t="n"/>
+      <c r="O3" s="54" t="n"/>
+      <c r="P3" s="54" t="n"/>
+      <c r="Q3" s="54" t="n"/>
+      <c r="R3" s="54" t="n"/>
+      <c r="S3" s="54" t="n"/>
+      <c r="T3" s="54" t="n"/>
       <c r="V3" s="7" t="inlineStr">
         <is>
           <t>굵은 글씨 = 3개 사이트 중 최고 입찰가</t>
@@ -1333,25 +9345,25 @@
           <t>1.스캐너-1  (74개)   grp-m001-01-000002035868099</t>
         </is>
       </c>
-      <c r="B6" s="11" t="n"/>
-      <c r="C6" s="11" t="n"/>
-      <c r="D6" s="11" t="n"/>
-      <c r="E6" s="11" t="n"/>
-      <c r="F6" s="11" t="n"/>
-      <c r="G6" s="11" t="n"/>
-      <c r="H6" s="11" t="n"/>
-      <c r="I6" s="11" t="n"/>
-      <c r="J6" s="11" t="n"/>
-      <c r="K6" s="11" t="n"/>
-      <c r="L6" s="11" t="n"/>
-      <c r="M6" s="11" t="n"/>
-      <c r="N6" s="11" t="n"/>
-      <c r="O6" s="11" t="n"/>
-      <c r="P6" s="11" t="n"/>
-      <c r="Q6" s="11" t="n"/>
-      <c r="R6" s="11" t="n"/>
-      <c r="S6" s="11" t="n"/>
-      <c r="T6" s="11" t="n"/>
+      <c r="B6" s="54" t="n"/>
+      <c r="C6" s="54" t="n"/>
+      <c r="D6" s="54" t="n"/>
+      <c r="E6" s="54" t="n"/>
+      <c r="F6" s="54" t="n"/>
+      <c r="G6" s="54" t="n"/>
+      <c r="H6" s="54" t="n"/>
+      <c r="I6" s="54" t="n"/>
+      <c r="J6" s="54" t="n"/>
+      <c r="K6" s="54" t="n"/>
+      <c r="L6" s="54" t="n"/>
+      <c r="M6" s="54" t="n"/>
+      <c r="N6" s="54" t="n"/>
+      <c r="O6" s="54" t="n"/>
+      <c r="P6" s="54" t="n"/>
+      <c r="Q6" s="54" t="n"/>
+      <c r="R6" s="54" t="n"/>
+      <c r="S6" s="54" t="n"/>
+      <c r="T6" s="54" t="n"/>
       <c r="V6" t="inlineStr">
         <is>
           <t>빨간 세모(메모) = 여러 그룹에 있음 / 분류 이유 / 직접 확인한 순위</t>
@@ -4940,25 +12952,25 @@
           <t>1.스캐너모델-2  (36개)   grp-a001-01-000000000071892</t>
         </is>
       </c>
-      <c r="B81" s="11" t="n"/>
-      <c r="C81" s="11" t="n"/>
-      <c r="D81" s="11" t="n"/>
-      <c r="E81" s="11" t="n"/>
-      <c r="F81" s="11" t="n"/>
-      <c r="G81" s="11" t="n"/>
-      <c r="H81" s="11" t="n"/>
-      <c r="I81" s="11" t="n"/>
-      <c r="J81" s="11" t="n"/>
-      <c r="K81" s="11" t="n"/>
-      <c r="L81" s="11" t="n"/>
-      <c r="M81" s="11" t="n"/>
-      <c r="N81" s="11" t="n"/>
-      <c r="O81" s="11" t="n"/>
-      <c r="P81" s="11" t="n"/>
-      <c r="Q81" s="11" t="n"/>
-      <c r="R81" s="11" t="n"/>
-      <c r="S81" s="11" t="n"/>
-      <c r="T81" s="11" t="n"/>
+      <c r="B81" s="54" t="n"/>
+      <c r="C81" s="54" t="n"/>
+      <c r="D81" s="54" t="n"/>
+      <c r="E81" s="54" t="n"/>
+      <c r="F81" s="54" t="n"/>
+      <c r="G81" s="54" t="n"/>
+      <c r="H81" s="54" t="n"/>
+      <c r="I81" s="54" t="n"/>
+      <c r="J81" s="54" t="n"/>
+      <c r="K81" s="54" t="n"/>
+      <c r="L81" s="54" t="n"/>
+      <c r="M81" s="54" t="n"/>
+      <c r="N81" s="54" t="n"/>
+      <c r="O81" s="54" t="n"/>
+      <c r="P81" s="54" t="n"/>
+      <c r="Q81" s="54" t="n"/>
+      <c r="R81" s="54" t="n"/>
+      <c r="S81" s="54" t="n"/>
+      <c r="T81" s="54" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="12" t="inlineStr">
@@ -6708,25 +14720,25 @@
           <t>2.프린터-1  (50개)   grp-m001-01-000001189421740</t>
         </is>
       </c>
-      <c r="B118" s="11" t="n"/>
-      <c r="C118" s="11" t="n"/>
-      <c r="D118" s="11" t="n"/>
-      <c r="E118" s="11" t="n"/>
-      <c r="F118" s="11" t="n"/>
-      <c r="G118" s="11" t="n"/>
-      <c r="H118" s="11" t="n"/>
-      <c r="I118" s="11" t="n"/>
-      <c r="J118" s="11" t="n"/>
-      <c r="K118" s="11" t="n"/>
-      <c r="L118" s="11" t="n"/>
-      <c r="M118" s="11" t="n"/>
-      <c r="N118" s="11" t="n"/>
-      <c r="O118" s="11" t="n"/>
-      <c r="P118" s="11" t="n"/>
-      <c r="Q118" s="11" t="n"/>
-      <c r="R118" s="11" t="n"/>
-      <c r="S118" s="11" t="n"/>
-      <c r="T118" s="11" t="n"/>
+      <c r="B118" s="54" t="n"/>
+      <c r="C118" s="54" t="n"/>
+      <c r="D118" s="54" t="n"/>
+      <c r="E118" s="54" t="n"/>
+      <c r="F118" s="54" t="n"/>
+      <c r="G118" s="54" t="n"/>
+      <c r="H118" s="54" t="n"/>
+      <c r="I118" s="54" t="n"/>
+      <c r="J118" s="54" t="n"/>
+      <c r="K118" s="54" t="n"/>
+      <c r="L118" s="54" t="n"/>
+      <c r="M118" s="54" t="n"/>
+      <c r="N118" s="54" t="n"/>
+      <c r="O118" s="54" t="n"/>
+      <c r="P118" s="54" t="n"/>
+      <c r="Q118" s="54" t="n"/>
+      <c r="R118" s="54" t="n"/>
+      <c r="S118" s="54" t="n"/>
+      <c r="T118" s="54" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="12" t="inlineStr">
@@ -9456,25 +17468,25 @@
           <t>2.프린터모델-2  (41개)   grp-m001-01-000001165672136</t>
         </is>
       </c>
-      <c r="B169" s="11" t="n"/>
-      <c r="C169" s="11" t="n"/>
-      <c r="D169" s="11" t="n"/>
-      <c r="E169" s="11" t="n"/>
-      <c r="F169" s="11" t="n"/>
-      <c r="G169" s="11" t="n"/>
-      <c r="H169" s="11" t="n"/>
-      <c r="I169" s="11" t="n"/>
-      <c r="J169" s="11" t="n"/>
-      <c r="K169" s="11" t="n"/>
-      <c r="L169" s="11" t="n"/>
-      <c r="M169" s="11" t="n"/>
-      <c r="N169" s="11" t="n"/>
-      <c r="O169" s="11" t="n"/>
-      <c r="P169" s="11" t="n"/>
-      <c r="Q169" s="11" t="n"/>
-      <c r="R169" s="11" t="n"/>
-      <c r="S169" s="11" t="n"/>
-      <c r="T169" s="11" t="n"/>
+      <c r="B169" s="54" t="n"/>
+      <c r="C169" s="54" t="n"/>
+      <c r="D169" s="54" t="n"/>
+      <c r="E169" s="54" t="n"/>
+      <c r="F169" s="54" t="n"/>
+      <c r="G169" s="54" t="n"/>
+      <c r="H169" s="54" t="n"/>
+      <c r="I169" s="54" t="n"/>
+      <c r="J169" s="54" t="n"/>
+      <c r="K169" s="54" t="n"/>
+      <c r="L169" s="54" t="n"/>
+      <c r="M169" s="54" t="n"/>
+      <c r="N169" s="54" t="n"/>
+      <c r="O169" s="54" t="n"/>
+      <c r="P169" s="54" t="n"/>
+      <c r="Q169" s="54" t="n"/>
+      <c r="R169" s="54" t="n"/>
+      <c r="S169" s="54" t="n"/>
+      <c r="T169" s="54" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="12" t="inlineStr">
@@ -11464,25 +19476,25 @@
           <t>3.라벨  (77개)   grp-a001-01-000000000071891</t>
         </is>
       </c>
-      <c r="B211" s="11" t="n"/>
-      <c r="C211" s="11" t="n"/>
-      <c r="D211" s="11" t="n"/>
-      <c r="E211" s="11" t="n"/>
-      <c r="F211" s="11" t="n"/>
-      <c r="G211" s="11" t="n"/>
-      <c r="H211" s="11" t="n"/>
-      <c r="I211" s="11" t="n"/>
-      <c r="J211" s="11" t="n"/>
-      <c r="K211" s="11" t="n"/>
-      <c r="L211" s="11" t="n"/>
-      <c r="M211" s="11" t="n"/>
-      <c r="N211" s="11" t="n"/>
-      <c r="O211" s="11" t="n"/>
-      <c r="P211" s="11" t="n"/>
-      <c r="Q211" s="11" t="n"/>
-      <c r="R211" s="11" t="n"/>
-      <c r="S211" s="11" t="n"/>
-      <c r="T211" s="11" t="n"/>
+      <c r="B211" s="54" t="n"/>
+      <c r="C211" s="54" t="n"/>
+      <c r="D211" s="54" t="n"/>
+      <c r="E211" s="54" t="n"/>
+      <c r="F211" s="54" t="n"/>
+      <c r="G211" s="54" t="n"/>
+      <c r="H211" s="54" t="n"/>
+      <c r="I211" s="54" t="n"/>
+      <c r="J211" s="54" t="n"/>
+      <c r="K211" s="54" t="n"/>
+      <c r="L211" s="54" t="n"/>
+      <c r="M211" s="54" t="n"/>
+      <c r="N211" s="54" t="n"/>
+      <c r="O211" s="54" t="n"/>
+      <c r="P211" s="54" t="n"/>
+      <c r="Q211" s="54" t="n"/>
+      <c r="R211" s="54" t="n"/>
+      <c r="S211" s="54" t="n"/>
+      <c r="T211" s="54" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="12" t="inlineStr">
@@ -15238,25 +23250,25 @@
           <t>4.솔루션SW-1  (26개)   grp-a001-01-000000000071886</t>
         </is>
       </c>
-      <c r="B289" s="11" t="n"/>
-      <c r="C289" s="11" t="n"/>
-      <c r="D289" s="11" t="n"/>
-      <c r="E289" s="11" t="n"/>
-      <c r="F289" s="11" t="n"/>
-      <c r="G289" s="11" t="n"/>
-      <c r="H289" s="11" t="n"/>
-      <c r="I289" s="11" t="n"/>
-      <c r="J289" s="11" t="n"/>
-      <c r="K289" s="11" t="n"/>
-      <c r="L289" s="11" t="n"/>
-      <c r="M289" s="11" t="n"/>
-      <c r="N289" s="11" t="n"/>
-      <c r="O289" s="11" t="n"/>
-      <c r="P289" s="11" t="n"/>
-      <c r="Q289" s="11" t="n"/>
-      <c r="R289" s="11" t="n"/>
-      <c r="S289" s="11" t="n"/>
-      <c r="T289" s="11" t="n"/>
+      <c r="B289" s="54" t="n"/>
+      <c r="C289" s="54" t="n"/>
+      <c r="D289" s="54" t="n"/>
+      <c r="E289" s="54" t="n"/>
+      <c r="F289" s="54" t="n"/>
+      <c r="G289" s="54" t="n"/>
+      <c r="H289" s="54" t="n"/>
+      <c r="I289" s="54" t="n"/>
+      <c r="J289" s="54" t="n"/>
+      <c r="K289" s="54" t="n"/>
+      <c r="L289" s="54" t="n"/>
+      <c r="M289" s="54" t="n"/>
+      <c r="N289" s="54" t="n"/>
+      <c r="O289" s="54" t="n"/>
+      <c r="P289" s="54" t="n"/>
+      <c r="Q289" s="54" t="n"/>
+      <c r="R289" s="54" t="n"/>
+      <c r="S289" s="54" t="n"/>
+      <c r="T289" s="54" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="12" t="inlineStr">
@@ -16486,25 +24498,25 @@
           <t>4.솔루션SW-2  (7개)   grp-a001-01-000000000071889</t>
         </is>
       </c>
-      <c r="B316" s="11" t="n"/>
-      <c r="C316" s="11" t="n"/>
-      <c r="D316" s="11" t="n"/>
-      <c r="E316" s="11" t="n"/>
-      <c r="F316" s="11" t="n"/>
-      <c r="G316" s="11" t="n"/>
-      <c r="H316" s="11" t="n"/>
-      <c r="I316" s="11" t="n"/>
-      <c r="J316" s="11" t="n"/>
-      <c r="K316" s="11" t="n"/>
-      <c r="L316" s="11" t="n"/>
-      <c r="M316" s="11" t="n"/>
-      <c r="N316" s="11" t="n"/>
-      <c r="O316" s="11" t="n"/>
-      <c r="P316" s="11" t="n"/>
-      <c r="Q316" s="11" t="n"/>
-      <c r="R316" s="11" t="n"/>
-      <c r="S316" s="11" t="n"/>
-      <c r="T316" s="11" t="n"/>
+      <c r="B316" s="54" t="n"/>
+      <c r="C316" s="54" t="n"/>
+      <c r="D316" s="54" t="n"/>
+      <c r="E316" s="54" t="n"/>
+      <c r="F316" s="54" t="n"/>
+      <c r="G316" s="54" t="n"/>
+      <c r="H316" s="54" t="n"/>
+      <c r="I316" s="54" t="n"/>
+      <c r="J316" s="54" t="n"/>
+      <c r="K316" s="54" t="n"/>
+      <c r="L316" s="54" t="n"/>
+      <c r="M316" s="54" t="n"/>
+      <c r="N316" s="54" t="n"/>
+      <c r="O316" s="54" t="n"/>
+      <c r="P316" s="54" t="n"/>
+      <c r="Q316" s="54" t="n"/>
+      <c r="R316" s="54" t="n"/>
+      <c r="S316" s="54" t="n"/>
+      <c r="T316" s="54" t="n"/>
     </row>
     <row r="317">
       <c r="A317" s="12" t="inlineStr">
@@ -16854,25 +24866,25 @@
           <t>4.솔루션SW-3  (5개)   grp-m001-01-000001878347665</t>
         </is>
       </c>
-      <c r="B324" s="11" t="n"/>
-      <c r="C324" s="11" t="n"/>
-      <c r="D324" s="11" t="n"/>
-      <c r="E324" s="11" t="n"/>
-      <c r="F324" s="11" t="n"/>
-      <c r="G324" s="11" t="n"/>
-      <c r="H324" s="11" t="n"/>
-      <c r="I324" s="11" t="n"/>
-      <c r="J324" s="11" t="n"/>
-      <c r="K324" s="11" t="n"/>
-      <c r="L324" s="11" t="n"/>
-      <c r="M324" s="11" t="n"/>
-      <c r="N324" s="11" t="n"/>
-      <c r="O324" s="11" t="n"/>
-      <c r="P324" s="11" t="n"/>
-      <c r="Q324" s="11" t="n"/>
-      <c r="R324" s="11" t="n"/>
-      <c r="S324" s="11" t="n"/>
-      <c r="T324" s="11" t="n"/>
+      <c r="B324" s="54" t="n"/>
+      <c r="C324" s="54" t="n"/>
+      <c r="D324" s="54" t="n"/>
+      <c r="E324" s="54" t="n"/>
+      <c r="F324" s="54" t="n"/>
+      <c r="G324" s="54" t="n"/>
+      <c r="H324" s="54" t="n"/>
+      <c r="I324" s="54" t="n"/>
+      <c r="J324" s="54" t="n"/>
+      <c r="K324" s="54" t="n"/>
+      <c r="L324" s="54" t="n"/>
+      <c r="M324" s="54" t="n"/>
+      <c r="N324" s="54" t="n"/>
+      <c r="O324" s="54" t="n"/>
+      <c r="P324" s="54" t="n"/>
+      <c r="Q324" s="54" t="n"/>
+      <c r="R324" s="54" t="n"/>
+      <c r="S324" s="54" t="n"/>
+      <c r="T324" s="54" t="n"/>
     </row>
     <row r="325">
       <c r="A325" s="12" t="inlineStr">
@@ -17114,25 +25126,25 @@
           <t>5.리본  (12개)   grp-a001-01-000000000071888</t>
         </is>
       </c>
-      <c r="B330" s="11" t="n"/>
-      <c r="C330" s="11" t="n"/>
-      <c r="D330" s="11" t="n"/>
-      <c r="E330" s="11" t="n"/>
-      <c r="F330" s="11" t="n"/>
-      <c r="G330" s="11" t="n"/>
-      <c r="H330" s="11" t="n"/>
-      <c r="I330" s="11" t="n"/>
-      <c r="J330" s="11" t="n"/>
-      <c r="K330" s="11" t="n"/>
-      <c r="L330" s="11" t="n"/>
-      <c r="M330" s="11" t="n"/>
-      <c r="N330" s="11" t="n"/>
-      <c r="O330" s="11" t="n"/>
-      <c r="P330" s="11" t="n"/>
-      <c r="Q330" s="11" t="n"/>
-      <c r="R330" s="11" t="n"/>
-      <c r="S330" s="11" t="n"/>
-      <c r="T330" s="11" t="n"/>
+      <c r="B330" s="54" t="n"/>
+      <c r="C330" s="54" t="n"/>
+      <c r="D330" s="54" t="n"/>
+      <c r="E330" s="54" t="n"/>
+      <c r="F330" s="54" t="n"/>
+      <c r="G330" s="54" t="n"/>
+      <c r="H330" s="54" t="n"/>
+      <c r="I330" s="54" t="n"/>
+      <c r="J330" s="54" t="n"/>
+      <c r="K330" s="54" t="n"/>
+      <c r="L330" s="54" t="n"/>
+      <c r="M330" s="54" t="n"/>
+      <c r="N330" s="54" t="n"/>
+      <c r="O330" s="54" t="n"/>
+      <c r="P330" s="54" t="n"/>
+      <c r="Q330" s="54" t="n"/>
+      <c r="R330" s="54" t="n"/>
+      <c r="S330" s="54" t="n"/>
+      <c r="T330" s="54" t="n"/>
     </row>
     <row r="331">
       <c r="A331" s="12" t="inlineStr">
@@ -17722,25 +25734,25 @@
           <t>6.PDA모델-3  (10개)   grp-a001-01-000000000071893</t>
         </is>
       </c>
-      <c r="B343" s="11" t="n"/>
-      <c r="C343" s="11" t="n"/>
-      <c r="D343" s="11" t="n"/>
-      <c r="E343" s="11" t="n"/>
-      <c r="F343" s="11" t="n"/>
-      <c r="G343" s="11" t="n"/>
-      <c r="H343" s="11" t="n"/>
-      <c r="I343" s="11" t="n"/>
-      <c r="J343" s="11" t="n"/>
-      <c r="K343" s="11" t="n"/>
-      <c r="L343" s="11" t="n"/>
-      <c r="M343" s="11" t="n"/>
-      <c r="N343" s="11" t="n"/>
-      <c r="O343" s="11" t="n"/>
-      <c r="P343" s="11" t="n"/>
-      <c r="Q343" s="11" t="n"/>
-      <c r="R343" s="11" t="n"/>
-      <c r="S343" s="11" t="n"/>
-      <c r="T343" s="11" t="n"/>
+      <c r="B343" s="54" t="n"/>
+      <c r="C343" s="54" t="n"/>
+      <c r="D343" s="54" t="n"/>
+      <c r="E343" s="54" t="n"/>
+      <c r="F343" s="54" t="n"/>
+      <c r="G343" s="54" t="n"/>
+      <c r="H343" s="54" t="n"/>
+      <c r="I343" s="54" t="n"/>
+      <c r="J343" s="54" t="n"/>
+      <c r="K343" s="54" t="n"/>
+      <c r="L343" s="54" t="n"/>
+      <c r="M343" s="54" t="n"/>
+      <c r="N343" s="54" t="n"/>
+      <c r="O343" s="54" t="n"/>
+      <c r="P343" s="54" t="n"/>
+      <c r="Q343" s="54" t="n"/>
+      <c r="R343" s="54" t="n"/>
+      <c r="S343" s="54" t="n"/>
+      <c r="T343" s="54" t="n"/>
     </row>
     <row r="344">
       <c r="A344" s="12" t="inlineStr">
@@ -18230,25 +26242,25 @@
           <t>6.PDA프로그램-2  (40개)   grp-a001-01-000000000071896</t>
         </is>
       </c>
-      <c r="B354" s="11" t="n"/>
-      <c r="C354" s="11" t="n"/>
-      <c r="D354" s="11" t="n"/>
-      <c r="E354" s="11" t="n"/>
-      <c r="F354" s="11" t="n"/>
-      <c r="G354" s="11" t="n"/>
-      <c r="H354" s="11" t="n"/>
-      <c r="I354" s="11" t="n"/>
-      <c r="J354" s="11" t="n"/>
-      <c r="K354" s="11" t="n"/>
-      <c r="L354" s="11" t="n"/>
-      <c r="M354" s="11" t="n"/>
-      <c r="N354" s="11" t="n"/>
-      <c r="O354" s="11" t="n"/>
-      <c r="P354" s="11" t="n"/>
-      <c r="Q354" s="11" t="n"/>
-      <c r="R354" s="11" t="n"/>
-      <c r="S354" s="11" t="n"/>
-      <c r="T354" s="11" t="n"/>
+      <c r="B354" s="54" t="n"/>
+      <c r="C354" s="54" t="n"/>
+      <c r="D354" s="54" t="n"/>
+      <c r="E354" s="54" t="n"/>
+      <c r="F354" s="54" t="n"/>
+      <c r="G354" s="54" t="n"/>
+      <c r="H354" s="54" t="n"/>
+      <c r="I354" s="54" t="n"/>
+      <c r="J354" s="54" t="n"/>
+      <c r="K354" s="54" t="n"/>
+      <c r="L354" s="54" t="n"/>
+      <c r="M354" s="54" t="n"/>
+      <c r="N354" s="54" t="n"/>
+      <c r="O354" s="54" t="n"/>
+      <c r="P354" s="54" t="n"/>
+      <c r="Q354" s="54" t="n"/>
+      <c r="R354" s="54" t="n"/>
+      <c r="S354" s="54" t="n"/>
+      <c r="T354" s="54" t="n"/>
     </row>
     <row r="355">
       <c r="A355" s="12" t="inlineStr">
@@ -20090,25 +28102,25 @@
           <t>6.산업용PDA-1  (10개)   grp-m001-01-000000322810324</t>
         </is>
       </c>
-      <c r="B395" s="11" t="n"/>
-      <c r="C395" s="11" t="n"/>
-      <c r="D395" s="11" t="n"/>
-      <c r="E395" s="11" t="n"/>
-      <c r="F395" s="11" t="n"/>
-      <c r="G395" s="11" t="n"/>
-      <c r="H395" s="11" t="n"/>
-      <c r="I395" s="11" t="n"/>
-      <c r="J395" s="11" t="n"/>
-      <c r="K395" s="11" t="n"/>
-      <c r="L395" s="11" t="n"/>
-      <c r="M395" s="11" t="n"/>
-      <c r="N395" s="11" t="n"/>
-      <c r="O395" s="11" t="n"/>
-      <c r="P395" s="11" t="n"/>
-      <c r="Q395" s="11" t="n"/>
-      <c r="R395" s="11" t="n"/>
-      <c r="S395" s="11" t="n"/>
-      <c r="T395" s="11" t="n"/>
+      <c r="B395" s="54" t="n"/>
+      <c r="C395" s="54" t="n"/>
+      <c r="D395" s="54" t="n"/>
+      <c r="E395" s="54" t="n"/>
+      <c r="F395" s="54" t="n"/>
+      <c r="G395" s="54" t="n"/>
+      <c r="H395" s="54" t="n"/>
+      <c r="I395" s="54" t="n"/>
+      <c r="J395" s="54" t="n"/>
+      <c r="K395" s="54" t="n"/>
+      <c r="L395" s="54" t="n"/>
+      <c r="M395" s="54" t="n"/>
+      <c r="N395" s="54" t="n"/>
+      <c r="O395" s="54" t="n"/>
+      <c r="P395" s="54" t="n"/>
+      <c r="Q395" s="54" t="n"/>
+      <c r="R395" s="54" t="n"/>
+      <c r="S395" s="54" t="n"/>
+      <c r="T395" s="54" t="n"/>
     </row>
     <row r="396">
       <c r="A396" s="12" t="inlineStr">
@@ -20596,25 +28608,25 @@
           <t>8.산업자동화  (40개)   grp-a001-01-000000000071897</t>
         </is>
       </c>
-      <c r="B406" s="11" t="n"/>
-      <c r="C406" s="11" t="n"/>
-      <c r="D406" s="11" t="n"/>
-      <c r="E406" s="11" t="n"/>
-      <c r="F406" s="11" t="n"/>
-      <c r="G406" s="11" t="n"/>
-      <c r="H406" s="11" t="n"/>
-      <c r="I406" s="11" t="n"/>
-      <c r="J406" s="11" t="n"/>
-      <c r="K406" s="11" t="n"/>
-      <c r="L406" s="11" t="n"/>
-      <c r="M406" s="11" t="n"/>
-      <c r="N406" s="11" t="n"/>
-      <c r="O406" s="11" t="n"/>
-      <c r="P406" s="11" t="n"/>
-      <c r="Q406" s="11" t="n"/>
-      <c r="R406" s="11" t="n"/>
-      <c r="S406" s="11" t="n"/>
-      <c r="T406" s="11" t="n"/>
+      <c r="B406" s="54" t="n"/>
+      <c r="C406" s="54" t="n"/>
+      <c r="D406" s="54" t="n"/>
+      <c r="E406" s="54" t="n"/>
+      <c r="F406" s="54" t="n"/>
+      <c r="G406" s="54" t="n"/>
+      <c r="H406" s="54" t="n"/>
+      <c r="I406" s="54" t="n"/>
+      <c r="J406" s="54" t="n"/>
+      <c r="K406" s="54" t="n"/>
+      <c r="L406" s="54" t="n"/>
+      <c r="M406" s="54" t="n"/>
+      <c r="N406" s="54" t="n"/>
+      <c r="O406" s="54" t="n"/>
+      <c r="P406" s="54" t="n"/>
+      <c r="Q406" s="54" t="n"/>
+      <c r="R406" s="54" t="n"/>
+      <c r="S406" s="54" t="n"/>
+      <c r="T406" s="54" t="n"/>
     </row>
     <row r="407">
       <c r="A407" s="12" t="inlineStr">
@@ -22413,7 +30425,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -22508,17 +30520,17 @@
           <t>#. 자사명  (2개)   grp-a001-01-000000000071885</t>
         </is>
       </c>
-      <c r="B2" s="11" t="n"/>
-      <c r="C2" s="11" t="n"/>
-      <c r="D2" s="11" t="n"/>
-      <c r="E2" s="11" t="n"/>
-      <c r="F2" s="11" t="n"/>
-      <c r="G2" s="11" t="n"/>
-      <c r="H2" s="11" t="n"/>
-      <c r="I2" s="11" t="n"/>
-      <c r="J2" s="11" t="n"/>
-      <c r="K2" s="11" t="n"/>
-      <c r="L2" s="11" t="n"/>
+      <c r="B2" s="54" t="n"/>
+      <c r="C2" s="54" t="n"/>
+      <c r="D2" s="54" t="n"/>
+      <c r="E2" s="54" t="n"/>
+      <c r="F2" s="54" t="n"/>
+      <c r="G2" s="54" t="n"/>
+      <c r="H2" s="54" t="n"/>
+      <c r="I2" s="54" t="n"/>
+      <c r="J2" s="54" t="n"/>
+      <c r="K2" s="54" t="n"/>
+      <c r="L2" s="54" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
@@ -22598,17 +30610,17 @@
           <t>1.스캐너-1  (74개)   grp-m001-01-000002035868099</t>
         </is>
       </c>
-      <c r="B5" s="11" t="n"/>
-      <c r="C5" s="11" t="n"/>
-      <c r="D5" s="11" t="n"/>
-      <c r="E5" s="11" t="n"/>
-      <c r="F5" s="11" t="n"/>
-      <c r="G5" s="11" t="n"/>
-      <c r="H5" s="11" t="n"/>
-      <c r="I5" s="11" t="n"/>
-      <c r="J5" s="11" t="n"/>
-      <c r="K5" s="11" t="n"/>
-      <c r="L5" s="11" t="n"/>
+      <c r="B5" s="54" t="n"/>
+      <c r="C5" s="54" t="n"/>
+      <c r="D5" s="54" t="n"/>
+      <c r="E5" s="54" t="n"/>
+      <c r="F5" s="54" t="n"/>
+      <c r="G5" s="54" t="n"/>
+      <c r="H5" s="54" t="n"/>
+      <c r="I5" s="54" t="n"/>
+      <c r="J5" s="54" t="n"/>
+      <c r="K5" s="54" t="n"/>
+      <c r="L5" s="54" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
@@ -25216,17 +33228,17 @@
           <t>1.스캐너모델-2  (36개)   grp-a001-01-000000000071892</t>
         </is>
       </c>
-      <c r="B80" s="11" t="n"/>
-      <c r="C80" s="11" t="n"/>
-      <c r="D80" s="11" t="n"/>
-      <c r="E80" s="11" t="n"/>
-      <c r="F80" s="11" t="n"/>
-      <c r="G80" s="11" t="n"/>
-      <c r="H80" s="11" t="n"/>
-      <c r="I80" s="11" t="n"/>
-      <c r="J80" s="11" t="n"/>
-      <c r="K80" s="11" t="n"/>
-      <c r="L80" s="11" t="n"/>
+      <c r="B80" s="54" t="n"/>
+      <c r="C80" s="54" t="n"/>
+      <c r="D80" s="54" t="n"/>
+      <c r="E80" s="54" t="n"/>
+      <c r="F80" s="54" t="n"/>
+      <c r="G80" s="54" t="n"/>
+      <c r="H80" s="54" t="n"/>
+      <c r="I80" s="54" t="n"/>
+      <c r="J80" s="54" t="n"/>
+      <c r="K80" s="54" t="n"/>
+      <c r="L80" s="54" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="12" t="inlineStr">
@@ -26498,17 +34510,17 @@
           <t>2.프린터-1  (50개)   grp-m001-01-000001189421740</t>
         </is>
       </c>
-      <c r="B117" s="11" t="n"/>
-      <c r="C117" s="11" t="n"/>
-      <c r="D117" s="11" t="n"/>
-      <c r="E117" s="11" t="n"/>
-      <c r="F117" s="11" t="n"/>
-      <c r="G117" s="11" t="n"/>
-      <c r="H117" s="11" t="n"/>
-      <c r="I117" s="11" t="n"/>
-      <c r="J117" s="11" t="n"/>
-      <c r="K117" s="11" t="n"/>
-      <c r="L117" s="11" t="n"/>
+      <c r="B117" s="54" t="n"/>
+      <c r="C117" s="54" t="n"/>
+      <c r="D117" s="54" t="n"/>
+      <c r="E117" s="54" t="n"/>
+      <c r="F117" s="54" t="n"/>
+      <c r="G117" s="54" t="n"/>
+      <c r="H117" s="54" t="n"/>
+      <c r="I117" s="54" t="n"/>
+      <c r="J117" s="54" t="n"/>
+      <c r="K117" s="54" t="n"/>
+      <c r="L117" s="54" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="12" t="inlineStr">
@@ -28738,17 +36750,17 @@
           <t>2.프린터모델-2  (41개)   grp-m001-01-000001165672136</t>
         </is>
       </c>
-      <c r="B168" s="11" t="n"/>
-      <c r="C168" s="11" t="n"/>
-      <c r="D168" s="11" t="n"/>
-      <c r="E168" s="11" t="n"/>
-      <c r="F168" s="11" t="n"/>
-      <c r="G168" s="11" t="n"/>
-      <c r="H168" s="11" t="n"/>
-      <c r="I168" s="11" t="n"/>
-      <c r="J168" s="11" t="n"/>
-      <c r="K168" s="11" t="n"/>
-      <c r="L168" s="11" t="n"/>
+      <c r="B168" s="54" t="n"/>
+      <c r="C168" s="54" t="n"/>
+      <c r="D168" s="54" t="n"/>
+      <c r="E168" s="54" t="n"/>
+      <c r="F168" s="54" t="n"/>
+      <c r="G168" s="54" t="n"/>
+      <c r="H168" s="54" t="n"/>
+      <c r="I168" s="54" t="n"/>
+      <c r="J168" s="54" t="n"/>
+      <c r="K168" s="54" t="n"/>
+      <c r="L168" s="54" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="12" t="inlineStr">
@@ -30194,17 +38206,17 @@
           <t>3.라벨  (77개)   grp-a001-01-000000000071891</t>
         </is>
       </c>
-      <c r="B210" s="11" t="n"/>
-      <c r="C210" s="11" t="n"/>
-      <c r="D210" s="11" t="n"/>
-      <c r="E210" s="11" t="n"/>
-      <c r="F210" s="11" t="n"/>
-      <c r="G210" s="11" t="n"/>
-      <c r="H210" s="11" t="n"/>
-      <c r="I210" s="11" t="n"/>
-      <c r="J210" s="11" t="n"/>
-      <c r="K210" s="11" t="n"/>
-      <c r="L210" s="11" t="n"/>
+      <c r="B210" s="54" t="n"/>
+      <c r="C210" s="54" t="n"/>
+      <c r="D210" s="54" t="n"/>
+      <c r="E210" s="54" t="n"/>
+      <c r="F210" s="54" t="n"/>
+      <c r="G210" s="54" t="n"/>
+      <c r="H210" s="54" t="n"/>
+      <c r="I210" s="54" t="n"/>
+      <c r="J210" s="54" t="n"/>
+      <c r="K210" s="54" t="n"/>
+      <c r="L210" s="54" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="12" t="inlineStr">
@@ -32906,17 +40918,17 @@
           <t>4.솔루션SW-1  (26개)   grp-a001-01-000000000071886</t>
         </is>
       </c>
-      <c r="B288" s="11" t="n"/>
-      <c r="C288" s="11" t="n"/>
-      <c r="D288" s="11" t="n"/>
-      <c r="E288" s="11" t="n"/>
-      <c r="F288" s="11" t="n"/>
-      <c r="G288" s="11" t="n"/>
-      <c r="H288" s="11" t="n"/>
-      <c r="I288" s="11" t="n"/>
-      <c r="J288" s="11" t="n"/>
-      <c r="K288" s="11" t="n"/>
-      <c r="L288" s="11" t="n"/>
+      <c r="B288" s="54" t="n"/>
+      <c r="C288" s="54" t="n"/>
+      <c r="D288" s="54" t="n"/>
+      <c r="E288" s="54" t="n"/>
+      <c r="F288" s="54" t="n"/>
+      <c r="G288" s="54" t="n"/>
+      <c r="H288" s="54" t="n"/>
+      <c r="I288" s="54" t="n"/>
+      <c r="J288" s="54" t="n"/>
+      <c r="K288" s="54" t="n"/>
+      <c r="L288" s="54" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="12" t="inlineStr">
@@ -33834,17 +41846,17 @@
           <t>4.솔루션SW-2  (7개)   grp-a001-01-000000000071889</t>
         </is>
       </c>
-      <c r="B315" s="11" t="n"/>
-      <c r="C315" s="11" t="n"/>
-      <c r="D315" s="11" t="n"/>
-      <c r="E315" s="11" t="n"/>
-      <c r="F315" s="11" t="n"/>
-      <c r="G315" s="11" t="n"/>
-      <c r="H315" s="11" t="n"/>
-      <c r="I315" s="11" t="n"/>
-      <c r="J315" s="11" t="n"/>
-      <c r="K315" s="11" t="n"/>
-      <c r="L315" s="11" t="n"/>
+      <c r="B315" s="54" t="n"/>
+      <c r="C315" s="54" t="n"/>
+      <c r="D315" s="54" t="n"/>
+      <c r="E315" s="54" t="n"/>
+      <c r="F315" s="54" t="n"/>
+      <c r="G315" s="54" t="n"/>
+      <c r="H315" s="54" t="n"/>
+      <c r="I315" s="54" t="n"/>
+      <c r="J315" s="54" t="n"/>
+      <c r="K315" s="54" t="n"/>
+      <c r="L315" s="54" t="n"/>
     </row>
     <row r="316">
       <c r="A316" s="12" t="inlineStr">
@@ -34102,17 +42114,17 @@
           <t>4.솔루션SW-3  (5개)   grp-m001-01-000001878347665</t>
         </is>
       </c>
-      <c r="B323" s="11" t="n"/>
-      <c r="C323" s="11" t="n"/>
-      <c r="D323" s="11" t="n"/>
-      <c r="E323" s="11" t="n"/>
-      <c r="F323" s="11" t="n"/>
-      <c r="G323" s="11" t="n"/>
-      <c r="H323" s="11" t="n"/>
-      <c r="I323" s="11" t="n"/>
-      <c r="J323" s="11" t="n"/>
-      <c r="K323" s="11" t="n"/>
-      <c r="L323" s="11" t="n"/>
+      <c r="B323" s="54" t="n"/>
+      <c r="C323" s="54" t="n"/>
+      <c r="D323" s="54" t="n"/>
+      <c r="E323" s="54" t="n"/>
+      <c r="F323" s="54" t="n"/>
+      <c r="G323" s="54" t="n"/>
+      <c r="H323" s="54" t="n"/>
+      <c r="I323" s="54" t="n"/>
+      <c r="J323" s="54" t="n"/>
+      <c r="K323" s="54" t="n"/>
+      <c r="L323" s="54" t="n"/>
     </row>
     <row r="324">
       <c r="A324" s="12" t="inlineStr">
@@ -34296,17 +42308,17 @@
           <t>5.리본  (12개)   grp-a001-01-000000000071888</t>
         </is>
       </c>
-      <c r="B329" s="11" t="n"/>
-      <c r="C329" s="11" t="n"/>
-      <c r="D329" s="11" t="n"/>
-      <c r="E329" s="11" t="n"/>
-      <c r="F329" s="11" t="n"/>
-      <c r="G329" s="11" t="n"/>
-      <c r="H329" s="11" t="n"/>
-      <c r="I329" s="11" t="n"/>
-      <c r="J329" s="11" t="n"/>
-      <c r="K329" s="11" t="n"/>
-      <c r="L329" s="11" t="n"/>
+      <c r="B329" s="54" t="n"/>
+      <c r="C329" s="54" t="n"/>
+      <c r="D329" s="54" t="n"/>
+      <c r="E329" s="54" t="n"/>
+      <c r="F329" s="54" t="n"/>
+      <c r="G329" s="54" t="n"/>
+      <c r="H329" s="54" t="n"/>
+      <c r="I329" s="54" t="n"/>
+      <c r="J329" s="54" t="n"/>
+      <c r="K329" s="54" t="n"/>
+      <c r="L329" s="54" t="n"/>
     </row>
     <row r="330">
       <c r="A330" s="12" t="inlineStr">
@@ -34742,17 +42754,17 @@
           <t>6.PDA모델-3  (10개)   grp-a001-01-000000000071893</t>
         </is>
       </c>
-      <c r="B342" s="11" t="n"/>
-      <c r="C342" s="11" t="n"/>
-      <c r="D342" s="11" t="n"/>
-      <c r="E342" s="11" t="n"/>
-      <c r="F342" s="11" t="n"/>
-      <c r="G342" s="11" t="n"/>
-      <c r="H342" s="11" t="n"/>
-      <c r="I342" s="11" t="n"/>
-      <c r="J342" s="11" t="n"/>
-      <c r="K342" s="11" t="n"/>
-      <c r="L342" s="11" t="n"/>
+      <c r="B342" s="54" t="n"/>
+      <c r="C342" s="54" t="n"/>
+      <c r="D342" s="54" t="n"/>
+      <c r="E342" s="54" t="n"/>
+      <c r="F342" s="54" t="n"/>
+      <c r="G342" s="54" t="n"/>
+      <c r="H342" s="54" t="n"/>
+      <c r="I342" s="54" t="n"/>
+      <c r="J342" s="54" t="n"/>
+      <c r="K342" s="54" t="n"/>
+      <c r="L342" s="54" t="n"/>
     </row>
     <row r="343">
       <c r="A343" s="12" t="inlineStr">
@@ -35112,17 +43124,17 @@
           <t>6.PDA프로그램-2  (40개)   grp-a001-01-000000000071896</t>
         </is>
       </c>
-      <c r="B353" s="11" t="n"/>
-      <c r="C353" s="11" t="n"/>
-      <c r="D353" s="11" t="n"/>
-      <c r="E353" s="11" t="n"/>
-      <c r="F353" s="11" t="n"/>
-      <c r="G353" s="11" t="n"/>
-      <c r="H353" s="11" t="n"/>
-      <c r="I353" s="11" t="n"/>
-      <c r="J353" s="11" t="n"/>
-      <c r="K353" s="11" t="n"/>
-      <c r="L353" s="11" t="n"/>
+      <c r="B353" s="54" t="n"/>
+      <c r="C353" s="54" t="n"/>
+      <c r="D353" s="54" t="n"/>
+      <c r="E353" s="54" t="n"/>
+      <c r="F353" s="54" t="n"/>
+      <c r="G353" s="54" t="n"/>
+      <c r="H353" s="54" t="n"/>
+      <c r="I353" s="54" t="n"/>
+      <c r="J353" s="54" t="n"/>
+      <c r="K353" s="54" t="n"/>
+      <c r="L353" s="54" t="n"/>
     </row>
     <row r="354">
       <c r="A354" s="12" t="inlineStr">
@@ -36494,17 +44506,17 @@
           <t>6.산업용PDA-1  (10개)   grp-m001-01-000000322810324</t>
         </is>
       </c>
-      <c r="B394" s="11" t="n"/>
-      <c r="C394" s="11" t="n"/>
-      <c r="D394" s="11" t="n"/>
-      <c r="E394" s="11" t="n"/>
-      <c r="F394" s="11" t="n"/>
-      <c r="G394" s="11" t="n"/>
-      <c r="H394" s="11" t="n"/>
-      <c r="I394" s="11" t="n"/>
-      <c r="J394" s="11" t="n"/>
-      <c r="K394" s="11" t="n"/>
-      <c r="L394" s="11" t="n"/>
+      <c r="B394" s="54" t="n"/>
+      <c r="C394" s="54" t="n"/>
+      <c r="D394" s="54" t="n"/>
+      <c r="E394" s="54" t="n"/>
+      <c r="F394" s="54" t="n"/>
+      <c r="G394" s="54" t="n"/>
+      <c r="H394" s="54" t="n"/>
+      <c r="I394" s="54" t="n"/>
+      <c r="J394" s="54" t="n"/>
+      <c r="K394" s="54" t="n"/>
+      <c r="L394" s="54" t="n"/>
     </row>
     <row r="395">
       <c r="A395" s="12" t="inlineStr">
@@ -36862,17 +44874,17 @@
           <t>8.산업자동화  (40개)   grp-a001-01-000000000071897</t>
         </is>
       </c>
-      <c r="B405" s="11" t="n"/>
-      <c r="C405" s="11" t="n"/>
-      <c r="D405" s="11" t="n"/>
-      <c r="E405" s="11" t="n"/>
-      <c r="F405" s="11" t="n"/>
-      <c r="G405" s="11" t="n"/>
-      <c r="H405" s="11" t="n"/>
-      <c r="I405" s="11" t="n"/>
-      <c r="J405" s="11" t="n"/>
-      <c r="K405" s="11" t="n"/>
-      <c r="L405" s="11" t="n"/>
+      <c r="B405" s="54" t="n"/>
+      <c r="C405" s="54" t="n"/>
+      <c r="D405" s="54" t="n"/>
+      <c r="E405" s="54" t="n"/>
+      <c r="F405" s="54" t="n"/>
+      <c r="G405" s="54" t="n"/>
+      <c r="H405" s="54" t="n"/>
+      <c r="I405" s="54" t="n"/>
+      <c r="J405" s="54" t="n"/>
+      <c r="K405" s="54" t="n"/>
+      <c r="L405" s="54" t="n"/>
     </row>
     <row r="406">
       <c r="A406" s="12" t="inlineStr">
@@ -38242,8 +46254,8 @@
   <mergeCells count="14">
     <mergeCell ref="A342:L342"/>
     <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A323:L323"/>
     <mergeCell ref="A210:L210"/>
-    <mergeCell ref="A323:L323"/>
     <mergeCell ref="A117:L117"/>
     <mergeCell ref="A5:L5"/>
     <mergeCell ref="A288:L288"/>
@@ -38259,7 +46271,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -47746,7 +55758,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -47765,7 +55777,6 @@
           <t>주력 사이트 정하는 기준 (위에서부터 순서대로 적용)</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -47827,17 +55838,13 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>조치 정하는 기준</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
